--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4717,7 +4717,7 @@
         <v>700273459200</v>
       </c>
       <c r="K2" t="n">
-        <v>32.250214</v>
+        <v>31.948042</v>
       </c>
       <c r="L2" t="n">
         <v>24.997501</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:02</t>
+          <t>2026-09-06 05:42:03</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4536,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4657,25 +4657,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4723,7 +4743,7 @@
         <v>24.997501</v>
       </c>
       <c r="M2" t="n">
-        <v>11.63</v>
+        <v>11.74</v>
       </c>
       <c r="N2" t="n">
         <v>385.57</v>
@@ -4759,29 +4779,41 @@
       <c r="W2" t="n">
         <v>0.985</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19.876524</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1704112694</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Credit Services</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.visa.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Visa Inc. operates as a payment technology company in the United States and internationally. The company operates VisaNet, a transaction processing network that enables authorization, clearing, and settlement of payment transactions. It also offers credit, debit, and prepaid card products; tap to pay, tokenization, and click to pay services; Visa Direct, a platform which facilitates money movement, enabling clients to collect, hold, convert, and send funds across its network; and issuing solutions, such as airport lounge access, dining reservations, shopping experiences, event tickets, and seller offers. In addition, the company provides acceptance solutions, an omnichannel payment integration with e-commerce platforms; risk detection and prevention solutions; and advisory and other services comprising consulting practice, proprietary analytics models, data scientists and economists, marketing services, and managed services. It provides its services under the Visa, Visa Electron, V PAY, Interlink, and PLUS brands. The company serves consumers, sellers, financial institutions, and government entities. Visa Inc. was founded in 1958 and is headquartered in San Francisco, California.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:03</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:06</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:06</t>
+          <t>2026-09-06 16:24:42</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:42</t>
+          <t>2026-09-06 16:34:36</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:36</t>
+          <t>2026-09-06 16:49:10</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4757,15 +4757,11 @@
       <c r="Q2" t="n">
         <v>0.71</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.50782</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.66130996</v>
       </c>
       <c r="T2" t="n">
         <v>0.6119</v>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:10</t>
+          <t>2026-09-06 16:59:41</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4536,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4677,25 +4677,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4787,29 +4802,38 @@
       <c r="AA2" t="n">
         <v>1704112694</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>44487999488</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>699948269568</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>31093999616</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Credit Services</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.visa.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Visa Inc. operates as a payment technology company in the United States and internationally. The company operates VisaNet, a transaction processing network that enables authorization, clearing, and settlement of payment transactions. It also offers credit, debit, and prepaid card products; tap to pay, tokenization, and click to pay services; Visa Direct, a platform which facilitates money movement, enabling clients to collect, hold, convert, and send funds across its network; and issuing solutions, such as airport lounge access, dining reservations, shopping experiences, event tickets, and seller offers. In addition, the company provides acceptance solutions, an omnichannel payment integration with e-commerce platforms; risk detection and prevention solutions; and advisory and other services comprising consulting practice, proprietary analytics models, data scientists and economists, marketing services, and managed services. It provides its services under the Visa, Visa Electron, V PAY, Interlink, and PLUS brands. The company serves consumers, sellers, financial institutions, and government entities. Visa Inc. was founded in 1958 and is headquartered in San Francisco, California.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:41</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:46</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:46</t>
+          <t>2026-09-06 22:41:40</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:40</t>
+          <t>2026-09-06 22:59:35</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>371.6096355733356</v>
+        <v>348.5921492449787</v>
       </c>
       <c r="C2" t="n">
-        <v>371.7094562365133</v>
+        <v>349.8223013732642</v>
       </c>
       <c r="D2" t="n">
-        <v>366.0399959154992</v>
+        <v>337.5008588435983</v>
       </c>
       <c r="E2" t="n">
-        <v>367.8566284179688</v>
+        <v>340.4968872070312</v>
       </c>
       <c r="F2" t="n">
-        <v>6065300</v>
+        <v>5448300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>368.8847254705448</v>
+        <v>339.6238280750231</v>
       </c>
       <c r="C3" t="n">
-        <v>370.4118872220017</v>
+        <v>341.6476509375095</v>
       </c>
       <c r="D3" t="n">
-        <v>364.5727285978463</v>
+        <v>338.2944634353397</v>
       </c>
       <c r="E3" t="n">
-        <v>369.7830505371094</v>
+        <v>339.5841369628906</v>
       </c>
       <c r="F3" t="n">
-        <v>5022300</v>
+        <v>4711600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>367.8266852879935</v>
+        <v>338.9790027080578</v>
       </c>
       <c r="C4" t="n">
-        <v>369.5634490756331</v>
+        <v>343.572272708629</v>
       </c>
       <c r="D4" t="n">
-        <v>360.8496260625997</v>
+        <v>338.5821823997351</v>
       </c>
       <c r="E4" t="n">
-        <v>361.8278198242188</v>
+        <v>341.2607421875</v>
       </c>
       <c r="F4" t="n">
-        <v>5112500</v>
+        <v>4646200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>361.3287562034755</v>
+        <v>339.8916830924824</v>
       </c>
       <c r="C5" t="n">
-        <v>363.4947458520614</v>
+        <v>339.8916830924824</v>
       </c>
       <c r="D5" t="n">
-        <v>358.2045551780129</v>
+        <v>333.7706534504743</v>
       </c>
       <c r="E5" t="n">
-        <v>360.6500244140625</v>
+        <v>335.4373168945312</v>
       </c>
       <c r="F5" t="n">
-        <v>7552200</v>
+        <v>6557900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,25 +573,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>360.9800109863281</v>
+        <v>336.0424662373603</v>
       </c>
       <c r="C6" t="n">
-        <v>364.5499877929688</v>
+        <v>340.8043700650184</v>
       </c>
       <c r="D6" t="n">
-        <v>359.9700012207031</v>
+        <v>335.1892738885992</v>
       </c>
       <c r="E6" t="n">
-        <v>362.8200073242188</v>
+        <v>340.7646789550781</v>
       </c>
       <c r="F6" t="n">
-        <v>4440900</v>
+        <v>5157600</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>338.5127143274361</v>
       </c>
       <c r="C7" t="n">
-        <v>363.3500061035156</v>
+        <v>340.467085284774</v>
       </c>
       <c r="D7" t="n">
-        <v>358.3099975585938</v>
+        <v>336.4789914224089</v>
       </c>
       <c r="E7" t="n">
-        <v>359.4200134277344</v>
+        <v>336.7369079589844</v>
       </c>
       <c r="F7" t="n">
-        <v>3794200</v>
+        <v>3518300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>363.7000122070312</v>
+        <v>337.907514008316</v>
       </c>
       <c r="C8" t="n">
-        <v>365.4500122070312</v>
+        <v>339.9908582212252</v>
       </c>
       <c r="D8" t="n">
-        <v>358.7099914550781</v>
+        <v>335.7051570201907</v>
       </c>
       <c r="E8" t="n">
-        <v>365.4500122070312</v>
+        <v>336.3598937988281</v>
       </c>
       <c r="F8" t="n">
-        <v>8142600</v>
+        <v>4367500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>365.8900146484375</v>
+        <v>333.5722152320537</v>
       </c>
       <c r="C9" t="n">
-        <v>366.7999877929688</v>
+        <v>337.8381165972889</v>
       </c>
       <c r="D9" t="n">
-        <v>362.760009765625</v>
+        <v>330.8242036977477</v>
       </c>
       <c r="E9" t="n">
-        <v>364.1499938964844</v>
+        <v>337.3321533203125</v>
       </c>
       <c r="F9" t="n">
-        <v>8106900</v>
+        <v>5527700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>362.8399963378906</v>
+        <v>337.2429044796542</v>
       </c>
       <c r="C10" t="n">
-        <v>363.5599975585938</v>
+        <v>343.4532470703125</v>
       </c>
       <c r="D10" t="n">
-        <v>358.5199890136719</v>
+        <v>336.8262234557313</v>
       </c>
       <c r="E10" t="n">
-        <v>358.8399963378906</v>
+        <v>343.4532470703125</v>
       </c>
       <c r="F10" t="n">
-        <v>15543400</v>
+        <v>5763500</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>359.6199951171875</v>
+        <v>341.9948446289807</v>
       </c>
       <c r="C11" t="n">
-        <v>365.9100036621094</v>
+        <v>342.5305383477728</v>
       </c>
       <c r="D11" t="n">
-        <v>358.0499877929688</v>
+        <v>335.4967956542969</v>
       </c>
       <c r="E11" t="n">
-        <v>364.25</v>
+        <v>335.4967956542969</v>
       </c>
       <c r="F11" t="n">
-        <v>6820300</v>
+        <v>7526600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>364.0899963378906</v>
+        <v>337.7488274356299</v>
       </c>
       <c r="C12" t="n">
-        <v>370.6400146484375</v>
+        <v>339.9710452297281</v>
       </c>
       <c r="D12" t="n">
-        <v>362.8999938964844</v>
+        <v>335.5662704768214</v>
       </c>
       <c r="E12" t="n">
-        <v>365.5400085449219</v>
+        <v>338.8995971679688</v>
       </c>
       <c r="F12" t="n">
-        <v>5866400</v>
+        <v>13674300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>365.1000061035156</v>
+        <v>336.3202190485207</v>
       </c>
       <c r="C13" t="n">
-        <v>368.9299926757812</v>
+        <v>342.1237794562243</v>
       </c>
       <c r="D13" t="n">
-        <v>363.6300048828125</v>
+        <v>335.9729899814968</v>
       </c>
       <c r="E13" t="n">
-        <v>365.7300109863281</v>
+        <v>341.6277465820312</v>
       </c>
       <c r="F13" t="n">
-        <v>6151500</v>
+        <v>5621800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>367.8699951171875</v>
+        <v>341.8559781228954</v>
       </c>
       <c r="C14" t="n">
-        <v>371.7999877929688</v>
+        <v>342.5206755840167</v>
       </c>
       <c r="D14" t="n">
-        <v>366.6600036621094</v>
+        <v>334.9512080718528</v>
       </c>
       <c r="E14" t="n">
-        <v>371.0400085449219</v>
+        <v>336.0127258300781</v>
       </c>
       <c r="F14" t="n">
-        <v>6667100</v>
+        <v>10142700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>373.260009765625</v>
+        <v>336.4393311929394</v>
       </c>
       <c r="C15" t="n">
-        <v>383.4299926757812</v>
+        <v>337.2032110769243</v>
       </c>
       <c r="D15" t="n">
-        <v>372.2099914550781</v>
+        <v>335.2389398679774</v>
       </c>
       <c r="E15" t="n">
-        <v>382.4100036621094</v>
+        <v>335.9928894042969</v>
       </c>
       <c r="F15" t="n">
-        <v>8477500</v>
+        <v>5207400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>381.2099914550781</v>
+        <v>335.6655229404874</v>
       </c>
       <c r="C16" t="n">
-        <v>384.2000122070312</v>
+        <v>337.5008510178562</v>
       </c>
       <c r="D16" t="n">
-        <v>380.2699890136719</v>
+        <v>331.8559932948658</v>
       </c>
       <c r="E16" t="n">
-        <v>384.1400146484375</v>
+        <v>332.2726440429688</v>
       </c>
       <c r="F16" t="n">
-        <v>6777600</v>
+        <v>5398700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>384.1400146484375</v>
+        <v>334.5543943395058</v>
       </c>
       <c r="C17" t="n">
-        <v>385.5700073242188</v>
+        <v>336.8063730332322</v>
       </c>
       <c r="D17" t="n">
-        <v>381.0799865722656</v>
+        <v>333.5623284395552</v>
       </c>
       <c r="E17" t="n">
-        <v>383.8999938964844</v>
+        <v>334.6932678222656</v>
       </c>
       <c r="F17" t="n">
-        <v>6075100</v>
+        <v>9619200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>381.1400146484375</v>
+        <v>334.7031787744378</v>
       </c>
       <c r="C18" t="n">
-        <v>381.7699890136719</v>
+        <v>337.9373231090121</v>
       </c>
       <c r="D18" t="n">
-        <v>378.5</v>
+        <v>332.8876813284792</v>
       </c>
       <c r="E18" t="n">
-        <v>379.6600036621094</v>
+        <v>337.4611206054688</v>
       </c>
       <c r="F18" t="n">
-        <v>6641500</v>
+        <v>7217800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>380.2999877929688</v>
+        <v>337.1238274360646</v>
       </c>
       <c r="C19" t="n">
-        <v>383.6799926757812</v>
+        <v>342.867866960749</v>
       </c>
       <c r="D19" t="n">
-        <v>379.0299987792969</v>
+        <v>335.824223582947</v>
       </c>
       <c r="E19" t="n">
-        <v>381.6000061035156</v>
+        <v>338.6714477539062</v>
       </c>
       <c r="F19" t="n">
-        <v>4643000</v>
+        <v>8164400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>381.3500061035156</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="C20" t="n">
-        <v>382.4800109863281</v>
+        <v>346.58811100512</v>
       </c>
       <c r="D20" t="n">
-        <v>378.7999877929688</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="E20" t="n">
-        <v>379.3699951171875</v>
+        <v>345.0702514648438</v>
       </c>
       <c r="F20" t="n">
-        <v>6744800</v>
+        <v>8381000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>379.6499938964844</v>
+        <v>343.4730470813312</v>
       </c>
       <c r="C21" t="n">
-        <v>380.75</v>
+        <v>344.425421840401</v>
       </c>
       <c r="D21" t="n">
-        <v>372.2200012207031</v>
+        <v>340.8341482313199</v>
       </c>
       <c r="E21" t="n">
-        <v>372.6700134277344</v>
+        <v>343.2052001953125</v>
       </c>
       <c r="F21" t="n">
-        <v>5857400</v>
+        <v>5198000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>374.010009765625</v>
+        <v>343.3639143460552</v>
       </c>
       <c r="C22" t="n">
-        <v>380.1700134277344</v>
+        <v>350.3579971109944</v>
       </c>
       <c r="D22" t="n">
-        <v>374.010009765625</v>
+        <v>343.2548016291976</v>
       </c>
       <c r="E22" t="n">
-        <v>378.3999938964844</v>
+        <v>347.0643310546875</v>
       </c>
       <c r="F22" t="n">
-        <v>5599900</v>
+        <v>5199700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>380.1700134277344</v>
+        <v>347.2330080952501</v>
       </c>
       <c r="C23" t="n">
-        <v>382.2099914550781</v>
+        <v>348.3341867524627</v>
       </c>
       <c r="D23" t="n">
-        <v>376.8599853515625</v>
+        <v>341.6179112620468</v>
       </c>
       <c r="E23" t="n">
-        <v>378.75</v>
+        <v>346.5087890625</v>
       </c>
       <c r="F23" t="n">
-        <v>3869500</v>
+        <v>4735600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>347.2825796289147</v>
+      </c>
+      <c r="C24" t="n">
+        <v>351.6278330286145</v>
+      </c>
+      <c r="D24" t="n">
+        <v>347.2825796289147</v>
+      </c>
+      <c r="E24" t="n">
+        <v>349.6238708496094</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5044600</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>350.9730784623077</v>
+      </c>
+      <c r="C25" t="n">
+        <v>352.1834000905383</v>
+      </c>
+      <c r="D25" t="n">
+        <v>348.3143490742109</v>
+      </c>
+      <c r="E25" t="n">
+        <v>348.572265625</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3927500</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>348.6814047504906</v>
+      </c>
+      <c r="C26" t="n">
+        <v>350.0702909620389</v>
+      </c>
+      <c r="D26" t="n">
+        <v>342.8381220393481</v>
+      </c>
+      <c r="E26" t="n">
+        <v>344.2865600585938</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4434800</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>344.8718644724454</v>
+      </c>
+      <c r="C27" t="n">
+        <v>347.619876043067</v>
+      </c>
+      <c r="D27" t="n">
+        <v>340.5266111021468</v>
+      </c>
+      <c r="E27" t="n">
+        <v>340.9234313964844</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6296200</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>340.9928833808045</v>
+      </c>
+      <c r="C28" t="n">
+        <v>344.9016253459246</v>
+      </c>
+      <c r="D28" t="n">
+        <v>338.0266161060487</v>
+      </c>
+      <c r="E28" t="n">
+        <v>340.5762023925781</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4030700</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>338.2944848137428</v>
+      </c>
+      <c r="C29" t="n">
+        <v>347.2330086020973</v>
+      </c>
+      <c r="D29" t="n">
+        <v>337.520674593222</v>
+      </c>
+      <c r="E29" t="n">
+        <v>345.6159362792969</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5731000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>345.615925335404</v>
+      </c>
+      <c r="C30" t="n">
+        <v>347.3024192111109</v>
+      </c>
+      <c r="D30" t="n">
+        <v>341.2706718210525</v>
+      </c>
+      <c r="E30" t="n">
+        <v>342.947265625</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3778200</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>342.2627301477191</v>
+      </c>
+      <c r="C31" t="n">
+        <v>342.9472580300504</v>
+      </c>
+      <c r="D31" t="n">
+        <v>331.5186699399313</v>
+      </c>
+      <c r="E31" t="n">
+        <v>332.7388916015625</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6241500</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>335.0900620604222</v>
+      </c>
+      <c r="C32" t="n">
+        <v>340.725018943138</v>
+      </c>
+      <c r="D32" t="n">
+        <v>334.3261822760441</v>
+      </c>
+      <c r="E32" t="n">
+        <v>339.1773986816406</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6267100</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>339.1873037416991</v>
+      </c>
+      <c r="C33" t="n">
+        <v>342.2230227820154</v>
+      </c>
+      <c r="D33" t="n">
+        <v>336.2507973402091</v>
+      </c>
+      <c r="E33" t="n">
+        <v>341.6773986816406</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4665000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>340.3976542086254</v>
+      </c>
+      <c r="C34" t="n">
+        <v>346.8758434662893</v>
+      </c>
+      <c r="D34" t="n">
+        <v>340.2786111420936</v>
+      </c>
+      <c r="E34" t="n">
+        <v>344.4552001953125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4121800</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>345.0603770187118</v>
+      </c>
+      <c r="C35" t="n">
+        <v>345.4076061472691</v>
+      </c>
+      <c r="D35" t="n">
+        <v>341.7667108842852</v>
+      </c>
+      <c r="E35" t="n">
+        <v>342.619873046875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5074400</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>343.4532042783919</v>
+      </c>
+      <c r="C36" t="n">
+        <v>344.3956486566242</v>
+      </c>
+      <c r="D36" t="n">
+        <v>341.7269891377298</v>
+      </c>
+      <c r="E36" t="n">
+        <v>343.215087890625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7217200</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>345.4373415963541</v>
+      </c>
+      <c r="C37" t="n">
+        <v>346.3103341142831</v>
+      </c>
+      <c r="D37" t="n">
+        <v>342.5801871000132</v>
+      </c>
+      <c r="E37" t="n">
+        <v>344.6238403320312</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3576700</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>346.2310248701323</v>
+      </c>
+      <c r="C38" t="n">
+        <v>346.7468882773667</v>
+      </c>
+      <c r="D38" t="n">
+        <v>342.2726913226552</v>
+      </c>
+      <c r="E38" t="n">
+        <v>345.0603942871094</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5400300</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>345.8143074374688</v>
+      </c>
+      <c r="C39" t="n">
+        <v>347.1139415798067</v>
+      </c>
+      <c r="D39" t="n">
+        <v>343.7508237502946</v>
+      </c>
+      <c r="E39" t="n">
+        <v>344.1476440429688</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7445400</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>343.2547871723516</v>
+      </c>
+      <c r="C40" t="n">
+        <v>348.1952860487332</v>
+      </c>
+      <c r="D40" t="n">
+        <v>336.3103261601942</v>
+      </c>
+      <c r="E40" t="n">
+        <v>338.5722351074219</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8361700</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>339.5047778404419</v>
+      </c>
+      <c r="C41" t="n">
+        <v>346.9452717470537</v>
+      </c>
+      <c r="D41" t="n">
+        <v>339.0781967892368</v>
+      </c>
+      <c r="E41" t="n">
+        <v>342.29248046875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6411800</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>339.3658942315137</v>
+      </c>
+      <c r="C42" t="n">
+        <v>340.2786081927618</v>
+      </c>
+      <c r="D42" t="n">
+        <v>335.4869431536939</v>
+      </c>
+      <c r="E42" t="n">
+        <v>338.0365295410156</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7301600</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>338.2944659192743</v>
+      </c>
+      <c r="C43" t="n">
+        <v>338.5027912774657</v>
+      </c>
+      <c r="D43" t="n">
+        <v>332.1635060317716</v>
+      </c>
+      <c r="E43" t="n">
+        <v>334.2269897460938</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5538000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>333.810367634687</v>
+      </c>
+      <c r="C44" t="n">
+        <v>337.6198973167316</v>
+      </c>
+      <c r="D44" t="n">
+        <v>331.5980496280586</v>
+      </c>
+      <c r="E44" t="n">
+        <v>337.6000366210938</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5920200</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>337.4313538243792</v>
+      </c>
+      <c r="C45" t="n">
+        <v>339.3956247811457</v>
+      </c>
+      <c r="D45" t="n">
+        <v>333.6912462886964</v>
+      </c>
+      <c r="E45" t="n">
+        <v>337.3420715332031</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4984600</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>335.9035711966457</v>
+      </c>
+      <c r="C46" t="n">
+        <v>335.9630927253758</v>
+      </c>
+      <c r="D46" t="n">
+        <v>331.062285023625</v>
+      </c>
+      <c r="E46" t="n">
+        <v>334.2864990234375</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8507900</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>334.0583313951361</v>
+      </c>
+      <c r="C47" t="n">
+        <v>335.6059516380656</v>
+      </c>
+      <c r="D47" t="n">
+        <v>332.1932428266196</v>
+      </c>
+      <c r="E47" t="n">
+        <v>333.3539428710938</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5318400</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>333.9789743060267</v>
+      </c>
+      <c r="C48" t="n">
+        <v>335.9928668426192</v>
+      </c>
+      <c r="D48" t="n">
+        <v>331.6674741139567</v>
+      </c>
+      <c r="E48" t="n">
+        <v>332.1932678222656</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5295800</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>332.838108855689</v>
+      </c>
+      <c r="C49" t="n">
+        <v>336.3996217972758</v>
+      </c>
+      <c r="D49" t="n">
+        <v>330.5563693999427</v>
+      </c>
+      <c r="E49" t="n">
+        <v>336.2309875488281</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4453300</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>336.230963908966</v>
+      </c>
+      <c r="C50" t="n">
+        <v>342.2050995382295</v>
+      </c>
+      <c r="D50" t="n">
+        <v>335.3860315467677</v>
+      </c>
+      <c r="E50" t="n">
+        <v>336.8572082519531</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6389600</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>337.01623628756</v>
+      </c>
+      <c r="C51" t="n">
+        <v>339.4217740167541</v>
+      </c>
+      <c r="D51" t="n">
+        <v>333.5967676514001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>334.0738830566406</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4961700</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>333.8850664354288</v>
+      </c>
+      <c r="C52" t="n">
+        <v>334.0739044051273</v>
+      </c>
+      <c r="D52" t="n">
+        <v>327.0659984240934</v>
+      </c>
+      <c r="E52" t="n">
+        <v>328.0500793457031</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6422300</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>329.1832834325262</v>
+      </c>
+      <c r="C53" t="n">
+        <v>331.370133257436</v>
+      </c>
+      <c r="D53" t="n">
+        <v>322.9904598740608</v>
+      </c>
+      <c r="E53" t="n">
+        <v>323.8055725097656</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6494800</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>322.5630378796905</v>
+      </c>
+      <c r="C54" t="n">
+        <v>323.0600533463772</v>
+      </c>
+      <c r="D54" t="n">
+        <v>316.101836812763</v>
+      </c>
+      <c r="E54" t="n">
+        <v>319.2628479003906</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9170400</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>319.6008465015586</v>
+      </c>
+      <c r="C55" t="n">
+        <v>322.6326593505401</v>
+      </c>
+      <c r="D55" t="n">
+        <v>317.9607013657724</v>
+      </c>
+      <c r="E55" t="n">
+        <v>322.1853332519531</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7066700</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>322.1852887063674</v>
+      </c>
+      <c r="C56" t="n">
+        <v>326.4397397218689</v>
+      </c>
+      <c r="D56" t="n">
+        <v>321.2111578443184</v>
+      </c>
+      <c r="E56" t="n">
+        <v>321.8373718261719</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6510300</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>323.4377913272098</v>
+      </c>
+      <c r="C57" t="n">
+        <v>329.1037494702317</v>
+      </c>
+      <c r="D57" t="n">
+        <v>322.354301245485</v>
+      </c>
+      <c r="E57" t="n">
+        <v>326.0222778320312</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8930000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>327.2747416730934</v>
+      </c>
+      <c r="C58" t="n">
+        <v>328.755868423024</v>
+      </c>
+      <c r="D58" t="n">
+        <v>324.0540910886259</v>
+      </c>
+      <c r="E58" t="n">
+        <v>327.3343811035156</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9337100</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>326.9367735032804</v>
+      </c>
+      <c r="C59" t="n">
+        <v>334.0540387480419</v>
+      </c>
+      <c r="D59" t="n">
+        <v>326.9367735032804</v>
+      </c>
+      <c r="E59" t="n">
+        <v>332.5331726074219</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5854300</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>332.533150050326</v>
+      </c>
+      <c r="C60" t="n">
+        <v>333.7060992116737</v>
+      </c>
+      <c r="D60" t="n">
+        <v>331.0719234390147</v>
+      </c>
+      <c r="E60" t="n">
+        <v>331.7975769042969</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4309900</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>331.4397445821358</v>
+      </c>
+      <c r="C61" t="n">
+        <v>333.0202502105825</v>
+      </c>
+      <c r="D61" t="n">
+        <v>330.0182875517957</v>
+      </c>
+      <c r="E61" t="n">
+        <v>332.4437255859375</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4586200</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>330.952674561706</v>
+      </c>
+      <c r="C62" t="n">
+        <v>331.3105111509684</v>
+      </c>
+      <c r="D62" t="n">
+        <v>328.1693999716056</v>
+      </c>
+      <c r="E62" t="n">
+        <v>328.4179077148438</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7082300</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>329.4715593852143</v>
+      </c>
+      <c r="C63" t="n">
+        <v>330.8134768540631</v>
+      </c>
+      <c r="D63" t="n">
+        <v>325.2568476714639</v>
+      </c>
+      <c r="E63" t="n">
+        <v>327.6524658203125</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8201900</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>327.6425170898438</v>
+      </c>
+      <c r="C64" t="n">
+        <v>330.3661824396382</v>
+      </c>
+      <c r="D64" t="n">
+        <v>327.3840896786403</v>
+      </c>
+      <c r="E64" t="n">
+        <v>327.6425170898438</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6296700</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>329.3025948705371</v>
+      </c>
+      <c r="C65" t="n">
+        <v>330.396035058885</v>
+      </c>
+      <c r="D65" t="n">
+        <v>322.3443777352205</v>
+      </c>
+      <c r="E65" t="n">
+        <v>325.1475524902344</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6277500</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>324.8791069392551</v>
+      </c>
+      <c r="C66" t="n">
+        <v>332.1156507054553</v>
+      </c>
+      <c r="D66" t="n">
+        <v>324.4516809311236</v>
+      </c>
+      <c r="E66" t="n">
+        <v>329.2627868652344</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5266600</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>327.9109311533039</v>
+      </c>
+      <c r="C67" t="n">
+        <v>329.3622078309571</v>
+      </c>
+      <c r="D67" t="n">
+        <v>322.77177784886</v>
+      </c>
+      <c r="E67" t="n">
+        <v>324.8890686035156</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6059400</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>324.6604152629651</v>
+      </c>
+      <c r="C68" t="n">
+        <v>326.2707707906858</v>
+      </c>
+      <c r="D68" t="n">
+        <v>323.1296295298985</v>
+      </c>
+      <c r="E68" t="n">
+        <v>324.5510864257812</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4325400</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>324.6902773524443</v>
+      </c>
+      <c r="C69" t="n">
+        <v>326.797618069185</v>
+      </c>
+      <c r="D69" t="n">
+        <v>323.3582492118315</v>
+      </c>
+      <c r="E69" t="n">
+        <v>323.7857055664062</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5467500</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>330.6146735055701</v>
+      </c>
+      <c r="C70" t="n">
+        <v>345.2468091287718</v>
+      </c>
+      <c r="D70" t="n">
+        <v>328.0898266012699</v>
+      </c>
+      <c r="E70" t="n">
+        <v>343.56689453125</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12953600</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>345.9227522622342</v>
+      </c>
+      <c r="C71" t="n">
+        <v>347.751765473026</v>
+      </c>
+      <c r="D71" t="n">
+        <v>343.9048707541211</v>
+      </c>
+      <c r="E71" t="n">
+        <v>345.7537536621094</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6942300</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>345.7537581195867</v>
+      </c>
+      <c r="C72" t="n">
+        <v>346.3700827656107</v>
+      </c>
+      <c r="D72" t="n">
+        <v>341.7776344791052</v>
+      </c>
+      <c r="E72" t="n">
+        <v>344.8193969726562</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7004600</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>343.9347204472646</v>
+      </c>
+      <c r="C73" t="n">
+        <v>345.5450457875993</v>
+      </c>
+      <c r="D73" t="n">
+        <v>341.6683310172716</v>
+      </c>
+      <c r="E73" t="n">
+        <v>343.0500183105469</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7269300</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>343.4873664669518</v>
+      </c>
+      <c r="C74" t="n">
+        <v>345.7140163182048</v>
+      </c>
+      <c r="D74" t="n">
+        <v>341.6285335316323</v>
+      </c>
+      <c r="E74" t="n">
+        <v>342.3541870117188</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7263500</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>343.1096587982668</v>
+      </c>
+      <c r="C75" t="n">
+        <v>345.4555571592003</v>
+      </c>
+      <c r="D75" t="n">
+        <v>342.2150067207226</v>
+      </c>
+      <c r="E75" t="n">
+        <v>343.9446411132812</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6805000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>343.9844025059169</v>
+      </c>
+      <c r="C76" t="n">
+        <v>347.8213777963309</v>
+      </c>
+      <c r="D76" t="n">
+        <v>343.9844025059169</v>
+      </c>
+      <c r="E76" t="n">
+        <v>347.1653137207031</v>
+      </c>
+      <c r="F76" t="n">
+        <v>18623900</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>347.9108213067459</v>
+      </c>
+      <c r="C77" t="n">
+        <v>351.3302900915655</v>
+      </c>
+      <c r="D77" t="n">
+        <v>347.5032649901081</v>
+      </c>
+      <c r="E77" t="n">
+        <v>349.9883422851562</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5043500</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>349.8988624434305</v>
+      </c>
+      <c r="C78" t="n">
+        <v>354.2527224604554</v>
+      </c>
+      <c r="D78" t="n">
+        <v>349.8988624434305</v>
+      </c>
+      <c r="E78" t="n">
+        <v>351.2706298828125</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3703200</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>351.2706679101954</v>
+      </c>
+      <c r="C79" t="n">
+        <v>353.8650741726075</v>
+      </c>
+      <c r="D79" t="n">
+        <v>350.9028813061371</v>
+      </c>
+      <c r="E79" t="n">
+        <v>353.0201721191406</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2023600</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>352.9803906057607</v>
+      </c>
+      <c r="C80" t="n">
+        <v>354.6006658812749</v>
+      </c>
+      <c r="D80" t="n">
+        <v>351.5986730469889</v>
+      </c>
+      <c r="E80" t="n">
+        <v>352.8809814453125</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2017000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>353.3680687798424</v>
+      </c>
+      <c r="C81" t="n">
+        <v>354.4217392079314</v>
+      </c>
+      <c r="D81" t="n">
+        <v>351.6881539711041</v>
+      </c>
+      <c r="E81" t="n">
+        <v>352.4933166503906</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3989900</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>351.8869529196318</v>
+      </c>
+      <c r="C82" t="n">
+        <v>352.7517549841574</v>
+      </c>
+      <c r="D82" t="n">
+        <v>350.5549550996776</v>
+      </c>
+      <c r="E82" t="n">
+        <v>351.5092163085938</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3366500</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>351.539030494231</v>
+      </c>
+      <c r="C83" t="n">
+        <v>353.0797966289462</v>
+      </c>
+      <c r="D83" t="n">
+        <v>348.5967074506911</v>
+      </c>
+      <c r="E83" t="n">
+        <v>348.6165771484375</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3503200</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>347.7816144857114</v>
+      </c>
+      <c r="C84" t="n">
+        <v>347.9605327817998</v>
+      </c>
+      <c r="D84" t="n">
+        <v>341.4297722912301</v>
+      </c>
+      <c r="E84" t="n">
+        <v>344.411865234375</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5403800</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>342.443665092254</v>
+      </c>
+      <c r="C85" t="n">
+        <v>355.4058372808095</v>
+      </c>
+      <c r="D85" t="n">
+        <v>341.996339026907</v>
+      </c>
+      <c r="E85" t="n">
+        <v>351.6881408691406</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7592200</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>351.5688750998228</v>
+      </c>
+      <c r="C86" t="n">
+        <v>356.4793906429162</v>
+      </c>
+      <c r="D86" t="n">
+        <v>349.8989103083969</v>
+      </c>
+      <c r="E86" t="n">
+        <v>355.4257202148438</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6775400</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>355.0181456831753</v>
+      </c>
+      <c r="C87" t="n">
+        <v>356.1414055038805</v>
+      </c>
+      <c r="D87" t="n">
+        <v>352.3939197646881</v>
+      </c>
+      <c r="E87" t="n">
+        <v>353.7557373046875</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6333900</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>352.8809877738215</v>
+      </c>
+      <c r="C88" t="n">
+        <v>354.2229356253969</v>
+      </c>
+      <c r="D88" t="n">
+        <v>347.4138175407059</v>
+      </c>
+      <c r="E88" t="n">
+        <v>350.1275329589844</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6357600</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>350.0579384420253</v>
+      </c>
+      <c r="C89" t="n">
+        <v>352.582785516123</v>
+      </c>
+      <c r="D89" t="n">
+        <v>347.075845630788</v>
+      </c>
+      <c r="E89" t="n">
+        <v>347.6821899414062</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4902900</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>340.7339218833562</v>
+      </c>
+      <c r="C90" t="n">
+        <v>344.4416681829234</v>
+      </c>
+      <c r="D90" t="n">
+        <v>335.306521484956</v>
+      </c>
+      <c r="E90" t="n">
+        <v>341.1514282226562</v>
+      </c>
+      <c r="F90" t="n">
+        <v>13281300</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>334.9884397502153</v>
+      </c>
+      <c r="C91" t="n">
+        <v>335.5053249382782</v>
+      </c>
+      <c r="D91" t="n">
+        <v>321.8970384159538</v>
+      </c>
+      <c r="E91" t="n">
+        <v>325.9228820800781</v>
+      </c>
+      <c r="F91" t="n">
+        <v>20383500</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>326.6982042036898</v>
+      </c>
+      <c r="C92" t="n">
+        <v>327.9307928311059</v>
+      </c>
+      <c r="D92" t="n">
+        <v>322.0063770709054</v>
+      </c>
+      <c r="E92" t="n">
+        <v>327.2051696777344</v>
+      </c>
+      <c r="F92" t="n">
+        <v>9388400</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>327.3641956721743</v>
+      </c>
+      <c r="C93" t="n">
+        <v>329.7101244617631</v>
+      </c>
+      <c r="D93" t="n">
+        <v>324.4218725877395</v>
+      </c>
+      <c r="E93" t="n">
+        <v>325.7936401367188</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8587700</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>324.8294159854098</v>
+      </c>
+      <c r="C94" t="n">
+        <v>327.2846735195349</v>
+      </c>
+      <c r="D94" t="n">
+        <v>323.4576484910236</v>
+      </c>
+      <c r="E94" t="n">
+        <v>326.34033203125</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8341600</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>320.3066155063486</v>
+      </c>
+      <c r="C95" t="n">
+        <v>326.3602605702113</v>
+      </c>
+      <c r="D95" t="n">
+        <v>319.6406013982136</v>
+      </c>
+      <c r="E95" t="n">
+        <v>323.8751831054688</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8279900</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>324.4815084058711</v>
+      </c>
+      <c r="C96" t="n">
+        <v>326.708158311709</v>
+      </c>
+      <c r="D96" t="n">
+        <v>321.0719896048092</v>
+      </c>
+      <c r="E96" t="n">
+        <v>323.33837890625</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8974600</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>324.5113354316111</v>
+      </c>
+      <c r="C97" t="n">
+        <v>326.4298382199604</v>
+      </c>
+      <c r="D97" t="n">
+        <v>322.0660277886144</v>
+      </c>
+      <c r="E97" t="n">
+        <v>324.4119262695312</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6938700</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>323.9149045306469</v>
+      </c>
+      <c r="C98" t="n">
+        <v>325.8433269631201</v>
+      </c>
+      <c r="D98" t="n">
+        <v>322.6823158838599</v>
+      </c>
+      <c r="E98" t="n">
+        <v>324.2330017089844</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5667900</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>326.0421398816049</v>
+      </c>
+      <c r="C99" t="n">
+        <v>330.0182635386976</v>
+      </c>
+      <c r="D99" t="n">
+        <v>323.0898668527969</v>
+      </c>
+      <c r="E99" t="n">
+        <v>326.5292053222656</v>
+      </c>
+      <c r="F99" t="n">
+        <v>7540200</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>326.5192927903481</v>
+      </c>
+      <c r="C100" t="n">
+        <v>326.9665885103149</v>
+      </c>
+      <c r="D100" t="n">
+        <v>322.9705950681941</v>
+      </c>
+      <c r="E100" t="n">
+        <v>323.3185119628906</v>
+      </c>
+      <c r="F100" t="n">
+        <v>6365800</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>324.7797515334782</v>
+      </c>
+      <c r="C101" t="n">
+        <v>326.4298465929955</v>
+      </c>
+      <c r="D101" t="n">
+        <v>322.9407881617898</v>
+      </c>
+      <c r="E101" t="n">
+        <v>325.0282592773438</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8106000</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>328.0302144269235</v>
+      </c>
+      <c r="C102" t="n">
+        <v>331.370143867361</v>
+      </c>
+      <c r="D102" t="n">
+        <v>321.5789632505275</v>
+      </c>
+      <c r="E102" t="n">
+        <v>329.8194580078125</v>
+      </c>
+      <c r="F102" t="n">
+        <v>10214200</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>330.2369936591709</v>
+      </c>
+      <c r="C103" t="n">
+        <v>331.0123366577452</v>
+      </c>
+      <c r="D103" t="n">
+        <v>319.6803888572667</v>
+      </c>
+      <c r="E103" t="n">
+        <v>319.9089965820312</v>
+      </c>
+      <c r="F103" t="n">
+        <v>11199100</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>322.8910614362982</v>
+      </c>
+      <c r="C104" t="n">
+        <v>332.6922224170356</v>
+      </c>
+      <c r="D104" t="n">
+        <v>322.1753579360102</v>
+      </c>
+      <c r="E104" t="n">
+        <v>331.8472900390625</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8502400</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>329.6703793378445</v>
+      </c>
+      <c r="C105" t="n">
+        <v>333.7856822919601</v>
+      </c>
+      <c r="D105" t="n">
+        <v>326.906974335595</v>
+      </c>
+      <c r="E105" t="n">
+        <v>326.9666137695312</v>
+      </c>
+      <c r="F105" t="n">
+        <v>9081200</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>325.15742488804</v>
+      </c>
+      <c r="C106" t="n">
+        <v>329.3323666962788</v>
+      </c>
+      <c r="D106" t="n">
+        <v>322.4835097434655</v>
+      </c>
+      <c r="E106" t="n">
+        <v>327.9804992675781</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8472300</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>331.0123001239136</v>
+      </c>
+      <c r="C107" t="n">
+        <v>335.5748984583446</v>
+      </c>
+      <c r="D107" t="n">
+        <v>326.8572581115669</v>
+      </c>
+      <c r="E107" t="n">
+        <v>327.1654052734375</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8339000</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>329.7995873671293</v>
+      </c>
+      <c r="C108" t="n">
+        <v>333.1295971166072</v>
+      </c>
+      <c r="D108" t="n">
+        <v>325.1475298017769</v>
+      </c>
+      <c r="E108" t="n">
+        <v>329.6007690429688</v>
+      </c>
+      <c r="F108" t="n">
+        <v>7798800</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>328.7857002676274</v>
+      </c>
+      <c r="C109" t="n">
+        <v>330.8334016821115</v>
+      </c>
+      <c r="D109" t="n">
+        <v>321.6883044313802</v>
+      </c>
+      <c r="E109" t="n">
+        <v>323.6365966796875</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8513400</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>323.4373584411114</v>
+      </c>
+      <c r="C110" t="n">
+        <v>328.5871090806843</v>
+      </c>
+      <c r="D110" t="n">
+        <v>323.2779818799478</v>
+      </c>
+      <c r="E110" t="n">
+        <v>326.8838195800781</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5801800</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>325.6387009449491</v>
+      </c>
+      <c r="C111" t="n">
+        <v>329.7425483778229</v>
+      </c>
+      <c r="D111" t="n">
+        <v>325.140660617698</v>
+      </c>
+      <c r="E111" t="n">
+        <v>327.9495849609375</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8264300</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>327.6010166244024</v>
+      </c>
+      <c r="C112" t="n">
+        <v>330.9378628609571</v>
+      </c>
+      <c r="D112" t="n">
+        <v>322.7301671039365</v>
+      </c>
+      <c r="E112" t="n">
+        <v>322.9094543457031</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9392600</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>322.5607854182599</v>
+      </c>
+      <c r="C113" t="n">
+        <v>325.2004234747151</v>
+      </c>
+      <c r="D113" t="n">
+        <v>311.5939580676488</v>
+      </c>
+      <c r="E113" t="n">
+        <v>312.8489990234375</v>
+      </c>
+      <c r="F113" t="n">
+        <v>11653900</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>313.1777553150958</v>
+      </c>
+      <c r="C114" t="n">
+        <v>320.1204394263468</v>
+      </c>
+      <c r="D114" t="n">
+        <v>313.1777553150958</v>
+      </c>
+      <c r="E114" t="n">
+        <v>318.247802734375</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8591700</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>318.2477947880967</v>
+      </c>
+      <c r="C115" t="n">
+        <v>321.0168980150915</v>
+      </c>
+      <c r="D115" t="n">
+        <v>315.4786915611019</v>
+      </c>
+      <c r="E115" t="n">
+        <v>319.0446472167969</v>
+      </c>
+      <c r="F115" t="n">
+        <v>7091900</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>316.2456341157693</v>
+      </c>
+      <c r="C116" t="n">
+        <v>318.9450345490796</v>
+      </c>
+      <c r="D116" t="n">
+        <v>314.4925528519528</v>
+      </c>
+      <c r="E116" t="n">
+        <v>317.6799926757812</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5967600</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>316.8632122574057</v>
+      </c>
+      <c r="C117" t="n">
+        <v>321.0866150343326</v>
+      </c>
+      <c r="D117" t="n">
+        <v>316.5743707451638</v>
+      </c>
+      <c r="E117" t="n">
+        <v>319.6921081542969</v>
+      </c>
+      <c r="F117" t="n">
+        <v>6831100</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>317.7896151590316</v>
+      </c>
+      <c r="C118" t="n">
+        <v>319.2637952336624</v>
+      </c>
+      <c r="D118" t="n">
+        <v>303.5157608014752</v>
+      </c>
+      <c r="E118" t="n">
+        <v>305.3186645507812</v>
+      </c>
+      <c r="F118" t="n">
+        <v>13048000</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>304.30263971785</v>
+      </c>
+      <c r="C119" t="n">
+        <v>308.0578528391844</v>
+      </c>
+      <c r="D119" t="n">
+        <v>301.8921111606905</v>
+      </c>
+      <c r="E119" t="n">
+        <v>306.0158996582031</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9120200</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>307.3407046816708</v>
+      </c>
+      <c r="C120" t="n">
+        <v>312.7095945401492</v>
+      </c>
+      <c r="D120" t="n">
+        <v>307.0418926144709</v>
+      </c>
+      <c r="E120" t="n">
+        <v>311.7633056640625</v>
+      </c>
+      <c r="F120" t="n">
+        <v>7624200</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>313.2475006793624</v>
+      </c>
+      <c r="C121" t="n">
+        <v>318.168142259306</v>
+      </c>
+      <c r="D121" t="n">
+        <v>312.7096085363555</v>
+      </c>
+      <c r="E121" t="n">
+        <v>315.4588012695312</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8725500</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>313.2275230423357</v>
+      </c>
+      <c r="C122" t="n">
+        <v>318.9749280375353</v>
+      </c>
+      <c r="D122" t="n">
+        <v>310.7273811988043</v>
+      </c>
+      <c r="E122" t="n">
+        <v>318.8852844238281</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12412900</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>314.2634710190134</v>
+      </c>
+      <c r="C123" t="n">
+        <v>321.3356502974509</v>
+      </c>
+      <c r="D123" t="n">
+        <v>313.3670044395995</v>
+      </c>
+      <c r="E123" t="n">
+        <v>319.2538452148438</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6674900</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>314.5722564235918</v>
+      </c>
+      <c r="C124" t="n">
+        <v>320.7778503840851</v>
+      </c>
+      <c r="D124" t="n">
+        <v>313.117987052978</v>
+      </c>
+      <c r="E124" t="n">
+        <v>319.5725708007812</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5474300</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>320.1801887712339</v>
+      </c>
+      <c r="C125" t="n">
+        <v>324.4932049097204</v>
+      </c>
+      <c r="D125" t="n">
+        <v>318.5466018009251</v>
+      </c>
+      <c r="E125" t="n">
+        <v>319.2139892578125</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5257900</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>318.0784411900573</v>
+      </c>
+      <c r="C126" t="n">
+        <v>321.5348424853333</v>
+      </c>
+      <c r="D126" t="n">
+        <v>313.5363155637196</v>
+      </c>
+      <c r="E126" t="n">
+        <v>318.5466003417969</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8267200</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>314.8113170354491</v>
+      </c>
+      <c r="C127" t="n">
+        <v>316.4449040988039</v>
+      </c>
+      <c r="D127" t="n">
+        <v>311.0760141261629</v>
+      </c>
+      <c r="E127" t="n">
+        <v>316.1161804199219</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6439700</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>312.2314560667069</v>
+      </c>
+      <c r="C128" t="n">
+        <v>315.1599358349184</v>
+      </c>
+      <c r="D128" t="n">
+        <v>308.9344312933075</v>
+      </c>
+      <c r="E128" t="n">
+        <v>314.7316284179688</v>
+      </c>
+      <c r="F128" t="n">
+        <v>8381500</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>314.1937124870568</v>
+      </c>
+      <c r="C129" t="n">
+        <v>315.8870617531473</v>
+      </c>
+      <c r="D129" t="n">
+        <v>310.2293309503021</v>
+      </c>
+      <c r="E129" t="n">
+        <v>313.1976318359375</v>
+      </c>
+      <c r="F129" t="n">
+        <v>5271300</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>312.0222791858673</v>
+      </c>
+      <c r="C130" t="n">
+        <v>313.8450934912395</v>
+      </c>
+      <c r="D130" t="n">
+        <v>307.1813415762761</v>
+      </c>
+      <c r="E130" t="n">
+        <v>307.7490844726562</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6376700</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>306.9323235221122</v>
+      </c>
+      <c r="C131" t="n">
+        <v>309.7313078758147</v>
+      </c>
+      <c r="D131" t="n">
+        <v>304.8206068898292</v>
+      </c>
+      <c r="E131" t="n">
+        <v>305.2987365722656</v>
+      </c>
+      <c r="F131" t="n">
+        <v>7514900</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>306.3844668672209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>309.1336593983733</v>
+      </c>
+      <c r="D132" t="n">
+        <v>305.2190694406472</v>
+      </c>
+      <c r="E132" t="n">
+        <v>305.9362487792969</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4814100</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>306.6434401255651</v>
+      </c>
+      <c r="C133" t="n">
+        <v>309.9105835049712</v>
+      </c>
+      <c r="D133" t="n">
+        <v>306.1752809950723</v>
+      </c>
+      <c r="E133" t="n">
+        <v>308.8945617675781</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6401200</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>310.0998441452866</v>
+      </c>
+      <c r="C134" t="n">
+        <v>311.4644698112407</v>
+      </c>
+      <c r="D134" t="n">
+        <v>306.1752838399166</v>
+      </c>
+      <c r="E134" t="n">
+        <v>307.2510375976562</v>
+      </c>
+      <c r="F134" t="n">
+        <v>6872200</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>306.2051850075188</v>
+      </c>
+      <c r="C135" t="n">
+        <v>306.7331065856557</v>
+      </c>
+      <c r="D135" t="n">
+        <v>297.3301019351647</v>
+      </c>
+      <c r="E135" t="n">
+        <v>297.8480529785156</v>
+      </c>
+      <c r="F135" t="n">
+        <v>7191700</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>296.8719016022564</v>
+      </c>
+      <c r="C136" t="n">
+        <v>301.2845318265138</v>
+      </c>
+      <c r="D136" t="n">
+        <v>295.8658503636263</v>
+      </c>
+      <c r="E136" t="n">
+        <v>298.5353393554688</v>
+      </c>
+      <c r="F136" t="n">
+        <v>6826400</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>298.6748142545254</v>
+      </c>
+      <c r="C137" t="n">
+        <v>301.7327894042891</v>
+      </c>
+      <c r="D137" t="n">
+        <v>297.8381100854838</v>
+      </c>
+      <c r="E137" t="n">
+        <v>300.4378662109375</v>
+      </c>
+      <c r="F137" t="n">
+        <v>14398100</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>304.0038572697504</v>
+      </c>
+      <c r="C138" t="n">
+        <v>306.6434651794843</v>
+      </c>
+      <c r="D138" t="n">
+        <v>301.6630614260347</v>
+      </c>
+      <c r="E138" t="n">
+        <v>303.246826171875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>7824500</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>300.8163767349488</v>
+      </c>
+      <c r="C139" t="n">
+        <v>304.8405513457489</v>
+      </c>
+      <c r="D139" t="n">
+        <v>299.4417804808951</v>
+      </c>
+      <c r="E139" t="n">
+        <v>302.5694885253906</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5375900</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>304.2827391072273</v>
+      </c>
+      <c r="C140" t="n">
+        <v>307.2809213034843</v>
+      </c>
+      <c r="D140" t="n">
+        <v>300.9857144661871</v>
+      </c>
+      <c r="E140" t="n">
+        <v>303.7149658203125</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6280900</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>302.9679242862715</v>
+      </c>
+      <c r="C141" t="n">
+        <v>306.6633753539059</v>
+      </c>
+      <c r="D141" t="n">
+        <v>301.8124669695884</v>
+      </c>
+      <c r="E141" t="n">
+        <v>304.3325500488281</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7652700</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>303.127283705864</v>
+      </c>
+      <c r="C142" t="n">
+        <v>303.3962145496307</v>
+      </c>
+      <c r="D142" t="n">
+        <v>293.1664767786049</v>
+      </c>
+      <c r="E142" t="n">
+        <v>294.3617553710938</v>
+      </c>
+      <c r="F142" t="n">
+        <v>9974400</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>297.5592048794472</v>
+      </c>
+      <c r="C143" t="n">
+        <v>299.5015440476056</v>
+      </c>
+      <c r="D143" t="n">
+        <v>294.7303392781201</v>
+      </c>
+      <c r="E143" t="n">
+        <v>298.3660278320312</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9330300</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>300.4179440831887</v>
+      </c>
+      <c r="C144" t="n">
+        <v>302.1511147673973</v>
+      </c>
+      <c r="D144" t="n">
+        <v>295.4275700673832</v>
+      </c>
+      <c r="E144" t="n">
+        <v>301.055419921875</v>
+      </c>
+      <c r="F144" t="n">
+        <v>10246900</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>303.8544344044319</v>
+      </c>
+      <c r="C145" t="n">
+        <v>303.8544344044319</v>
+      </c>
+      <c r="D145" t="n">
+        <v>292.7381994806606</v>
+      </c>
+      <c r="E145" t="n">
+        <v>297.340087890625</v>
+      </c>
+      <c r="F145" t="n">
+        <v>7707600</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>296.6328211241279</v>
+      </c>
+      <c r="C146" t="n">
+        <v>301.2845313811459</v>
+      </c>
+      <c r="D146" t="n">
+        <v>294.6904819925192</v>
+      </c>
+      <c r="E146" t="n">
+        <v>299.6210632324219</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4376000</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>299.5612984468797</v>
+      </c>
+      <c r="C147" t="n">
+        <v>303.2268985064469</v>
+      </c>
+      <c r="D147" t="n">
+        <v>298.286316373369</v>
+      </c>
+      <c r="E147" t="n">
+        <v>302.1411437988281</v>
+      </c>
+      <c r="F147" t="n">
+        <v>5501000</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>301.2546730003434</v>
+      </c>
+      <c r="C148" t="n">
+        <v>303.7847266884853</v>
+      </c>
+      <c r="D148" t="n">
+        <v>299.9398390775635</v>
+      </c>
+      <c r="E148" t="n">
+        <v>301.3642272949219</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4413900</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>306.5239246667074</v>
+      </c>
+      <c r="C149" t="n">
+        <v>309.8607706923777</v>
+      </c>
+      <c r="D149" t="n">
+        <v>306.4940434616348</v>
+      </c>
+      <c r="E149" t="n">
+        <v>307.7490844726562</v>
+      </c>
+      <c r="F149" t="n">
+        <v>6879300</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>306.792884650012</v>
+      </c>
+      <c r="C150" t="n">
+        <v>308.3666789299265</v>
+      </c>
+      <c r="D150" t="n">
+        <v>302.4001646993119</v>
+      </c>
+      <c r="E150" t="n">
+        <v>307.0817565917969</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4811500</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>307.5000714824076</v>
+      </c>
+      <c r="C151" t="n">
+        <v>307.7889434035062</v>
+      </c>
+      <c r="D151" t="n">
+        <v>302.3204699616491</v>
+      </c>
+      <c r="E151" t="n">
+        <v>303.1671142578125</v>
+      </c>
+      <c r="F151" t="n">
+        <v>5190000</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>302.7388065700545</v>
+      </c>
+      <c r="C152" t="n">
+        <v>308.5360036681458</v>
+      </c>
+      <c r="D152" t="n">
+        <v>301.155041869684</v>
+      </c>
+      <c r="E152" t="n">
+        <v>308.1774291992188</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6787200</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>307.2610301082847</v>
+      </c>
+      <c r="C153" t="n">
+        <v>310.8967187654788</v>
+      </c>
+      <c r="D153" t="n">
+        <v>306.2848600302058</v>
+      </c>
+      <c r="E153" t="n">
+        <v>310.149658203125</v>
+      </c>
+      <c r="F153" t="n">
+        <v>5571000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>311.7732461183575</v>
+      </c>
+      <c r="C154" t="n">
+        <v>315.4886379179251</v>
+      </c>
+      <c r="D154" t="n">
+        <v>310.2990358004714</v>
+      </c>
+      <c r="E154" t="n">
+        <v>314.6718444824219</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4831400</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>315.1101522104624</v>
+      </c>
+      <c r="C155" t="n">
+        <v>316.7536793728972</v>
+      </c>
+      <c r="D155" t="n">
+        <v>313.3371296864953</v>
+      </c>
+      <c r="E155" t="n">
+        <v>313.8650512695312</v>
+      </c>
+      <c r="F155" t="n">
+        <v>5695800</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>315.3591594617635</v>
+      </c>
+      <c r="C156" t="n">
+        <v>318.1880250357548</v>
+      </c>
+      <c r="D156" t="n">
+        <v>313.9447114757824</v>
+      </c>
+      <c r="E156" t="n">
+        <v>315.7774963378906</v>
+      </c>
+      <c r="F156" t="n">
+        <v>8082300</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>315.159944872979</v>
+      </c>
+      <c r="C157" t="n">
+        <v>316.305431661891</v>
+      </c>
+      <c r="D157" t="n">
+        <v>311.1258299735145</v>
+      </c>
+      <c r="E157" t="n">
+        <v>312.7095947265625</v>
+      </c>
+      <c r="F157" t="n">
+        <v>5506800</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>312.7793059315876</v>
+      </c>
+      <c r="C158" t="n">
+        <v>315.6480231708821</v>
+      </c>
+      <c r="D158" t="n">
+        <v>307.6096447395195</v>
+      </c>
+      <c r="E158" t="n">
+        <v>308.7252502441406</v>
+      </c>
+      <c r="F158" t="n">
+        <v>6806900</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>309.7910754200902</v>
+      </c>
+      <c r="C159" t="n">
+        <v>310.1396793547997</v>
+      </c>
+      <c r="D159" t="n">
+        <v>306.8526251277434</v>
+      </c>
+      <c r="E159" t="n">
+        <v>310.0699768066406</v>
+      </c>
+      <c r="F159" t="n">
+        <v>5666600</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>309.2830795800573</v>
+      </c>
+      <c r="C160" t="n">
+        <v>310.9764290509568</v>
+      </c>
+      <c r="D160" t="n">
+        <v>303.8146058713554</v>
+      </c>
+      <c r="E160" t="n">
+        <v>307.66943359375</v>
+      </c>
+      <c r="F160" t="n">
+        <v>7275000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>305.8963913711518</v>
+      </c>
+      <c r="C161" t="n">
+        <v>308.7651086725988</v>
+      </c>
+      <c r="D161" t="n">
+        <v>303.3065754519026</v>
+      </c>
+      <c r="E161" t="n">
+        <v>308.2073059082031</v>
+      </c>
+      <c r="F161" t="n">
+        <v>5616900</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>306.3048043469537</v>
+      </c>
+      <c r="C162" t="n">
+        <v>309.6018292319215</v>
+      </c>
+      <c r="D162" t="n">
+        <v>304.8604750852367</v>
+      </c>
+      <c r="E162" t="n">
+        <v>308.4364013671875</v>
+      </c>
+      <c r="F162" t="n">
+        <v>6261500</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>310.9763962887836</v>
+      </c>
+      <c r="C163" t="n">
+        <v>312.7294775914766</v>
+      </c>
+      <c r="D163" t="n">
+        <v>307.5299352956203</v>
+      </c>
+      <c r="E163" t="n">
+        <v>308.0877380371094</v>
+      </c>
+      <c r="F163" t="n">
+        <v>8839900</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>335.0815497318694</v>
+      </c>
+      <c r="C164" t="n">
+        <v>340.6396971989305</v>
+      </c>
+      <c r="D164" t="n">
+        <v>332.4817936312549</v>
+      </c>
+      <c r="E164" t="n">
+        <v>333.5475769042969</v>
+      </c>
+      <c r="F164" t="n">
+        <v>16658600</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>330.8183346281009</v>
+      </c>
+      <c r="C165" t="n">
+        <v>331.1968501776938</v>
+      </c>
+      <c r="D165" t="n">
+        <v>326.7941598769157</v>
+      </c>
+      <c r="E165" t="n">
+        <v>328.5472717285156</v>
+      </c>
+      <c r="F165" t="n">
+        <v>11241100</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>331.5753827423343</v>
+      </c>
+      <c r="C166" t="n">
+        <v>334.5337439447337</v>
+      </c>
+      <c r="D166" t="n">
+        <v>326.6447706056774</v>
+      </c>
+      <c r="E166" t="n">
+        <v>326.744384765625</v>
+      </c>
+      <c r="F166" t="n">
+        <v>6726100</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>326.7144870306598</v>
+      </c>
+      <c r="C167" t="n">
+        <v>328.4974800902166</v>
+      </c>
+      <c r="D167" t="n">
+        <v>324.1246709928955</v>
+      </c>
+      <c r="E167" t="n">
+        <v>325.5690002441406</v>
+      </c>
+      <c r="F167" t="n">
+        <v>6712400</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>323.8357678318997</v>
+      </c>
+      <c r="C168" t="n">
+        <v>324.3039269566456</v>
+      </c>
+      <c r="D168" t="n">
+        <v>318.3971759556802</v>
+      </c>
+      <c r="E168" t="n">
+        <v>320.7678527832031</v>
+      </c>
+      <c r="F168" t="n">
+        <v>5893200</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>322.4811180854182</v>
+      </c>
+      <c r="C169" t="n">
+        <v>323.3078516694185</v>
+      </c>
+      <c r="D169" t="n">
+        <v>316.7536542120865</v>
+      </c>
+      <c r="E169" t="n">
+        <v>317.5505065917969</v>
+      </c>
+      <c r="F169" t="n">
+        <v>7808400</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>318.2876422602183</v>
+      </c>
+      <c r="C170" t="n">
+        <v>322.4213711748579</v>
+      </c>
+      <c r="D170" t="n">
+        <v>318.2876422602183</v>
+      </c>
+      <c r="E170" t="n">
+        <v>320.0208129882812</v>
+      </c>
+      <c r="F170" t="n">
+        <v>7186100</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>319.7319477733878</v>
+      </c>
+      <c r="C171" t="n">
+        <v>319.8116512556435</v>
+      </c>
+      <c r="D171" t="n">
+        <v>314.9208911627371</v>
+      </c>
+      <c r="E171" t="n">
+        <v>317.5405883789062</v>
+      </c>
+      <c r="F171" t="n">
+        <v>5950200</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>317.8493444570379</v>
+      </c>
+      <c r="C172" t="n">
+        <v>323.9055014903766</v>
+      </c>
+      <c r="D172" t="n">
+        <v>316.7636201861749</v>
+      </c>
+      <c r="E172" t="n">
+        <v>322.5906677246094</v>
+      </c>
+      <c r="F172" t="n">
+        <v>9586200</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>323.7186157532602</v>
+      </c>
+      <c r="C173" t="n">
+        <v>328.3001007904417</v>
+      </c>
+      <c r="D173" t="n">
+        <v>323.5988431448615</v>
+      </c>
+      <c r="E173" t="n">
+        <v>325.8147277832031</v>
+      </c>
+      <c r="F173" t="n">
+        <v>6235200</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>323.1895917984963</v>
+      </c>
+      <c r="C174" t="n">
+        <v>324.8165740981451</v>
+      </c>
+      <c r="D174" t="n">
+        <v>319.2069699014023</v>
+      </c>
+      <c r="E174" t="n">
+        <v>319.7160339355469</v>
+      </c>
+      <c r="F174" t="n">
+        <v>7950400</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>320.7740745871976</v>
+      </c>
+      <c r="C175" t="n">
+        <v>322.7304316048222</v>
+      </c>
+      <c r="D175" t="n">
+        <v>319.6561562914121</v>
+      </c>
+      <c r="E175" t="n">
+        <v>321.9219360351562</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5277400</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>323.3992105807512</v>
+      </c>
+      <c r="C176" t="n">
+        <v>328.3999303437295</v>
+      </c>
+      <c r="D176" t="n">
+        <v>323.2395036115653</v>
+      </c>
+      <c r="E176" t="n">
+        <v>325.1459655761719</v>
+      </c>
+      <c r="F176" t="n">
+        <v>6054500</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>323.8283954010087</v>
+      </c>
+      <c r="C177" t="n">
+        <v>332.8117065140525</v>
+      </c>
+      <c r="D177" t="n">
+        <v>323.1696155974001</v>
+      </c>
+      <c r="E177" t="n">
+        <v>332.023193359375</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5305800</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>332.7118894931572</v>
+      </c>
+      <c r="C178" t="n">
+        <v>334.5485043686942</v>
+      </c>
+      <c r="D178" t="n">
+        <v>328.8790136983196</v>
+      </c>
+      <c r="E178" t="n">
+        <v>329.2982482910156</v>
+      </c>
+      <c r="F178" t="n">
+        <v>12858100</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>329.4779084191791</v>
+      </c>
+      <c r="C179" t="n">
+        <v>331.0450044691208</v>
+      </c>
+      <c r="D179" t="n">
+        <v>326.2139829663294</v>
+      </c>
+      <c r="E179" t="n">
+        <v>330.1366882324219</v>
+      </c>
+      <c r="F179" t="n">
+        <v>9422500</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>329.2283866364193</v>
+      </c>
+      <c r="C180" t="n">
+        <v>331.9034099041888</v>
+      </c>
+      <c r="D180" t="n">
+        <v>326.6332016248708</v>
+      </c>
+      <c r="E180" t="n">
+        <v>330.5060119628906</v>
+      </c>
+      <c r="F180" t="n">
+        <v>7034500</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>329.9071152744464</v>
+      </c>
+      <c r="C181" t="n">
+        <v>332.8117230001985</v>
+      </c>
+      <c r="D181" t="n">
+        <v>328.2102858122996</v>
+      </c>
+      <c r="E181" t="n">
+        <v>328.2701721191406</v>
+      </c>
+      <c r="F181" t="n">
+        <v>7462100</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>325.8546513791287</v>
+      </c>
+      <c r="C182" t="n">
+        <v>327.890877227978</v>
+      </c>
+      <c r="D182" t="n">
+        <v>323.908285453</v>
+      </c>
+      <c r="E182" t="n">
+        <v>325.8746337890625</v>
+      </c>
+      <c r="F182" t="n">
+        <v>8705100</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>325.2258042905605</v>
+      </c>
+      <c r="C183" t="n">
+        <v>330.8453695289686</v>
+      </c>
+      <c r="D183" t="n">
+        <v>325.0561365774909</v>
+      </c>
+      <c r="E183" t="n">
+        <v>327.0025024414062</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5917400</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>325.4054745838858</v>
+      </c>
+      <c r="C184" t="n">
+        <v>326.473467283892</v>
+      </c>
+      <c r="D184" t="n">
+        <v>320.304934449476</v>
+      </c>
+      <c r="E184" t="n">
+        <v>324.3474426269531</v>
+      </c>
+      <c r="F184" t="n">
+        <v>8105400</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>324.8964310814758</v>
+      </c>
+      <c r="C185" t="n">
+        <v>331.0550035619541</v>
+      </c>
+      <c r="D185" t="n">
+        <v>324.7467153160326</v>
+      </c>
+      <c r="E185" t="n">
+        <v>325.7548217773438</v>
+      </c>
+      <c r="F185" t="n">
+        <v>14104500</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>326.6531732008884</v>
+      </c>
+      <c r="C186" t="n">
+        <v>327.2520362551611</v>
+      </c>
+      <c r="D186" t="n">
+        <v>318.0890659929148</v>
+      </c>
+      <c r="E186" t="n">
+        <v>322.1714782714844</v>
+      </c>
+      <c r="F186" t="n">
+        <v>10079300</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>321.911976472278</v>
+      </c>
+      <c r="C187" t="n">
+        <v>322.900130958607</v>
+      </c>
+      <c r="D187" t="n">
+        <v>312.8088926463686</v>
+      </c>
+      <c r="E187" t="n">
+        <v>316.7315979003906</v>
+      </c>
+      <c r="F187" t="n">
+        <v>10125300</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>317.0609741306723</v>
+      </c>
+      <c r="C188" t="n">
+        <v>317.0609741306723</v>
+      </c>
+      <c r="D188" t="n">
+        <v>308.4270199555073</v>
+      </c>
+      <c r="E188" t="n">
+        <v>311.8207092285156</v>
+      </c>
+      <c r="F188" t="n">
+        <v>8992800</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>316.2025752130079</v>
+      </c>
+      <c r="C189" t="n">
+        <v>324.1577974184449</v>
+      </c>
+      <c r="D189" t="n">
+        <v>316.1127457580593</v>
+      </c>
+      <c r="E189" t="n">
+        <v>319.5862731933594</v>
+      </c>
+      <c r="F189" t="n">
+        <v>6981700</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>321.8021573858913</v>
+      </c>
+      <c r="C190" t="n">
+        <v>325.3755359367605</v>
+      </c>
+      <c r="D190" t="n">
+        <v>320.3748163907789</v>
+      </c>
+      <c r="E190" t="n">
+        <v>322.9700012207031</v>
+      </c>
+      <c r="F190" t="n">
+        <v>7176300</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>320.7541174065557</v>
+      </c>
+      <c r="C191" t="n">
+        <v>323.3193590911711</v>
+      </c>
+      <c r="D191" t="n">
+        <v>317.8395186449595</v>
+      </c>
+      <c r="E191" t="n">
+        <v>319.0772399902344</v>
+      </c>
+      <c r="F191" t="n">
+        <v>5582000</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>318.0691001697331</v>
+      </c>
+      <c r="C192" t="n">
+        <v>324.8864216353897</v>
+      </c>
+      <c r="D192" t="n">
+        <v>316.4121747162161</v>
+      </c>
+      <c r="E192" t="n">
+        <v>324.4472351074219</v>
+      </c>
+      <c r="F192" t="n">
+        <v>6340400</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>326.0143312805488</v>
+      </c>
+      <c r="C193" t="n">
+        <v>326.2938108474966</v>
+      </c>
+      <c r="D193" t="n">
+        <v>319.5862707797614</v>
+      </c>
+      <c r="E193" t="n">
+        <v>322.3611145019531</v>
+      </c>
+      <c r="F193" t="n">
+        <v>5793100</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>321.4029160285921</v>
+      </c>
+      <c r="C194" t="n">
+        <v>323.1097366498532</v>
+      </c>
+      <c r="D194" t="n">
+        <v>317.3703988636284</v>
+      </c>
+      <c r="E194" t="n">
+        <v>318.4583740234375</v>
+      </c>
+      <c r="F194" t="n">
+        <v>5958900</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>321.1633691478087</v>
+      </c>
+      <c r="C195" t="n">
+        <v>325.3256196452838</v>
+      </c>
+      <c r="D195" t="n">
+        <v>319.206981650181</v>
+      </c>
+      <c r="E195" t="n">
+        <v>321.7922058105469</v>
+      </c>
+      <c r="F195" t="n">
+        <v>5543200</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>322.7603745094088</v>
+      </c>
+      <c r="C196" t="n">
+        <v>325.8346802814496</v>
+      </c>
+      <c r="D196" t="n">
+        <v>322.1515202620241</v>
+      </c>
+      <c r="E196" t="n">
+        <v>323.2195434570312</v>
+      </c>
+      <c r="F196" t="n">
+        <v>6803000</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>325.0860736201939</v>
+      </c>
+      <c r="C197" t="n">
+        <v>332.6719869892291</v>
+      </c>
+      <c r="D197" t="n">
+        <v>323.7785051975129</v>
+      </c>
+      <c r="E197" t="n">
+        <v>332.5022888183594</v>
+      </c>
+      <c r="F197" t="n">
+        <v>9248400</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>332.8816048599044</v>
+      </c>
+      <c r="C198" t="n">
+        <v>336.1954560330155</v>
+      </c>
+      <c r="D198" t="n">
+        <v>329.3581516101117</v>
+      </c>
+      <c r="E198" t="n">
+        <v>329.7673950195312</v>
+      </c>
+      <c r="F198" t="n">
+        <v>6895200</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>330.3862161708477</v>
+      </c>
+      <c r="C199" t="n">
+        <v>331.7137365067053</v>
+      </c>
+      <c r="D199" t="n">
+        <v>326.3936334980882</v>
+      </c>
+      <c r="E199" t="n">
+        <v>326.6331787109375</v>
+      </c>
+      <c r="F199" t="n">
+        <v>14716700</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>327.7211572947962</v>
+      </c>
+      <c r="C200" t="n">
+        <v>332.3825110173034</v>
+      </c>
+      <c r="D200" t="n">
+        <v>325.255736249892</v>
+      </c>
+      <c r="E200" t="n">
+        <v>325.994384765625</v>
+      </c>
+      <c r="F200" t="n">
+        <v>15132400</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>328.2102765273601</v>
+      </c>
+      <c r="C201" t="n">
+        <v>330.6657064213508</v>
+      </c>
+      <c r="D201" t="n">
+        <v>327.4816192000871</v>
+      </c>
+      <c r="E201" t="n">
+        <v>327.8709106445312</v>
+      </c>
+      <c r="F201" t="n">
+        <v>11113400</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>328.3899311009871</v>
+      </c>
+      <c r="C202" t="n">
+        <v>334.1791639025663</v>
+      </c>
+      <c r="D202" t="n">
+        <v>326.6132329961447</v>
+      </c>
+      <c r="E202" t="n">
+        <v>331.6139526367188</v>
+      </c>
+      <c r="F202" t="n">
+        <v>8197200</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>331.9433302412046</v>
+      </c>
+      <c r="C203" t="n">
+        <v>339.3096503518051</v>
+      </c>
+      <c r="D203" t="n">
+        <v>329.457957205559</v>
+      </c>
+      <c r="E203" t="n">
+        <v>329.9071044921875</v>
+      </c>
+      <c r="F203" t="n">
+        <v>7050200</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>331.6239148421282</v>
+      </c>
+      <c r="C204" t="n">
+        <v>339.0900555815327</v>
+      </c>
+      <c r="D204" t="n">
+        <v>330.8254104732138</v>
+      </c>
+      <c r="E204" t="n">
+        <v>335.6065368652344</v>
+      </c>
+      <c r="F204" t="n">
+        <v>16717400</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>337.6427420814022</v>
+      </c>
+      <c r="C205" t="n">
+        <v>345.168769346924</v>
+      </c>
+      <c r="D205" t="n">
+        <v>337.6427420814022</v>
+      </c>
+      <c r="E205" t="n">
+        <v>341.0164794921875</v>
+      </c>
+      <c r="F205" t="n">
+        <v>11710900</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>341.1262760402287</v>
+      </c>
+      <c r="C206" t="n">
+        <v>343.6515833825353</v>
+      </c>
+      <c r="D206" t="n">
+        <v>338.4512224777037</v>
+      </c>
+      <c r="E206" t="n">
+        <v>342.4537963867188</v>
+      </c>
+      <c r="F206" t="n">
+        <v>7957900</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>343.9210864742992</v>
+      </c>
+      <c r="C207" t="n">
+        <v>352.7047566164018</v>
+      </c>
+      <c r="D207" t="n">
+        <v>340.3477382034001</v>
+      </c>
+      <c r="E207" t="n">
+        <v>350.4289855957031</v>
+      </c>
+      <c r="F207" t="n">
+        <v>13025900</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>351.8563396289383</v>
+      </c>
+      <c r="C208" t="n">
+        <v>361.45849609375</v>
+      </c>
+      <c r="D208" t="n">
+        <v>351.8563396289383</v>
+      </c>
+      <c r="E208" t="n">
+        <v>361.45849609375</v>
+      </c>
+      <c r="F208" t="n">
+        <v>9814800</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>362.3268927646901</v>
+      </c>
+      <c r="C209" t="n">
+        <v>364.3431361331269</v>
+      </c>
+      <c r="D209" t="n">
+        <v>348.2031370590358</v>
+      </c>
+      <c r="E209" t="n">
+        <v>356.5875549316406</v>
+      </c>
+      <c r="F209" t="n">
+        <v>11623800</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>347.744003265132</v>
+      </c>
+      <c r="C210" t="n">
+        <v>355.4197158554798</v>
+      </c>
+      <c r="D210" t="n">
+        <v>346.2767278330053</v>
+      </c>
+      <c r="E210" t="n">
+        <v>351.5469360351562</v>
+      </c>
+      <c r="F210" t="n">
+        <v>7332500</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>349.650411586948</v>
+      </c>
+      <c r="C211" t="n">
+        <v>350.9480192181019</v>
+      </c>
+      <c r="D211" t="n">
+        <v>345.0489747278172</v>
+      </c>
+      <c r="E211" t="n">
+        <v>346.8855590820312</v>
+      </c>
+      <c r="F211" t="n">
+        <v>10215200</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>344.6597048505295</v>
+      </c>
+      <c r="C212" t="n">
+        <v>347.8537833381742</v>
+      </c>
+      <c r="D212" t="n">
+        <v>343.7813622043677</v>
+      </c>
+      <c r="E212" t="n">
+        <v>347.5543518066406</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6606300</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>349.9798320131086</v>
+      </c>
+      <c r="C213" t="n">
+        <v>350.5188392207221</v>
+      </c>
+      <c r="D213" t="n">
+        <v>344.6896415212494</v>
+      </c>
+      <c r="E213" t="n">
+        <v>348.3229064941406</v>
+      </c>
+      <c r="F213" t="n">
+        <v>4702800</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>351.0777829959364</v>
+      </c>
+      <c r="C214" t="n">
+        <v>358.8233725828445</v>
+      </c>
+      <c r="D214" t="n">
+        <v>350.3990207986449</v>
+      </c>
+      <c r="E214" t="n">
+        <v>357.0866088867188</v>
+      </c>
+      <c r="F214" t="n">
+        <v>9964600</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>355.1102963305153</v>
+      </c>
+      <c r="C215" t="n">
+        <v>359.2725774384029</v>
+      </c>
+      <c r="D215" t="n">
+        <v>353.0241754046451</v>
+      </c>
+      <c r="E215" t="n">
+        <v>355.3598327636719</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6632400</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>353.3435751194357</v>
+      </c>
+      <c r="C216" t="n">
+        <v>359.7616446111089</v>
+      </c>
+      <c r="D216" t="n">
+        <v>348.4726192666298</v>
+      </c>
+      <c r="E216" t="n">
+        <v>354.4814758300781</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8850000</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>357.3760808599296</v>
+      </c>
+      <c r="C217" t="n">
+        <v>364.4629211425781</v>
+      </c>
+      <c r="D217" t="n">
+        <v>356.4477822451955</v>
+      </c>
+      <c r="E217" t="n">
+        <v>364.4629211425781</v>
+      </c>
+      <c r="F217" t="n">
+        <v>9073200</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>362.8958306673428</v>
+      </c>
+      <c r="C218" t="n">
+        <v>363.9538626468295</v>
+      </c>
+      <c r="D218" t="n">
+        <v>356.3380062665893</v>
+      </c>
+      <c r="E218" t="n">
+        <v>357.8951110839844</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7400400</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>356.4378309524324</v>
+      </c>
+      <c r="C219" t="n">
+        <v>362.3268844140721</v>
+      </c>
+      <c r="D219" t="n">
+        <v>355.7690599392462</v>
+      </c>
+      <c r="E219" t="n">
+        <v>359.9013977050781</v>
+      </c>
+      <c r="F219" t="n">
+        <v>7616800</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>356.3280307190208</v>
+      </c>
+      <c r="C220" t="n">
+        <v>358.4540859756855</v>
+      </c>
+      <c r="D220" t="n">
+        <v>354.0323077481659</v>
+      </c>
+      <c r="E220" t="n">
+        <v>355.1602172851562</v>
+      </c>
+      <c r="F220" t="n">
+        <v>6027300</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>355.9088319271366</v>
+      </c>
+      <c r="C221" t="n">
+        <v>356.8670433033565</v>
+      </c>
+      <c r="D221" t="n">
+        <v>351.6167869913984</v>
+      </c>
+      <c r="E221" t="n">
+        <v>352.7646789550781</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4622200</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>351.3971758456315</v>
+      </c>
+      <c r="C222" t="n">
+        <v>351.3971758456315</v>
+      </c>
+      <c r="D222" t="n">
+        <v>347.8537708520506</v>
+      </c>
+      <c r="E222" t="n">
+        <v>350.9480285644531</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4183300</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>352.8145729386106</v>
+      </c>
+      <c r="C223" t="n">
+        <v>355.1801734485531</v>
+      </c>
+      <c r="D223" t="n">
+        <v>350.3990468654978</v>
+      </c>
+      <c r="E223" t="n">
+        <v>355.0803527832031</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4482800</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>358.6836615690858</v>
+      </c>
+      <c r="C224" t="n">
+        <v>362.9856670774005</v>
+      </c>
+      <c r="D224" t="n">
+        <v>357.5856952124533</v>
+      </c>
+      <c r="E224" t="n">
+        <v>361.8577575683594</v>
+      </c>
+      <c r="F224" t="n">
+        <v>6631100</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>364.3830556294341</v>
+      </c>
+      <c r="C225" t="n">
+        <v>370.4717503048907</v>
+      </c>
+      <c r="D225" t="n">
+        <v>362.057389622598</v>
+      </c>
+      <c r="E225" t="n">
+        <v>365.9102172851562</v>
+      </c>
+      <c r="F225" t="n">
+        <v>11061900</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>356.3380049484608</v>
+      </c>
+      <c r="C226" t="n">
+        <v>373.2765382228537</v>
+      </c>
+      <c r="D226" t="n">
+        <v>354.8208344927874</v>
+      </c>
+      <c r="E226" t="n">
+        <v>368.0462646484375</v>
+      </c>
+      <c r="F226" t="n">
+        <v>11289900</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>364.3231862195555</v>
+      </c>
+      <c r="C227" t="n">
+        <v>366.3194776508955</v>
+      </c>
+      <c r="D227" t="n">
+        <v>360.0810669279579</v>
+      </c>
+      <c r="E227" t="n">
+        <v>365.5908203125</v>
+      </c>
+      <c r="F227" t="n">
+        <v>8391400</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>363.0854799497644</v>
+      </c>
+      <c r="C228" t="n">
+        <v>366.199689577411</v>
+      </c>
+      <c r="D228" t="n">
+        <v>359.4322631293363</v>
+      </c>
+      <c r="E228" t="n">
+        <v>365.4510803222656</v>
+      </c>
+      <c r="F228" t="n">
+        <v>7828400</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>367.8166822243689</v>
+      </c>
+      <c r="C229" t="n">
+        <v>371.2802489443513</v>
+      </c>
+      <c r="D229" t="n">
+        <v>363.6743837542027</v>
+      </c>
+      <c r="E229" t="n">
+        <v>364.991943359375</v>
+      </c>
+      <c r="F229" t="n">
+        <v>5521300</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>361.0891957111975</v>
+      </c>
+      <c r="C230" t="n">
+        <v>370.4218335736103</v>
+      </c>
+      <c r="D230" t="n">
+        <v>359.4222790007568</v>
+      </c>
+      <c r="E230" t="n">
+        <v>368.9046630859375</v>
+      </c>
+      <c r="F230" t="n">
+        <v>7497500</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>371.6096355733356</v>
+      </c>
+      <c r="C231" t="n">
+        <v>371.7094562365133</v>
+      </c>
+      <c r="D231" t="n">
+        <v>366.0399959154992</v>
+      </c>
+      <c r="E231" t="n">
+        <v>367.8566284179688</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6065300</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>368.8847254705448</v>
+      </c>
+      <c r="C232" t="n">
+        <v>370.4118872220017</v>
+      </c>
+      <c r="D232" t="n">
+        <v>364.5727285978463</v>
+      </c>
+      <c r="E232" t="n">
+        <v>369.7830505371094</v>
+      </c>
+      <c r="F232" t="n">
+        <v>5022300</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>367.8266852879935</v>
+      </c>
+      <c r="C233" t="n">
+        <v>369.5634490756331</v>
+      </c>
+      <c r="D233" t="n">
+        <v>360.8496260625997</v>
+      </c>
+      <c r="E233" t="n">
+        <v>361.8278198242188</v>
+      </c>
+      <c r="F233" t="n">
+        <v>5112500</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>361.3287562034755</v>
+      </c>
+      <c r="C234" t="n">
+        <v>363.4947458520614</v>
+      </c>
+      <c r="D234" t="n">
+        <v>358.2045551780129</v>
+      </c>
+      <c r="E234" t="n">
+        <v>360.6500244140625</v>
+      </c>
+      <c r="F234" t="n">
+        <v>7552200</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>360.9800109863281</v>
+      </c>
+      <c r="C235" t="n">
+        <v>364.5499877929688</v>
+      </c>
+      <c r="D235" t="n">
+        <v>359.9700012207031</v>
+      </c>
+      <c r="E235" t="n">
+        <v>362.8200073242188</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4440900</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>361</v>
+      </c>
+      <c r="C236" t="n">
+        <v>363.3500061035156</v>
+      </c>
+      <c r="D236" t="n">
+        <v>358.3099975585938</v>
+      </c>
+      <c r="E236" t="n">
+        <v>359.4200134277344</v>
+      </c>
+      <c r="F236" t="n">
+        <v>3794200</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>363.7000122070312</v>
+      </c>
+      <c r="C237" t="n">
+        <v>365.4500122070312</v>
+      </c>
+      <c r="D237" t="n">
+        <v>358.7099914550781</v>
+      </c>
+      <c r="E237" t="n">
+        <v>365.4500122070312</v>
+      </c>
+      <c r="F237" t="n">
+        <v>8142600</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>365.8900146484375</v>
+      </c>
+      <c r="C238" t="n">
+        <v>366.7999877929688</v>
+      </c>
+      <c r="D238" t="n">
+        <v>362.760009765625</v>
+      </c>
+      <c r="E238" t="n">
+        <v>364.1499938964844</v>
+      </c>
+      <c r="F238" t="n">
+        <v>8106900</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>362.8399963378906</v>
+      </c>
+      <c r="C239" t="n">
+        <v>363.5599975585938</v>
+      </c>
+      <c r="D239" t="n">
+        <v>358.5199890136719</v>
+      </c>
+      <c r="E239" t="n">
+        <v>358.8399963378906</v>
+      </c>
+      <c r="F239" t="n">
+        <v>15543400</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>359.6199951171875</v>
+      </c>
+      <c r="C240" t="n">
+        <v>365.9100036621094</v>
+      </c>
+      <c r="D240" t="n">
+        <v>358.0499877929688</v>
+      </c>
+      <c r="E240" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="F240" t="n">
+        <v>6820300</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>364.0899963378906</v>
+      </c>
+      <c r="C241" t="n">
+        <v>370.6400146484375</v>
+      </c>
+      <c r="D241" t="n">
+        <v>362.8999938964844</v>
+      </c>
+      <c r="E241" t="n">
+        <v>365.5400085449219</v>
+      </c>
+      <c r="F241" t="n">
+        <v>5866400</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>365.1000061035156</v>
+      </c>
+      <c r="C242" t="n">
+        <v>368.9299926757812</v>
+      </c>
+      <c r="D242" t="n">
+        <v>363.6300048828125</v>
+      </c>
+      <c r="E242" t="n">
+        <v>365.7300109863281</v>
+      </c>
+      <c r="F242" t="n">
+        <v>6151500</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>367.8699951171875</v>
+      </c>
+      <c r="C243" t="n">
+        <v>371.7999877929688</v>
+      </c>
+      <c r="D243" t="n">
+        <v>366.6600036621094</v>
+      </c>
+      <c r="E243" t="n">
+        <v>371.0400085449219</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6667100</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>373.260009765625</v>
+      </c>
+      <c r="C244" t="n">
+        <v>383.4299926757812</v>
+      </c>
+      <c r="D244" t="n">
+        <v>372.2099914550781</v>
+      </c>
+      <c r="E244" t="n">
+        <v>382.4100036621094</v>
+      </c>
+      <c r="F244" t="n">
+        <v>8477500</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>381.2099914550781</v>
+      </c>
+      <c r="C245" t="n">
+        <v>384.2000122070312</v>
+      </c>
+      <c r="D245" t="n">
+        <v>380.2699890136719</v>
+      </c>
+      <c r="E245" t="n">
+        <v>384.1400146484375</v>
+      </c>
+      <c r="F245" t="n">
+        <v>6777600</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>384.1400146484375</v>
+      </c>
+      <c r="C246" t="n">
+        <v>385.5700073242188</v>
+      </c>
+      <c r="D246" t="n">
+        <v>381.0799865722656</v>
+      </c>
+      <c r="E246" t="n">
+        <v>383.8999938964844</v>
+      </c>
+      <c r="F246" t="n">
+        <v>6075100</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>381.1400146484375</v>
+      </c>
+      <c r="C247" t="n">
+        <v>381.7699890136719</v>
+      </c>
+      <c r="D247" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="E247" t="n">
+        <v>379.6600036621094</v>
+      </c>
+      <c r="F247" t="n">
+        <v>6641500</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>380.2999877929688</v>
+      </c>
+      <c r="C248" t="n">
+        <v>383.6799926757812</v>
+      </c>
+      <c r="D248" t="n">
+        <v>379.0299987792969</v>
+      </c>
+      <c r="E248" t="n">
+        <v>381.6000061035156</v>
+      </c>
+      <c r="F248" t="n">
+        <v>4643000</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>381.3500061035156</v>
+      </c>
+      <c r="C249" t="n">
+        <v>382.4800109863281</v>
+      </c>
+      <c r="D249" t="n">
+        <v>378.7999877929688</v>
+      </c>
+      <c r="E249" t="n">
+        <v>379.3699951171875</v>
+      </c>
+      <c r="F249" t="n">
+        <v>6744800</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>379.6499938964844</v>
+      </c>
+      <c r="C250" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="D250" t="n">
+        <v>372.2200012207031</v>
+      </c>
+      <c r="E250" t="n">
+        <v>372.6700134277344</v>
+      </c>
+      <c r="F250" t="n">
+        <v>5857400</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>374.010009765625</v>
+      </c>
+      <c r="C251" t="n">
+        <v>380.1700134277344</v>
+      </c>
+      <c r="D251" t="n">
+        <v>374.010009765625</v>
+      </c>
+      <c r="E251" t="n">
+        <v>378.3999938964844</v>
+      </c>
+      <c r="F251" t="n">
+        <v>5599900</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>380.1700134277344</v>
+      </c>
+      <c r="C252" t="n">
+        <v>382.2099914550781</v>
+      </c>
+      <c r="D252" t="n">
+        <v>376.8599853515625</v>
+      </c>
+      <c r="E252" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3869500</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>374.8900146484375</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>377.5</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>373.6400146484375</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>375.0700073242188</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>4645100</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4833,7 +10787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:35</t>
+          <t>2026-09-07 03:08:26</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:26</t>
+          <t>2026-09-08 08:52:17</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>348.5921492449787</v>
+        <v>338.9790027080578</v>
       </c>
       <c r="C2" t="n">
-        <v>349.8223013732642</v>
+        <v>343.572272708629</v>
       </c>
       <c r="D2" t="n">
-        <v>337.5008588435983</v>
+        <v>338.5821823997351</v>
       </c>
       <c r="E2" t="n">
-        <v>340.4968872070312</v>
+        <v>341.2607421875</v>
       </c>
       <c r="F2" t="n">
-        <v>5448300</v>
+        <v>4646200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>339.6238280750231</v>
+        <v>339.8916521696528</v>
       </c>
       <c r="C3" t="n">
-        <v>341.6476509375095</v>
+        <v>339.8916521696528</v>
       </c>
       <c r="D3" t="n">
-        <v>338.2944634353397</v>
+        <v>333.7706230845267</v>
       </c>
       <c r="E3" t="n">
-        <v>339.5841369628906</v>
+        <v>335.4372863769531</v>
       </c>
       <c r="F3" t="n">
-        <v>4711600</v>
+        <v>6557900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>338.9790027080578</v>
+        <v>336.0424963320352</v>
       </c>
       <c r="C4" t="n">
-        <v>343.572272708629</v>
+        <v>340.8044005861511</v>
       </c>
       <c r="D4" t="n">
-        <v>338.5821823997351</v>
+        <v>335.1893039068655</v>
       </c>
       <c r="E4" t="n">
-        <v>341.2607421875</v>
+        <v>340.7647094726562</v>
       </c>
       <c r="F4" t="n">
-        <v>4646200</v>
+        <v>5157600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>339.8916830924824</v>
+        <v>338.5127143274361</v>
       </c>
       <c r="C5" t="n">
-        <v>339.8916830924824</v>
+        <v>340.467085284774</v>
       </c>
       <c r="D5" t="n">
-        <v>333.7706534504743</v>
+        <v>336.4789914224089</v>
       </c>
       <c r="E5" t="n">
-        <v>335.4373168945312</v>
+        <v>336.7369079589844</v>
       </c>
       <c r="F5" t="n">
-        <v>6557900</v>
+        <v>3518300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>336.0424662373603</v>
+        <v>337.907514008316</v>
       </c>
       <c r="C6" t="n">
-        <v>340.8043700650184</v>
+        <v>339.9908582212252</v>
       </c>
       <c r="D6" t="n">
-        <v>335.1892738885992</v>
+        <v>335.7051570201907</v>
       </c>
       <c r="E6" t="n">
-        <v>340.7646789550781</v>
+        <v>336.3598937988281</v>
       </c>
       <c r="F6" t="n">
-        <v>5157600</v>
+        <v>4367500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>338.5127143274361</v>
+        <v>333.5722454094798</v>
       </c>
       <c r="C7" t="n">
-        <v>340.467085284774</v>
+        <v>337.8381471606402</v>
       </c>
       <c r="D7" t="n">
-        <v>336.4789914224089</v>
+        <v>330.8242336265683</v>
       </c>
       <c r="E7" t="n">
-        <v>336.7369079589844</v>
+        <v>337.3321838378906</v>
       </c>
       <c r="F7" t="n">
-        <v>3518300</v>
+        <v>5527700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>337.907514008316</v>
+        <v>337.2428445481393</v>
       </c>
       <c r="C8" t="n">
-        <v>339.9908582212252</v>
+        <v>343.4531860351562</v>
       </c>
       <c r="D8" t="n">
-        <v>335.7051570201907</v>
+        <v>336.826163598265</v>
       </c>
       <c r="E8" t="n">
-        <v>336.3598937988281</v>
+        <v>343.4531860351562</v>
       </c>
       <c r="F8" t="n">
-        <v>4367500</v>
+        <v>5763500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>333.5722152320537</v>
+        <v>341.9949068462926</v>
       </c>
       <c r="C9" t="n">
-        <v>337.8381165972889</v>
+        <v>342.5306006625406</v>
       </c>
       <c r="D9" t="n">
-        <v>330.8242036977477</v>
+        <v>335.4968566894531</v>
       </c>
       <c r="E9" t="n">
-        <v>337.3321533203125</v>
+        <v>335.4968566894531</v>
       </c>
       <c r="F9" t="n">
-        <v>5527700</v>
+        <v>7526600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>337.2429044796542</v>
+        <v>337.7488274356299</v>
       </c>
       <c r="C10" t="n">
-        <v>343.4532470703125</v>
+        <v>339.9710452297281</v>
       </c>
       <c r="D10" t="n">
-        <v>336.8262234557313</v>
+        <v>335.5662704768214</v>
       </c>
       <c r="E10" t="n">
-        <v>343.4532470703125</v>
+        <v>338.8995971679688</v>
       </c>
       <c r="F10" t="n">
-        <v>5763500</v>
+        <v>13674300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>341.9948446289807</v>
+        <v>336.3202791354349</v>
       </c>
       <c r="C11" t="n">
-        <v>342.5305383477728</v>
+        <v>342.1238405800017</v>
       </c>
       <c r="D11" t="n">
-        <v>335.4967956542969</v>
+        <v>335.9730500063751</v>
       </c>
       <c r="E11" t="n">
-        <v>335.4967956542969</v>
+        <v>341.6278076171875</v>
       </c>
       <c r="F11" t="n">
-        <v>7526600</v>
+        <v>5621800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>337.7488274356299</v>
+        <v>341.8559781228954</v>
       </c>
       <c r="C12" t="n">
-        <v>339.9710452297281</v>
+        <v>342.5206755840167</v>
       </c>
       <c r="D12" t="n">
-        <v>335.5662704768214</v>
+        <v>334.9512080718528</v>
       </c>
       <c r="E12" t="n">
-        <v>338.8995971679688</v>
+        <v>336.0127258300781</v>
       </c>
       <c r="F12" t="n">
-        <v>13674300</v>
+        <v>10142700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>336.3202190485207</v>
+        <v>336.4393006348119</v>
       </c>
       <c r="C13" t="n">
-        <v>342.1237794562243</v>
+        <v>337.2031804494151</v>
       </c>
       <c r="D13" t="n">
-        <v>335.9729899814968</v>
+        <v>335.2389094188791</v>
       </c>
       <c r="E13" t="n">
-        <v>341.6277465820312</v>
+        <v>335.9928588867188</v>
       </c>
       <c r="F13" t="n">
-        <v>5621800</v>
+        <v>5207400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>341.8559781228954</v>
+        <v>335.6654921112904</v>
       </c>
       <c r="C14" t="n">
-        <v>342.5206755840167</v>
+        <v>337.5008200200934</v>
       </c>
       <c r="D14" t="n">
-        <v>334.9512080718528</v>
+        <v>331.855962815555</v>
       </c>
       <c r="E14" t="n">
-        <v>336.0127258300781</v>
+        <v>332.2726135253906</v>
       </c>
       <c r="F14" t="n">
-        <v>10142700</v>
+        <v>5398700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>336.4393311929394</v>
+        <v>334.5544248444214</v>
       </c>
       <c r="C15" t="n">
-        <v>337.2032110769243</v>
+        <v>336.8064037434848</v>
       </c>
       <c r="D15" t="n">
-        <v>335.2389398679774</v>
+        <v>333.5623588540134</v>
       </c>
       <c r="E15" t="n">
-        <v>335.9928894042969</v>
+        <v>334.6932983398438</v>
       </c>
       <c r="F15" t="n">
-        <v>5207400</v>
+        <v>9619200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>335.6655229404874</v>
+        <v>334.7031787744378</v>
       </c>
       <c r="C16" t="n">
-        <v>337.5008510178562</v>
+        <v>337.9373231090121</v>
       </c>
       <c r="D16" t="n">
-        <v>331.8559932948658</v>
+        <v>332.8876813284792</v>
       </c>
       <c r="E16" t="n">
-        <v>332.2726440429688</v>
+        <v>337.4611206054688</v>
       </c>
       <c r="F16" t="n">
-        <v>5398700</v>
+        <v>7217800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>334.5543943395058</v>
+        <v>337.1238578141872</v>
       </c>
       <c r="C17" t="n">
-        <v>336.8063730332322</v>
+        <v>342.8678978564652</v>
       </c>
       <c r="D17" t="n">
-        <v>333.5623284395552</v>
+        <v>335.8242538439627</v>
       </c>
       <c r="E17" t="n">
-        <v>334.6932678222656</v>
+        <v>338.6714782714844</v>
       </c>
       <c r="F17" t="n">
-        <v>9619200</v>
+        <v>8164400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>334.7031787744378</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="C18" t="n">
-        <v>337.9373231090121</v>
+        <v>346.58811100512</v>
       </c>
       <c r="D18" t="n">
-        <v>332.8876813284792</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="E18" t="n">
-        <v>337.4611206054688</v>
+        <v>345.0702514648438</v>
       </c>
       <c r="F18" t="n">
-        <v>7217800</v>
+        <v>8381000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>337.1238274360646</v>
+        <v>343.4730470813312</v>
       </c>
       <c r="C19" t="n">
-        <v>342.867866960749</v>
+        <v>344.425421840401</v>
       </c>
       <c r="D19" t="n">
-        <v>335.824223582947</v>
+        <v>340.8341482313199</v>
       </c>
       <c r="E19" t="n">
-        <v>338.6714477539062</v>
+        <v>343.2052001953125</v>
       </c>
       <c r="F19" t="n">
-        <v>8164400</v>
+        <v>5198000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>337.6099271681015</v>
+        <v>343.3639143460552</v>
       </c>
       <c r="C20" t="n">
-        <v>346.58811100512</v>
+        <v>350.3579971109944</v>
       </c>
       <c r="D20" t="n">
-        <v>337.6099271681015</v>
+        <v>343.2548016291976</v>
       </c>
       <c r="E20" t="n">
-        <v>345.0702514648438</v>
+        <v>347.0643310546875</v>
       </c>
       <c r="F20" t="n">
-        <v>8381000</v>
+        <v>5199700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>343.4730470813312</v>
+        <v>347.2329775138888</v>
       </c>
       <c r="C21" t="n">
-        <v>344.425421840401</v>
+        <v>348.3341560741189</v>
       </c>
       <c r="D21" t="n">
-        <v>340.8341482313199</v>
+        <v>341.6178811752161</v>
       </c>
       <c r="E21" t="n">
-        <v>343.2052001953125</v>
+        <v>346.5087585449219</v>
       </c>
       <c r="F21" t="n">
-        <v>5198000</v>
+        <v>4735600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>343.3639143460552</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="C22" t="n">
-        <v>350.3579971109944</v>
+        <v>351.6278330286145</v>
       </c>
       <c r="D22" t="n">
-        <v>343.2548016291976</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="E22" t="n">
-        <v>347.0643310546875</v>
+        <v>349.6238708496094</v>
       </c>
       <c r="F22" t="n">
-        <v>5199700</v>
+        <v>5044600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>347.2330080952501</v>
+        <v>350.9730784623077</v>
       </c>
       <c r="C23" t="n">
-        <v>348.3341867524627</v>
+        <v>352.1834000905383</v>
       </c>
       <c r="D23" t="n">
-        <v>341.6179112620468</v>
+        <v>348.3143490742109</v>
       </c>
       <c r="E23" t="n">
-        <v>346.5087890625</v>
+        <v>348.572265625</v>
       </c>
       <c r="F23" t="n">
-        <v>4735600</v>
+        <v>3927500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>347.2825796289147</v>
+        <v>348.681435657628</v>
       </c>
       <c r="C24" t="n">
-        <v>351.6278330286145</v>
+        <v>350.0703219922872</v>
       </c>
       <c r="D24" t="n">
-        <v>347.2825796289147</v>
+        <v>342.8381524285367</v>
       </c>
       <c r="E24" t="n">
-        <v>349.6238708496094</v>
+        <v>344.2865905761719</v>
       </c>
       <c r="F24" t="n">
-        <v>5044600</v>
+        <v>4434800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>350.9730784623077</v>
+        <v>344.8718644724454</v>
       </c>
       <c r="C25" t="n">
-        <v>352.1834000905383</v>
+        <v>347.619876043067</v>
       </c>
       <c r="D25" t="n">
-        <v>348.3143490742109</v>
+        <v>340.5266111021468</v>
       </c>
       <c r="E25" t="n">
-        <v>348.572265625</v>
+        <v>340.9234313964844</v>
       </c>
       <c r="F25" t="n">
-        <v>3927500</v>
+        <v>6296200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>348.6814047504906</v>
+        <v>340.9928833808045</v>
       </c>
       <c r="C26" t="n">
-        <v>350.0702909620389</v>
+        <v>344.9016253459246</v>
       </c>
       <c r="D26" t="n">
-        <v>342.8381220393481</v>
+        <v>338.0266161060487</v>
       </c>
       <c r="E26" t="n">
-        <v>344.2865600585938</v>
+        <v>340.5762023925781</v>
       </c>
       <c r="F26" t="n">
-        <v>4434800</v>
+        <v>4030700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>344.8718644724454</v>
+        <v>338.2944848137428</v>
       </c>
       <c r="C27" t="n">
-        <v>347.619876043067</v>
+        <v>347.2330086020973</v>
       </c>
       <c r="D27" t="n">
-        <v>340.5266111021468</v>
+        <v>337.520674593222</v>
       </c>
       <c r="E27" t="n">
-        <v>340.9234313964844</v>
+        <v>345.6159362792969</v>
       </c>
       <c r="F27" t="n">
-        <v>6296200</v>
+        <v>5731000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>340.9928833808045</v>
+        <v>345.615925335404</v>
       </c>
       <c r="C28" t="n">
-        <v>344.9016253459246</v>
+        <v>347.3024192111109</v>
       </c>
       <c r="D28" t="n">
-        <v>338.0266161060487</v>
+        <v>341.2706718210525</v>
       </c>
       <c r="E28" t="n">
-        <v>340.5762023925781</v>
+        <v>342.947265625</v>
       </c>
       <c r="F28" t="n">
-        <v>4030700</v>
+        <v>3778200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>338.2944848137428</v>
+        <v>342.2627615387884</v>
       </c>
       <c r="C29" t="n">
-        <v>347.2330086020973</v>
+        <v>342.947289483902</v>
       </c>
       <c r="D29" t="n">
-        <v>337.520674593222</v>
+        <v>331.5187003455953</v>
       </c>
       <c r="E29" t="n">
-        <v>345.6159362792969</v>
+        <v>332.7389221191406</v>
       </c>
       <c r="F29" t="n">
-        <v>5731000</v>
+        <v>6241500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>345.615925335404</v>
+        <v>335.0900620604222</v>
       </c>
       <c r="C30" t="n">
-        <v>347.3024192111109</v>
+        <v>340.725018943138</v>
       </c>
       <c r="D30" t="n">
-        <v>341.2706718210525</v>
+        <v>334.3261822760441</v>
       </c>
       <c r="E30" t="n">
-        <v>342.947265625</v>
+        <v>339.1773986816406</v>
       </c>
       <c r="F30" t="n">
-        <v>3778200</v>
+        <v>6267100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>342.2627301477191</v>
+        <v>339.1873340368696</v>
       </c>
       <c r="C31" t="n">
-        <v>342.9472580300504</v>
+        <v>342.223053348327</v>
       </c>
       <c r="D31" t="n">
-        <v>331.5186699399313</v>
+        <v>336.2508273730998</v>
       </c>
       <c r="E31" t="n">
-        <v>332.7388916015625</v>
+        <v>341.6774291992188</v>
       </c>
       <c r="F31" t="n">
-        <v>6241500</v>
+        <v>4665000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>335.0900620604222</v>
+        <v>340.3976240505323</v>
       </c>
       <c r="C32" t="n">
-        <v>340.725018943138</v>
+        <v>346.8758127342502</v>
       </c>
       <c r="D32" t="n">
-        <v>334.3261822760441</v>
+        <v>340.2785809945473</v>
       </c>
       <c r="E32" t="n">
-        <v>339.1773986816406</v>
+        <v>344.4551696777344</v>
       </c>
       <c r="F32" t="n">
-        <v>6267100</v>
+        <v>4121800</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>339.1873037416991</v>
+        <v>345.060346283755</v>
       </c>
       <c r="C33" t="n">
-        <v>342.2230227820154</v>
+        <v>345.4075753813841</v>
       </c>
       <c r="D33" t="n">
-        <v>336.2507973402091</v>
+        <v>341.7666804426993</v>
       </c>
       <c r="E33" t="n">
-        <v>341.6773986816406</v>
+        <v>342.6198425292969</v>
       </c>
       <c r="F33" t="n">
-        <v>4665000</v>
+        <v>5074400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>340.3976542086254</v>
+        <v>343.4532348171426</v>
       </c>
       <c r="C34" t="n">
-        <v>346.8758434662893</v>
+        <v>344.395679279174</v>
       </c>
       <c r="D34" t="n">
-        <v>340.2786111420936</v>
+        <v>341.727019522991</v>
       </c>
       <c r="E34" t="n">
-        <v>344.4552001953125</v>
+        <v>343.2151184082031</v>
       </c>
       <c r="F34" t="n">
-        <v>4121800</v>
+        <v>7217200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>345.0603770187118</v>
+        <v>345.4373721859704</v>
       </c>
       <c r="C35" t="n">
-        <v>345.4076061472691</v>
+        <v>346.3103647812057</v>
       </c>
       <c r="D35" t="n">
-        <v>341.7667108842852</v>
+        <v>342.5802174366191</v>
       </c>
       <c r="E35" t="n">
-        <v>342.619873046875</v>
+        <v>344.6238708496094</v>
       </c>
       <c r="F35" t="n">
-        <v>5074400</v>
+        <v>3576700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>343.4532042783919</v>
+        <v>346.2309942490221</v>
       </c>
       <c r="C36" t="n">
-        <v>344.3956486566242</v>
+        <v>346.746857610633</v>
       </c>
       <c r="D36" t="n">
-        <v>341.7269891377298</v>
+        <v>342.2726610516251</v>
       </c>
       <c r="E36" t="n">
-        <v>343.215087890625</v>
+        <v>345.0603637695312</v>
       </c>
       <c r="F36" t="n">
-        <v>7217200</v>
+        <v>5400300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>345.4373415963541</v>
+        <v>345.8143074374688</v>
       </c>
       <c r="C37" t="n">
-        <v>346.3103341142831</v>
+        <v>347.1139415798067</v>
       </c>
       <c r="D37" t="n">
-        <v>342.5801871000132</v>
+        <v>343.7508237502946</v>
       </c>
       <c r="E37" t="n">
-        <v>344.6238403320312</v>
+        <v>344.1476440429688</v>
       </c>
       <c r="F37" t="n">
-        <v>3576700</v>
+        <v>7445400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>346.2310248701323</v>
+        <v>343.2548181119967</v>
       </c>
       <c r="C38" t="n">
-        <v>346.7468882773667</v>
+        <v>348.1953174336955</v>
       </c>
       <c r="D38" t="n">
-        <v>342.2726913226552</v>
+        <v>336.3103564738927</v>
       </c>
       <c r="E38" t="n">
-        <v>345.0603942871094</v>
+        <v>338.572265625</v>
       </c>
       <c r="F38" t="n">
-        <v>5400300</v>
+        <v>8361700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>345.8143074374688</v>
+        <v>339.5047778404419</v>
       </c>
       <c r="C39" t="n">
-        <v>347.1139415798067</v>
+        <v>346.9452717470537</v>
       </c>
       <c r="D39" t="n">
-        <v>343.7508237502946</v>
+        <v>339.0781967892368</v>
       </c>
       <c r="E39" t="n">
-        <v>344.1476440429688</v>
+        <v>342.29248046875</v>
       </c>
       <c r="F39" t="n">
-        <v>7445400</v>
+        <v>6411800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>343.2547871723516</v>
+        <v>339.3658942315137</v>
       </c>
       <c r="C40" t="n">
-        <v>348.1952860487332</v>
+        <v>340.2786081927618</v>
       </c>
       <c r="D40" t="n">
-        <v>336.3103261601942</v>
+        <v>335.4869431536939</v>
       </c>
       <c r="E40" t="n">
-        <v>338.5722351074219</v>
+        <v>338.0365295410156</v>
       </c>
       <c r="F40" t="n">
-        <v>8361700</v>
+        <v>7301600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>339.5047778404419</v>
+        <v>338.2944659192743</v>
       </c>
       <c r="C41" t="n">
-        <v>346.9452717470537</v>
+        <v>338.5027912774657</v>
       </c>
       <c r="D41" t="n">
-        <v>339.0781967892368</v>
+        <v>332.1635060317716</v>
       </c>
       <c r="E41" t="n">
-        <v>342.29248046875</v>
+        <v>334.2269897460938</v>
       </c>
       <c r="F41" t="n">
-        <v>6411800</v>
+        <v>5538000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>339.3658942315137</v>
+        <v>333.8103374596785</v>
       </c>
       <c r="C42" t="n">
-        <v>340.2786081927618</v>
+        <v>337.6198667973582</v>
       </c>
       <c r="D42" t="n">
-        <v>335.4869431536939</v>
+        <v>331.598019653034</v>
       </c>
       <c r="E42" t="n">
-        <v>338.0365295410156</v>
+        <v>337.6000061035156</v>
       </c>
       <c r="F42" t="n">
-        <v>7301600</v>
+        <v>5920200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>338.2944659192743</v>
+        <v>337.4313538243792</v>
       </c>
       <c r="C43" t="n">
-        <v>338.5027912774657</v>
+        <v>339.3956247811457</v>
       </c>
       <c r="D43" t="n">
-        <v>332.1635060317716</v>
+        <v>333.6912462886964</v>
       </c>
       <c r="E43" t="n">
-        <v>334.2269897460938</v>
+        <v>337.3420715332031</v>
       </c>
       <c r="F43" t="n">
-        <v>5538000</v>
+        <v>4984600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>333.810367634687</v>
+        <v>335.9035711966457</v>
       </c>
       <c r="C44" t="n">
-        <v>337.6198973167316</v>
+        <v>335.9630927253758</v>
       </c>
       <c r="D44" t="n">
-        <v>331.5980496280586</v>
+        <v>331.062285023625</v>
       </c>
       <c r="E44" t="n">
-        <v>337.6000366210938</v>
+        <v>334.2864990234375</v>
       </c>
       <c r="F44" t="n">
-        <v>5920200</v>
+        <v>8507900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>337.4313538243792</v>
+        <v>334.058361977199</v>
       </c>
       <c r="C45" t="n">
-        <v>339.3956247811457</v>
+        <v>335.6059823618086</v>
       </c>
       <c r="D45" t="n">
-        <v>333.6912462886964</v>
+        <v>332.193273237939</v>
       </c>
       <c r="E45" t="n">
-        <v>337.3420715332031</v>
+        <v>333.3539733886719</v>
       </c>
       <c r="F45" t="n">
-        <v>4984600</v>
+        <v>5318400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>335.9035711966457</v>
+        <v>333.9789743060267</v>
       </c>
       <c r="C46" t="n">
-        <v>335.9630927253758</v>
+        <v>335.9928668426192</v>
       </c>
       <c r="D46" t="n">
-        <v>331.062285023625</v>
+        <v>331.6674741139567</v>
       </c>
       <c r="E46" t="n">
-        <v>334.2864990234375</v>
+        <v>332.1932678222656</v>
       </c>
       <c r="F46" t="n">
-        <v>8507900</v>
+        <v>5295800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>334.0583313951361</v>
+        <v>332.838108855689</v>
       </c>
       <c r="C47" t="n">
-        <v>335.6059516380656</v>
+        <v>336.3996217972758</v>
       </c>
       <c r="D47" t="n">
-        <v>332.1932428266196</v>
+        <v>330.5563693999427</v>
       </c>
       <c r="E47" t="n">
-        <v>333.3539428710938</v>
+        <v>336.2309875488281</v>
       </c>
       <c r="F47" t="n">
-        <v>5318400</v>
+        <v>4453300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>333.9789743060267</v>
+        <v>336.230963908966</v>
       </c>
       <c r="C48" t="n">
-        <v>335.9928668426192</v>
+        <v>342.2050995382295</v>
       </c>
       <c r="D48" t="n">
-        <v>331.6674741139567</v>
+        <v>335.3860315467677</v>
       </c>
       <c r="E48" t="n">
-        <v>332.1932678222656</v>
+        <v>336.8572082519531</v>
       </c>
       <c r="F48" t="n">
-        <v>5295800</v>
+        <v>6389600</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>332.838108855689</v>
+        <v>337.0162670739215</v>
       </c>
       <c r="C49" t="n">
-        <v>336.3996217972758</v>
+        <v>339.4218050228609</v>
       </c>
       <c r="D49" t="n">
-        <v>330.5563693999427</v>
+        <v>333.5967981253938</v>
       </c>
       <c r="E49" t="n">
-        <v>336.2309875488281</v>
+        <v>334.0739135742188</v>
       </c>
       <c r="F49" t="n">
-        <v>4453300</v>
+        <v>4961700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>336.230963908966</v>
+        <v>333.8850664354288</v>
       </c>
       <c r="C50" t="n">
-        <v>342.2050995382295</v>
+        <v>334.0739044051273</v>
       </c>
       <c r="D50" t="n">
-        <v>335.3860315467677</v>
+        <v>327.0659984240934</v>
       </c>
       <c r="E50" t="n">
-        <v>336.8572082519531</v>
+        <v>328.0500793457031</v>
       </c>
       <c r="F50" t="n">
-        <v>6389600</v>
+        <v>6422300</v>
       </c>
       <c r="G50" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>337.01623628756</v>
+        <v>329.1832834325262</v>
       </c>
       <c r="C51" t="n">
-        <v>339.4217740167541</v>
+        <v>331.370133257436</v>
       </c>
       <c r="D51" t="n">
-        <v>333.5967676514001</v>
+        <v>322.9904598740608</v>
       </c>
       <c r="E51" t="n">
-        <v>334.0738830566406</v>
+        <v>323.8055725097656</v>
       </c>
       <c r="F51" t="n">
-        <v>4961700</v>
+        <v>6494800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>333.8850664354288</v>
+        <v>322.5630378796905</v>
       </c>
       <c r="C52" t="n">
-        <v>334.0739044051273</v>
+        <v>323.0600533463772</v>
       </c>
       <c r="D52" t="n">
-        <v>327.0659984240934</v>
+        <v>316.101836812763</v>
       </c>
       <c r="E52" t="n">
-        <v>328.0500793457031</v>
+        <v>319.2628479003906</v>
       </c>
       <c r="F52" t="n">
-        <v>6422300</v>
+        <v>9170400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>329.1832834325262</v>
+        <v>319.6008162287846</v>
       </c>
       <c r="C53" t="n">
-        <v>331.370133257436</v>
+        <v>322.632628790591</v>
       </c>
       <c r="D53" t="n">
-        <v>322.9904598740608</v>
+        <v>317.9606712483538</v>
       </c>
       <c r="E53" t="n">
-        <v>323.8055725097656</v>
+        <v>322.185302734375</v>
       </c>
       <c r="F53" t="n">
-        <v>6494800</v>
+        <v>7066700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>322.5630378796905</v>
+        <v>322.1852887063674</v>
       </c>
       <c r="C54" t="n">
-        <v>323.0600533463772</v>
+        <v>326.4397397218689</v>
       </c>
       <c r="D54" t="n">
-        <v>316.101836812763</v>
+        <v>321.2111578443184</v>
       </c>
       <c r="E54" t="n">
-        <v>319.2628479003906</v>
+        <v>321.8373718261719</v>
       </c>
       <c r="F54" t="n">
-        <v>9170400</v>
+        <v>6510300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>319.6008465015586</v>
+        <v>323.437821602865</v>
       </c>
       <c r="C55" t="n">
-        <v>322.6326593505401</v>
+        <v>329.1037802762534</v>
       </c>
       <c r="D55" t="n">
-        <v>317.9607013657724</v>
+        <v>322.3543314197192</v>
       </c>
       <c r="E55" t="n">
-        <v>322.1853332519531</v>
+        <v>326.0223083496094</v>
       </c>
       <c r="F55" t="n">
-        <v>7066700</v>
+        <v>8930000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>322.1852887063674</v>
+        <v>327.2747416730934</v>
       </c>
       <c r="C56" t="n">
-        <v>326.4397397218689</v>
+        <v>328.755868423024</v>
       </c>
       <c r="D56" t="n">
-        <v>321.2111578443184</v>
+        <v>324.0540910886259</v>
       </c>
       <c r="E56" t="n">
-        <v>321.8373718261719</v>
+        <v>327.3343811035156</v>
       </c>
       <c r="F56" t="n">
-        <v>6510300</v>
+        <v>9337100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>323.4377913272098</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="C57" t="n">
-        <v>329.1037494702317</v>
+        <v>334.0540387480419</v>
       </c>
       <c r="D57" t="n">
-        <v>322.354301245485</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="E57" t="n">
-        <v>326.0222778320312</v>
+        <v>332.5331726074219</v>
       </c>
       <c r="F57" t="n">
-        <v>8930000</v>
+        <v>5854300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>327.2747416730934</v>
+        <v>332.5331806355595</v>
       </c>
       <c r="C58" t="n">
-        <v>328.755868423024</v>
+        <v>333.7061299047911</v>
       </c>
       <c r="D58" t="n">
-        <v>324.0540910886259</v>
+        <v>331.0719538898497</v>
       </c>
       <c r="E58" t="n">
-        <v>327.3343811035156</v>
+        <v>331.797607421875</v>
       </c>
       <c r="F58" t="n">
-        <v>9337100</v>
+        <v>4309900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>326.9367735032804</v>
+        <v>331.4397445821358</v>
       </c>
       <c r="C59" t="n">
-        <v>334.0540387480419</v>
+        <v>333.0202502105825</v>
       </c>
       <c r="D59" t="n">
-        <v>326.9367735032804</v>
+        <v>330.0182875517957</v>
       </c>
       <c r="E59" t="n">
-        <v>332.5331726074219</v>
+        <v>332.4437255859375</v>
       </c>
       <c r="F59" t="n">
-        <v>5854300</v>
+        <v>4586200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>332.533150050326</v>
+        <v>330.952674561706</v>
       </c>
       <c r="C60" t="n">
-        <v>333.7060992116737</v>
+        <v>331.3105111509684</v>
       </c>
       <c r="D60" t="n">
-        <v>331.0719234390147</v>
+        <v>328.1693999716056</v>
       </c>
       <c r="E60" t="n">
-        <v>331.7975769042969</v>
+        <v>328.4179077148438</v>
       </c>
       <c r="F60" t="n">
-        <v>4309900</v>
+        <v>7082300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>331.4397445821358</v>
+        <v>329.4715593852143</v>
       </c>
       <c r="C61" t="n">
-        <v>333.0202502105825</v>
+        <v>330.8134768540631</v>
       </c>
       <c r="D61" t="n">
-        <v>330.0182875517957</v>
+        <v>325.2568476714639</v>
       </c>
       <c r="E61" t="n">
-        <v>332.4437255859375</v>
+        <v>327.6524658203125</v>
       </c>
       <c r="F61" t="n">
-        <v>4586200</v>
+        <v>8201900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>330.952674561706</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="C62" t="n">
-        <v>331.3105111509684</v>
+        <v>330.3661824396382</v>
       </c>
       <c r="D62" t="n">
-        <v>328.1693999716056</v>
+        <v>327.3840896786403</v>
       </c>
       <c r="E62" t="n">
-        <v>328.4179077148438</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="F62" t="n">
-        <v>7082300</v>
+        <v>6296700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>329.4715593852143</v>
+        <v>329.3025639629765</v>
       </c>
       <c r="C63" t="n">
-        <v>330.8134768540631</v>
+        <v>330.3960040486967</v>
       </c>
       <c r="D63" t="n">
-        <v>325.2568476714639</v>
+        <v>322.3443474807417</v>
       </c>
       <c r="E63" t="n">
-        <v>327.6524658203125</v>
+        <v>325.1475219726562</v>
       </c>
       <c r="F63" t="n">
-        <v>8201900</v>
+        <v>6277500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>327.6425170898438</v>
+        <v>324.8791069392551</v>
       </c>
       <c r="C64" t="n">
-        <v>330.3661824396382</v>
+        <v>332.1156507054553</v>
       </c>
       <c r="D64" t="n">
-        <v>327.3840896786403</v>
+        <v>324.4516809311236</v>
       </c>
       <c r="E64" t="n">
-        <v>327.6425170898438</v>
+        <v>329.2627868652344</v>
       </c>
       <c r="F64" t="n">
-        <v>6296700</v>
+        <v>5266600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>329.3025948705371</v>
+        <v>327.9109619547325</v>
       </c>
       <c r="C65" t="n">
-        <v>330.396035058885</v>
+        <v>329.3622387687074</v>
       </c>
       <c r="D65" t="n">
-        <v>322.3443777352205</v>
+        <v>322.7718081675561</v>
       </c>
       <c r="E65" t="n">
-        <v>325.1475524902344</v>
+        <v>324.8890991210938</v>
       </c>
       <c r="F65" t="n">
-        <v>6277500</v>
+        <v>6059400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>324.8791069392551</v>
+        <v>324.6604457908234</v>
       </c>
       <c r="C66" t="n">
-        <v>332.1156507054553</v>
+        <v>326.270801469966</v>
       </c>
       <c r="D66" t="n">
-        <v>324.4516809311236</v>
+        <v>323.1296599138169</v>
       </c>
       <c r="E66" t="n">
-        <v>329.2627868652344</v>
+        <v>324.5511169433594</v>
       </c>
       <c r="F66" t="n">
-        <v>5266600</v>
+        <v>4325400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>327.9109311533039</v>
+        <v>324.6902773524443</v>
       </c>
       <c r="C67" t="n">
-        <v>329.3622078309571</v>
+        <v>326.797618069185</v>
       </c>
       <c r="D67" t="n">
-        <v>322.77177784886</v>
+        <v>323.3582492118315</v>
       </c>
       <c r="E67" t="n">
-        <v>324.8890686035156</v>
+        <v>323.7857055664062</v>
       </c>
       <c r="F67" t="n">
-        <v>6059400</v>
+        <v>5467500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>324.6604152629651</v>
+        <v>330.6147322397455</v>
       </c>
       <c r="C68" t="n">
-        <v>326.2707707906858</v>
+        <v>345.2468704623673</v>
       </c>
       <c r="D68" t="n">
-        <v>323.1296295298985</v>
+        <v>328.0898848869026</v>
       </c>
       <c r="E68" t="n">
-        <v>324.5510864257812</v>
+        <v>343.5669555664062</v>
       </c>
       <c r="F68" t="n">
-        <v>4325400</v>
+        <v>12953600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>324.6902773524443</v>
+        <v>345.9227522622342</v>
       </c>
       <c r="C69" t="n">
-        <v>326.797618069185</v>
+        <v>347.751765473026</v>
       </c>
       <c r="D69" t="n">
-        <v>323.3582492118315</v>
+        <v>343.9048707541211</v>
       </c>
       <c r="E69" t="n">
-        <v>323.7857055664062</v>
+        <v>345.7537536621094</v>
       </c>
       <c r="F69" t="n">
-        <v>5467500</v>
+        <v>6942300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>330.6146735055701</v>
+        <v>345.7537581195867</v>
       </c>
       <c r="C70" t="n">
-        <v>345.2468091287718</v>
+        <v>346.3700827656107</v>
       </c>
       <c r="D70" t="n">
-        <v>328.0898266012699</v>
+        <v>341.7776344791052</v>
       </c>
       <c r="E70" t="n">
-        <v>343.56689453125</v>
+        <v>344.8193969726562</v>
       </c>
       <c r="F70" t="n">
-        <v>12953600</v>
+        <v>7004600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>345.9227522622342</v>
+        <v>343.9347204472646</v>
       </c>
       <c r="C71" t="n">
-        <v>347.751765473026</v>
+        <v>345.5450457875993</v>
       </c>
       <c r="D71" t="n">
-        <v>343.9048707541211</v>
+        <v>341.6683310172716</v>
       </c>
       <c r="E71" t="n">
-        <v>345.7537536621094</v>
+        <v>343.0500183105469</v>
       </c>
       <c r="F71" t="n">
-        <v>6942300</v>
+        <v>7269300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>345.7537581195867</v>
+        <v>343.4873664669518</v>
       </c>
       <c r="C72" t="n">
-        <v>346.3700827656107</v>
+        <v>345.7140163182048</v>
       </c>
       <c r="D72" t="n">
-        <v>341.7776344791052</v>
+        <v>341.6285335316323</v>
       </c>
       <c r="E72" t="n">
-        <v>344.8193969726562</v>
+        <v>342.3541870117188</v>
       </c>
       <c r="F72" t="n">
-        <v>7004600</v>
+        <v>7263500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>343.9347204472646</v>
+        <v>343.1096892417585</v>
       </c>
       <c r="C73" t="n">
-        <v>345.5450457875993</v>
+        <v>345.4555878108393</v>
       </c>
       <c r="D73" t="n">
-        <v>341.6683310172716</v>
+        <v>342.2150370848335</v>
       </c>
       <c r="E73" t="n">
-        <v>343.0500183105469</v>
+        <v>343.9446716308594</v>
       </c>
       <c r="F73" t="n">
-        <v>7269300</v>
+        <v>6805000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>343.4873664669518</v>
+        <v>343.9843722679569</v>
       </c>
       <c r="C74" t="n">
-        <v>345.7140163182048</v>
+        <v>347.8213472210815</v>
       </c>
       <c r="D74" t="n">
-        <v>341.6285335316323</v>
+        <v>343.9843722679569</v>
       </c>
       <c r="E74" t="n">
-        <v>342.3541870117188</v>
+        <v>347.165283203125</v>
       </c>
       <c r="F74" t="n">
-        <v>7263500</v>
+        <v>18623900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>343.1096587982668</v>
+        <v>347.9108516431725</v>
       </c>
       <c r="C75" t="n">
-        <v>345.4555571592003</v>
+        <v>351.3303207261561</v>
       </c>
       <c r="D75" t="n">
-        <v>342.2150067207226</v>
+        <v>347.5032952909974</v>
       </c>
       <c r="E75" t="n">
-        <v>343.9446411132812</v>
+        <v>349.9883728027344</v>
       </c>
       <c r="F75" t="n">
-        <v>6805000</v>
+        <v>5043500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>343.9844025059169</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="C76" t="n">
-        <v>347.8213777963309</v>
+        <v>354.2527532371108</v>
       </c>
       <c r="D76" t="n">
-        <v>343.9844025059169</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="E76" t="n">
-        <v>347.1653137207031</v>
+        <v>351.2706604003906</v>
       </c>
       <c r="F76" t="n">
-        <v>18623900</v>
+        <v>3703200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>347.9108213067459</v>
+        <v>351.2706375438569</v>
       </c>
       <c r="C77" t="n">
-        <v>351.3302900915655</v>
+        <v>353.86504358199</v>
       </c>
       <c r="D77" t="n">
-        <v>347.5032649901081</v>
+        <v>350.9028509715926</v>
       </c>
       <c r="E77" t="n">
-        <v>349.9883422851562</v>
+        <v>353.0201416015625</v>
       </c>
       <c r="F77" t="n">
-        <v>5043500</v>
+        <v>2023600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>349.8988624434305</v>
+        <v>352.9804211319358</v>
       </c>
       <c r="C78" t="n">
-        <v>354.2527224604554</v>
+        <v>354.6006965475734</v>
       </c>
       <c r="D78" t="n">
-        <v>349.8988624434305</v>
+        <v>351.5987034536714</v>
       </c>
       <c r="E78" t="n">
-        <v>351.2706298828125</v>
+        <v>352.8810119628906</v>
       </c>
       <c r="F78" t="n">
-        <v>3703200</v>
+        <v>2017000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>351.2706679101954</v>
+        <v>353.3680381865314</v>
       </c>
       <c r="C79" t="n">
-        <v>353.8650741726075</v>
+        <v>354.4217085233975</v>
       </c>
       <c r="D79" t="n">
-        <v>350.9028813061371</v>
+        <v>351.688123523234</v>
       </c>
       <c r="E79" t="n">
-        <v>353.0201721191406</v>
+        <v>352.4932861328125</v>
       </c>
       <c r="F79" t="n">
-        <v>2023600</v>
+        <v>3989900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>352.9803906057607</v>
+        <v>351.8869529196318</v>
       </c>
       <c r="C80" t="n">
-        <v>354.6006658812749</v>
+        <v>352.7517549841574</v>
       </c>
       <c r="D80" t="n">
-        <v>351.5986730469889</v>
+        <v>350.5549550996776</v>
       </c>
       <c r="E80" t="n">
-        <v>352.8809814453125</v>
+        <v>351.5092163085938</v>
       </c>
       <c r="F80" t="n">
-        <v>2017000</v>
+        <v>3366500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>353.3680687798424</v>
+        <v>351.539030494231</v>
       </c>
       <c r="C81" t="n">
-        <v>354.4217392079314</v>
+        <v>353.0797966289462</v>
       </c>
       <c r="D81" t="n">
-        <v>351.6881539711041</v>
+        <v>348.5967074506911</v>
       </c>
       <c r="E81" t="n">
-        <v>352.4933166503906</v>
+        <v>348.6165771484375</v>
       </c>
       <c r="F81" t="n">
-        <v>3989900</v>
+        <v>3503200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>351.8869529196318</v>
+        <v>347.7815836695472</v>
       </c>
       <c r="C82" t="n">
-        <v>352.7517549841574</v>
+        <v>347.960501949782</v>
       </c>
       <c r="D82" t="n">
-        <v>350.5549550996776</v>
+        <v>341.4297420378886</v>
       </c>
       <c r="E82" t="n">
-        <v>351.5092163085938</v>
+        <v>344.4118347167969</v>
       </c>
       <c r="F82" t="n">
-        <v>3366500</v>
+        <v>5403800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>351.539030494231</v>
+        <v>342.443665092254</v>
       </c>
       <c r="C83" t="n">
-        <v>353.0797966289462</v>
+        <v>355.4058372808095</v>
       </c>
       <c r="D83" t="n">
-        <v>348.5967074506911</v>
+        <v>341.996339026907</v>
       </c>
       <c r="E83" t="n">
-        <v>348.6165771484375</v>
+        <v>351.6881408691406</v>
       </c>
       <c r="F83" t="n">
-        <v>3503200</v>
+        <v>7592200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>347.7816144857114</v>
+        <v>351.5688750998228</v>
       </c>
       <c r="C84" t="n">
-        <v>347.9605327817998</v>
+        <v>356.4793906429162</v>
       </c>
       <c r="D84" t="n">
-        <v>341.4297722912301</v>
+        <v>349.8989103083969</v>
       </c>
       <c r="E84" t="n">
-        <v>344.411865234375</v>
+        <v>355.4257202148438</v>
       </c>
       <c r="F84" t="n">
-        <v>5403800</v>
+        <v>6775400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>342.443665092254</v>
+        <v>355.0181150566925</v>
       </c>
       <c r="C85" t="n">
-        <v>355.4058372808095</v>
+        <v>356.1413747804971</v>
       </c>
       <c r="D85" t="n">
-        <v>341.996339026907</v>
+        <v>352.3938893645904</v>
       </c>
       <c r="E85" t="n">
-        <v>351.6881408691406</v>
+        <v>353.7557067871094</v>
       </c>
       <c r="F85" t="n">
-        <v>7592200</v>
+        <v>6333900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>351.5688750998228</v>
+        <v>352.8809877738215</v>
       </c>
       <c r="C86" t="n">
-        <v>356.4793906429162</v>
+        <v>354.2229356253969</v>
       </c>
       <c r="D86" t="n">
-        <v>349.8989103083969</v>
+        <v>347.4138175407059</v>
       </c>
       <c r="E86" t="n">
-        <v>355.4257202148438</v>
+        <v>350.1275329589844</v>
       </c>
       <c r="F86" t="n">
-        <v>6775400</v>
+        <v>6357600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>355.0181456831753</v>
+        <v>350.0579384420253</v>
       </c>
       <c r="C87" t="n">
-        <v>356.1414055038805</v>
+        <v>352.582785516123</v>
       </c>
       <c r="D87" t="n">
-        <v>352.3939197646881</v>
+        <v>347.075845630788</v>
       </c>
       <c r="E87" t="n">
-        <v>353.7557373046875</v>
+        <v>347.6821899414062</v>
       </c>
       <c r="F87" t="n">
-        <v>6333900</v>
+        <v>4902900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>352.8809877738215</v>
+        <v>340.7339218833562</v>
       </c>
       <c r="C88" t="n">
-        <v>354.2229356253969</v>
+        <v>344.4416681829234</v>
       </c>
       <c r="D88" t="n">
-        <v>347.4138175407059</v>
+        <v>335.306521484956</v>
       </c>
       <c r="E88" t="n">
-        <v>350.1275329589844</v>
+        <v>341.1514282226562</v>
       </c>
       <c r="F88" t="n">
-        <v>6357600</v>
+        <v>13281300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>350.0579384420253</v>
+        <v>334.9884397502153</v>
       </c>
       <c r="C89" t="n">
-        <v>352.582785516123</v>
+        <v>335.5053249382782</v>
       </c>
       <c r="D89" t="n">
-        <v>347.075845630788</v>
+        <v>321.8970384159538</v>
       </c>
       <c r="E89" t="n">
-        <v>347.6821899414062</v>
+        <v>325.9228820800781</v>
       </c>
       <c r="F89" t="n">
-        <v>4902900</v>
+        <v>20383500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>340.7339218833562</v>
+        <v>326.6982346739846</v>
       </c>
       <c r="C90" t="n">
-        <v>344.4416681829234</v>
+        <v>327.930823416361</v>
       </c>
       <c r="D90" t="n">
-        <v>335.306521484956</v>
+        <v>322.0064071036056</v>
       </c>
       <c r="E90" t="n">
-        <v>341.1514282226562</v>
+        <v>327.2052001953125</v>
       </c>
       <c r="F90" t="n">
-        <v>13281300</v>
+        <v>9388400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>334.9884397502153</v>
+        <v>327.3641650074799</v>
       </c>
       <c r="C91" t="n">
-        <v>335.5053249382782</v>
+        <v>329.7100935773221</v>
       </c>
       <c r="D91" t="n">
-        <v>321.8970384159538</v>
+        <v>324.421842198657</v>
       </c>
       <c r="E91" t="n">
-        <v>325.9228820800781</v>
+        <v>325.7936096191406</v>
       </c>
       <c r="F91" t="n">
-        <v>20383500</v>
+        <v>8587700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>326.6982042036898</v>
+        <v>324.8294159854098</v>
       </c>
       <c r="C92" t="n">
-        <v>327.9307928311059</v>
+        <v>327.2846735195349</v>
       </c>
       <c r="D92" t="n">
-        <v>322.0063770709054</v>
+        <v>323.4576484910236</v>
       </c>
       <c r="E92" t="n">
-        <v>327.2051696777344</v>
+        <v>326.34033203125</v>
       </c>
       <c r="F92" t="n">
-        <v>9388400</v>
+        <v>8341600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>327.3641956721743</v>
+        <v>320.3065853250236</v>
       </c>
       <c r="C93" t="n">
-        <v>329.7101244617631</v>
+        <v>326.3602298184734</v>
       </c>
       <c r="D93" t="n">
-        <v>324.4218725877395</v>
+        <v>319.6405712796447</v>
       </c>
       <c r="E93" t="n">
-        <v>325.7936401367188</v>
+        <v>323.8751525878906</v>
       </c>
       <c r="F93" t="n">
-        <v>8587700</v>
+        <v>8279900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>324.8294159854098</v>
+        <v>324.4815084058711</v>
       </c>
       <c r="C94" t="n">
-        <v>327.2846735195349</v>
+        <v>326.708158311709</v>
       </c>
       <c r="D94" t="n">
-        <v>323.4576484910236</v>
+        <v>321.0719896048092</v>
       </c>
       <c r="E94" t="n">
-        <v>326.34033203125</v>
+        <v>323.33837890625</v>
       </c>
       <c r="F94" t="n">
-        <v>8341600</v>
+        <v>8974600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>320.3066155063486</v>
+        <v>324.5113354316111</v>
       </c>
       <c r="C95" t="n">
-        <v>326.3602605702113</v>
+        <v>326.4298382199604</v>
       </c>
       <c r="D95" t="n">
-        <v>319.6406013982136</v>
+        <v>322.0660277886144</v>
       </c>
       <c r="E95" t="n">
-        <v>323.8751831054688</v>
+        <v>324.4119262695312</v>
       </c>
       <c r="F95" t="n">
-        <v>8279900</v>
+        <v>6938700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>324.4815084058711</v>
+        <v>323.9148740430089</v>
       </c>
       <c r="C96" t="n">
-        <v>326.708158311709</v>
+        <v>325.8432962939743</v>
       </c>
       <c r="D96" t="n">
-        <v>321.0719896048092</v>
+        <v>322.682285512236</v>
       </c>
       <c r="E96" t="n">
-        <v>323.33837890625</v>
+        <v>324.2329711914062</v>
       </c>
       <c r="F96" t="n">
-        <v>8974600</v>
+        <v>5667900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>324.5113354316111</v>
+        <v>326.0421398816049</v>
       </c>
       <c r="C97" t="n">
-        <v>326.4298382199604</v>
+        <v>330.0182635386976</v>
       </c>
       <c r="D97" t="n">
-        <v>322.0660277886144</v>
+        <v>323.0898668527969</v>
       </c>
       <c r="E97" t="n">
-        <v>324.4119262695312</v>
+        <v>326.5292053222656</v>
       </c>
       <c r="F97" t="n">
-        <v>6938700</v>
+        <v>7540200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>323.9149045306469</v>
+        <v>326.5192927903481</v>
       </c>
       <c r="C98" t="n">
-        <v>325.8433269631201</v>
+        <v>326.9665885103149</v>
       </c>
       <c r="D98" t="n">
-        <v>322.6823158838599</v>
+        <v>322.9705950681941</v>
       </c>
       <c r="E98" t="n">
-        <v>324.2330017089844</v>
+        <v>323.3185119628906</v>
       </c>
       <c r="F98" t="n">
-        <v>5667900</v>
+        <v>6365800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>326.0421398816049</v>
+        <v>324.779721039233</v>
       </c>
       <c r="C99" t="n">
-        <v>330.0182635386976</v>
+        <v>326.4298159438193</v>
       </c>
       <c r="D99" t="n">
-        <v>323.0898668527969</v>
+        <v>322.9407578402086</v>
       </c>
       <c r="E99" t="n">
-        <v>326.5292053222656</v>
+        <v>325.0282287597656</v>
       </c>
       <c r="F99" t="n">
-        <v>7540200</v>
+        <v>8106000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>326.5192927903481</v>
+        <v>328.0301840749007</v>
       </c>
       <c r="C100" t="n">
-        <v>326.9665885103149</v>
+        <v>331.3701132063007</v>
       </c>
       <c r="D100" t="n">
-        <v>322.9705950681941</v>
+        <v>321.578933495427</v>
       </c>
       <c r="E100" t="n">
-        <v>323.3185119628906</v>
+        <v>329.8194274902344</v>
       </c>
       <c r="F100" t="n">
-        <v>6365800</v>
+        <v>10214200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>324.7797515334782</v>
+        <v>330.236962156358</v>
       </c>
       <c r="C101" t="n">
-        <v>326.4298465929955</v>
+        <v>331.0123050809688</v>
       </c>
       <c r="D101" t="n">
-        <v>322.9407881617898</v>
+        <v>319.6803583614965</v>
       </c>
       <c r="E101" t="n">
-        <v>325.0282592773438</v>
+        <v>319.9089660644531</v>
       </c>
       <c r="F101" t="n">
-        <v>8106000</v>
+        <v>11199100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>328.0302144269235</v>
+        <v>322.8910614362982</v>
       </c>
       <c r="C102" t="n">
-        <v>331.370143867361</v>
+        <v>332.6922224170356</v>
       </c>
       <c r="D102" t="n">
-        <v>321.5789632505275</v>
+        <v>322.1753579360102</v>
       </c>
       <c r="E102" t="n">
-        <v>329.8194580078125</v>
+        <v>331.8472900390625</v>
       </c>
       <c r="F102" t="n">
-        <v>10214200</v>
+        <v>8502400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>330.2369936591709</v>
+        <v>329.6703485679092</v>
       </c>
       <c r="C103" t="n">
-        <v>331.0123366577452</v>
+        <v>333.7856511379211</v>
       </c>
       <c r="D103" t="n">
-        <v>319.6803888572667</v>
+        <v>326.9069438235834</v>
       </c>
       <c r="E103" t="n">
-        <v>319.9089965820312</v>
+        <v>326.9665832519531</v>
       </c>
       <c r="F103" t="n">
-        <v>11199100</v>
+        <v>9081200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>322.8910614362982</v>
+        <v>325.15742488804</v>
       </c>
       <c r="C104" t="n">
-        <v>332.6922224170356</v>
+        <v>329.3323666962788</v>
       </c>
       <c r="D104" t="n">
-        <v>322.1753579360102</v>
+        <v>322.4835097434655</v>
       </c>
       <c r="E104" t="n">
-        <v>331.8472900390625</v>
+        <v>327.9804992675781</v>
       </c>
       <c r="F104" t="n">
-        <v>8502400</v>
+        <v>8472300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>329.6703793378445</v>
+        <v>331.0123001239136</v>
       </c>
       <c r="C105" t="n">
-        <v>333.7856822919601</v>
+        <v>335.5748984583446</v>
       </c>
       <c r="D105" t="n">
-        <v>326.906974335595</v>
+        <v>326.8572581115669</v>
       </c>
       <c r="E105" t="n">
-        <v>326.9666137695312</v>
+        <v>327.1654052734375</v>
       </c>
       <c r="F105" t="n">
-        <v>9081200</v>
+        <v>8339000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>325.15742488804</v>
+        <v>329.7995873671293</v>
       </c>
       <c r="C106" t="n">
-        <v>329.3323666962788</v>
+        <v>333.1295971166072</v>
       </c>
       <c r="D106" t="n">
-        <v>322.4835097434655</v>
+        <v>325.1475298017769</v>
       </c>
       <c r="E106" t="n">
-        <v>327.9804992675781</v>
+        <v>329.6007690429688</v>
       </c>
       <c r="F106" t="n">
-        <v>8472300</v>
+        <v>7798800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>331.0123001239136</v>
+        <v>328.7857002676274</v>
       </c>
       <c r="C107" t="n">
-        <v>335.5748984583446</v>
+        <v>330.8334016821115</v>
       </c>
       <c r="D107" t="n">
-        <v>326.8572581115669</v>
+        <v>321.6883044313802</v>
       </c>
       <c r="E107" t="n">
-        <v>327.1654052734375</v>
+        <v>323.6365966796875</v>
       </c>
       <c r="F107" t="n">
-        <v>8339000</v>
+        <v>8513400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,25 +3225,25 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>329.7995873671293</v>
+        <v>323.4373584411114</v>
       </c>
       <c r="C108" t="n">
-        <v>333.1295971166072</v>
+        <v>328.5871090806843</v>
       </c>
       <c r="D108" t="n">
-        <v>325.1475298017769</v>
+        <v>323.2779818799478</v>
       </c>
       <c r="E108" t="n">
-        <v>329.6007690429688</v>
+        <v>326.8838195800781</v>
       </c>
       <c r="F108" t="n">
-        <v>7798800</v>
+        <v>5801800</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>328.7857002676274</v>
+        <v>325.6387009449491</v>
       </c>
       <c r="C109" t="n">
-        <v>330.8334016821115</v>
+        <v>329.7425483778229</v>
       </c>
       <c r="D109" t="n">
-        <v>321.6883044313802</v>
+        <v>325.140660617698</v>
       </c>
       <c r="E109" t="n">
-        <v>323.6365966796875</v>
+        <v>327.9495849609375</v>
       </c>
       <c r="F109" t="n">
-        <v>8513400</v>
+        <v>8264300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,25 +3277,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>323.4373584411114</v>
+        <v>327.6010166244024</v>
       </c>
       <c r="C110" t="n">
-        <v>328.5871090806843</v>
+        <v>330.9378628609571</v>
       </c>
       <c r="D110" t="n">
-        <v>323.2779818799478</v>
+        <v>322.7301671039365</v>
       </c>
       <c r="E110" t="n">
-        <v>326.8838195800781</v>
+        <v>322.9094543457031</v>
       </c>
       <c r="F110" t="n">
-        <v>5801800</v>
+        <v>9392600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>325.6387009449491</v>
+        <v>322.5607854182599</v>
       </c>
       <c r="C111" t="n">
-        <v>329.7425483778229</v>
+        <v>325.2004234747151</v>
       </c>
       <c r="D111" t="n">
-        <v>325.140660617698</v>
+        <v>311.5939580676488</v>
       </c>
       <c r="E111" t="n">
-        <v>327.9495849609375</v>
+        <v>312.8489990234375</v>
       </c>
       <c r="F111" t="n">
-        <v>8264300</v>
+        <v>11653900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>327.6010166244024</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="C112" t="n">
-        <v>330.9378628609571</v>
+        <v>320.1204394263468</v>
       </c>
       <c r="D112" t="n">
-        <v>322.7301671039365</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="E112" t="n">
-        <v>322.9094543457031</v>
+        <v>318.247802734375</v>
       </c>
       <c r="F112" t="n">
-        <v>9392600</v>
+        <v>8591700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>322.5607854182599</v>
+        <v>318.2477947880967</v>
       </c>
       <c r="C113" t="n">
-        <v>325.2004234747151</v>
+        <v>321.0168980150915</v>
       </c>
       <c r="D113" t="n">
-        <v>311.5939580676488</v>
+        <v>315.4786915611019</v>
       </c>
       <c r="E113" t="n">
-        <v>312.8489990234375</v>
+        <v>319.0446472167969</v>
       </c>
       <c r="F113" t="n">
-        <v>11653900</v>
+        <v>7091900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>313.1777553150958</v>
+        <v>316.2456341157693</v>
       </c>
       <c r="C114" t="n">
-        <v>320.1204394263468</v>
+        <v>318.9450345490796</v>
       </c>
       <c r="D114" t="n">
-        <v>313.1777553150958</v>
+        <v>314.4925528519528</v>
       </c>
       <c r="E114" t="n">
-        <v>318.247802734375</v>
+        <v>317.6799926757812</v>
       </c>
       <c r="F114" t="n">
-        <v>8591700</v>
+        <v>5967600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>318.2477947880967</v>
+        <v>316.8632122574057</v>
       </c>
       <c r="C115" t="n">
-        <v>321.0168980150915</v>
+        <v>321.0866150343326</v>
       </c>
       <c r="D115" t="n">
-        <v>315.4786915611019</v>
+        <v>316.5743707451638</v>
       </c>
       <c r="E115" t="n">
-        <v>319.0446472167969</v>
+        <v>319.6921081542969</v>
       </c>
       <c r="F115" t="n">
-        <v>7091900</v>
+        <v>6831100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>316.2456341157693</v>
+        <v>317.7896151590316</v>
       </c>
       <c r="C116" t="n">
-        <v>318.9450345490796</v>
+        <v>319.2637952336624</v>
       </c>
       <c r="D116" t="n">
-        <v>314.4925528519528</v>
+        <v>303.5157608014752</v>
       </c>
       <c r="E116" t="n">
-        <v>317.6799926757812</v>
+        <v>305.3186645507812</v>
       </c>
       <c r="F116" t="n">
-        <v>5967600</v>
+        <v>13048000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>316.8632122574057</v>
+        <v>304.30263971785</v>
       </c>
       <c r="C117" t="n">
-        <v>321.0866150343326</v>
+        <v>308.0578528391844</v>
       </c>
       <c r="D117" t="n">
-        <v>316.5743707451638</v>
+        <v>301.8921111606905</v>
       </c>
       <c r="E117" t="n">
-        <v>319.6921081542969</v>
+        <v>306.0158996582031</v>
       </c>
       <c r="F117" t="n">
-        <v>6831100</v>
+        <v>9120200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>317.7896151590316</v>
+        <v>307.3407046816708</v>
       </c>
       <c r="C118" t="n">
-        <v>319.2637952336624</v>
+        <v>312.7095945401492</v>
       </c>
       <c r="D118" t="n">
-        <v>303.5157608014752</v>
+        <v>307.0418926144709</v>
       </c>
       <c r="E118" t="n">
-        <v>305.3186645507812</v>
+        <v>311.7633056640625</v>
       </c>
       <c r="F118" t="n">
-        <v>13048000</v>
+        <v>7624200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>304.30263971785</v>
+        <v>313.2475006793624</v>
       </c>
       <c r="C119" t="n">
-        <v>308.0578528391844</v>
+        <v>318.168142259306</v>
       </c>
       <c r="D119" t="n">
-        <v>301.8921111606905</v>
+        <v>312.7096085363555</v>
       </c>
       <c r="E119" t="n">
-        <v>306.0158996582031</v>
+        <v>315.4588012695312</v>
       </c>
       <c r="F119" t="n">
-        <v>9120200</v>
+        <v>8725500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>307.3407046816708</v>
+        <v>313.2275230423357</v>
       </c>
       <c r="C120" t="n">
-        <v>312.7095945401492</v>
+        <v>318.9749280375353</v>
       </c>
       <c r="D120" t="n">
-        <v>307.0418926144709</v>
+        <v>310.7273811988043</v>
       </c>
       <c r="E120" t="n">
-        <v>311.7633056640625</v>
+        <v>318.8852844238281</v>
       </c>
       <c r="F120" t="n">
-        <v>7624200</v>
+        <v>12412900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>313.2475006793624</v>
+        <v>314.2634710190134</v>
       </c>
       <c r="C121" t="n">
-        <v>318.168142259306</v>
+        <v>321.3356502974509</v>
       </c>
       <c r="D121" t="n">
-        <v>312.7096085363555</v>
+        <v>313.3670044395995</v>
       </c>
       <c r="E121" t="n">
-        <v>315.4588012695312</v>
+        <v>319.2538452148438</v>
       </c>
       <c r="F121" t="n">
-        <v>8725500</v>
+        <v>6674900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>313.2275230423357</v>
+        <v>314.5722564235918</v>
       </c>
       <c r="C122" t="n">
-        <v>318.9749280375353</v>
+        <v>320.7778503840851</v>
       </c>
       <c r="D122" t="n">
-        <v>310.7273811988043</v>
+        <v>313.117987052978</v>
       </c>
       <c r="E122" t="n">
-        <v>318.8852844238281</v>
+        <v>319.5725708007812</v>
       </c>
       <c r="F122" t="n">
-        <v>12412900</v>
+        <v>5474300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>314.2634710190134</v>
+        <v>320.1801887712339</v>
       </c>
       <c r="C123" t="n">
-        <v>321.3356502974509</v>
+        <v>324.4932049097204</v>
       </c>
       <c r="D123" t="n">
-        <v>313.3670044395995</v>
+        <v>318.5466018009251</v>
       </c>
       <c r="E123" t="n">
-        <v>319.2538452148438</v>
+        <v>319.2139892578125</v>
       </c>
       <c r="F123" t="n">
-        <v>6674900</v>
+        <v>5257900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>314.5722564235918</v>
+        <v>318.0784411900573</v>
       </c>
       <c r="C124" t="n">
-        <v>320.7778503840851</v>
+        <v>321.5348424853333</v>
       </c>
       <c r="D124" t="n">
-        <v>313.117987052978</v>
+        <v>313.5363155637196</v>
       </c>
       <c r="E124" t="n">
-        <v>319.5725708007812</v>
+        <v>318.5466003417969</v>
       </c>
       <c r="F124" t="n">
-        <v>5474300</v>
+        <v>8267200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>320.1801887712339</v>
+        <v>314.8113170354491</v>
       </c>
       <c r="C125" t="n">
-        <v>324.4932049097204</v>
+        <v>316.4449040988039</v>
       </c>
       <c r="D125" t="n">
-        <v>318.5466018009251</v>
+        <v>311.0760141261629</v>
       </c>
       <c r="E125" t="n">
-        <v>319.2139892578125</v>
+        <v>316.1161804199219</v>
       </c>
       <c r="F125" t="n">
-        <v>5257900</v>
+        <v>6439700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>318.0784411900573</v>
+        <v>312.2314560667069</v>
       </c>
       <c r="C126" t="n">
-        <v>321.5348424853333</v>
+        <v>315.1599358349184</v>
       </c>
       <c r="D126" t="n">
-        <v>313.5363155637196</v>
+        <v>308.9344312933075</v>
       </c>
       <c r="E126" t="n">
-        <v>318.5466003417969</v>
+        <v>314.7316284179688</v>
       </c>
       <c r="F126" t="n">
-        <v>8267200</v>
+        <v>8381500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>314.8113170354491</v>
+        <v>314.1937124870568</v>
       </c>
       <c r="C127" t="n">
-        <v>316.4449040988039</v>
+        <v>315.8870617531473</v>
       </c>
       <c r="D127" t="n">
-        <v>311.0760141261629</v>
+        <v>310.2293309503021</v>
       </c>
       <c r="E127" t="n">
-        <v>316.1161804199219</v>
+        <v>313.1976318359375</v>
       </c>
       <c r="F127" t="n">
-        <v>6439700</v>
+        <v>5271300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>312.2314560667069</v>
+        <v>312.0222791858673</v>
       </c>
       <c r="C128" t="n">
-        <v>315.1599358349184</v>
+        <v>313.8450934912395</v>
       </c>
       <c r="D128" t="n">
-        <v>308.9344312933075</v>
+        <v>307.1813415762761</v>
       </c>
       <c r="E128" t="n">
-        <v>314.7316284179688</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F128" t="n">
-        <v>8381500</v>
+        <v>6376700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>314.1937124870568</v>
+        <v>306.9323235221122</v>
       </c>
       <c r="C129" t="n">
-        <v>315.8870617531473</v>
+        <v>309.7313078758147</v>
       </c>
       <c r="D129" t="n">
-        <v>310.2293309503021</v>
+        <v>304.8206068898292</v>
       </c>
       <c r="E129" t="n">
-        <v>313.1976318359375</v>
+        <v>305.2987365722656</v>
       </c>
       <c r="F129" t="n">
-        <v>5271300</v>
+        <v>7514900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>312.0222791858673</v>
+        <v>306.3844668672209</v>
       </c>
       <c r="C130" t="n">
-        <v>313.8450934912395</v>
+        <v>309.1336593983733</v>
       </c>
       <c r="D130" t="n">
-        <v>307.1813415762761</v>
+        <v>305.2190694406472</v>
       </c>
       <c r="E130" t="n">
-        <v>307.7490844726562</v>
+        <v>305.9362487792969</v>
       </c>
       <c r="F130" t="n">
-        <v>6376700</v>
+        <v>4814100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>306.9323235221122</v>
+        <v>306.6434401255651</v>
       </c>
       <c r="C131" t="n">
-        <v>309.7313078758147</v>
+        <v>309.9105835049712</v>
       </c>
       <c r="D131" t="n">
-        <v>304.8206068898292</v>
+        <v>306.1752809950723</v>
       </c>
       <c r="E131" t="n">
-        <v>305.2987365722656</v>
+        <v>308.8945617675781</v>
       </c>
       <c r="F131" t="n">
-        <v>7514900</v>
+        <v>6401200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>306.3844668672209</v>
+        <v>310.0998441452866</v>
       </c>
       <c r="C132" t="n">
-        <v>309.1336593983733</v>
+        <v>311.4644698112407</v>
       </c>
       <c r="D132" t="n">
-        <v>305.2190694406472</v>
+        <v>306.1752838399166</v>
       </c>
       <c r="E132" t="n">
-        <v>305.9362487792969</v>
+        <v>307.2510375976562</v>
       </c>
       <c r="F132" t="n">
-        <v>4814100</v>
+        <v>6872200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>306.6434401255651</v>
+        <v>306.2051850075188</v>
       </c>
       <c r="C133" t="n">
-        <v>309.9105835049712</v>
+        <v>306.7331065856557</v>
       </c>
       <c r="D133" t="n">
-        <v>306.1752809950723</v>
+        <v>297.3301019351647</v>
       </c>
       <c r="E133" t="n">
-        <v>308.8945617675781</v>
+        <v>297.8480529785156</v>
       </c>
       <c r="F133" t="n">
-        <v>6401200</v>
+        <v>7191700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>310.0998441452866</v>
+        <v>296.8719016022564</v>
       </c>
       <c r="C134" t="n">
-        <v>311.4644698112407</v>
+        <v>301.2845318265138</v>
       </c>
       <c r="D134" t="n">
-        <v>306.1752838399166</v>
+        <v>295.8658503636263</v>
       </c>
       <c r="E134" t="n">
-        <v>307.2510375976562</v>
+        <v>298.5353393554688</v>
       </c>
       <c r="F134" t="n">
-        <v>6872200</v>
+        <v>6826400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>306.2051850075188</v>
+        <v>298.6748142545254</v>
       </c>
       <c r="C135" t="n">
-        <v>306.7331065856557</v>
+        <v>301.7327894042891</v>
       </c>
       <c r="D135" t="n">
-        <v>297.3301019351647</v>
+        <v>297.8381100854838</v>
       </c>
       <c r="E135" t="n">
-        <v>297.8480529785156</v>
+        <v>300.4378662109375</v>
       </c>
       <c r="F135" t="n">
-        <v>7191700</v>
+        <v>14398100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>296.8719016022564</v>
+        <v>304.0038572697504</v>
       </c>
       <c r="C136" t="n">
-        <v>301.2845318265138</v>
+        <v>306.6434651794843</v>
       </c>
       <c r="D136" t="n">
-        <v>295.8658503636263</v>
+        <v>301.6630614260347</v>
       </c>
       <c r="E136" t="n">
-        <v>298.5353393554688</v>
+        <v>303.246826171875</v>
       </c>
       <c r="F136" t="n">
-        <v>6826400</v>
+        <v>7824500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>298.6748142545254</v>
+        <v>300.8163767349488</v>
       </c>
       <c r="C137" t="n">
-        <v>301.7327894042891</v>
+        <v>304.8405513457489</v>
       </c>
       <c r="D137" t="n">
-        <v>297.8381100854838</v>
+        <v>299.4417804808951</v>
       </c>
       <c r="E137" t="n">
-        <v>300.4378662109375</v>
+        <v>302.5694885253906</v>
       </c>
       <c r="F137" t="n">
-        <v>14398100</v>
+        <v>5375900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>304.0038572697504</v>
+        <v>304.2827391072273</v>
       </c>
       <c r="C138" t="n">
-        <v>306.6434651794843</v>
+        <v>307.2809213034843</v>
       </c>
       <c r="D138" t="n">
-        <v>301.6630614260347</v>
+        <v>300.9857144661871</v>
       </c>
       <c r="E138" t="n">
-        <v>303.246826171875</v>
+        <v>303.7149658203125</v>
       </c>
       <c r="F138" t="n">
-        <v>7824500</v>
+        <v>6280900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>300.8163767349488</v>
+        <v>302.9679242862715</v>
       </c>
       <c r="C139" t="n">
-        <v>304.8405513457489</v>
+        <v>306.6633753539059</v>
       </c>
       <c r="D139" t="n">
-        <v>299.4417804808951</v>
+        <v>301.8124669695884</v>
       </c>
       <c r="E139" t="n">
-        <v>302.5694885253906</v>
+        <v>304.3325500488281</v>
       </c>
       <c r="F139" t="n">
-        <v>5375900</v>
+        <v>7652700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>304.2827391072273</v>
+        <v>303.127283705864</v>
       </c>
       <c r="C140" t="n">
-        <v>307.2809213034843</v>
+        <v>303.3962145496307</v>
       </c>
       <c r="D140" t="n">
-        <v>300.9857144661871</v>
+        <v>293.1664767786049</v>
       </c>
       <c r="E140" t="n">
-        <v>303.7149658203125</v>
+        <v>294.3617553710938</v>
       </c>
       <c r="F140" t="n">
-        <v>6280900</v>
+        <v>9974400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>302.9679242862715</v>
+        <v>297.5592048794472</v>
       </c>
       <c r="C141" t="n">
-        <v>306.6633753539059</v>
+        <v>299.5015440476056</v>
       </c>
       <c r="D141" t="n">
-        <v>301.8124669695884</v>
+        <v>294.7303392781201</v>
       </c>
       <c r="E141" t="n">
-        <v>304.3325500488281</v>
+        <v>298.3660278320312</v>
       </c>
       <c r="F141" t="n">
-        <v>7652700</v>
+        <v>9330300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>303.127283705864</v>
+        <v>300.4179440831887</v>
       </c>
       <c r="C142" t="n">
-        <v>303.3962145496307</v>
+        <v>302.1511147673973</v>
       </c>
       <c r="D142" t="n">
-        <v>293.1664767786049</v>
+        <v>295.4275700673832</v>
       </c>
       <c r="E142" t="n">
-        <v>294.3617553710938</v>
+        <v>301.055419921875</v>
       </c>
       <c r="F142" t="n">
-        <v>9974400</v>
+        <v>10246900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>297.5592048794472</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="C143" t="n">
-        <v>299.5015440476056</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="D143" t="n">
-        <v>294.7303392781201</v>
+        <v>292.7381994806606</v>
       </c>
       <c r="E143" t="n">
-        <v>298.3660278320312</v>
+        <v>297.340087890625</v>
       </c>
       <c r="F143" t="n">
-        <v>9330300</v>
+        <v>7707600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>300.4179440831887</v>
+        <v>296.6328211241279</v>
       </c>
       <c r="C144" t="n">
-        <v>302.1511147673973</v>
+        <v>301.2845313811459</v>
       </c>
       <c r="D144" t="n">
-        <v>295.4275700673832</v>
+        <v>294.6904819925192</v>
       </c>
       <c r="E144" t="n">
-        <v>301.055419921875</v>
+        <v>299.6210632324219</v>
       </c>
       <c r="F144" t="n">
-        <v>10246900</v>
+        <v>4376000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>303.8544344044319</v>
+        <v>299.5612984468797</v>
       </c>
       <c r="C145" t="n">
-        <v>303.8544344044319</v>
+        <v>303.2268985064469</v>
       </c>
       <c r="D145" t="n">
-        <v>292.7381994806606</v>
+        <v>298.286316373369</v>
       </c>
       <c r="E145" t="n">
-        <v>297.340087890625</v>
+        <v>302.1411437988281</v>
       </c>
       <c r="F145" t="n">
-        <v>7707600</v>
+        <v>5501000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>296.6328211241279</v>
+        <v>301.2546730003434</v>
       </c>
       <c r="C146" t="n">
-        <v>301.2845313811459</v>
+        <v>303.7847266884853</v>
       </c>
       <c r="D146" t="n">
-        <v>294.6904819925192</v>
+        <v>299.9398390775635</v>
       </c>
       <c r="E146" t="n">
-        <v>299.6210632324219</v>
+        <v>301.3642272949219</v>
       </c>
       <c r="F146" t="n">
-        <v>4376000</v>
+        <v>4413900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>299.5612984468797</v>
+        <v>306.5239246667074</v>
       </c>
       <c r="C147" t="n">
-        <v>303.2268985064469</v>
+        <v>309.8607706923777</v>
       </c>
       <c r="D147" t="n">
-        <v>298.286316373369</v>
+        <v>306.4940434616348</v>
       </c>
       <c r="E147" t="n">
-        <v>302.1411437988281</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F147" t="n">
-        <v>5501000</v>
+        <v>6879300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>301.2546730003434</v>
+        <v>306.792884650012</v>
       </c>
       <c r="C148" t="n">
-        <v>303.7847266884853</v>
+        <v>308.3666789299265</v>
       </c>
       <c r="D148" t="n">
-        <v>299.9398390775635</v>
+        <v>302.4001646993119</v>
       </c>
       <c r="E148" t="n">
-        <v>301.3642272949219</v>
+        <v>307.0817565917969</v>
       </c>
       <c r="F148" t="n">
-        <v>4413900</v>
+        <v>4811500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>306.5239246667074</v>
+        <v>307.5000714824076</v>
       </c>
       <c r="C149" t="n">
-        <v>309.8607706923777</v>
+        <v>307.7889434035062</v>
       </c>
       <c r="D149" t="n">
-        <v>306.4940434616348</v>
+        <v>302.3204699616491</v>
       </c>
       <c r="E149" t="n">
-        <v>307.7490844726562</v>
+        <v>303.1671142578125</v>
       </c>
       <c r="F149" t="n">
-        <v>6879300</v>
+        <v>5190000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>306.792884650012</v>
+        <v>302.7388065700545</v>
       </c>
       <c r="C150" t="n">
-        <v>308.3666789299265</v>
+        <v>308.5360036681458</v>
       </c>
       <c r="D150" t="n">
-        <v>302.4001646993119</v>
+        <v>301.155041869684</v>
       </c>
       <c r="E150" t="n">
-        <v>307.0817565917969</v>
+        <v>308.1774291992188</v>
       </c>
       <c r="F150" t="n">
-        <v>4811500</v>
+        <v>6787200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>307.5000714824076</v>
+        <v>307.2610301082847</v>
       </c>
       <c r="C151" t="n">
-        <v>307.7889434035062</v>
+        <v>310.8967187654788</v>
       </c>
       <c r="D151" t="n">
-        <v>302.3204699616491</v>
+        <v>306.2848600302058</v>
       </c>
       <c r="E151" t="n">
-        <v>303.1671142578125</v>
+        <v>310.149658203125</v>
       </c>
       <c r="F151" t="n">
-        <v>5190000</v>
+        <v>5571000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>302.7388065700545</v>
+        <v>311.7732461183575</v>
       </c>
       <c r="C152" t="n">
-        <v>308.5360036681458</v>
+        <v>315.4886379179251</v>
       </c>
       <c r="D152" t="n">
-        <v>301.155041869684</v>
+        <v>310.2990358004714</v>
       </c>
       <c r="E152" t="n">
-        <v>308.1774291992188</v>
+        <v>314.6718444824219</v>
       </c>
       <c r="F152" t="n">
-        <v>6787200</v>
+        <v>4831400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>307.2610301082847</v>
+        <v>315.1101522104624</v>
       </c>
       <c r="C153" t="n">
-        <v>310.8967187654788</v>
+        <v>316.7536793728972</v>
       </c>
       <c r="D153" t="n">
-        <v>306.2848600302058</v>
+        <v>313.3371296864953</v>
       </c>
       <c r="E153" t="n">
-        <v>310.149658203125</v>
+        <v>313.8650512695312</v>
       </c>
       <c r="F153" t="n">
-        <v>5571000</v>
+        <v>5695800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>311.7732461183575</v>
+        <v>315.3591594617635</v>
       </c>
       <c r="C154" t="n">
-        <v>315.4886379179251</v>
+        <v>318.1880250357548</v>
       </c>
       <c r="D154" t="n">
-        <v>310.2990358004714</v>
+        <v>313.9447114757824</v>
       </c>
       <c r="E154" t="n">
-        <v>314.6718444824219</v>
+        <v>315.7774963378906</v>
       </c>
       <c r="F154" t="n">
-        <v>4831400</v>
+        <v>8082300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>315.1101522104624</v>
+        <v>315.159944872979</v>
       </c>
       <c r="C155" t="n">
-        <v>316.7536793728972</v>
+        <v>316.305431661891</v>
       </c>
       <c r="D155" t="n">
-        <v>313.3371296864953</v>
+        <v>311.1258299735145</v>
       </c>
       <c r="E155" t="n">
-        <v>313.8650512695312</v>
+        <v>312.7095947265625</v>
       </c>
       <c r="F155" t="n">
-        <v>5695800</v>
+        <v>5506800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>315.3591594617635</v>
+        <v>312.7793059315876</v>
       </c>
       <c r="C156" t="n">
-        <v>318.1880250357548</v>
+        <v>315.6480231708821</v>
       </c>
       <c r="D156" t="n">
-        <v>313.9447114757824</v>
+        <v>307.6096447395195</v>
       </c>
       <c r="E156" t="n">
-        <v>315.7774963378906</v>
+        <v>308.7252502441406</v>
       </c>
       <c r="F156" t="n">
-        <v>8082300</v>
+        <v>6806900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>315.159944872979</v>
+        <v>309.7910754200902</v>
       </c>
       <c r="C157" t="n">
-        <v>316.305431661891</v>
+        <v>310.1396793547997</v>
       </c>
       <c r="D157" t="n">
-        <v>311.1258299735145</v>
+        <v>306.8526251277434</v>
       </c>
       <c r="E157" t="n">
-        <v>312.7095947265625</v>
+        <v>310.0699768066406</v>
       </c>
       <c r="F157" t="n">
-        <v>5506800</v>
+        <v>5666600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>312.7793059315876</v>
+        <v>309.2830795800573</v>
       </c>
       <c r="C158" t="n">
-        <v>315.6480231708821</v>
+        <v>310.9764290509568</v>
       </c>
       <c r="D158" t="n">
-        <v>307.6096447395195</v>
+        <v>303.8146058713554</v>
       </c>
       <c r="E158" t="n">
-        <v>308.7252502441406</v>
+        <v>307.66943359375</v>
       </c>
       <c r="F158" t="n">
-        <v>6806900</v>
+        <v>7275000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>309.7910754200902</v>
+        <v>305.8963913711518</v>
       </c>
       <c r="C159" t="n">
-        <v>310.1396793547997</v>
+        <v>308.7651086725988</v>
       </c>
       <c r="D159" t="n">
-        <v>306.8526251277434</v>
+        <v>303.3065754519026</v>
       </c>
       <c r="E159" t="n">
-        <v>310.0699768066406</v>
+        <v>308.2073059082031</v>
       </c>
       <c r="F159" t="n">
-        <v>5666600</v>
+        <v>5616900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>309.2830795800573</v>
+        <v>306.3048043469537</v>
       </c>
       <c r="C160" t="n">
-        <v>310.9764290509568</v>
+        <v>309.6018292319215</v>
       </c>
       <c r="D160" t="n">
-        <v>303.8146058713554</v>
+        <v>304.8604750852367</v>
       </c>
       <c r="E160" t="n">
-        <v>307.66943359375</v>
+        <v>308.4364013671875</v>
       </c>
       <c r="F160" t="n">
-        <v>7275000</v>
+        <v>6261500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>305.8963913711518</v>
+        <v>310.9763962887836</v>
       </c>
       <c r="C161" t="n">
-        <v>308.7651086725988</v>
+        <v>312.7294775914766</v>
       </c>
       <c r="D161" t="n">
-        <v>303.3065754519026</v>
+        <v>307.5299352956203</v>
       </c>
       <c r="E161" t="n">
-        <v>308.2073059082031</v>
+        <v>308.0877380371094</v>
       </c>
       <c r="F161" t="n">
-        <v>5616900</v>
+        <v>8839900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>306.3048043469537</v>
+        <v>335.0815497318694</v>
       </c>
       <c r="C162" t="n">
-        <v>309.6018292319215</v>
+        <v>340.6396971989305</v>
       </c>
       <c r="D162" t="n">
-        <v>304.8604750852367</v>
+        <v>332.4817936312549</v>
       </c>
       <c r="E162" t="n">
-        <v>308.4364013671875</v>
+        <v>333.5475769042969</v>
       </c>
       <c r="F162" t="n">
-        <v>6261500</v>
+        <v>16658600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>310.9763962887836</v>
+        <v>330.8183346281009</v>
       </c>
       <c r="C163" t="n">
-        <v>312.7294775914766</v>
+        <v>331.1968501776938</v>
       </c>
       <c r="D163" t="n">
-        <v>307.5299352956203</v>
+        <v>326.7941598769157</v>
       </c>
       <c r="E163" t="n">
-        <v>308.0877380371094</v>
+        <v>328.5472717285156</v>
       </c>
       <c r="F163" t="n">
-        <v>8839900</v>
+        <v>11241100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>335.0815497318694</v>
+        <v>331.5753827423343</v>
       </c>
       <c r="C164" t="n">
-        <v>340.6396971989305</v>
+        <v>334.5337439447337</v>
       </c>
       <c r="D164" t="n">
-        <v>332.4817936312549</v>
+        <v>326.6447706056774</v>
       </c>
       <c r="E164" t="n">
-        <v>333.5475769042969</v>
+        <v>326.744384765625</v>
       </c>
       <c r="F164" t="n">
-        <v>16658600</v>
+        <v>6726100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>330.8183346281009</v>
+        <v>326.7144870306598</v>
       </c>
       <c r="C165" t="n">
-        <v>331.1968501776938</v>
+        <v>328.4974800902166</v>
       </c>
       <c r="D165" t="n">
-        <v>326.7941598769157</v>
+        <v>324.1246709928955</v>
       </c>
       <c r="E165" t="n">
-        <v>328.5472717285156</v>
+        <v>325.5690002441406</v>
       </c>
       <c r="F165" t="n">
-        <v>11241100</v>
+        <v>6712400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>331.5753827423343</v>
+        <v>323.8357678318997</v>
       </c>
       <c r="C166" t="n">
-        <v>334.5337439447337</v>
+        <v>324.3039269566456</v>
       </c>
       <c r="D166" t="n">
-        <v>326.6447706056774</v>
+        <v>318.3971759556802</v>
       </c>
       <c r="E166" t="n">
-        <v>326.744384765625</v>
+        <v>320.7678527832031</v>
       </c>
       <c r="F166" t="n">
-        <v>6726100</v>
+        <v>5893200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>326.7144870306598</v>
+        <v>322.4811180854182</v>
       </c>
       <c r="C167" t="n">
-        <v>328.4974800902166</v>
+        <v>323.3078516694185</v>
       </c>
       <c r="D167" t="n">
-        <v>324.1246709928955</v>
+        <v>316.7536542120865</v>
       </c>
       <c r="E167" t="n">
-        <v>325.5690002441406</v>
+        <v>317.5505065917969</v>
       </c>
       <c r="F167" t="n">
-        <v>6712400</v>
+        <v>7808400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>323.8357678318997</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="C168" t="n">
-        <v>324.3039269566456</v>
+        <v>322.4213711748579</v>
       </c>
       <c r="D168" t="n">
-        <v>318.3971759556802</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="E168" t="n">
-        <v>320.7678527832031</v>
+        <v>320.0208129882812</v>
       </c>
       <c r="F168" t="n">
-        <v>5893200</v>
+        <v>7186100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>322.4811180854182</v>
+        <v>319.7319477733878</v>
       </c>
       <c r="C169" t="n">
-        <v>323.3078516694185</v>
+        <v>319.8116512556435</v>
       </c>
       <c r="D169" t="n">
-        <v>316.7536542120865</v>
+        <v>314.9208911627371</v>
       </c>
       <c r="E169" t="n">
-        <v>317.5505065917969</v>
+        <v>317.5405883789062</v>
       </c>
       <c r="F169" t="n">
-        <v>7808400</v>
+        <v>5950200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>318.2876422602183</v>
+        <v>317.8493444570379</v>
       </c>
       <c r="C170" t="n">
-        <v>322.4213711748579</v>
+        <v>323.9055014903766</v>
       </c>
       <c r="D170" t="n">
-        <v>318.2876422602183</v>
+        <v>316.7636201861749</v>
       </c>
       <c r="E170" t="n">
-        <v>320.0208129882812</v>
+        <v>322.5906677246094</v>
       </c>
       <c r="F170" t="n">
-        <v>7186100</v>
+        <v>9586200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>319.7319477733878</v>
+        <v>323.7186157532602</v>
       </c>
       <c r="C171" t="n">
-        <v>319.8116512556435</v>
+        <v>328.3001007904417</v>
       </c>
       <c r="D171" t="n">
-        <v>314.9208911627371</v>
+        <v>323.5988431448615</v>
       </c>
       <c r="E171" t="n">
-        <v>317.5405883789062</v>
+        <v>325.8147277832031</v>
       </c>
       <c r="F171" t="n">
-        <v>5950200</v>
+        <v>6235200</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>317.8493444570379</v>
+        <v>323.1895917984963</v>
       </c>
       <c r="C172" t="n">
-        <v>323.9055014903766</v>
+        <v>324.8165740981451</v>
       </c>
       <c r="D172" t="n">
-        <v>316.7636201861749</v>
+        <v>319.2069699014023</v>
       </c>
       <c r="E172" t="n">
-        <v>322.5906677246094</v>
+        <v>319.7160339355469</v>
       </c>
       <c r="F172" t="n">
-        <v>9586200</v>
+        <v>7950400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,25 +4915,25 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>323.7186157532602</v>
+        <v>320.7740745871976</v>
       </c>
       <c r="C173" t="n">
-        <v>328.3001007904417</v>
+        <v>322.7304316048222</v>
       </c>
       <c r="D173" t="n">
-        <v>323.5988431448615</v>
+        <v>319.6561562914121</v>
       </c>
       <c r="E173" t="n">
-        <v>325.8147277832031</v>
+        <v>321.9219360351562</v>
       </c>
       <c r="F173" t="n">
-        <v>6235200</v>
+        <v>5277400</v>
       </c>
       <c r="G173" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>323.1895917984963</v>
+        <v>323.3992105807512</v>
       </c>
       <c r="C174" t="n">
-        <v>324.8165740981451</v>
+        <v>328.3999303437295</v>
       </c>
       <c r="D174" t="n">
-        <v>319.2069699014023</v>
+        <v>323.2395036115653</v>
       </c>
       <c r="E174" t="n">
-        <v>319.7160339355469</v>
+        <v>325.1459655761719</v>
       </c>
       <c r="F174" t="n">
-        <v>7950400</v>
+        <v>6054500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>320.7740745871976</v>
+        <v>323.8283954010087</v>
       </c>
       <c r="C175" t="n">
-        <v>322.7304316048222</v>
+        <v>332.8117065140525</v>
       </c>
       <c r="D175" t="n">
-        <v>319.6561562914121</v>
+        <v>323.1696155974001</v>
       </c>
       <c r="E175" t="n">
-        <v>321.9219360351562</v>
+        <v>332.023193359375</v>
       </c>
       <c r="F175" t="n">
-        <v>5277400</v>
+        <v>5305800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>323.3992105807512</v>
+        <v>332.7118894931572</v>
       </c>
       <c r="C176" t="n">
-        <v>328.3999303437295</v>
+        <v>334.5485043686942</v>
       </c>
       <c r="D176" t="n">
-        <v>323.2395036115653</v>
+        <v>328.8790136983196</v>
       </c>
       <c r="E176" t="n">
-        <v>325.1459655761719</v>
+        <v>329.2982482910156</v>
       </c>
       <c r="F176" t="n">
-        <v>6054500</v>
+        <v>12858100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>323.8283954010087</v>
+        <v>329.4779084191791</v>
       </c>
       <c r="C177" t="n">
-        <v>332.8117065140525</v>
+        <v>331.0450044691208</v>
       </c>
       <c r="D177" t="n">
-        <v>323.1696155974001</v>
+        <v>326.2139829663294</v>
       </c>
       <c r="E177" t="n">
-        <v>332.023193359375</v>
+        <v>330.1366882324219</v>
       </c>
       <c r="F177" t="n">
-        <v>5305800</v>
+        <v>9422500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>332.7118894931572</v>
+        <v>329.2283866364193</v>
       </c>
       <c r="C178" t="n">
-        <v>334.5485043686942</v>
+        <v>331.9034099041888</v>
       </c>
       <c r="D178" t="n">
-        <v>328.8790136983196</v>
+        <v>326.6332016248708</v>
       </c>
       <c r="E178" t="n">
-        <v>329.2982482910156</v>
+        <v>330.5060119628906</v>
       </c>
       <c r="F178" t="n">
-        <v>12858100</v>
+        <v>7034500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>329.4779084191791</v>
+        <v>329.9071152744464</v>
       </c>
       <c r="C179" t="n">
-        <v>331.0450044691208</v>
+        <v>332.8117230001985</v>
       </c>
       <c r="D179" t="n">
-        <v>326.2139829663294</v>
+        <v>328.2102858122996</v>
       </c>
       <c r="E179" t="n">
-        <v>330.1366882324219</v>
+        <v>328.2701721191406</v>
       </c>
       <c r="F179" t="n">
-        <v>9422500</v>
+        <v>7462100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>329.2283866364193</v>
+        <v>325.8546513791287</v>
       </c>
       <c r="C180" t="n">
-        <v>331.9034099041888</v>
+        <v>327.890877227978</v>
       </c>
       <c r="D180" t="n">
-        <v>326.6332016248708</v>
+        <v>323.908285453</v>
       </c>
       <c r="E180" t="n">
-        <v>330.5060119628906</v>
+        <v>325.8746337890625</v>
       </c>
       <c r="F180" t="n">
-        <v>7034500</v>
+        <v>8705100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>329.9071152744464</v>
+        <v>325.2258042905605</v>
       </c>
       <c r="C181" t="n">
-        <v>332.8117230001985</v>
+        <v>330.8453695289686</v>
       </c>
       <c r="D181" t="n">
-        <v>328.2102858122996</v>
+        <v>325.0561365774909</v>
       </c>
       <c r="E181" t="n">
-        <v>328.2701721191406</v>
+        <v>327.0025024414062</v>
       </c>
       <c r="F181" t="n">
-        <v>7462100</v>
+        <v>5917400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>325.8546513791287</v>
+        <v>325.4054745838858</v>
       </c>
       <c r="C182" t="n">
-        <v>327.890877227978</v>
+        <v>326.473467283892</v>
       </c>
       <c r="D182" t="n">
-        <v>323.908285453</v>
+        <v>320.304934449476</v>
       </c>
       <c r="E182" t="n">
-        <v>325.8746337890625</v>
+        <v>324.3474426269531</v>
       </c>
       <c r="F182" t="n">
-        <v>8705100</v>
+        <v>8105400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>325.2258042905605</v>
+        <v>324.8964310814758</v>
       </c>
       <c r="C183" t="n">
-        <v>330.8453695289686</v>
+        <v>331.0550035619541</v>
       </c>
       <c r="D183" t="n">
-        <v>325.0561365774909</v>
+        <v>324.7467153160326</v>
       </c>
       <c r="E183" t="n">
-        <v>327.0025024414062</v>
+        <v>325.7548217773438</v>
       </c>
       <c r="F183" t="n">
-        <v>5917400</v>
+        <v>14104500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>325.4054745838858</v>
+        <v>326.6531732008884</v>
       </c>
       <c r="C184" t="n">
-        <v>326.473467283892</v>
+        <v>327.2520362551611</v>
       </c>
       <c r="D184" t="n">
-        <v>320.304934449476</v>
+        <v>318.0890659929148</v>
       </c>
       <c r="E184" t="n">
-        <v>324.3474426269531</v>
+        <v>322.1714782714844</v>
       </c>
       <c r="F184" t="n">
-        <v>8105400</v>
+        <v>10079300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>324.8964310814758</v>
+        <v>321.911976472278</v>
       </c>
       <c r="C185" t="n">
-        <v>331.0550035619541</v>
+        <v>322.900130958607</v>
       </c>
       <c r="D185" t="n">
-        <v>324.7467153160326</v>
+        <v>312.8088926463686</v>
       </c>
       <c r="E185" t="n">
-        <v>325.7548217773438</v>
+        <v>316.7315979003906</v>
       </c>
       <c r="F185" t="n">
-        <v>14104500</v>
+        <v>10125300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>326.6531732008884</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="C186" t="n">
-        <v>327.2520362551611</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="D186" t="n">
-        <v>318.0890659929148</v>
+        <v>308.4270199555073</v>
       </c>
       <c r="E186" t="n">
-        <v>322.1714782714844</v>
+        <v>311.8207092285156</v>
       </c>
       <c r="F186" t="n">
-        <v>10079300</v>
+        <v>8992800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>321.911976472278</v>
+        <v>316.2025752130079</v>
       </c>
       <c r="C187" t="n">
-        <v>322.900130958607</v>
+        <v>324.1577974184449</v>
       </c>
       <c r="D187" t="n">
-        <v>312.8088926463686</v>
+        <v>316.1127457580593</v>
       </c>
       <c r="E187" t="n">
-        <v>316.7315979003906</v>
+        <v>319.5862731933594</v>
       </c>
       <c r="F187" t="n">
-        <v>10125300</v>
+        <v>6981700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>317.0609741306723</v>
+        <v>321.8021573858913</v>
       </c>
       <c r="C188" t="n">
-        <v>317.0609741306723</v>
+        <v>325.3755359367605</v>
       </c>
       <c r="D188" t="n">
-        <v>308.4270199555073</v>
+        <v>320.3748163907789</v>
       </c>
       <c r="E188" t="n">
-        <v>311.8207092285156</v>
+        <v>322.9700012207031</v>
       </c>
       <c r="F188" t="n">
-        <v>8992800</v>
+        <v>7176300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>316.2025752130079</v>
+        <v>320.7541174065557</v>
       </c>
       <c r="C189" t="n">
-        <v>324.1577974184449</v>
+        <v>323.3193590911711</v>
       </c>
       <c r="D189" t="n">
-        <v>316.1127457580593</v>
+        <v>317.8395186449595</v>
       </c>
       <c r="E189" t="n">
-        <v>319.5862731933594</v>
+        <v>319.0772399902344</v>
       </c>
       <c r="F189" t="n">
-        <v>6981700</v>
+        <v>5582000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>321.8021573858913</v>
+        <v>318.0691001697331</v>
       </c>
       <c r="C190" t="n">
-        <v>325.3755359367605</v>
+        <v>324.8864216353897</v>
       </c>
       <c r="D190" t="n">
-        <v>320.3748163907789</v>
+        <v>316.4121747162161</v>
       </c>
       <c r="E190" t="n">
-        <v>322.9700012207031</v>
+        <v>324.4472351074219</v>
       </c>
       <c r="F190" t="n">
-        <v>7176300</v>
+        <v>6340400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>320.7541174065557</v>
+        <v>326.0143312805488</v>
       </c>
       <c r="C191" t="n">
-        <v>323.3193590911711</v>
+        <v>326.2938108474966</v>
       </c>
       <c r="D191" t="n">
-        <v>317.8395186449595</v>
+        <v>319.5862707797614</v>
       </c>
       <c r="E191" t="n">
-        <v>319.0772399902344</v>
+        <v>322.3611145019531</v>
       </c>
       <c r="F191" t="n">
-        <v>5582000</v>
+        <v>5793100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>318.0691001697331</v>
+        <v>321.4029160285921</v>
       </c>
       <c r="C192" t="n">
-        <v>324.8864216353897</v>
+        <v>323.1097366498532</v>
       </c>
       <c r="D192" t="n">
-        <v>316.4121747162161</v>
+        <v>317.3703988636284</v>
       </c>
       <c r="E192" t="n">
-        <v>324.4472351074219</v>
+        <v>318.4583740234375</v>
       </c>
       <c r="F192" t="n">
-        <v>6340400</v>
+        <v>5958900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>326.0143312805488</v>
+        <v>321.1633691478087</v>
       </c>
       <c r="C193" t="n">
-        <v>326.2938108474966</v>
+        <v>325.3256196452838</v>
       </c>
       <c r="D193" t="n">
-        <v>319.5862707797614</v>
+        <v>319.206981650181</v>
       </c>
       <c r="E193" t="n">
-        <v>322.3611145019531</v>
+        <v>321.7922058105469</v>
       </c>
       <c r="F193" t="n">
-        <v>5793100</v>
+        <v>5543200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>321.4029160285921</v>
+        <v>322.7603745094088</v>
       </c>
       <c r="C194" t="n">
-        <v>323.1097366498532</v>
+        <v>325.8346802814496</v>
       </c>
       <c r="D194" t="n">
-        <v>317.3703988636284</v>
+        <v>322.1515202620241</v>
       </c>
       <c r="E194" t="n">
-        <v>318.4583740234375</v>
+        <v>323.2195434570312</v>
       </c>
       <c r="F194" t="n">
-        <v>5958900</v>
+        <v>6803000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>321.1633691478087</v>
+        <v>325.0860736201939</v>
       </c>
       <c r="C195" t="n">
-        <v>325.3256196452838</v>
+        <v>332.6719869892291</v>
       </c>
       <c r="D195" t="n">
-        <v>319.206981650181</v>
+        <v>323.7785051975129</v>
       </c>
       <c r="E195" t="n">
-        <v>321.7922058105469</v>
+        <v>332.5022888183594</v>
       </c>
       <c r="F195" t="n">
-        <v>5543200</v>
+        <v>9248400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>322.7603745094088</v>
+        <v>332.8816048599044</v>
       </c>
       <c r="C196" t="n">
-        <v>325.8346802814496</v>
+        <v>336.1954560330155</v>
       </c>
       <c r="D196" t="n">
-        <v>322.1515202620241</v>
+        <v>329.3581516101117</v>
       </c>
       <c r="E196" t="n">
-        <v>323.2195434570312</v>
+        <v>329.7673950195312</v>
       </c>
       <c r="F196" t="n">
-        <v>6803000</v>
+        <v>6895200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>325.0860736201939</v>
+        <v>330.3862161708477</v>
       </c>
       <c r="C197" t="n">
-        <v>332.6719869892291</v>
+        <v>331.7137365067053</v>
       </c>
       <c r="D197" t="n">
-        <v>323.7785051975129</v>
+        <v>326.3936334980882</v>
       </c>
       <c r="E197" t="n">
-        <v>332.5022888183594</v>
+        <v>326.6331787109375</v>
       </c>
       <c r="F197" t="n">
-        <v>9248400</v>
+        <v>14716700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>332.8816048599044</v>
+        <v>327.7211572947962</v>
       </c>
       <c r="C198" t="n">
-        <v>336.1954560330155</v>
+        <v>332.3825110173034</v>
       </c>
       <c r="D198" t="n">
-        <v>329.3581516101117</v>
+        <v>325.255736249892</v>
       </c>
       <c r="E198" t="n">
-        <v>329.7673950195312</v>
+        <v>325.994384765625</v>
       </c>
       <c r="F198" t="n">
-        <v>6895200</v>
+        <v>15132400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>330.3862161708477</v>
+        <v>328.2102765273601</v>
       </c>
       <c r="C199" t="n">
-        <v>331.7137365067053</v>
+        <v>330.6657064213508</v>
       </c>
       <c r="D199" t="n">
-        <v>326.3936334980882</v>
+        <v>327.4816192000871</v>
       </c>
       <c r="E199" t="n">
-        <v>326.6331787109375</v>
+        <v>327.8709106445312</v>
       </c>
       <c r="F199" t="n">
-        <v>14716700</v>
+        <v>11113400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>327.7211572947962</v>
+        <v>328.3899311009871</v>
       </c>
       <c r="C200" t="n">
-        <v>332.3825110173034</v>
+        <v>334.1791639025663</v>
       </c>
       <c r="D200" t="n">
-        <v>325.255736249892</v>
+        <v>326.6132329961447</v>
       </c>
       <c r="E200" t="n">
-        <v>325.994384765625</v>
+        <v>331.6139526367188</v>
       </c>
       <c r="F200" t="n">
-        <v>15132400</v>
+        <v>8197200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>328.2102765273601</v>
+        <v>331.9433302412046</v>
       </c>
       <c r="C201" t="n">
-        <v>330.6657064213508</v>
+        <v>339.3096503518051</v>
       </c>
       <c r="D201" t="n">
-        <v>327.4816192000871</v>
+        <v>329.457957205559</v>
       </c>
       <c r="E201" t="n">
-        <v>327.8709106445312</v>
+        <v>329.9071044921875</v>
       </c>
       <c r="F201" t="n">
-        <v>11113400</v>
+        <v>7050200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>328.3899311009871</v>
+        <v>331.6239148421282</v>
       </c>
       <c r="C202" t="n">
-        <v>334.1791639025663</v>
+        <v>339.0900555815327</v>
       </c>
       <c r="D202" t="n">
-        <v>326.6132329961447</v>
+        <v>330.8254104732138</v>
       </c>
       <c r="E202" t="n">
-        <v>331.6139526367188</v>
+        <v>335.6065368652344</v>
       </c>
       <c r="F202" t="n">
-        <v>8197200</v>
+        <v>16717400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>331.9433302412046</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="C203" t="n">
-        <v>339.3096503518051</v>
+        <v>345.168769346924</v>
       </c>
       <c r="D203" t="n">
-        <v>329.457957205559</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="E203" t="n">
-        <v>329.9071044921875</v>
+        <v>341.0164794921875</v>
       </c>
       <c r="F203" t="n">
-        <v>7050200</v>
+        <v>11710900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>331.6239148421282</v>
+        <v>341.1262760402287</v>
       </c>
       <c r="C204" t="n">
-        <v>339.0900555815327</v>
+        <v>343.6515833825353</v>
       </c>
       <c r="D204" t="n">
-        <v>330.8254104732138</v>
+        <v>338.4512224777037</v>
       </c>
       <c r="E204" t="n">
-        <v>335.6065368652344</v>
+        <v>342.4537963867188</v>
       </c>
       <c r="F204" t="n">
-        <v>16717400</v>
+        <v>7957900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>337.6427420814022</v>
+        <v>343.9210864742992</v>
       </c>
       <c r="C205" t="n">
-        <v>345.168769346924</v>
+        <v>352.7047566164018</v>
       </c>
       <c r="D205" t="n">
-        <v>337.6427420814022</v>
+        <v>340.3477382034001</v>
       </c>
       <c r="E205" t="n">
-        <v>341.0164794921875</v>
+        <v>350.4289855957031</v>
       </c>
       <c r="F205" t="n">
-        <v>11710900</v>
+        <v>13025900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>341.1262760402287</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="C206" t="n">
-        <v>343.6515833825353</v>
+        <v>361.45849609375</v>
       </c>
       <c r="D206" t="n">
-        <v>338.4512224777037</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="E206" t="n">
-        <v>342.4537963867188</v>
+        <v>361.45849609375</v>
       </c>
       <c r="F206" t="n">
-        <v>7957900</v>
+        <v>9814800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>343.9210864742992</v>
+        <v>362.3268927646901</v>
       </c>
       <c r="C207" t="n">
-        <v>352.7047566164018</v>
+        <v>364.3431361331269</v>
       </c>
       <c r="D207" t="n">
-        <v>340.3477382034001</v>
+        <v>348.2031370590358</v>
       </c>
       <c r="E207" t="n">
-        <v>350.4289855957031</v>
+        <v>356.5875549316406</v>
       </c>
       <c r="F207" t="n">
-        <v>13025900</v>
+        <v>11623800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>351.8563396289383</v>
+        <v>347.744003265132</v>
       </c>
       <c r="C208" t="n">
-        <v>361.45849609375</v>
+        <v>355.4197158554798</v>
       </c>
       <c r="D208" t="n">
-        <v>351.8563396289383</v>
+        <v>346.2767278330053</v>
       </c>
       <c r="E208" t="n">
-        <v>361.45849609375</v>
+        <v>351.5469360351562</v>
       </c>
       <c r="F208" t="n">
-        <v>9814800</v>
+        <v>7332500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>362.3268927646901</v>
+        <v>349.650411586948</v>
       </c>
       <c r="C209" t="n">
-        <v>364.3431361331269</v>
+        <v>350.9480192181019</v>
       </c>
       <c r="D209" t="n">
-        <v>348.2031370590358</v>
+        <v>345.0489747278172</v>
       </c>
       <c r="E209" t="n">
-        <v>356.5875549316406</v>
+        <v>346.8855590820312</v>
       </c>
       <c r="F209" t="n">
-        <v>11623800</v>
+        <v>10215200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>347.744003265132</v>
+        <v>344.6597048505295</v>
       </c>
       <c r="C210" t="n">
-        <v>355.4197158554798</v>
+        <v>347.8537833381742</v>
       </c>
       <c r="D210" t="n">
-        <v>346.2767278330053</v>
+        <v>343.7813622043677</v>
       </c>
       <c r="E210" t="n">
-        <v>351.5469360351562</v>
+        <v>347.5543518066406</v>
       </c>
       <c r="F210" t="n">
-        <v>7332500</v>
+        <v>6606300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>349.650411586948</v>
+        <v>349.9798320131086</v>
       </c>
       <c r="C211" t="n">
-        <v>350.9480192181019</v>
+        <v>350.5188392207221</v>
       </c>
       <c r="D211" t="n">
-        <v>345.0489747278172</v>
+        <v>344.6896415212494</v>
       </c>
       <c r="E211" t="n">
-        <v>346.8855590820312</v>
+        <v>348.3229064941406</v>
       </c>
       <c r="F211" t="n">
-        <v>10215200</v>
+        <v>4702800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>344.6597048505295</v>
+        <v>351.0777829959364</v>
       </c>
       <c r="C212" t="n">
-        <v>347.8537833381742</v>
+        <v>358.8233725828445</v>
       </c>
       <c r="D212" t="n">
-        <v>343.7813622043677</v>
+        <v>350.3990207986449</v>
       </c>
       <c r="E212" t="n">
-        <v>347.5543518066406</v>
+        <v>357.0866088867188</v>
       </c>
       <c r="F212" t="n">
-        <v>6606300</v>
+        <v>9964600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>349.9798320131086</v>
+        <v>355.1102963305153</v>
       </c>
       <c r="C213" t="n">
-        <v>350.5188392207221</v>
+        <v>359.2725774384029</v>
       </c>
       <c r="D213" t="n">
-        <v>344.6896415212494</v>
+        <v>353.0241754046451</v>
       </c>
       <c r="E213" t="n">
-        <v>348.3229064941406</v>
+        <v>355.3598327636719</v>
       </c>
       <c r="F213" t="n">
-        <v>4702800</v>
+        <v>6632400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>351.0777829959364</v>
+        <v>353.3435751194357</v>
       </c>
       <c r="C214" t="n">
-        <v>358.8233725828445</v>
+        <v>359.7616446111089</v>
       </c>
       <c r="D214" t="n">
-        <v>350.3990207986449</v>
+        <v>348.4726192666298</v>
       </c>
       <c r="E214" t="n">
-        <v>357.0866088867188</v>
+        <v>354.4814758300781</v>
       </c>
       <c r="F214" t="n">
-        <v>9964600</v>
+        <v>8850000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>355.1102963305153</v>
+        <v>357.3760808599296</v>
       </c>
       <c r="C215" t="n">
-        <v>359.2725774384029</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="D215" t="n">
-        <v>353.0241754046451</v>
+        <v>356.4477822451955</v>
       </c>
       <c r="E215" t="n">
-        <v>355.3598327636719</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="F215" t="n">
-        <v>6632400</v>
+        <v>9073200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>353.3435751194357</v>
+        <v>362.8958306673428</v>
       </c>
       <c r="C216" t="n">
-        <v>359.7616446111089</v>
+        <v>363.9538626468295</v>
       </c>
       <c r="D216" t="n">
-        <v>348.4726192666298</v>
+        <v>356.3380062665893</v>
       </c>
       <c r="E216" t="n">
-        <v>354.4814758300781</v>
+        <v>357.8951110839844</v>
       </c>
       <c r="F216" t="n">
-        <v>8850000</v>
+        <v>7400400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>357.3760808599296</v>
+        <v>356.4378309524324</v>
       </c>
       <c r="C217" t="n">
-        <v>364.4629211425781</v>
+        <v>362.3268844140721</v>
       </c>
       <c r="D217" t="n">
-        <v>356.4477822451955</v>
+        <v>355.7690599392462</v>
       </c>
       <c r="E217" t="n">
-        <v>364.4629211425781</v>
+        <v>359.9013977050781</v>
       </c>
       <c r="F217" t="n">
-        <v>9073200</v>
+        <v>7616800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>362.8958306673428</v>
+        <v>356.3280307190208</v>
       </c>
       <c r="C218" t="n">
-        <v>363.9538626468295</v>
+        <v>358.4540859756855</v>
       </c>
       <c r="D218" t="n">
-        <v>356.3380062665893</v>
+        <v>354.0323077481659</v>
       </c>
       <c r="E218" t="n">
-        <v>357.8951110839844</v>
+        <v>355.1602172851562</v>
       </c>
       <c r="F218" t="n">
-        <v>7400400</v>
+        <v>6027300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>356.4378309524324</v>
+        <v>355.9088319271366</v>
       </c>
       <c r="C219" t="n">
-        <v>362.3268844140721</v>
+        <v>356.8670433033565</v>
       </c>
       <c r="D219" t="n">
-        <v>355.7690599392462</v>
+        <v>351.6167869913984</v>
       </c>
       <c r="E219" t="n">
-        <v>359.9013977050781</v>
+        <v>352.7646789550781</v>
       </c>
       <c r="F219" t="n">
-        <v>7616800</v>
+        <v>4622200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>356.3280307190208</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="C220" t="n">
-        <v>358.4540859756855</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="D220" t="n">
-        <v>354.0323077481659</v>
+        <v>347.8537708520506</v>
       </c>
       <c r="E220" t="n">
-        <v>355.1602172851562</v>
+        <v>350.9480285644531</v>
       </c>
       <c r="F220" t="n">
-        <v>6027300</v>
+        <v>4183300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>355.9088319271366</v>
+        <v>352.8145729386106</v>
       </c>
       <c r="C221" t="n">
-        <v>356.8670433033565</v>
+        <v>355.1801734485531</v>
       </c>
       <c r="D221" t="n">
-        <v>351.6167869913984</v>
+        <v>350.3990468654978</v>
       </c>
       <c r="E221" t="n">
-        <v>352.7646789550781</v>
+        <v>355.0803527832031</v>
       </c>
       <c r="F221" t="n">
-        <v>4622200</v>
+        <v>4482800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>351.3971758456315</v>
+        <v>358.6836615690858</v>
       </c>
       <c r="C222" t="n">
-        <v>351.3971758456315</v>
+        <v>362.9856670774005</v>
       </c>
       <c r="D222" t="n">
-        <v>347.8537708520506</v>
+        <v>357.5856952124533</v>
       </c>
       <c r="E222" t="n">
-        <v>350.9480285644531</v>
+        <v>361.8577575683594</v>
       </c>
       <c r="F222" t="n">
-        <v>4183300</v>
+        <v>6631100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>352.8145729386106</v>
+        <v>364.3830556294341</v>
       </c>
       <c r="C223" t="n">
-        <v>355.1801734485531</v>
+        <v>370.4717503048907</v>
       </c>
       <c r="D223" t="n">
-        <v>350.3990468654978</v>
+        <v>362.057389622598</v>
       </c>
       <c r="E223" t="n">
-        <v>355.0803527832031</v>
+        <v>365.9102172851562</v>
       </c>
       <c r="F223" t="n">
-        <v>4482800</v>
+        <v>11061900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>358.6836615690858</v>
+        <v>356.3380049484608</v>
       </c>
       <c r="C224" t="n">
-        <v>362.9856670774005</v>
+        <v>373.2765382228537</v>
       </c>
       <c r="D224" t="n">
-        <v>357.5856952124533</v>
+        <v>354.8208344927874</v>
       </c>
       <c r="E224" t="n">
-        <v>361.8577575683594</v>
+        <v>368.0462646484375</v>
       </c>
       <c r="F224" t="n">
-        <v>6631100</v>
+        <v>11289900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>364.3830556294341</v>
+        <v>364.3231862195555</v>
       </c>
       <c r="C225" t="n">
-        <v>370.4717503048907</v>
+        <v>366.3194776508955</v>
       </c>
       <c r="D225" t="n">
-        <v>362.057389622598</v>
+        <v>360.0810669279579</v>
       </c>
       <c r="E225" t="n">
-        <v>365.9102172851562</v>
+        <v>365.5908203125</v>
       </c>
       <c r="F225" t="n">
-        <v>11061900</v>
+        <v>8391400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>356.3380049484608</v>
+        <v>363.0854799497644</v>
       </c>
       <c r="C226" t="n">
-        <v>373.2765382228537</v>
+        <v>366.199689577411</v>
       </c>
       <c r="D226" t="n">
-        <v>354.8208344927874</v>
+        <v>359.4322631293363</v>
       </c>
       <c r="E226" t="n">
-        <v>368.0462646484375</v>
+        <v>365.4510803222656</v>
       </c>
       <c r="F226" t="n">
-        <v>11289900</v>
+        <v>7828400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>364.3231862195555</v>
+        <v>367.8166822243689</v>
       </c>
       <c r="C227" t="n">
-        <v>366.3194776508955</v>
+        <v>371.2802489443513</v>
       </c>
       <c r="D227" t="n">
-        <v>360.0810669279579</v>
+        <v>363.6743837542027</v>
       </c>
       <c r="E227" t="n">
-        <v>365.5908203125</v>
+        <v>364.991943359375</v>
       </c>
       <c r="F227" t="n">
-        <v>8391400</v>
+        <v>5521300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>363.0854799497644</v>
+        <v>361.0891957111975</v>
       </c>
       <c r="C228" t="n">
-        <v>366.199689577411</v>
+        <v>370.4218335736103</v>
       </c>
       <c r="D228" t="n">
-        <v>359.4322631293363</v>
+        <v>359.4222790007568</v>
       </c>
       <c r="E228" t="n">
-        <v>365.4510803222656</v>
+        <v>368.9046630859375</v>
       </c>
       <c r="F228" t="n">
-        <v>7828400</v>
+        <v>7497500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>367.8166822243689</v>
+        <v>371.6096355733356</v>
       </c>
       <c r="C229" t="n">
-        <v>371.2802489443513</v>
+        <v>371.7094562365133</v>
       </c>
       <c r="D229" t="n">
-        <v>363.6743837542027</v>
+        <v>366.0399959154992</v>
       </c>
       <c r="E229" t="n">
-        <v>364.991943359375</v>
+        <v>367.8566284179688</v>
       </c>
       <c r="F229" t="n">
-        <v>5521300</v>
+        <v>6065300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>361.0891957111975</v>
+        <v>368.8847254705448</v>
       </c>
       <c r="C230" t="n">
-        <v>370.4218335736103</v>
+        <v>370.4118872220017</v>
       </c>
       <c r="D230" t="n">
-        <v>359.4222790007568</v>
+        <v>364.5727285978463</v>
       </c>
       <c r="E230" t="n">
-        <v>368.9046630859375</v>
+        <v>369.7830505371094</v>
       </c>
       <c r="F230" t="n">
-        <v>7497500</v>
+        <v>5022300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>371.6096355733356</v>
+        <v>367.8266852879935</v>
       </c>
       <c r="C231" t="n">
-        <v>371.7094562365133</v>
+        <v>369.5634490756331</v>
       </c>
       <c r="D231" t="n">
-        <v>366.0399959154992</v>
+        <v>360.8496260625997</v>
       </c>
       <c r="E231" t="n">
-        <v>367.8566284179688</v>
+        <v>361.8278198242188</v>
       </c>
       <c r="F231" t="n">
-        <v>6065300</v>
+        <v>5112500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>368.8847254705448</v>
+        <v>361.3287562034755</v>
       </c>
       <c r="C232" t="n">
-        <v>370.4118872220017</v>
+        <v>363.4947458520614</v>
       </c>
       <c r="D232" t="n">
-        <v>364.5727285978463</v>
+        <v>358.2045551780129</v>
       </c>
       <c r="E232" t="n">
-        <v>369.7830505371094</v>
+        <v>360.6500244140625</v>
       </c>
       <c r="F232" t="n">
-        <v>5022300</v>
+        <v>7552200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,25 +6475,25 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>367.8266852879935</v>
+        <v>360.9800109863281</v>
       </c>
       <c r="C233" t="n">
-        <v>369.5634490756331</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="D233" t="n">
-        <v>360.8496260625997</v>
+        <v>359.9700012207031</v>
       </c>
       <c r="E233" t="n">
-        <v>361.8278198242188</v>
+        <v>362.8200073242188</v>
       </c>
       <c r="F233" t="n">
-        <v>5112500</v>
+        <v>4440900</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>361.3287562034755</v>
+        <v>361</v>
       </c>
       <c r="C234" t="n">
-        <v>363.4947458520614</v>
+        <v>363.3500061035156</v>
       </c>
       <c r="D234" t="n">
-        <v>358.2045551780129</v>
+        <v>358.3099975585938</v>
       </c>
       <c r="E234" t="n">
-        <v>360.6500244140625</v>
+        <v>359.4200134277344</v>
       </c>
       <c r="F234" t="n">
-        <v>7552200</v>
+        <v>3794200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,25 +6527,25 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>360.9800109863281</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="C235" t="n">
-        <v>364.5499877929688</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="D235" t="n">
-        <v>359.9700012207031</v>
+        <v>358.7099914550781</v>
       </c>
       <c r="E235" t="n">
-        <v>362.8200073242188</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="F235" t="n">
-        <v>4440900</v>
+        <v>8142600</v>
       </c>
       <c r="G235" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>361</v>
+        <v>365.8900146484375</v>
       </c>
       <c r="C236" t="n">
-        <v>363.3500061035156</v>
+        <v>366.7999877929688</v>
       </c>
       <c r="D236" t="n">
-        <v>358.3099975585938</v>
+        <v>362.760009765625</v>
       </c>
       <c r="E236" t="n">
-        <v>359.4200134277344</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="F236" t="n">
-        <v>3794200</v>
+        <v>8106900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>363.7000122070312</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="C237" t="n">
-        <v>365.4500122070312</v>
+        <v>363.5599975585938</v>
       </c>
       <c r="D237" t="n">
-        <v>358.7099914550781</v>
+        <v>358.5199890136719</v>
       </c>
       <c r="E237" t="n">
-        <v>365.4500122070312</v>
+        <v>358.8399963378906</v>
       </c>
       <c r="F237" t="n">
-        <v>8142600</v>
+        <v>15543400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>365.8900146484375</v>
+        <v>359.6199951171875</v>
       </c>
       <c r="C238" t="n">
-        <v>366.7999877929688</v>
+        <v>365.9100036621094</v>
       </c>
       <c r="D238" t="n">
-        <v>362.760009765625</v>
+        <v>358.0499877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>364.1499938964844</v>
+        <v>364.25</v>
       </c>
       <c r="F238" t="n">
-        <v>8106900</v>
+        <v>6820300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>362.8399963378906</v>
+        <v>364.0899963378906</v>
       </c>
       <c r="C239" t="n">
-        <v>363.5599975585938</v>
+        <v>370.6400146484375</v>
       </c>
       <c r="D239" t="n">
-        <v>358.5199890136719</v>
+        <v>362.8999938964844</v>
       </c>
       <c r="E239" t="n">
-        <v>358.8399963378906</v>
+        <v>365.5400085449219</v>
       </c>
       <c r="F239" t="n">
-        <v>15543400</v>
+        <v>5866400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>359.6199951171875</v>
+        <v>365.1000061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>365.9100036621094</v>
+        <v>368.9299926757812</v>
       </c>
       <c r="D240" t="n">
-        <v>358.0499877929688</v>
+        <v>363.6300048828125</v>
       </c>
       <c r="E240" t="n">
-        <v>364.25</v>
+        <v>365.7300109863281</v>
       </c>
       <c r="F240" t="n">
-        <v>6820300</v>
+        <v>6151500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>364.0899963378906</v>
+        <v>367.8699951171875</v>
       </c>
       <c r="C241" t="n">
-        <v>370.6400146484375</v>
+        <v>371.7999877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>362.8999938964844</v>
+        <v>366.6600036621094</v>
       </c>
       <c r="E241" t="n">
-        <v>365.5400085449219</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F241" t="n">
-        <v>5866400</v>
+        <v>6667100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>365.1000061035156</v>
+        <v>373.260009765625</v>
       </c>
       <c r="C242" t="n">
-        <v>368.9299926757812</v>
+        <v>383.4299926757812</v>
       </c>
       <c r="D242" t="n">
-        <v>363.6300048828125</v>
+        <v>372.2099914550781</v>
       </c>
       <c r="E242" t="n">
-        <v>365.7300109863281</v>
+        <v>382.4100036621094</v>
       </c>
       <c r="F242" t="n">
-        <v>6151500</v>
+        <v>8477500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>367.8699951171875</v>
+        <v>381.2099914550781</v>
       </c>
       <c r="C243" t="n">
-        <v>371.7999877929688</v>
+        <v>384.2000122070312</v>
       </c>
       <c r="D243" t="n">
-        <v>366.6600036621094</v>
+        <v>380.2699890136719</v>
       </c>
       <c r="E243" t="n">
-        <v>371.0400085449219</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="F243" t="n">
-        <v>6667100</v>
+        <v>6777600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>373.260009765625</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>383.4299926757812</v>
+        <v>385.5700073242188</v>
       </c>
       <c r="D244" t="n">
-        <v>372.2099914550781</v>
+        <v>381.0799865722656</v>
       </c>
       <c r="E244" t="n">
-        <v>382.4100036621094</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F244" t="n">
-        <v>8477500</v>
+        <v>6075100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>381.2099914550781</v>
+        <v>381.1400146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>384.2000122070312</v>
+        <v>381.7699890136719</v>
       </c>
       <c r="D245" t="n">
-        <v>380.2699890136719</v>
+        <v>378.5</v>
       </c>
       <c r="E245" t="n">
-        <v>384.1400146484375</v>
+        <v>379.6600036621094</v>
       </c>
       <c r="F245" t="n">
-        <v>6777600</v>
+        <v>6641500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>384.1400146484375</v>
+        <v>380.2999877929688</v>
       </c>
       <c r="C246" t="n">
-        <v>385.5700073242188</v>
+        <v>383.6799926757812</v>
       </c>
       <c r="D246" t="n">
-        <v>381.0799865722656</v>
+        <v>379.0299987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>383.8999938964844</v>
+        <v>381.6000061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>6075100</v>
+        <v>4643000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>381.1400146484375</v>
+        <v>381.3500061035156</v>
       </c>
       <c r="C247" t="n">
-        <v>381.7699890136719</v>
+        <v>382.4800109863281</v>
       </c>
       <c r="D247" t="n">
-        <v>378.5</v>
+        <v>378.7999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>379.6600036621094</v>
+        <v>379.3699951171875</v>
       </c>
       <c r="F247" t="n">
-        <v>6641500</v>
+        <v>6744800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>380.2999877929688</v>
+        <v>379.6499938964844</v>
       </c>
       <c r="C248" t="n">
-        <v>383.6799926757812</v>
+        <v>380.75</v>
       </c>
       <c r="D248" t="n">
-        <v>379.0299987792969</v>
+        <v>372.2200012207031</v>
       </c>
       <c r="E248" t="n">
-        <v>381.6000061035156</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F248" t="n">
-        <v>4643000</v>
+        <v>5857400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>381.3500061035156</v>
+        <v>374.010009765625</v>
       </c>
       <c r="C249" t="n">
-        <v>382.4800109863281</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="D249" t="n">
-        <v>378.7999877929688</v>
+        <v>374.010009765625</v>
       </c>
       <c r="E249" t="n">
-        <v>379.3699951171875</v>
+        <v>378.3999938964844</v>
       </c>
       <c r="F249" t="n">
-        <v>6744800</v>
+        <v>5599900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>379.6499938964844</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="C250" t="n">
-        <v>380.75</v>
+        <v>382.2099914550781</v>
       </c>
       <c r="D250" t="n">
-        <v>372.2200012207031</v>
+        <v>376.8599853515625</v>
       </c>
       <c r="E250" t="n">
-        <v>372.6700134277344</v>
+        <v>378.75</v>
       </c>
       <c r="F250" t="n">
-        <v>5857400</v>
+        <v>3869500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>374.010009765625</v>
+        <v>374.8900146484375</v>
       </c>
       <c r="C251" t="n">
-        <v>380.1700134277344</v>
+        <v>377.5</v>
       </c>
       <c r="D251" t="n">
-        <v>374.010009765625</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="E251" t="n">
-        <v>378.3999938964844</v>
+        <v>375.0700073242188</v>
       </c>
       <c r="F251" t="n">
-        <v>5599900</v>
+        <v>4645100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>380.1700134277344</v>
-      </c>
-      <c r="C252" t="n">
-        <v>382.2099914550781</v>
-      </c>
-      <c r="D252" t="n">
-        <v>376.8599853515625</v>
-      </c>
-      <c r="E252" t="n">
-        <v>378.75</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>3869500</v>
+        <v>4909005</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>374.8900146484375</v>
-      </c>
-      <c r="C253" t="n">
-        <v>377.5</v>
-      </c>
-      <c r="D253" t="n">
-        <v>373.6400146484375</v>
-      </c>
-      <c r="E253" t="n">
-        <v>375.0700073242188</v>
-      </c>
-      <c r="F253" t="n">
-        <v>4645100</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10682,34 +10648,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="D2" t="n">
         <v>375.07</v>
       </c>
-      <c r="D2" t="n">
-        <v>378.75</v>
-      </c>
       <c r="E2" t="n">
-        <v>374.89</v>
+        <v>371.6</v>
       </c>
       <c r="F2" t="n">
-        <v>377.5</v>
+        <v>373.5</v>
       </c>
       <c r="G2" t="n">
-        <v>373.64</v>
+        <v>367.44</v>
       </c>
       <c r="H2" t="n">
-        <v>4613280</v>
+        <v>4909005</v>
       </c>
       <c r="I2" t="n">
-        <v>7678938</v>
+        <v>7712759</v>
       </c>
       <c r="J2" t="n">
-        <v>700273459200</v>
+        <v>688268312576</v>
       </c>
       <c r="K2" t="n">
-        <v>31.948042</v>
+        <v>31.400343</v>
       </c>
       <c r="L2" t="n">
-        <v>24.997501</v>
+        <v>24.568958</v>
       </c>
       <c r="M2" t="n">
         <v>11.74</v>
@@ -10748,7 +10714,7 @@
         <v>18.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.876524</v>
+        <v>19.53577</v>
       </c>
       <c r="Z2" t="n">
         <v>0.102</v>
@@ -10760,7 +10726,7 @@
         <v>44487999488</v>
       </c>
       <c r="AC2" t="n">
-        <v>699948269568</v>
+        <v>688130162688</v>
       </c>
       <c r="AD2" t="n">
         <v>31093999616</v>
@@ -10787,7 +10753,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:17</t>
+          <t>2026-09-09 09:15:14</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>338.9790027080578</v>
+        <v>339.8916830924824</v>
       </c>
       <c r="C2" t="n">
-        <v>343.572272708629</v>
+        <v>339.8916830924824</v>
       </c>
       <c r="D2" t="n">
-        <v>338.5821823997351</v>
+        <v>333.7706534504743</v>
       </c>
       <c r="E2" t="n">
-        <v>341.2607421875</v>
+        <v>335.4373168945312</v>
       </c>
       <c r="F2" t="n">
-        <v>4646200</v>
+        <v>6557900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>339.8916521696528</v>
+        <v>336.0424662373603</v>
       </c>
       <c r="C3" t="n">
-        <v>339.8916521696528</v>
+        <v>340.8043700650184</v>
       </c>
       <c r="D3" t="n">
-        <v>333.7706230845267</v>
+        <v>335.1892738885992</v>
       </c>
       <c r="E3" t="n">
-        <v>335.4372863769531</v>
+        <v>340.7646789550781</v>
       </c>
       <c r="F3" t="n">
-        <v>6557900</v>
+        <v>5157600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>336.0424963320352</v>
+        <v>338.5127143274361</v>
       </c>
       <c r="C4" t="n">
-        <v>340.8044005861511</v>
+        <v>340.467085284774</v>
       </c>
       <c r="D4" t="n">
-        <v>335.1893039068655</v>
+        <v>336.4789914224089</v>
       </c>
       <c r="E4" t="n">
-        <v>340.7647094726562</v>
+        <v>336.7369079589844</v>
       </c>
       <c r="F4" t="n">
-        <v>5157600</v>
+        <v>3518300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>338.5127143274361</v>
+        <v>337.907514008316</v>
       </c>
       <c r="C5" t="n">
-        <v>340.467085284774</v>
+        <v>339.9908582212252</v>
       </c>
       <c r="D5" t="n">
-        <v>336.4789914224089</v>
+        <v>335.7051570201907</v>
       </c>
       <c r="E5" t="n">
-        <v>336.7369079589844</v>
+        <v>336.3598937988281</v>
       </c>
       <c r="F5" t="n">
-        <v>3518300</v>
+        <v>4367500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>337.907514008316</v>
+        <v>333.5722152320537</v>
       </c>
       <c r="C6" t="n">
-        <v>339.9908582212252</v>
+        <v>337.8381165972889</v>
       </c>
       <c r="D6" t="n">
-        <v>335.7051570201907</v>
+        <v>330.8242036977477</v>
       </c>
       <c r="E6" t="n">
-        <v>336.3598937988281</v>
+        <v>337.3321533203125</v>
       </c>
       <c r="F6" t="n">
-        <v>4367500</v>
+        <v>5527700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>333.5722454094798</v>
+        <v>337.2429044796542</v>
       </c>
       <c r="C7" t="n">
-        <v>337.8381471606402</v>
+        <v>343.4532470703125</v>
       </c>
       <c r="D7" t="n">
-        <v>330.8242336265683</v>
+        <v>336.8262234557313</v>
       </c>
       <c r="E7" t="n">
-        <v>337.3321838378906</v>
+        <v>343.4532470703125</v>
       </c>
       <c r="F7" t="n">
-        <v>5527700</v>
+        <v>5763500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>337.2428445481393</v>
+        <v>341.9948446289807</v>
       </c>
       <c r="C8" t="n">
-        <v>343.4531860351562</v>
+        <v>342.5305383477728</v>
       </c>
       <c r="D8" t="n">
-        <v>336.826163598265</v>
+        <v>335.4967956542969</v>
       </c>
       <c r="E8" t="n">
-        <v>343.4531860351562</v>
+        <v>335.4967956542969</v>
       </c>
       <c r="F8" t="n">
-        <v>5763500</v>
+        <v>7526600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>341.9949068462926</v>
+        <v>337.7488274356299</v>
       </c>
       <c r="C9" t="n">
-        <v>342.5306006625406</v>
+        <v>339.9710452297281</v>
       </c>
       <c r="D9" t="n">
-        <v>335.4968566894531</v>
+        <v>335.5662704768214</v>
       </c>
       <c r="E9" t="n">
-        <v>335.4968566894531</v>
+        <v>338.8995971679688</v>
       </c>
       <c r="F9" t="n">
-        <v>7526600</v>
+        <v>13674300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>337.7488274356299</v>
+        <v>336.3202190485207</v>
       </c>
       <c r="C10" t="n">
-        <v>339.9710452297281</v>
+        <v>342.1237794562243</v>
       </c>
       <c r="D10" t="n">
-        <v>335.5662704768214</v>
+        <v>335.9729899814968</v>
       </c>
       <c r="E10" t="n">
-        <v>338.8995971679688</v>
+        <v>341.6277465820312</v>
       </c>
       <c r="F10" t="n">
-        <v>13674300</v>
+        <v>5621800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>336.3202791354349</v>
+        <v>341.8559781228954</v>
       </c>
       <c r="C11" t="n">
-        <v>342.1238405800017</v>
+        <v>342.5206755840167</v>
       </c>
       <c r="D11" t="n">
-        <v>335.9730500063751</v>
+        <v>334.9512080718528</v>
       </c>
       <c r="E11" t="n">
-        <v>341.6278076171875</v>
+        <v>336.0127258300781</v>
       </c>
       <c r="F11" t="n">
-        <v>5621800</v>
+        <v>10142700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>341.8559781228954</v>
+        <v>336.4393311929394</v>
       </c>
       <c r="C12" t="n">
-        <v>342.5206755840167</v>
+        <v>337.2032110769243</v>
       </c>
       <c r="D12" t="n">
-        <v>334.9512080718528</v>
+        <v>335.2389398679774</v>
       </c>
       <c r="E12" t="n">
-        <v>336.0127258300781</v>
+        <v>335.9928894042969</v>
       </c>
       <c r="F12" t="n">
-        <v>10142700</v>
+        <v>5207400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>336.4393006348119</v>
+        <v>335.6655229404874</v>
       </c>
       <c r="C13" t="n">
-        <v>337.2031804494151</v>
+        <v>337.5008510178562</v>
       </c>
       <c r="D13" t="n">
-        <v>335.2389094188791</v>
+        <v>331.8559932948658</v>
       </c>
       <c r="E13" t="n">
-        <v>335.9928588867188</v>
+        <v>332.2726440429688</v>
       </c>
       <c r="F13" t="n">
-        <v>5207400</v>
+        <v>5398700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>335.6654921112904</v>
+        <v>334.5543943395058</v>
       </c>
       <c r="C14" t="n">
-        <v>337.5008200200934</v>
+        <v>336.8063730332322</v>
       </c>
       <c r="D14" t="n">
-        <v>331.855962815555</v>
+        <v>333.5623284395552</v>
       </c>
       <c r="E14" t="n">
-        <v>332.2726135253906</v>
+        <v>334.6932678222656</v>
       </c>
       <c r="F14" t="n">
-        <v>5398700</v>
+        <v>9619200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>334.5544248444214</v>
+        <v>334.7031787744378</v>
       </c>
       <c r="C15" t="n">
-        <v>336.8064037434848</v>
+        <v>337.9373231090121</v>
       </c>
       <c r="D15" t="n">
-        <v>333.5623588540134</v>
+        <v>332.8876813284792</v>
       </c>
       <c r="E15" t="n">
-        <v>334.6932983398438</v>
+        <v>337.4611206054688</v>
       </c>
       <c r="F15" t="n">
-        <v>9619200</v>
+        <v>7217800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>334.7031787744378</v>
+        <v>337.1238274360646</v>
       </c>
       <c r="C16" t="n">
-        <v>337.9373231090121</v>
+        <v>342.867866960749</v>
       </c>
       <c r="D16" t="n">
-        <v>332.8876813284792</v>
+        <v>335.824223582947</v>
       </c>
       <c r="E16" t="n">
-        <v>337.4611206054688</v>
+        <v>338.6714477539062</v>
       </c>
       <c r="F16" t="n">
-        <v>7217800</v>
+        <v>8164400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>337.1238578141872</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="C17" t="n">
-        <v>342.8678978564652</v>
+        <v>346.58811100512</v>
       </c>
       <c r="D17" t="n">
-        <v>335.8242538439627</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="E17" t="n">
-        <v>338.6714782714844</v>
+        <v>345.0702514648438</v>
       </c>
       <c r="F17" t="n">
-        <v>8164400</v>
+        <v>8381000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>337.6099271681015</v>
+        <v>343.4730470813312</v>
       </c>
       <c r="C18" t="n">
-        <v>346.58811100512</v>
+        <v>344.425421840401</v>
       </c>
       <c r="D18" t="n">
-        <v>337.6099271681015</v>
+        <v>340.8341482313199</v>
       </c>
       <c r="E18" t="n">
-        <v>345.0702514648438</v>
+        <v>343.2052001953125</v>
       </c>
       <c r="F18" t="n">
-        <v>8381000</v>
+        <v>5198000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>343.4730470813312</v>
+        <v>343.3639143460552</v>
       </c>
       <c r="C19" t="n">
-        <v>344.425421840401</v>
+        <v>350.3579971109944</v>
       </c>
       <c r="D19" t="n">
-        <v>340.8341482313199</v>
+        <v>343.2548016291976</v>
       </c>
       <c r="E19" t="n">
-        <v>343.2052001953125</v>
+        <v>347.0643310546875</v>
       </c>
       <c r="F19" t="n">
-        <v>5198000</v>
+        <v>5199700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>343.3639143460552</v>
+        <v>347.2330080952501</v>
       </c>
       <c r="C20" t="n">
-        <v>350.3579971109944</v>
+        <v>348.3341867524627</v>
       </c>
       <c r="D20" t="n">
-        <v>343.2548016291976</v>
+        <v>341.6179112620468</v>
       </c>
       <c r="E20" t="n">
-        <v>347.0643310546875</v>
+        <v>346.5087890625</v>
       </c>
       <c r="F20" t="n">
-        <v>5199700</v>
+        <v>4735600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>347.2329775138888</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="C21" t="n">
-        <v>348.3341560741189</v>
+        <v>351.6278330286145</v>
       </c>
       <c r="D21" t="n">
-        <v>341.6178811752161</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="E21" t="n">
-        <v>346.5087585449219</v>
+        <v>349.6238708496094</v>
       </c>
       <c r="F21" t="n">
-        <v>4735600</v>
+        <v>5044600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>347.2825796289147</v>
+        <v>350.9730784623077</v>
       </c>
       <c r="C22" t="n">
-        <v>351.6278330286145</v>
+        <v>352.1834000905383</v>
       </c>
       <c r="D22" t="n">
-        <v>347.2825796289147</v>
+        <v>348.3143490742109</v>
       </c>
       <c r="E22" t="n">
-        <v>349.6238708496094</v>
+        <v>348.572265625</v>
       </c>
       <c r="F22" t="n">
-        <v>5044600</v>
+        <v>3927500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>350.9730784623077</v>
+        <v>348.6814047504906</v>
       </c>
       <c r="C23" t="n">
-        <v>352.1834000905383</v>
+        <v>350.0702909620389</v>
       </c>
       <c r="D23" t="n">
-        <v>348.3143490742109</v>
+        <v>342.8381220393481</v>
       </c>
       <c r="E23" t="n">
-        <v>348.572265625</v>
+        <v>344.2865600585938</v>
       </c>
       <c r="F23" t="n">
-        <v>3927500</v>
+        <v>4434800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>348.681435657628</v>
+        <v>344.8718644724454</v>
       </c>
       <c r="C24" t="n">
-        <v>350.0703219922872</v>
+        <v>347.619876043067</v>
       </c>
       <c r="D24" t="n">
-        <v>342.8381524285367</v>
+        <v>340.5266111021468</v>
       </c>
       <c r="E24" t="n">
-        <v>344.2865905761719</v>
+        <v>340.9234313964844</v>
       </c>
       <c r="F24" t="n">
-        <v>4434800</v>
+        <v>6296200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>344.8718644724454</v>
+        <v>340.9928833808045</v>
       </c>
       <c r="C25" t="n">
-        <v>347.619876043067</v>
+        <v>344.9016253459246</v>
       </c>
       <c r="D25" t="n">
-        <v>340.5266111021468</v>
+        <v>338.0266161060487</v>
       </c>
       <c r="E25" t="n">
-        <v>340.9234313964844</v>
+        <v>340.5762023925781</v>
       </c>
       <c r="F25" t="n">
-        <v>6296200</v>
+        <v>4030700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>340.9928833808045</v>
+        <v>338.2944848137428</v>
       </c>
       <c r="C26" t="n">
-        <v>344.9016253459246</v>
+        <v>347.2330086020973</v>
       </c>
       <c r="D26" t="n">
-        <v>338.0266161060487</v>
+        <v>337.520674593222</v>
       </c>
       <c r="E26" t="n">
-        <v>340.5762023925781</v>
+        <v>345.6159362792969</v>
       </c>
       <c r="F26" t="n">
-        <v>4030700</v>
+        <v>5731000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>338.2944848137428</v>
+        <v>345.615925335404</v>
       </c>
       <c r="C27" t="n">
-        <v>347.2330086020973</v>
+        <v>347.3024192111109</v>
       </c>
       <c r="D27" t="n">
-        <v>337.520674593222</v>
+        <v>341.2706718210525</v>
       </c>
       <c r="E27" t="n">
-        <v>345.6159362792969</v>
+        <v>342.947265625</v>
       </c>
       <c r="F27" t="n">
-        <v>5731000</v>
+        <v>3778200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>345.615925335404</v>
+        <v>342.2627301477191</v>
       </c>
       <c r="C28" t="n">
-        <v>347.3024192111109</v>
+        <v>342.9472580300504</v>
       </c>
       <c r="D28" t="n">
-        <v>341.2706718210525</v>
+        <v>331.5186699399313</v>
       </c>
       <c r="E28" t="n">
-        <v>342.947265625</v>
+        <v>332.7388916015625</v>
       </c>
       <c r="F28" t="n">
-        <v>3778200</v>
+        <v>6241500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>342.2627615387884</v>
+        <v>335.0900620604222</v>
       </c>
       <c r="C29" t="n">
-        <v>342.947289483902</v>
+        <v>340.725018943138</v>
       </c>
       <c r="D29" t="n">
-        <v>331.5187003455953</v>
+        <v>334.3261822760441</v>
       </c>
       <c r="E29" t="n">
-        <v>332.7389221191406</v>
+        <v>339.1773986816406</v>
       </c>
       <c r="F29" t="n">
-        <v>6241500</v>
+        <v>6267100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>335.0900620604222</v>
+        <v>339.1873037416991</v>
       </c>
       <c r="C30" t="n">
-        <v>340.725018943138</v>
+        <v>342.2230227820154</v>
       </c>
       <c r="D30" t="n">
-        <v>334.3261822760441</v>
+        <v>336.2507973402091</v>
       </c>
       <c r="E30" t="n">
-        <v>339.1773986816406</v>
+        <v>341.6773986816406</v>
       </c>
       <c r="F30" t="n">
-        <v>6267100</v>
+        <v>4665000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>339.1873340368696</v>
+        <v>340.3976542086254</v>
       </c>
       <c r="C31" t="n">
-        <v>342.223053348327</v>
+        <v>346.8758434662893</v>
       </c>
       <c r="D31" t="n">
-        <v>336.2508273730998</v>
+        <v>340.2786111420936</v>
       </c>
       <c r="E31" t="n">
-        <v>341.6774291992188</v>
+        <v>344.4552001953125</v>
       </c>
       <c r="F31" t="n">
-        <v>4665000</v>
+        <v>4121800</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>340.3976240505323</v>
+        <v>345.0603770187118</v>
       </c>
       <c r="C32" t="n">
-        <v>346.8758127342502</v>
+        <v>345.4076061472691</v>
       </c>
       <c r="D32" t="n">
-        <v>340.2785809945473</v>
+        <v>341.7667108842852</v>
       </c>
       <c r="E32" t="n">
-        <v>344.4551696777344</v>
+        <v>342.619873046875</v>
       </c>
       <c r="F32" t="n">
-        <v>4121800</v>
+        <v>5074400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>345.060346283755</v>
+        <v>343.4532042783919</v>
       </c>
       <c r="C33" t="n">
-        <v>345.4075753813841</v>
+        <v>344.3956486566242</v>
       </c>
       <c r="D33" t="n">
-        <v>341.7666804426993</v>
+        <v>341.7269891377298</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6198425292969</v>
+        <v>343.215087890625</v>
       </c>
       <c r="F33" t="n">
-        <v>5074400</v>
+        <v>7217200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>343.4532348171426</v>
+        <v>345.4373415963541</v>
       </c>
       <c r="C34" t="n">
-        <v>344.395679279174</v>
+        <v>346.3103341142831</v>
       </c>
       <c r="D34" t="n">
-        <v>341.727019522991</v>
+        <v>342.5801871000132</v>
       </c>
       <c r="E34" t="n">
-        <v>343.2151184082031</v>
+        <v>344.6238403320312</v>
       </c>
       <c r="F34" t="n">
-        <v>7217200</v>
+        <v>3576700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>345.4373721859704</v>
+        <v>346.2310248701323</v>
       </c>
       <c r="C35" t="n">
-        <v>346.3103647812057</v>
+        <v>346.7468882773667</v>
       </c>
       <c r="D35" t="n">
-        <v>342.5802174366191</v>
+        <v>342.2726913226552</v>
       </c>
       <c r="E35" t="n">
-        <v>344.6238708496094</v>
+        <v>345.0603942871094</v>
       </c>
       <c r="F35" t="n">
-        <v>3576700</v>
+        <v>5400300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>346.2309942490221</v>
+        <v>345.8143074374688</v>
       </c>
       <c r="C36" t="n">
-        <v>346.746857610633</v>
+        <v>347.1139415798067</v>
       </c>
       <c r="D36" t="n">
-        <v>342.2726610516251</v>
+        <v>343.7508237502946</v>
       </c>
       <c r="E36" t="n">
-        <v>345.0603637695312</v>
+        <v>344.1476440429688</v>
       </c>
       <c r="F36" t="n">
-        <v>5400300</v>
+        <v>7445400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>345.8143074374688</v>
+        <v>343.2547871723516</v>
       </c>
       <c r="C37" t="n">
-        <v>347.1139415798067</v>
+        <v>348.1952860487332</v>
       </c>
       <c r="D37" t="n">
-        <v>343.7508237502946</v>
+        <v>336.3103261601942</v>
       </c>
       <c r="E37" t="n">
-        <v>344.1476440429688</v>
+        <v>338.5722351074219</v>
       </c>
       <c r="F37" t="n">
-        <v>7445400</v>
+        <v>8361700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>343.2548181119967</v>
+        <v>339.5047778404419</v>
       </c>
       <c r="C38" t="n">
-        <v>348.1953174336955</v>
+        <v>346.9452717470537</v>
       </c>
       <c r="D38" t="n">
-        <v>336.3103564738927</v>
+        <v>339.0781967892368</v>
       </c>
       <c r="E38" t="n">
-        <v>338.572265625</v>
+        <v>342.29248046875</v>
       </c>
       <c r="F38" t="n">
-        <v>8361700</v>
+        <v>6411800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>339.5047778404419</v>
+        <v>339.3658942315137</v>
       </c>
       <c r="C39" t="n">
-        <v>346.9452717470537</v>
+        <v>340.2786081927618</v>
       </c>
       <c r="D39" t="n">
-        <v>339.0781967892368</v>
+        <v>335.4869431536939</v>
       </c>
       <c r="E39" t="n">
-        <v>342.29248046875</v>
+        <v>338.0365295410156</v>
       </c>
       <c r="F39" t="n">
-        <v>6411800</v>
+        <v>7301600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>339.3658942315137</v>
+        <v>338.2944659192743</v>
       </c>
       <c r="C40" t="n">
-        <v>340.2786081927618</v>
+        <v>338.5027912774657</v>
       </c>
       <c r="D40" t="n">
-        <v>335.4869431536939</v>
+        <v>332.1635060317716</v>
       </c>
       <c r="E40" t="n">
-        <v>338.0365295410156</v>
+        <v>334.2269897460938</v>
       </c>
       <c r="F40" t="n">
-        <v>7301600</v>
+        <v>5538000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>338.2944659192743</v>
+        <v>333.810367634687</v>
       </c>
       <c r="C41" t="n">
-        <v>338.5027912774657</v>
+        <v>337.6198973167316</v>
       </c>
       <c r="D41" t="n">
-        <v>332.1635060317716</v>
+        <v>331.5980496280586</v>
       </c>
       <c r="E41" t="n">
-        <v>334.2269897460938</v>
+        <v>337.6000366210938</v>
       </c>
       <c r="F41" t="n">
-        <v>5538000</v>
+        <v>5920200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>333.8103374596785</v>
+        <v>337.4313538243792</v>
       </c>
       <c r="C42" t="n">
-        <v>337.6198667973582</v>
+        <v>339.3956247811457</v>
       </c>
       <c r="D42" t="n">
-        <v>331.598019653034</v>
+        <v>333.6912462886964</v>
       </c>
       <c r="E42" t="n">
-        <v>337.6000061035156</v>
+        <v>337.3420715332031</v>
       </c>
       <c r="F42" t="n">
-        <v>5920200</v>
+        <v>4984600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>337.4313538243792</v>
+        <v>335.9035711966457</v>
       </c>
       <c r="C43" t="n">
-        <v>339.3956247811457</v>
+        <v>335.9630927253758</v>
       </c>
       <c r="D43" t="n">
-        <v>333.6912462886964</v>
+        <v>331.062285023625</v>
       </c>
       <c r="E43" t="n">
-        <v>337.3420715332031</v>
+        <v>334.2864990234375</v>
       </c>
       <c r="F43" t="n">
-        <v>4984600</v>
+        <v>8507900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>335.9035711966457</v>
+        <v>334.0583313951361</v>
       </c>
       <c r="C44" t="n">
-        <v>335.9630927253758</v>
+        <v>335.6059516380656</v>
       </c>
       <c r="D44" t="n">
-        <v>331.062285023625</v>
+        <v>332.1932428266196</v>
       </c>
       <c r="E44" t="n">
-        <v>334.2864990234375</v>
+        <v>333.3539428710938</v>
       </c>
       <c r="F44" t="n">
-        <v>8507900</v>
+        <v>5318400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>334.058361977199</v>
+        <v>333.9789743060267</v>
       </c>
       <c r="C45" t="n">
-        <v>335.6059823618086</v>
+        <v>335.9928668426192</v>
       </c>
       <c r="D45" t="n">
-        <v>332.193273237939</v>
+        <v>331.6674741139567</v>
       </c>
       <c r="E45" t="n">
-        <v>333.3539733886719</v>
+        <v>332.1932678222656</v>
       </c>
       <c r="F45" t="n">
-        <v>5318400</v>
+        <v>5295800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>333.9789743060267</v>
+        <v>332.838108855689</v>
       </c>
       <c r="C46" t="n">
-        <v>335.9928668426192</v>
+        <v>336.3996217972758</v>
       </c>
       <c r="D46" t="n">
-        <v>331.6674741139567</v>
+        <v>330.5563693999427</v>
       </c>
       <c r="E46" t="n">
-        <v>332.1932678222656</v>
+        <v>336.2309875488281</v>
       </c>
       <c r="F46" t="n">
-        <v>5295800</v>
+        <v>4453300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>332.838108855689</v>
+        <v>336.230963908966</v>
       </c>
       <c r="C47" t="n">
-        <v>336.3996217972758</v>
+        <v>342.2050995382295</v>
       </c>
       <c r="D47" t="n">
-        <v>330.5563693999427</v>
+        <v>335.3860315467677</v>
       </c>
       <c r="E47" t="n">
-        <v>336.2309875488281</v>
+        <v>336.8572082519531</v>
       </c>
       <c r="F47" t="n">
-        <v>4453300</v>
+        <v>6389600</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,25 +1665,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>336.230963908966</v>
+        <v>337.01623628756</v>
       </c>
       <c r="C48" t="n">
-        <v>342.2050995382295</v>
+        <v>339.4217740167541</v>
       </c>
       <c r="D48" t="n">
-        <v>335.3860315467677</v>
+        <v>333.5967676514001</v>
       </c>
       <c r="E48" t="n">
-        <v>336.8572082519531</v>
+        <v>334.0738830566406</v>
       </c>
       <c r="F48" t="n">
-        <v>6389600</v>
+        <v>4961700</v>
       </c>
       <c r="G48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>337.0162670739215</v>
+        <v>333.8850664354288</v>
       </c>
       <c r="C49" t="n">
-        <v>339.4218050228609</v>
+        <v>334.0739044051273</v>
       </c>
       <c r="D49" t="n">
-        <v>333.5967981253938</v>
+        <v>327.0659984240934</v>
       </c>
       <c r="E49" t="n">
-        <v>334.0739135742188</v>
+        <v>328.0500793457031</v>
       </c>
       <c r="F49" t="n">
-        <v>4961700</v>
+        <v>6422300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>333.8850664354288</v>
+        <v>329.1832834325262</v>
       </c>
       <c r="C50" t="n">
-        <v>334.0739044051273</v>
+        <v>331.370133257436</v>
       </c>
       <c r="D50" t="n">
-        <v>327.0659984240934</v>
+        <v>322.9904598740608</v>
       </c>
       <c r="E50" t="n">
-        <v>328.0500793457031</v>
+        <v>323.8055725097656</v>
       </c>
       <c r="F50" t="n">
-        <v>6422300</v>
+        <v>6494800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>329.1832834325262</v>
+        <v>322.5630378796905</v>
       </c>
       <c r="C51" t="n">
-        <v>331.370133257436</v>
+        <v>323.0600533463772</v>
       </c>
       <c r="D51" t="n">
-        <v>322.9904598740608</v>
+        <v>316.101836812763</v>
       </c>
       <c r="E51" t="n">
-        <v>323.8055725097656</v>
+        <v>319.2628479003906</v>
       </c>
       <c r="F51" t="n">
-        <v>6494800</v>
+        <v>9170400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>322.5630378796905</v>
+        <v>319.6008465015586</v>
       </c>
       <c r="C52" t="n">
-        <v>323.0600533463772</v>
+        <v>322.6326593505401</v>
       </c>
       <c r="D52" t="n">
-        <v>316.101836812763</v>
+        <v>317.9607013657724</v>
       </c>
       <c r="E52" t="n">
-        <v>319.2628479003906</v>
+        <v>322.1853332519531</v>
       </c>
       <c r="F52" t="n">
-        <v>9170400</v>
+        <v>7066700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>319.6008162287846</v>
+        <v>322.1852887063674</v>
       </c>
       <c r="C53" t="n">
-        <v>322.632628790591</v>
+        <v>326.4397397218689</v>
       </c>
       <c r="D53" t="n">
-        <v>317.9606712483538</v>
+        <v>321.2111578443184</v>
       </c>
       <c r="E53" t="n">
-        <v>322.185302734375</v>
+        <v>321.8373718261719</v>
       </c>
       <c r="F53" t="n">
-        <v>7066700</v>
+        <v>6510300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>322.1852887063674</v>
+        <v>323.4377913272098</v>
       </c>
       <c r="C54" t="n">
-        <v>326.4397397218689</v>
+        <v>329.1037494702317</v>
       </c>
       <c r="D54" t="n">
-        <v>321.2111578443184</v>
+        <v>322.354301245485</v>
       </c>
       <c r="E54" t="n">
-        <v>321.8373718261719</v>
+        <v>326.0222778320312</v>
       </c>
       <c r="F54" t="n">
-        <v>6510300</v>
+        <v>8930000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>323.437821602865</v>
+        <v>327.2747416730934</v>
       </c>
       <c r="C55" t="n">
-        <v>329.1037802762534</v>
+        <v>328.755868423024</v>
       </c>
       <c r="D55" t="n">
-        <v>322.3543314197192</v>
+        <v>324.0540910886259</v>
       </c>
       <c r="E55" t="n">
-        <v>326.0223083496094</v>
+        <v>327.3343811035156</v>
       </c>
       <c r="F55" t="n">
-        <v>8930000</v>
+        <v>9337100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>327.2747416730934</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="C56" t="n">
-        <v>328.755868423024</v>
+        <v>334.0540387480419</v>
       </c>
       <c r="D56" t="n">
-        <v>324.0540910886259</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="E56" t="n">
-        <v>327.3343811035156</v>
+        <v>332.5331726074219</v>
       </c>
       <c r="F56" t="n">
-        <v>9337100</v>
+        <v>5854300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>326.9367735032804</v>
+        <v>332.533150050326</v>
       </c>
       <c r="C57" t="n">
-        <v>334.0540387480419</v>
+        <v>333.7060992116737</v>
       </c>
       <c r="D57" t="n">
-        <v>326.9367735032804</v>
+        <v>331.0719234390147</v>
       </c>
       <c r="E57" t="n">
-        <v>332.5331726074219</v>
+        <v>331.7975769042969</v>
       </c>
       <c r="F57" t="n">
-        <v>5854300</v>
+        <v>4309900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>332.5331806355595</v>
+        <v>331.4397445821358</v>
       </c>
       <c r="C58" t="n">
-        <v>333.7061299047911</v>
+        <v>333.0202502105825</v>
       </c>
       <c r="D58" t="n">
-        <v>331.0719538898497</v>
+        <v>330.0182875517957</v>
       </c>
       <c r="E58" t="n">
-        <v>331.797607421875</v>
+        <v>332.4437255859375</v>
       </c>
       <c r="F58" t="n">
-        <v>4309900</v>
+        <v>4586200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>331.4397445821358</v>
+        <v>330.952674561706</v>
       </c>
       <c r="C59" t="n">
-        <v>333.0202502105825</v>
+        <v>331.3105111509684</v>
       </c>
       <c r="D59" t="n">
-        <v>330.0182875517957</v>
+        <v>328.1693999716056</v>
       </c>
       <c r="E59" t="n">
-        <v>332.4437255859375</v>
+        <v>328.4179077148438</v>
       </c>
       <c r="F59" t="n">
-        <v>4586200</v>
+        <v>7082300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>330.952674561706</v>
+        <v>329.4715593852143</v>
       </c>
       <c r="C60" t="n">
-        <v>331.3105111509684</v>
+        <v>330.8134768540631</v>
       </c>
       <c r="D60" t="n">
-        <v>328.1693999716056</v>
+        <v>325.2568476714639</v>
       </c>
       <c r="E60" t="n">
-        <v>328.4179077148438</v>
+        <v>327.6524658203125</v>
       </c>
       <c r="F60" t="n">
-        <v>7082300</v>
+        <v>8201900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>329.4715593852143</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="C61" t="n">
-        <v>330.8134768540631</v>
+        <v>330.3661824396382</v>
       </c>
       <c r="D61" t="n">
-        <v>325.2568476714639</v>
+        <v>327.3840896786403</v>
       </c>
       <c r="E61" t="n">
-        <v>327.6524658203125</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="F61" t="n">
-        <v>8201900</v>
+        <v>6296700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>327.6425170898438</v>
+        <v>329.3025948705371</v>
       </c>
       <c r="C62" t="n">
-        <v>330.3661824396382</v>
+        <v>330.396035058885</v>
       </c>
       <c r="D62" t="n">
-        <v>327.3840896786403</v>
+        <v>322.3443777352205</v>
       </c>
       <c r="E62" t="n">
-        <v>327.6425170898438</v>
+        <v>325.1475524902344</v>
       </c>
       <c r="F62" t="n">
-        <v>6296700</v>
+        <v>6277500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>329.3025639629765</v>
+        <v>324.8791069392551</v>
       </c>
       <c r="C63" t="n">
-        <v>330.3960040486967</v>
+        <v>332.1156507054553</v>
       </c>
       <c r="D63" t="n">
-        <v>322.3443474807417</v>
+        <v>324.4516809311236</v>
       </c>
       <c r="E63" t="n">
-        <v>325.1475219726562</v>
+        <v>329.2627868652344</v>
       </c>
       <c r="F63" t="n">
-        <v>6277500</v>
+        <v>5266600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>324.8791069392551</v>
+        <v>327.9109311533039</v>
       </c>
       <c r="C64" t="n">
-        <v>332.1156507054553</v>
+        <v>329.3622078309571</v>
       </c>
       <c r="D64" t="n">
-        <v>324.4516809311236</v>
+        <v>322.77177784886</v>
       </c>
       <c r="E64" t="n">
-        <v>329.2627868652344</v>
+        <v>324.8890686035156</v>
       </c>
       <c r="F64" t="n">
-        <v>5266600</v>
+        <v>6059400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>327.9109619547325</v>
+        <v>324.6604152629651</v>
       </c>
       <c r="C65" t="n">
-        <v>329.3622387687074</v>
+        <v>326.2707707906858</v>
       </c>
       <c r="D65" t="n">
-        <v>322.7718081675561</v>
+        <v>323.1296295298985</v>
       </c>
       <c r="E65" t="n">
-        <v>324.8890991210938</v>
+        <v>324.5510864257812</v>
       </c>
       <c r="F65" t="n">
-        <v>6059400</v>
+        <v>4325400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>324.6604457908234</v>
+        <v>324.6902773524443</v>
       </c>
       <c r="C66" t="n">
-        <v>326.270801469966</v>
+        <v>326.797618069185</v>
       </c>
       <c r="D66" t="n">
-        <v>323.1296599138169</v>
+        <v>323.3582492118315</v>
       </c>
       <c r="E66" t="n">
-        <v>324.5511169433594</v>
+        <v>323.7857055664062</v>
       </c>
       <c r="F66" t="n">
-        <v>4325400</v>
+        <v>5467500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>324.6902773524443</v>
+        <v>330.6146735055701</v>
       </c>
       <c r="C67" t="n">
-        <v>326.797618069185</v>
+        <v>345.2468091287718</v>
       </c>
       <c r="D67" t="n">
-        <v>323.3582492118315</v>
+        <v>328.0898266012699</v>
       </c>
       <c r="E67" t="n">
-        <v>323.7857055664062</v>
+        <v>343.56689453125</v>
       </c>
       <c r="F67" t="n">
-        <v>5467500</v>
+        <v>12953600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>330.6147322397455</v>
+        <v>345.9227522622342</v>
       </c>
       <c r="C68" t="n">
-        <v>345.2468704623673</v>
+        <v>347.751765473026</v>
       </c>
       <c r="D68" t="n">
-        <v>328.0898848869026</v>
+        <v>343.9048707541211</v>
       </c>
       <c r="E68" t="n">
-        <v>343.5669555664062</v>
+        <v>345.7537536621094</v>
       </c>
       <c r="F68" t="n">
-        <v>12953600</v>
+        <v>6942300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>345.9227522622342</v>
+        <v>345.7537581195867</v>
       </c>
       <c r="C69" t="n">
-        <v>347.751765473026</v>
+        <v>346.3700827656107</v>
       </c>
       <c r="D69" t="n">
-        <v>343.9048707541211</v>
+        <v>341.7776344791052</v>
       </c>
       <c r="E69" t="n">
-        <v>345.7537536621094</v>
+        <v>344.8193969726562</v>
       </c>
       <c r="F69" t="n">
-        <v>6942300</v>
+        <v>7004600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>345.7537581195867</v>
+        <v>343.9347204472646</v>
       </c>
       <c r="C70" t="n">
-        <v>346.3700827656107</v>
+        <v>345.5450457875993</v>
       </c>
       <c r="D70" t="n">
-        <v>341.7776344791052</v>
+        <v>341.6683310172716</v>
       </c>
       <c r="E70" t="n">
-        <v>344.8193969726562</v>
+        <v>343.0500183105469</v>
       </c>
       <c r="F70" t="n">
-        <v>7004600</v>
+        <v>7269300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>343.9347204472646</v>
+        <v>343.4873664669518</v>
       </c>
       <c r="C71" t="n">
-        <v>345.5450457875993</v>
+        <v>345.7140163182048</v>
       </c>
       <c r="D71" t="n">
-        <v>341.6683310172716</v>
+        <v>341.6285335316323</v>
       </c>
       <c r="E71" t="n">
-        <v>343.0500183105469</v>
+        <v>342.3541870117188</v>
       </c>
       <c r="F71" t="n">
-        <v>7269300</v>
+        <v>7263500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>343.4873664669518</v>
+        <v>343.1096587982668</v>
       </c>
       <c r="C72" t="n">
-        <v>345.7140163182048</v>
+        <v>345.4555571592003</v>
       </c>
       <c r="D72" t="n">
-        <v>341.6285335316323</v>
+        <v>342.2150067207226</v>
       </c>
       <c r="E72" t="n">
-        <v>342.3541870117188</v>
+        <v>343.9446411132812</v>
       </c>
       <c r="F72" t="n">
-        <v>7263500</v>
+        <v>6805000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>343.1096892417585</v>
+        <v>343.9844025059169</v>
       </c>
       <c r="C73" t="n">
-        <v>345.4555878108393</v>
+        <v>347.8213777963309</v>
       </c>
       <c r="D73" t="n">
-        <v>342.2150370848335</v>
+        <v>343.9844025059169</v>
       </c>
       <c r="E73" t="n">
-        <v>343.9446716308594</v>
+        <v>347.1653137207031</v>
       </c>
       <c r="F73" t="n">
-        <v>6805000</v>
+        <v>18623900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>343.9843722679569</v>
+        <v>347.9108213067459</v>
       </c>
       <c r="C74" t="n">
-        <v>347.8213472210815</v>
+        <v>351.3302900915655</v>
       </c>
       <c r="D74" t="n">
-        <v>343.9843722679569</v>
+        <v>347.5032649901081</v>
       </c>
       <c r="E74" t="n">
-        <v>347.165283203125</v>
+        <v>349.9883422851562</v>
       </c>
       <c r="F74" t="n">
-        <v>18623900</v>
+        <v>5043500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>347.9108516431725</v>
+        <v>349.8988624434305</v>
       </c>
       <c r="C75" t="n">
-        <v>351.3303207261561</v>
+        <v>354.2527224604554</v>
       </c>
       <c r="D75" t="n">
-        <v>347.5032952909974</v>
+        <v>349.8988624434305</v>
       </c>
       <c r="E75" t="n">
-        <v>349.9883728027344</v>
+        <v>351.2706298828125</v>
       </c>
       <c r="F75" t="n">
-        <v>5043500</v>
+        <v>3703200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>349.8988928418326</v>
+        <v>351.2706679101954</v>
       </c>
       <c r="C76" t="n">
-        <v>354.2527532371108</v>
+        <v>353.8650741726075</v>
       </c>
       <c r="D76" t="n">
-        <v>349.8988928418326</v>
+        <v>350.9028813061371</v>
       </c>
       <c r="E76" t="n">
-        <v>351.2706604003906</v>
+        <v>353.0201721191406</v>
       </c>
       <c r="F76" t="n">
-        <v>3703200</v>
+        <v>2023600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>351.2706375438569</v>
+        <v>352.9803906057607</v>
       </c>
       <c r="C77" t="n">
-        <v>353.86504358199</v>
+        <v>354.6006658812749</v>
       </c>
       <c r="D77" t="n">
-        <v>350.9028509715926</v>
+        <v>351.5986730469889</v>
       </c>
       <c r="E77" t="n">
-        <v>353.0201416015625</v>
+        <v>352.8809814453125</v>
       </c>
       <c r="F77" t="n">
-        <v>2023600</v>
+        <v>2017000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>352.9804211319358</v>
+        <v>353.3680687798424</v>
       </c>
       <c r="C78" t="n">
-        <v>354.6006965475734</v>
+        <v>354.4217392079314</v>
       </c>
       <c r="D78" t="n">
-        <v>351.5987034536714</v>
+        <v>351.6881539711041</v>
       </c>
       <c r="E78" t="n">
-        <v>352.8810119628906</v>
+        <v>352.4933166503906</v>
       </c>
       <c r="F78" t="n">
-        <v>2017000</v>
+        <v>3989900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>353.3680381865314</v>
+        <v>351.8869529196318</v>
       </c>
       <c r="C79" t="n">
-        <v>354.4217085233975</v>
+        <v>352.7517549841574</v>
       </c>
       <c r="D79" t="n">
-        <v>351.688123523234</v>
+        <v>350.5549550996776</v>
       </c>
       <c r="E79" t="n">
-        <v>352.4932861328125</v>
+        <v>351.5092163085938</v>
       </c>
       <c r="F79" t="n">
-        <v>3989900</v>
+        <v>3366500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>351.8869529196318</v>
+        <v>351.539030494231</v>
       </c>
       <c r="C80" t="n">
-        <v>352.7517549841574</v>
+        <v>353.0797966289462</v>
       </c>
       <c r="D80" t="n">
-        <v>350.5549550996776</v>
+        <v>348.5967074506911</v>
       </c>
       <c r="E80" t="n">
-        <v>351.5092163085938</v>
+        <v>348.6165771484375</v>
       </c>
       <c r="F80" t="n">
-        <v>3366500</v>
+        <v>3503200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>351.539030494231</v>
+        <v>347.7816144857114</v>
       </c>
       <c r="C81" t="n">
-        <v>353.0797966289462</v>
+        <v>347.9605327817998</v>
       </c>
       <c r="D81" t="n">
-        <v>348.5967074506911</v>
+        <v>341.4297722912301</v>
       </c>
       <c r="E81" t="n">
-        <v>348.6165771484375</v>
+        <v>344.411865234375</v>
       </c>
       <c r="F81" t="n">
-        <v>3503200</v>
+        <v>5403800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>347.7815836695472</v>
+        <v>342.443665092254</v>
       </c>
       <c r="C82" t="n">
-        <v>347.960501949782</v>
+        <v>355.4058372808095</v>
       </c>
       <c r="D82" t="n">
-        <v>341.4297420378886</v>
+        <v>341.996339026907</v>
       </c>
       <c r="E82" t="n">
-        <v>344.4118347167969</v>
+        <v>351.6881408691406</v>
       </c>
       <c r="F82" t="n">
-        <v>5403800</v>
+        <v>7592200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>342.443665092254</v>
+        <v>351.5688750998228</v>
       </c>
       <c r="C83" t="n">
-        <v>355.4058372808095</v>
+        <v>356.4793906429162</v>
       </c>
       <c r="D83" t="n">
-        <v>341.996339026907</v>
+        <v>349.8989103083969</v>
       </c>
       <c r="E83" t="n">
-        <v>351.6881408691406</v>
+        <v>355.4257202148438</v>
       </c>
       <c r="F83" t="n">
-        <v>7592200</v>
+        <v>6775400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>351.5688750998228</v>
+        <v>355.0181456831753</v>
       </c>
       <c r="C84" t="n">
-        <v>356.4793906429162</v>
+        <v>356.1414055038805</v>
       </c>
       <c r="D84" t="n">
-        <v>349.8989103083969</v>
+        <v>352.3939197646881</v>
       </c>
       <c r="E84" t="n">
-        <v>355.4257202148438</v>
+        <v>353.7557373046875</v>
       </c>
       <c r="F84" t="n">
-        <v>6775400</v>
+        <v>6333900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>355.0181150566925</v>
+        <v>352.8809877738215</v>
       </c>
       <c r="C85" t="n">
-        <v>356.1413747804971</v>
+        <v>354.2229356253969</v>
       </c>
       <c r="D85" t="n">
-        <v>352.3938893645904</v>
+        <v>347.4138175407059</v>
       </c>
       <c r="E85" t="n">
-        <v>353.7557067871094</v>
+        <v>350.1275329589844</v>
       </c>
       <c r="F85" t="n">
-        <v>6333900</v>
+        <v>6357600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>352.8809877738215</v>
+        <v>350.0579384420253</v>
       </c>
       <c r="C86" t="n">
-        <v>354.2229356253969</v>
+        <v>352.582785516123</v>
       </c>
       <c r="D86" t="n">
-        <v>347.4138175407059</v>
+        <v>347.075845630788</v>
       </c>
       <c r="E86" t="n">
-        <v>350.1275329589844</v>
+        <v>347.6821899414062</v>
       </c>
       <c r="F86" t="n">
-        <v>6357600</v>
+        <v>4902900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>350.0579384420253</v>
+        <v>340.7339218833562</v>
       </c>
       <c r="C87" t="n">
-        <v>352.582785516123</v>
+        <v>344.4416681829234</v>
       </c>
       <c r="D87" t="n">
-        <v>347.075845630788</v>
+        <v>335.306521484956</v>
       </c>
       <c r="E87" t="n">
-        <v>347.6821899414062</v>
+        <v>341.1514282226562</v>
       </c>
       <c r="F87" t="n">
-        <v>4902900</v>
+        <v>13281300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>340.7339218833562</v>
+        <v>334.9884397502153</v>
       </c>
       <c r="C88" t="n">
-        <v>344.4416681829234</v>
+        <v>335.5053249382782</v>
       </c>
       <c r="D88" t="n">
-        <v>335.306521484956</v>
+        <v>321.8970384159538</v>
       </c>
       <c r="E88" t="n">
-        <v>341.1514282226562</v>
+        <v>325.9228820800781</v>
       </c>
       <c r="F88" t="n">
-        <v>13281300</v>
+        <v>20383500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>334.9884397502153</v>
+        <v>326.6982042036898</v>
       </c>
       <c r="C89" t="n">
-        <v>335.5053249382782</v>
+        <v>327.9307928311059</v>
       </c>
       <c r="D89" t="n">
-        <v>321.8970384159538</v>
+        <v>322.0063770709054</v>
       </c>
       <c r="E89" t="n">
-        <v>325.9228820800781</v>
+        <v>327.2051696777344</v>
       </c>
       <c r="F89" t="n">
-        <v>20383500</v>
+        <v>9388400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>326.6982346739846</v>
+        <v>327.3641956721743</v>
       </c>
       <c r="C90" t="n">
-        <v>327.930823416361</v>
+        <v>329.7101244617631</v>
       </c>
       <c r="D90" t="n">
-        <v>322.0064071036056</v>
+        <v>324.4218725877395</v>
       </c>
       <c r="E90" t="n">
-        <v>327.2052001953125</v>
+        <v>325.7936401367188</v>
       </c>
       <c r="F90" t="n">
-        <v>9388400</v>
+        <v>8587700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>327.3641650074799</v>
+        <v>324.8294159854098</v>
       </c>
       <c r="C91" t="n">
-        <v>329.7100935773221</v>
+        <v>327.2846735195349</v>
       </c>
       <c r="D91" t="n">
-        <v>324.421842198657</v>
+        <v>323.4576484910236</v>
       </c>
       <c r="E91" t="n">
-        <v>325.7936096191406</v>
+        <v>326.34033203125</v>
       </c>
       <c r="F91" t="n">
-        <v>8587700</v>
+        <v>8341600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>324.8294159854098</v>
+        <v>320.3066155063486</v>
       </c>
       <c r="C92" t="n">
-        <v>327.2846735195349</v>
+        <v>326.3602605702113</v>
       </c>
       <c r="D92" t="n">
-        <v>323.4576484910236</v>
+        <v>319.6406013982136</v>
       </c>
       <c r="E92" t="n">
-        <v>326.34033203125</v>
+        <v>323.8751831054688</v>
       </c>
       <c r="F92" t="n">
-        <v>8341600</v>
+        <v>8279900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>320.3065853250236</v>
+        <v>324.4815084058711</v>
       </c>
       <c r="C93" t="n">
-        <v>326.3602298184734</v>
+        <v>326.708158311709</v>
       </c>
       <c r="D93" t="n">
-        <v>319.6405712796447</v>
+        <v>321.0719896048092</v>
       </c>
       <c r="E93" t="n">
-        <v>323.8751525878906</v>
+        <v>323.33837890625</v>
       </c>
       <c r="F93" t="n">
-        <v>8279900</v>
+        <v>8974600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>324.4815084058711</v>
+        <v>324.5113354316111</v>
       </c>
       <c r="C94" t="n">
-        <v>326.708158311709</v>
+        <v>326.4298382199604</v>
       </c>
       <c r="D94" t="n">
-        <v>321.0719896048092</v>
+        <v>322.0660277886144</v>
       </c>
       <c r="E94" t="n">
-        <v>323.33837890625</v>
+        <v>324.4119262695312</v>
       </c>
       <c r="F94" t="n">
-        <v>8974600</v>
+        <v>6938700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>324.5113354316111</v>
+        <v>323.9149045306469</v>
       </c>
       <c r="C95" t="n">
-        <v>326.4298382199604</v>
+        <v>325.8433269631201</v>
       </c>
       <c r="D95" t="n">
-        <v>322.0660277886144</v>
+        <v>322.6823158838599</v>
       </c>
       <c r="E95" t="n">
-        <v>324.4119262695312</v>
+        <v>324.2330017089844</v>
       </c>
       <c r="F95" t="n">
-        <v>6938700</v>
+        <v>5667900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>323.9148740430089</v>
+        <v>326.0421398816049</v>
       </c>
       <c r="C96" t="n">
-        <v>325.8432962939743</v>
+        <v>330.0182635386976</v>
       </c>
       <c r="D96" t="n">
-        <v>322.682285512236</v>
+        <v>323.0898668527969</v>
       </c>
       <c r="E96" t="n">
-        <v>324.2329711914062</v>
+        <v>326.5292053222656</v>
       </c>
       <c r="F96" t="n">
-        <v>5667900</v>
+        <v>7540200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>326.0421398816049</v>
+        <v>326.5192927903481</v>
       </c>
       <c r="C97" t="n">
-        <v>330.0182635386976</v>
+        <v>326.9665885103149</v>
       </c>
       <c r="D97" t="n">
-        <v>323.0898668527969</v>
+        <v>322.9705950681941</v>
       </c>
       <c r="E97" t="n">
-        <v>326.5292053222656</v>
+        <v>323.3185119628906</v>
       </c>
       <c r="F97" t="n">
-        <v>7540200</v>
+        <v>6365800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>326.5192927903481</v>
+        <v>324.7797515334782</v>
       </c>
       <c r="C98" t="n">
-        <v>326.9665885103149</v>
+        <v>326.4298465929955</v>
       </c>
       <c r="D98" t="n">
-        <v>322.9705950681941</v>
+        <v>322.9407881617898</v>
       </c>
       <c r="E98" t="n">
-        <v>323.3185119628906</v>
+        <v>325.0282592773438</v>
       </c>
       <c r="F98" t="n">
-        <v>6365800</v>
+        <v>8106000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>324.779721039233</v>
+        <v>328.0302144269235</v>
       </c>
       <c r="C99" t="n">
-        <v>326.4298159438193</v>
+        <v>331.370143867361</v>
       </c>
       <c r="D99" t="n">
-        <v>322.9407578402086</v>
+        <v>321.5789632505275</v>
       </c>
       <c r="E99" t="n">
-        <v>325.0282287597656</v>
+        <v>329.8194580078125</v>
       </c>
       <c r="F99" t="n">
-        <v>8106000</v>
+        <v>10214200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>328.0301840749007</v>
+        <v>330.2369936591709</v>
       </c>
       <c r="C100" t="n">
-        <v>331.3701132063007</v>
+        <v>331.0123366577452</v>
       </c>
       <c r="D100" t="n">
-        <v>321.578933495427</v>
+        <v>319.6803888572667</v>
       </c>
       <c r="E100" t="n">
-        <v>329.8194274902344</v>
+        <v>319.9089965820312</v>
       </c>
       <c r="F100" t="n">
-        <v>10214200</v>
+        <v>11199100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>330.236962156358</v>
+        <v>322.8910614362982</v>
       </c>
       <c r="C101" t="n">
-        <v>331.0123050809688</v>
+        <v>332.6922224170356</v>
       </c>
       <c r="D101" t="n">
-        <v>319.6803583614965</v>
+        <v>322.1753579360102</v>
       </c>
       <c r="E101" t="n">
-        <v>319.9089660644531</v>
+        <v>331.8472900390625</v>
       </c>
       <c r="F101" t="n">
-        <v>11199100</v>
+        <v>8502400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>322.8910614362982</v>
+        <v>329.6703793378445</v>
       </c>
       <c r="C102" t="n">
-        <v>332.6922224170356</v>
+        <v>333.7856822919601</v>
       </c>
       <c r="D102" t="n">
-        <v>322.1753579360102</v>
+        <v>326.906974335595</v>
       </c>
       <c r="E102" t="n">
-        <v>331.8472900390625</v>
+        <v>326.9666137695312</v>
       </c>
       <c r="F102" t="n">
-        <v>8502400</v>
+        <v>9081200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>329.6703485679092</v>
+        <v>325.15742488804</v>
       </c>
       <c r="C103" t="n">
-        <v>333.7856511379211</v>
+        <v>329.3323666962788</v>
       </c>
       <c r="D103" t="n">
-        <v>326.9069438235834</v>
+        <v>322.4835097434655</v>
       </c>
       <c r="E103" t="n">
-        <v>326.9665832519531</v>
+        <v>327.9804992675781</v>
       </c>
       <c r="F103" t="n">
-        <v>9081200</v>
+        <v>8472300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>325.15742488804</v>
+        <v>331.0123001239136</v>
       </c>
       <c r="C104" t="n">
-        <v>329.3323666962788</v>
+        <v>335.5748984583446</v>
       </c>
       <c r="D104" t="n">
-        <v>322.4835097434655</v>
+        <v>326.8572581115669</v>
       </c>
       <c r="E104" t="n">
-        <v>327.9804992675781</v>
+        <v>327.1654052734375</v>
       </c>
       <c r="F104" t="n">
-        <v>8472300</v>
+        <v>8339000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>331.0123001239136</v>
+        <v>329.7995873671293</v>
       </c>
       <c r="C105" t="n">
-        <v>335.5748984583446</v>
+        <v>333.1295971166072</v>
       </c>
       <c r="D105" t="n">
-        <v>326.8572581115669</v>
+        <v>325.1475298017769</v>
       </c>
       <c r="E105" t="n">
-        <v>327.1654052734375</v>
+        <v>329.6007690429688</v>
       </c>
       <c r="F105" t="n">
-        <v>8339000</v>
+        <v>7798800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>329.7995873671293</v>
+        <v>328.7857002676274</v>
       </c>
       <c r="C106" t="n">
-        <v>333.1295971166072</v>
+        <v>330.8334016821115</v>
       </c>
       <c r="D106" t="n">
-        <v>325.1475298017769</v>
+        <v>321.6883044313802</v>
       </c>
       <c r="E106" t="n">
-        <v>329.6007690429688</v>
+        <v>323.6365966796875</v>
       </c>
       <c r="F106" t="n">
-        <v>7798800</v>
+        <v>8513400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,25 +3199,25 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>328.7857002676274</v>
+        <v>323.4373584411114</v>
       </c>
       <c r="C107" t="n">
-        <v>330.8334016821115</v>
+        <v>328.5871090806843</v>
       </c>
       <c r="D107" t="n">
-        <v>321.6883044313802</v>
+        <v>323.2779818799478</v>
       </c>
       <c r="E107" t="n">
-        <v>323.6365966796875</v>
+        <v>326.8838195800781</v>
       </c>
       <c r="F107" t="n">
-        <v>8513400</v>
+        <v>5801800</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3225,25 +3225,25 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>323.4373584411114</v>
+        <v>325.6387009449491</v>
       </c>
       <c r="C108" t="n">
-        <v>328.5871090806843</v>
+        <v>329.7425483778229</v>
       </c>
       <c r="D108" t="n">
-        <v>323.2779818799478</v>
+        <v>325.140660617698</v>
       </c>
       <c r="E108" t="n">
-        <v>326.8838195800781</v>
+        <v>327.9495849609375</v>
       </c>
       <c r="F108" t="n">
-        <v>5801800</v>
+        <v>8264300</v>
       </c>
       <c r="G108" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>325.6387009449491</v>
+        <v>327.6010166244024</v>
       </c>
       <c r="C109" t="n">
-        <v>329.7425483778229</v>
+        <v>330.9378628609571</v>
       </c>
       <c r="D109" t="n">
-        <v>325.140660617698</v>
+        <v>322.7301671039365</v>
       </c>
       <c r="E109" t="n">
-        <v>327.9495849609375</v>
+        <v>322.9094543457031</v>
       </c>
       <c r="F109" t="n">
-        <v>8264300</v>
+        <v>9392600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>327.6010166244024</v>
+        <v>322.5607854182599</v>
       </c>
       <c r="C110" t="n">
-        <v>330.9378628609571</v>
+        <v>325.2004234747151</v>
       </c>
       <c r="D110" t="n">
-        <v>322.7301671039365</v>
+        <v>311.5939580676488</v>
       </c>
       <c r="E110" t="n">
-        <v>322.9094543457031</v>
+        <v>312.8489990234375</v>
       </c>
       <c r="F110" t="n">
-        <v>9392600</v>
+        <v>11653900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>322.5607854182599</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="C111" t="n">
-        <v>325.2004234747151</v>
+        <v>320.1204394263468</v>
       </c>
       <c r="D111" t="n">
-        <v>311.5939580676488</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="E111" t="n">
-        <v>312.8489990234375</v>
+        <v>318.247802734375</v>
       </c>
       <c r="F111" t="n">
-        <v>11653900</v>
+        <v>8591700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>313.1777553150958</v>
+        <v>318.2477947880967</v>
       </c>
       <c r="C112" t="n">
-        <v>320.1204394263468</v>
+        <v>321.0168980150915</v>
       </c>
       <c r="D112" t="n">
-        <v>313.1777553150958</v>
+        <v>315.4786915611019</v>
       </c>
       <c r="E112" t="n">
-        <v>318.247802734375</v>
+        <v>319.0446472167969</v>
       </c>
       <c r="F112" t="n">
-        <v>8591700</v>
+        <v>7091900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>318.2477947880967</v>
+        <v>316.2456341157693</v>
       </c>
       <c r="C113" t="n">
-        <v>321.0168980150915</v>
+        <v>318.9450345490796</v>
       </c>
       <c r="D113" t="n">
-        <v>315.4786915611019</v>
+        <v>314.4925528519528</v>
       </c>
       <c r="E113" t="n">
-        <v>319.0446472167969</v>
+        <v>317.6799926757812</v>
       </c>
       <c r="F113" t="n">
-        <v>7091900</v>
+        <v>5967600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>316.2456341157693</v>
+        <v>316.8632122574057</v>
       </c>
       <c r="C114" t="n">
-        <v>318.9450345490796</v>
+        <v>321.0866150343326</v>
       </c>
       <c r="D114" t="n">
-        <v>314.4925528519528</v>
+        <v>316.5743707451638</v>
       </c>
       <c r="E114" t="n">
-        <v>317.6799926757812</v>
+        <v>319.6921081542969</v>
       </c>
       <c r="F114" t="n">
-        <v>5967600</v>
+        <v>6831100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>316.8632122574057</v>
+        <v>317.7896151590316</v>
       </c>
       <c r="C115" t="n">
-        <v>321.0866150343326</v>
+        <v>319.2637952336624</v>
       </c>
       <c r="D115" t="n">
-        <v>316.5743707451638</v>
+        <v>303.5157608014752</v>
       </c>
       <c r="E115" t="n">
-        <v>319.6921081542969</v>
+        <v>305.3186645507812</v>
       </c>
       <c r="F115" t="n">
-        <v>6831100</v>
+        <v>13048000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>317.7896151590316</v>
+        <v>304.30263971785</v>
       </c>
       <c r="C116" t="n">
-        <v>319.2637952336624</v>
+        <v>308.0578528391844</v>
       </c>
       <c r="D116" t="n">
-        <v>303.5157608014752</v>
+        <v>301.8921111606905</v>
       </c>
       <c r="E116" t="n">
-        <v>305.3186645507812</v>
+        <v>306.0158996582031</v>
       </c>
       <c r="F116" t="n">
-        <v>13048000</v>
+        <v>9120200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>304.30263971785</v>
+        <v>307.3407046816708</v>
       </c>
       <c r="C117" t="n">
-        <v>308.0578528391844</v>
+        <v>312.7095945401492</v>
       </c>
       <c r="D117" t="n">
-        <v>301.8921111606905</v>
+        <v>307.0418926144709</v>
       </c>
       <c r="E117" t="n">
-        <v>306.0158996582031</v>
+        <v>311.7633056640625</v>
       </c>
       <c r="F117" t="n">
-        <v>9120200</v>
+        <v>7624200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>307.3407046816708</v>
+        <v>313.2475006793624</v>
       </c>
       <c r="C118" t="n">
-        <v>312.7095945401492</v>
+        <v>318.168142259306</v>
       </c>
       <c r="D118" t="n">
-        <v>307.0418926144709</v>
+        <v>312.7096085363555</v>
       </c>
       <c r="E118" t="n">
-        <v>311.7633056640625</v>
+        <v>315.4588012695312</v>
       </c>
       <c r="F118" t="n">
-        <v>7624200</v>
+        <v>8725500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>313.2475006793624</v>
+        <v>313.2275230423357</v>
       </c>
       <c r="C119" t="n">
-        <v>318.168142259306</v>
+        <v>318.9749280375353</v>
       </c>
       <c r="D119" t="n">
-        <v>312.7096085363555</v>
+        <v>310.7273811988043</v>
       </c>
       <c r="E119" t="n">
-        <v>315.4588012695312</v>
+        <v>318.8852844238281</v>
       </c>
       <c r="F119" t="n">
-        <v>8725500</v>
+        <v>12412900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>313.2275230423357</v>
+        <v>314.2634710190134</v>
       </c>
       <c r="C120" t="n">
-        <v>318.9749280375353</v>
+        <v>321.3356502974509</v>
       </c>
       <c r="D120" t="n">
-        <v>310.7273811988043</v>
+        <v>313.3670044395995</v>
       </c>
       <c r="E120" t="n">
-        <v>318.8852844238281</v>
+        <v>319.2538452148438</v>
       </c>
       <c r="F120" t="n">
-        <v>12412900</v>
+        <v>6674900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>314.2634710190134</v>
+        <v>314.5722564235918</v>
       </c>
       <c r="C121" t="n">
-        <v>321.3356502974509</v>
+        <v>320.7778503840851</v>
       </c>
       <c r="D121" t="n">
-        <v>313.3670044395995</v>
+        <v>313.117987052978</v>
       </c>
       <c r="E121" t="n">
-        <v>319.2538452148438</v>
+        <v>319.5725708007812</v>
       </c>
       <c r="F121" t="n">
-        <v>6674900</v>
+        <v>5474300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>314.5722564235918</v>
+        <v>320.1801887712339</v>
       </c>
       <c r="C122" t="n">
-        <v>320.7778503840851</v>
+        <v>324.4932049097204</v>
       </c>
       <c r="D122" t="n">
-        <v>313.117987052978</v>
+        <v>318.5466018009251</v>
       </c>
       <c r="E122" t="n">
-        <v>319.5725708007812</v>
+        <v>319.2139892578125</v>
       </c>
       <c r="F122" t="n">
-        <v>5474300</v>
+        <v>5257900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>320.1801887712339</v>
+        <v>318.0784411900573</v>
       </c>
       <c r="C123" t="n">
-        <v>324.4932049097204</v>
+        <v>321.5348424853333</v>
       </c>
       <c r="D123" t="n">
-        <v>318.5466018009251</v>
+        <v>313.5363155637196</v>
       </c>
       <c r="E123" t="n">
-        <v>319.2139892578125</v>
+        <v>318.5466003417969</v>
       </c>
       <c r="F123" t="n">
-        <v>5257900</v>
+        <v>8267200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>318.0784411900573</v>
+        <v>314.8113170354491</v>
       </c>
       <c r="C124" t="n">
-        <v>321.5348424853333</v>
+        <v>316.4449040988039</v>
       </c>
       <c r="D124" t="n">
-        <v>313.5363155637196</v>
+        <v>311.0760141261629</v>
       </c>
       <c r="E124" t="n">
-        <v>318.5466003417969</v>
+        <v>316.1161804199219</v>
       </c>
       <c r="F124" t="n">
-        <v>8267200</v>
+        <v>6439700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>314.8113170354491</v>
+        <v>312.2314560667069</v>
       </c>
       <c r="C125" t="n">
-        <v>316.4449040988039</v>
+        <v>315.1599358349184</v>
       </c>
       <c r="D125" t="n">
-        <v>311.0760141261629</v>
+        <v>308.9344312933075</v>
       </c>
       <c r="E125" t="n">
-        <v>316.1161804199219</v>
+        <v>314.7316284179688</v>
       </c>
       <c r="F125" t="n">
-        <v>6439700</v>
+        <v>8381500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>312.2314560667069</v>
+        <v>314.1937124870568</v>
       </c>
       <c r="C126" t="n">
-        <v>315.1599358349184</v>
+        <v>315.8870617531473</v>
       </c>
       <c r="D126" t="n">
-        <v>308.9344312933075</v>
+        <v>310.2293309503021</v>
       </c>
       <c r="E126" t="n">
-        <v>314.7316284179688</v>
+        <v>313.1976318359375</v>
       </c>
       <c r="F126" t="n">
-        <v>8381500</v>
+        <v>5271300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>314.1937124870568</v>
+        <v>312.0222791858673</v>
       </c>
       <c r="C127" t="n">
-        <v>315.8870617531473</v>
+        <v>313.8450934912395</v>
       </c>
       <c r="D127" t="n">
-        <v>310.2293309503021</v>
+        <v>307.1813415762761</v>
       </c>
       <c r="E127" t="n">
-        <v>313.1976318359375</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F127" t="n">
-        <v>5271300</v>
+        <v>6376700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>312.0222791858673</v>
+        <v>306.9323235221122</v>
       </c>
       <c r="C128" t="n">
-        <v>313.8450934912395</v>
+        <v>309.7313078758147</v>
       </c>
       <c r="D128" t="n">
-        <v>307.1813415762761</v>
+        <v>304.8206068898292</v>
       </c>
       <c r="E128" t="n">
-        <v>307.7490844726562</v>
+        <v>305.2987365722656</v>
       </c>
       <c r="F128" t="n">
-        <v>6376700</v>
+        <v>7514900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>306.9323235221122</v>
+        <v>306.3844668672209</v>
       </c>
       <c r="C129" t="n">
-        <v>309.7313078758147</v>
+        <v>309.1336593983733</v>
       </c>
       <c r="D129" t="n">
-        <v>304.8206068898292</v>
+        <v>305.2190694406472</v>
       </c>
       <c r="E129" t="n">
-        <v>305.2987365722656</v>
+        <v>305.9362487792969</v>
       </c>
       <c r="F129" t="n">
-        <v>7514900</v>
+        <v>4814100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>306.3844668672209</v>
+        <v>306.6434401255651</v>
       </c>
       <c r="C130" t="n">
-        <v>309.1336593983733</v>
+        <v>309.9105835049712</v>
       </c>
       <c r="D130" t="n">
-        <v>305.2190694406472</v>
+        <v>306.1752809950723</v>
       </c>
       <c r="E130" t="n">
-        <v>305.9362487792969</v>
+        <v>308.8945617675781</v>
       </c>
       <c r="F130" t="n">
-        <v>4814100</v>
+        <v>6401200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>306.6434401255651</v>
+        <v>310.0998441452866</v>
       </c>
       <c r="C131" t="n">
-        <v>309.9105835049712</v>
+        <v>311.4644698112407</v>
       </c>
       <c r="D131" t="n">
-        <v>306.1752809950723</v>
+        <v>306.1752838399166</v>
       </c>
       <c r="E131" t="n">
-        <v>308.8945617675781</v>
+        <v>307.2510375976562</v>
       </c>
       <c r="F131" t="n">
-        <v>6401200</v>
+        <v>6872200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>310.0998441452866</v>
+        <v>306.2051850075188</v>
       </c>
       <c r="C132" t="n">
-        <v>311.4644698112407</v>
+        <v>306.7331065856557</v>
       </c>
       <c r="D132" t="n">
-        <v>306.1752838399166</v>
+        <v>297.3301019351647</v>
       </c>
       <c r="E132" t="n">
-        <v>307.2510375976562</v>
+        <v>297.8480529785156</v>
       </c>
       <c r="F132" t="n">
-        <v>6872200</v>
+        <v>7191700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>306.2051850075188</v>
+        <v>296.8719016022564</v>
       </c>
       <c r="C133" t="n">
-        <v>306.7331065856557</v>
+        <v>301.2845318265138</v>
       </c>
       <c r="D133" t="n">
-        <v>297.3301019351647</v>
+        <v>295.8658503636263</v>
       </c>
       <c r="E133" t="n">
-        <v>297.8480529785156</v>
+        <v>298.5353393554688</v>
       </c>
       <c r="F133" t="n">
-        <v>7191700</v>
+        <v>6826400</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>296.8719016022564</v>
+        <v>298.6748142545254</v>
       </c>
       <c r="C134" t="n">
-        <v>301.2845318265138</v>
+        <v>301.7327894042891</v>
       </c>
       <c r="D134" t="n">
-        <v>295.8658503636263</v>
+        <v>297.8381100854838</v>
       </c>
       <c r="E134" t="n">
-        <v>298.5353393554688</v>
+        <v>300.4378662109375</v>
       </c>
       <c r="F134" t="n">
-        <v>6826400</v>
+        <v>14398100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>298.6748142545254</v>
+        <v>304.0038572697504</v>
       </c>
       <c r="C135" t="n">
-        <v>301.7327894042891</v>
+        <v>306.6434651794843</v>
       </c>
       <c r="D135" t="n">
-        <v>297.8381100854838</v>
+        <v>301.6630614260347</v>
       </c>
       <c r="E135" t="n">
-        <v>300.4378662109375</v>
+        <v>303.246826171875</v>
       </c>
       <c r="F135" t="n">
-        <v>14398100</v>
+        <v>7824500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>304.0038572697504</v>
+        <v>300.8163767349488</v>
       </c>
       <c r="C136" t="n">
-        <v>306.6434651794843</v>
+        <v>304.8405513457489</v>
       </c>
       <c r="D136" t="n">
-        <v>301.6630614260347</v>
+        <v>299.4417804808951</v>
       </c>
       <c r="E136" t="n">
-        <v>303.246826171875</v>
+        <v>302.5694885253906</v>
       </c>
       <c r="F136" t="n">
-        <v>7824500</v>
+        <v>5375900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>300.8163767349488</v>
+        <v>304.2827391072273</v>
       </c>
       <c r="C137" t="n">
-        <v>304.8405513457489</v>
+        <v>307.2809213034843</v>
       </c>
       <c r="D137" t="n">
-        <v>299.4417804808951</v>
+        <v>300.9857144661871</v>
       </c>
       <c r="E137" t="n">
-        <v>302.5694885253906</v>
+        <v>303.7149658203125</v>
       </c>
       <c r="F137" t="n">
-        <v>5375900</v>
+        <v>6280900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>304.2827391072273</v>
+        <v>302.9679242862715</v>
       </c>
       <c r="C138" t="n">
-        <v>307.2809213034843</v>
+        <v>306.6633753539059</v>
       </c>
       <c r="D138" t="n">
-        <v>300.9857144661871</v>
+        <v>301.8124669695884</v>
       </c>
       <c r="E138" t="n">
-        <v>303.7149658203125</v>
+        <v>304.3325500488281</v>
       </c>
       <c r="F138" t="n">
-        <v>6280900</v>
+        <v>7652700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>302.9679242862715</v>
+        <v>303.127283705864</v>
       </c>
       <c r="C139" t="n">
-        <v>306.6633753539059</v>
+        <v>303.3962145496307</v>
       </c>
       <c r="D139" t="n">
-        <v>301.8124669695884</v>
+        <v>293.1664767786049</v>
       </c>
       <c r="E139" t="n">
-        <v>304.3325500488281</v>
+        <v>294.3617553710938</v>
       </c>
       <c r="F139" t="n">
-        <v>7652700</v>
+        <v>9974400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>303.127283705864</v>
+        <v>297.5592048794472</v>
       </c>
       <c r="C140" t="n">
-        <v>303.3962145496307</v>
+        <v>299.5015440476056</v>
       </c>
       <c r="D140" t="n">
-        <v>293.1664767786049</v>
+        <v>294.7303392781201</v>
       </c>
       <c r="E140" t="n">
-        <v>294.3617553710938</v>
+        <v>298.3660278320312</v>
       </c>
       <c r="F140" t="n">
-        <v>9974400</v>
+        <v>9330300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>297.5592048794472</v>
+        <v>300.4179440831887</v>
       </c>
       <c r="C141" t="n">
-        <v>299.5015440476056</v>
+        <v>302.1511147673973</v>
       </c>
       <c r="D141" t="n">
-        <v>294.7303392781201</v>
+        <v>295.4275700673832</v>
       </c>
       <c r="E141" t="n">
-        <v>298.3660278320312</v>
+        <v>301.055419921875</v>
       </c>
       <c r="F141" t="n">
-        <v>9330300</v>
+        <v>10246900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>300.4179440831887</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="C142" t="n">
-        <v>302.1511147673973</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="D142" t="n">
-        <v>295.4275700673832</v>
+        <v>292.7381994806606</v>
       </c>
       <c r="E142" t="n">
-        <v>301.055419921875</v>
+        <v>297.340087890625</v>
       </c>
       <c r="F142" t="n">
-        <v>10246900</v>
+        <v>7707600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>303.8544344044319</v>
+        <v>296.6328211241279</v>
       </c>
       <c r="C143" t="n">
-        <v>303.8544344044319</v>
+        <v>301.2845313811459</v>
       </c>
       <c r="D143" t="n">
-        <v>292.7381994806606</v>
+        <v>294.6904819925192</v>
       </c>
       <c r="E143" t="n">
-        <v>297.340087890625</v>
+        <v>299.6210632324219</v>
       </c>
       <c r="F143" t="n">
-        <v>7707600</v>
+        <v>4376000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>296.6328211241279</v>
+        <v>299.5612984468797</v>
       </c>
       <c r="C144" t="n">
-        <v>301.2845313811459</v>
+        <v>303.2268985064469</v>
       </c>
       <c r="D144" t="n">
-        <v>294.6904819925192</v>
+        <v>298.286316373369</v>
       </c>
       <c r="E144" t="n">
-        <v>299.6210632324219</v>
+        <v>302.1411437988281</v>
       </c>
       <c r="F144" t="n">
-        <v>4376000</v>
+        <v>5501000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>299.5612984468797</v>
+        <v>301.2546730003434</v>
       </c>
       <c r="C145" t="n">
-        <v>303.2268985064469</v>
+        <v>303.7847266884853</v>
       </c>
       <c r="D145" t="n">
-        <v>298.286316373369</v>
+        <v>299.9398390775635</v>
       </c>
       <c r="E145" t="n">
-        <v>302.1411437988281</v>
+        <v>301.3642272949219</v>
       </c>
       <c r="F145" t="n">
-        <v>5501000</v>
+        <v>4413900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>301.2546730003434</v>
+        <v>306.5239246667074</v>
       </c>
       <c r="C146" t="n">
-        <v>303.7847266884853</v>
+        <v>309.8607706923777</v>
       </c>
       <c r="D146" t="n">
-        <v>299.9398390775635</v>
+        <v>306.4940434616348</v>
       </c>
       <c r="E146" t="n">
-        <v>301.3642272949219</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F146" t="n">
-        <v>4413900</v>
+        <v>6879300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>306.5239246667074</v>
+        <v>306.792884650012</v>
       </c>
       <c r="C147" t="n">
-        <v>309.8607706923777</v>
+        <v>308.3666789299265</v>
       </c>
       <c r="D147" t="n">
-        <v>306.4940434616348</v>
+        <v>302.4001646993119</v>
       </c>
       <c r="E147" t="n">
-        <v>307.7490844726562</v>
+        <v>307.0817565917969</v>
       </c>
       <c r="F147" t="n">
-        <v>6879300</v>
+        <v>4811500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>306.792884650012</v>
+        <v>307.5000714824076</v>
       </c>
       <c r="C148" t="n">
-        <v>308.3666789299265</v>
+        <v>307.7889434035062</v>
       </c>
       <c r="D148" t="n">
-        <v>302.4001646993119</v>
+        <v>302.3204699616491</v>
       </c>
       <c r="E148" t="n">
-        <v>307.0817565917969</v>
+        <v>303.1671142578125</v>
       </c>
       <c r="F148" t="n">
-        <v>4811500</v>
+        <v>5190000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>307.5000714824076</v>
+        <v>302.7388065700545</v>
       </c>
       <c r="C149" t="n">
-        <v>307.7889434035062</v>
+        <v>308.5360036681458</v>
       </c>
       <c r="D149" t="n">
-        <v>302.3204699616491</v>
+        <v>301.155041869684</v>
       </c>
       <c r="E149" t="n">
-        <v>303.1671142578125</v>
+        <v>308.1774291992188</v>
       </c>
       <c r="F149" t="n">
-        <v>5190000</v>
+        <v>6787200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>302.7388065700545</v>
+        <v>307.2610301082847</v>
       </c>
       <c r="C150" t="n">
-        <v>308.5360036681458</v>
+        <v>310.8967187654788</v>
       </c>
       <c r="D150" t="n">
-        <v>301.155041869684</v>
+        <v>306.2848600302058</v>
       </c>
       <c r="E150" t="n">
-        <v>308.1774291992188</v>
+        <v>310.149658203125</v>
       </c>
       <c r="F150" t="n">
-        <v>6787200</v>
+        <v>5571000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>307.2610301082847</v>
+        <v>311.7732461183575</v>
       </c>
       <c r="C151" t="n">
-        <v>310.8967187654788</v>
+        <v>315.4886379179251</v>
       </c>
       <c r="D151" t="n">
-        <v>306.2848600302058</v>
+        <v>310.2990358004714</v>
       </c>
       <c r="E151" t="n">
-        <v>310.149658203125</v>
+        <v>314.6718444824219</v>
       </c>
       <c r="F151" t="n">
-        <v>5571000</v>
+        <v>4831400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>311.7732461183575</v>
+        <v>315.1101522104624</v>
       </c>
       <c r="C152" t="n">
-        <v>315.4886379179251</v>
+        <v>316.7536793728972</v>
       </c>
       <c r="D152" t="n">
-        <v>310.2990358004714</v>
+        <v>313.3371296864953</v>
       </c>
       <c r="E152" t="n">
-        <v>314.6718444824219</v>
+        <v>313.8650512695312</v>
       </c>
       <c r="F152" t="n">
-        <v>4831400</v>
+        <v>5695800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>315.1101522104624</v>
+        <v>315.3591594617635</v>
       </c>
       <c r="C153" t="n">
-        <v>316.7536793728972</v>
+        <v>318.1880250357548</v>
       </c>
       <c r="D153" t="n">
-        <v>313.3371296864953</v>
+        <v>313.9447114757824</v>
       </c>
       <c r="E153" t="n">
-        <v>313.8650512695312</v>
+        <v>315.7774963378906</v>
       </c>
       <c r="F153" t="n">
-        <v>5695800</v>
+        <v>8082300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>315.3591594617635</v>
+        <v>315.159944872979</v>
       </c>
       <c r="C154" t="n">
-        <v>318.1880250357548</v>
+        <v>316.305431661891</v>
       </c>
       <c r="D154" t="n">
-        <v>313.9447114757824</v>
+        <v>311.1258299735145</v>
       </c>
       <c r="E154" t="n">
-        <v>315.7774963378906</v>
+        <v>312.7095947265625</v>
       </c>
       <c r="F154" t="n">
-        <v>8082300</v>
+        <v>5506800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>315.159944872979</v>
+        <v>312.7793059315876</v>
       </c>
       <c r="C155" t="n">
-        <v>316.305431661891</v>
+        <v>315.6480231708821</v>
       </c>
       <c r="D155" t="n">
-        <v>311.1258299735145</v>
+        <v>307.6096447395195</v>
       </c>
       <c r="E155" t="n">
-        <v>312.7095947265625</v>
+        <v>308.7252502441406</v>
       </c>
       <c r="F155" t="n">
-        <v>5506800</v>
+        <v>6806900</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>312.7793059315876</v>
+        <v>309.7910754200902</v>
       </c>
       <c r="C156" t="n">
-        <v>315.6480231708821</v>
+        <v>310.1396793547997</v>
       </c>
       <c r="D156" t="n">
-        <v>307.6096447395195</v>
+        <v>306.8526251277434</v>
       </c>
       <c r="E156" t="n">
-        <v>308.7252502441406</v>
+        <v>310.0699768066406</v>
       </c>
       <c r="F156" t="n">
-        <v>6806900</v>
+        <v>5666600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>309.7910754200902</v>
+        <v>309.2830795800573</v>
       </c>
       <c r="C157" t="n">
-        <v>310.1396793547997</v>
+        <v>310.9764290509568</v>
       </c>
       <c r="D157" t="n">
-        <v>306.8526251277434</v>
+        <v>303.8146058713554</v>
       </c>
       <c r="E157" t="n">
-        <v>310.0699768066406</v>
+        <v>307.66943359375</v>
       </c>
       <c r="F157" t="n">
-        <v>5666600</v>
+        <v>7275000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>309.2830795800573</v>
+        <v>305.8963913711518</v>
       </c>
       <c r="C158" t="n">
-        <v>310.9764290509568</v>
+        <v>308.7651086725988</v>
       </c>
       <c r="D158" t="n">
-        <v>303.8146058713554</v>
+        <v>303.3065754519026</v>
       </c>
       <c r="E158" t="n">
-        <v>307.66943359375</v>
+        <v>308.2073059082031</v>
       </c>
       <c r="F158" t="n">
-        <v>7275000</v>
+        <v>5616900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>305.8963913711518</v>
+        <v>306.3048043469537</v>
       </c>
       <c r="C159" t="n">
-        <v>308.7651086725988</v>
+        <v>309.6018292319215</v>
       </c>
       <c r="D159" t="n">
-        <v>303.3065754519026</v>
+        <v>304.8604750852367</v>
       </c>
       <c r="E159" t="n">
-        <v>308.2073059082031</v>
+        <v>308.4364013671875</v>
       </c>
       <c r="F159" t="n">
-        <v>5616900</v>
+        <v>6261500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>306.3048043469537</v>
+        <v>310.9763962887836</v>
       </c>
       <c r="C160" t="n">
-        <v>309.6018292319215</v>
+        <v>312.7294775914766</v>
       </c>
       <c r="D160" t="n">
-        <v>304.8604750852367</v>
+        <v>307.5299352956203</v>
       </c>
       <c r="E160" t="n">
-        <v>308.4364013671875</v>
+        <v>308.0877380371094</v>
       </c>
       <c r="F160" t="n">
-        <v>6261500</v>
+        <v>8839900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>310.9763962887836</v>
+        <v>335.0815497318694</v>
       </c>
       <c r="C161" t="n">
-        <v>312.7294775914766</v>
+        <v>340.6396971989305</v>
       </c>
       <c r="D161" t="n">
-        <v>307.5299352956203</v>
+        <v>332.4817936312549</v>
       </c>
       <c r="E161" t="n">
-        <v>308.0877380371094</v>
+        <v>333.5475769042969</v>
       </c>
       <c r="F161" t="n">
-        <v>8839900</v>
+        <v>16658600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>335.0815497318694</v>
+        <v>330.8183346281009</v>
       </c>
       <c r="C162" t="n">
-        <v>340.6396971989305</v>
+        <v>331.1968501776938</v>
       </c>
       <c r="D162" t="n">
-        <v>332.4817936312549</v>
+        <v>326.7941598769157</v>
       </c>
       <c r="E162" t="n">
-        <v>333.5475769042969</v>
+        <v>328.5472717285156</v>
       </c>
       <c r="F162" t="n">
-        <v>16658600</v>
+        <v>11241100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>330.8183346281009</v>
+        <v>331.5753827423343</v>
       </c>
       <c r="C163" t="n">
-        <v>331.1968501776938</v>
+        <v>334.5337439447337</v>
       </c>
       <c r="D163" t="n">
-        <v>326.7941598769157</v>
+        <v>326.6447706056774</v>
       </c>
       <c r="E163" t="n">
-        <v>328.5472717285156</v>
+        <v>326.744384765625</v>
       </c>
       <c r="F163" t="n">
-        <v>11241100</v>
+        <v>6726100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>331.5753827423343</v>
+        <v>326.7144870306598</v>
       </c>
       <c r="C164" t="n">
-        <v>334.5337439447337</v>
+        <v>328.4974800902166</v>
       </c>
       <c r="D164" t="n">
-        <v>326.6447706056774</v>
+        <v>324.1246709928955</v>
       </c>
       <c r="E164" t="n">
-        <v>326.744384765625</v>
+        <v>325.5690002441406</v>
       </c>
       <c r="F164" t="n">
-        <v>6726100</v>
+        <v>6712400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>326.7144870306598</v>
+        <v>323.8357678318997</v>
       </c>
       <c r="C165" t="n">
-        <v>328.4974800902166</v>
+        <v>324.3039269566456</v>
       </c>
       <c r="D165" t="n">
-        <v>324.1246709928955</v>
+        <v>318.3971759556802</v>
       </c>
       <c r="E165" t="n">
-        <v>325.5690002441406</v>
+        <v>320.7678527832031</v>
       </c>
       <c r="F165" t="n">
-        <v>6712400</v>
+        <v>5893200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>323.8357678318997</v>
+        <v>322.4811180854182</v>
       </c>
       <c r="C166" t="n">
-        <v>324.3039269566456</v>
+        <v>323.3078516694185</v>
       </c>
       <c r="D166" t="n">
-        <v>318.3971759556802</v>
+        <v>316.7536542120865</v>
       </c>
       <c r="E166" t="n">
-        <v>320.7678527832031</v>
+        <v>317.5505065917969</v>
       </c>
       <c r="F166" t="n">
-        <v>5893200</v>
+        <v>7808400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>322.4811180854182</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="C167" t="n">
-        <v>323.3078516694185</v>
+        <v>322.4213711748579</v>
       </c>
       <c r="D167" t="n">
-        <v>316.7536542120865</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="E167" t="n">
-        <v>317.5505065917969</v>
+        <v>320.0208129882812</v>
       </c>
       <c r="F167" t="n">
-        <v>7808400</v>
+        <v>7186100</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>318.2876422602183</v>
+        <v>319.7319477733878</v>
       </c>
       <c r="C168" t="n">
-        <v>322.4213711748579</v>
+        <v>319.8116512556435</v>
       </c>
       <c r="D168" t="n">
-        <v>318.2876422602183</v>
+        <v>314.9208911627371</v>
       </c>
       <c r="E168" t="n">
-        <v>320.0208129882812</v>
+        <v>317.5405883789062</v>
       </c>
       <c r="F168" t="n">
-        <v>7186100</v>
+        <v>5950200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>319.7319477733878</v>
+        <v>317.8493444570379</v>
       </c>
       <c r="C169" t="n">
-        <v>319.8116512556435</v>
+        <v>323.9055014903766</v>
       </c>
       <c r="D169" t="n">
-        <v>314.9208911627371</v>
+        <v>316.7636201861749</v>
       </c>
       <c r="E169" t="n">
-        <v>317.5405883789062</v>
+        <v>322.5906677246094</v>
       </c>
       <c r="F169" t="n">
-        <v>5950200</v>
+        <v>9586200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,25 +4837,25 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>317.8493444570379</v>
+        <v>323.7186157532602</v>
       </c>
       <c r="C170" t="n">
-        <v>323.9055014903766</v>
+        <v>328.3001007904417</v>
       </c>
       <c r="D170" t="n">
-        <v>316.7636201861749</v>
+        <v>323.5988431448615</v>
       </c>
       <c r="E170" t="n">
-        <v>322.5906677246094</v>
+        <v>325.8147277832031</v>
       </c>
       <c r="F170" t="n">
-        <v>9586200</v>
+        <v>6235200</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -4863,25 +4863,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>323.7186157532602</v>
+        <v>323.1895917984963</v>
       </c>
       <c r="C171" t="n">
-        <v>328.3001007904417</v>
+        <v>324.8165740981451</v>
       </c>
       <c r="D171" t="n">
-        <v>323.5988431448615</v>
+        <v>319.2069699014023</v>
       </c>
       <c r="E171" t="n">
-        <v>325.8147277832031</v>
+        <v>319.7160339355469</v>
       </c>
       <c r="F171" t="n">
-        <v>6235200</v>
+        <v>7950400</v>
       </c>
       <c r="G171" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>323.1895917984963</v>
+        <v>320.7740745871976</v>
       </c>
       <c r="C172" t="n">
-        <v>324.8165740981451</v>
+        <v>322.7304316048222</v>
       </c>
       <c r="D172" t="n">
-        <v>319.2069699014023</v>
+        <v>319.6561562914121</v>
       </c>
       <c r="E172" t="n">
-        <v>319.7160339355469</v>
+        <v>321.9219360351562</v>
       </c>
       <c r="F172" t="n">
-        <v>7950400</v>
+        <v>5277400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>320.7740745871976</v>
+        <v>323.3992105807512</v>
       </c>
       <c r="C173" t="n">
-        <v>322.7304316048222</v>
+        <v>328.3999303437295</v>
       </c>
       <c r="D173" t="n">
-        <v>319.6561562914121</v>
+        <v>323.2395036115653</v>
       </c>
       <c r="E173" t="n">
-        <v>321.9219360351562</v>
+        <v>325.1459655761719</v>
       </c>
       <c r="F173" t="n">
-        <v>5277400</v>
+        <v>6054500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>323.3992105807512</v>
+        <v>323.8283954010087</v>
       </c>
       <c r="C174" t="n">
-        <v>328.3999303437295</v>
+        <v>332.8117065140525</v>
       </c>
       <c r="D174" t="n">
-        <v>323.2395036115653</v>
+        <v>323.1696155974001</v>
       </c>
       <c r="E174" t="n">
-        <v>325.1459655761719</v>
+        <v>332.023193359375</v>
       </c>
       <c r="F174" t="n">
-        <v>6054500</v>
+        <v>5305800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>323.8283954010087</v>
+        <v>332.7118894931572</v>
       </c>
       <c r="C175" t="n">
-        <v>332.8117065140525</v>
+        <v>334.5485043686942</v>
       </c>
       <c r="D175" t="n">
-        <v>323.1696155974001</v>
+        <v>328.8790136983196</v>
       </c>
       <c r="E175" t="n">
-        <v>332.023193359375</v>
+        <v>329.2982482910156</v>
       </c>
       <c r="F175" t="n">
-        <v>5305800</v>
+        <v>12858100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>332.7118894931572</v>
+        <v>329.4779084191791</v>
       </c>
       <c r="C176" t="n">
-        <v>334.5485043686942</v>
+        <v>331.0450044691208</v>
       </c>
       <c r="D176" t="n">
-        <v>328.8790136983196</v>
+        <v>326.2139829663294</v>
       </c>
       <c r="E176" t="n">
-        <v>329.2982482910156</v>
+        <v>330.1366882324219</v>
       </c>
       <c r="F176" t="n">
-        <v>12858100</v>
+        <v>9422500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>329.4779084191791</v>
+        <v>329.2283866364193</v>
       </c>
       <c r="C177" t="n">
-        <v>331.0450044691208</v>
+        <v>331.9034099041888</v>
       </c>
       <c r="D177" t="n">
-        <v>326.2139829663294</v>
+        <v>326.6332016248708</v>
       </c>
       <c r="E177" t="n">
-        <v>330.1366882324219</v>
+        <v>330.5060119628906</v>
       </c>
       <c r="F177" t="n">
-        <v>9422500</v>
+        <v>7034500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>329.2283866364193</v>
+        <v>329.9071152744464</v>
       </c>
       <c r="C178" t="n">
-        <v>331.9034099041888</v>
+        <v>332.8117230001985</v>
       </c>
       <c r="D178" t="n">
-        <v>326.6332016248708</v>
+        <v>328.2102858122996</v>
       </c>
       <c r="E178" t="n">
-        <v>330.5060119628906</v>
+        <v>328.2701721191406</v>
       </c>
       <c r="F178" t="n">
-        <v>7034500</v>
+        <v>7462100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>329.9071152744464</v>
+        <v>325.8546513791287</v>
       </c>
       <c r="C179" t="n">
-        <v>332.8117230001985</v>
+        <v>327.890877227978</v>
       </c>
       <c r="D179" t="n">
-        <v>328.2102858122996</v>
+        <v>323.908285453</v>
       </c>
       <c r="E179" t="n">
-        <v>328.2701721191406</v>
+        <v>325.8746337890625</v>
       </c>
       <c r="F179" t="n">
-        <v>7462100</v>
+        <v>8705100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>325.8546513791287</v>
+        <v>325.2258042905605</v>
       </c>
       <c r="C180" t="n">
-        <v>327.890877227978</v>
+        <v>330.8453695289686</v>
       </c>
       <c r="D180" t="n">
-        <v>323.908285453</v>
+        <v>325.0561365774909</v>
       </c>
       <c r="E180" t="n">
-        <v>325.8746337890625</v>
+        <v>327.0025024414062</v>
       </c>
       <c r="F180" t="n">
-        <v>8705100</v>
+        <v>5917400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>325.2258042905605</v>
+        <v>325.4054745838858</v>
       </c>
       <c r="C181" t="n">
-        <v>330.8453695289686</v>
+        <v>326.473467283892</v>
       </c>
       <c r="D181" t="n">
-        <v>325.0561365774909</v>
+        <v>320.304934449476</v>
       </c>
       <c r="E181" t="n">
-        <v>327.0025024414062</v>
+        <v>324.3474426269531</v>
       </c>
       <c r="F181" t="n">
-        <v>5917400</v>
+        <v>8105400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>325.4054745838858</v>
+        <v>324.8964310814758</v>
       </c>
       <c r="C182" t="n">
-        <v>326.473467283892</v>
+        <v>331.0550035619541</v>
       </c>
       <c r="D182" t="n">
-        <v>320.304934449476</v>
+        <v>324.7467153160326</v>
       </c>
       <c r="E182" t="n">
-        <v>324.3474426269531</v>
+        <v>325.7548217773438</v>
       </c>
       <c r="F182" t="n">
-        <v>8105400</v>
+        <v>14104500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>324.8964310814758</v>
+        <v>326.6531732008884</v>
       </c>
       <c r="C183" t="n">
-        <v>331.0550035619541</v>
+        <v>327.2520362551611</v>
       </c>
       <c r="D183" t="n">
-        <v>324.7467153160326</v>
+        <v>318.0890659929148</v>
       </c>
       <c r="E183" t="n">
-        <v>325.7548217773438</v>
+        <v>322.1714782714844</v>
       </c>
       <c r="F183" t="n">
-        <v>14104500</v>
+        <v>10079300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>326.6531732008884</v>
+        <v>321.911976472278</v>
       </c>
       <c r="C184" t="n">
-        <v>327.2520362551611</v>
+        <v>322.900130958607</v>
       </c>
       <c r="D184" t="n">
-        <v>318.0890659929148</v>
+        <v>312.8088926463686</v>
       </c>
       <c r="E184" t="n">
-        <v>322.1714782714844</v>
+        <v>316.7315979003906</v>
       </c>
       <c r="F184" t="n">
-        <v>10079300</v>
+        <v>10125300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>321.911976472278</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="C185" t="n">
-        <v>322.900130958607</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="D185" t="n">
-        <v>312.8088926463686</v>
+        <v>308.4270199555073</v>
       </c>
       <c r="E185" t="n">
-        <v>316.7315979003906</v>
+        <v>311.8207092285156</v>
       </c>
       <c r="F185" t="n">
-        <v>10125300</v>
+        <v>8992800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>317.0609741306723</v>
+        <v>316.2025752130079</v>
       </c>
       <c r="C186" t="n">
-        <v>317.0609741306723</v>
+        <v>324.1577974184449</v>
       </c>
       <c r="D186" t="n">
-        <v>308.4270199555073</v>
+        <v>316.1127457580593</v>
       </c>
       <c r="E186" t="n">
-        <v>311.8207092285156</v>
+        <v>319.5862731933594</v>
       </c>
       <c r="F186" t="n">
-        <v>8992800</v>
+        <v>6981700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>316.2025752130079</v>
+        <v>321.8021573858913</v>
       </c>
       <c r="C187" t="n">
-        <v>324.1577974184449</v>
+        <v>325.3755359367605</v>
       </c>
       <c r="D187" t="n">
-        <v>316.1127457580593</v>
+        <v>320.3748163907789</v>
       </c>
       <c r="E187" t="n">
-        <v>319.5862731933594</v>
+        <v>322.9700012207031</v>
       </c>
       <c r="F187" t="n">
-        <v>6981700</v>
+        <v>7176300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>321.8021573858913</v>
+        <v>320.7541174065557</v>
       </c>
       <c r="C188" t="n">
-        <v>325.3755359367605</v>
+        <v>323.3193590911711</v>
       </c>
       <c r="D188" t="n">
-        <v>320.3748163907789</v>
+        <v>317.8395186449595</v>
       </c>
       <c r="E188" t="n">
-        <v>322.9700012207031</v>
+        <v>319.0772399902344</v>
       </c>
       <c r="F188" t="n">
-        <v>7176300</v>
+        <v>5582000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>320.7541174065557</v>
+        <v>318.0691001697331</v>
       </c>
       <c r="C189" t="n">
-        <v>323.3193590911711</v>
+        <v>324.8864216353897</v>
       </c>
       <c r="D189" t="n">
-        <v>317.8395186449595</v>
+        <v>316.4121747162161</v>
       </c>
       <c r="E189" t="n">
-        <v>319.0772399902344</v>
+        <v>324.4472351074219</v>
       </c>
       <c r="F189" t="n">
-        <v>5582000</v>
+        <v>6340400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>318.0691001697331</v>
+        <v>326.0143312805488</v>
       </c>
       <c r="C190" t="n">
-        <v>324.8864216353897</v>
+        <v>326.2938108474966</v>
       </c>
       <c r="D190" t="n">
-        <v>316.4121747162161</v>
+        <v>319.5862707797614</v>
       </c>
       <c r="E190" t="n">
-        <v>324.4472351074219</v>
+        <v>322.3611145019531</v>
       </c>
       <c r="F190" t="n">
-        <v>6340400</v>
+        <v>5793100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>326.0143312805488</v>
+        <v>321.4029160285921</v>
       </c>
       <c r="C191" t="n">
-        <v>326.2938108474966</v>
+        <v>323.1097366498532</v>
       </c>
       <c r="D191" t="n">
-        <v>319.5862707797614</v>
+        <v>317.3703988636284</v>
       </c>
       <c r="E191" t="n">
-        <v>322.3611145019531</v>
+        <v>318.4583740234375</v>
       </c>
       <c r="F191" t="n">
-        <v>5793100</v>
+        <v>5958900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>321.4029160285921</v>
+        <v>321.1633691478087</v>
       </c>
       <c r="C192" t="n">
-        <v>323.1097366498532</v>
+        <v>325.3256196452838</v>
       </c>
       <c r="D192" t="n">
-        <v>317.3703988636284</v>
+        <v>319.206981650181</v>
       </c>
       <c r="E192" t="n">
-        <v>318.4583740234375</v>
+        <v>321.7922058105469</v>
       </c>
       <c r="F192" t="n">
-        <v>5958900</v>
+        <v>5543200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>321.1633691478087</v>
+        <v>322.7603745094088</v>
       </c>
       <c r="C193" t="n">
-        <v>325.3256196452838</v>
+        <v>325.8346802814496</v>
       </c>
       <c r="D193" t="n">
-        <v>319.206981650181</v>
+        <v>322.1515202620241</v>
       </c>
       <c r="E193" t="n">
-        <v>321.7922058105469</v>
+        <v>323.2195434570312</v>
       </c>
       <c r="F193" t="n">
-        <v>5543200</v>
+        <v>6803000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>322.7603745094088</v>
+        <v>325.0860736201939</v>
       </c>
       <c r="C194" t="n">
-        <v>325.8346802814496</v>
+        <v>332.6719869892291</v>
       </c>
       <c r="D194" t="n">
-        <v>322.1515202620241</v>
+        <v>323.7785051975129</v>
       </c>
       <c r="E194" t="n">
-        <v>323.2195434570312</v>
+        <v>332.5022888183594</v>
       </c>
       <c r="F194" t="n">
-        <v>6803000</v>
+        <v>9248400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>325.0860736201939</v>
+        <v>332.8816048599044</v>
       </c>
       <c r="C195" t="n">
-        <v>332.6719869892291</v>
+        <v>336.1954560330155</v>
       </c>
       <c r="D195" t="n">
-        <v>323.7785051975129</v>
+        <v>329.3581516101117</v>
       </c>
       <c r="E195" t="n">
-        <v>332.5022888183594</v>
+        <v>329.7673950195312</v>
       </c>
       <c r="F195" t="n">
-        <v>9248400</v>
+        <v>6895200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>332.8816048599044</v>
+        <v>330.3862161708477</v>
       </c>
       <c r="C196" t="n">
-        <v>336.1954560330155</v>
+        <v>331.7137365067053</v>
       </c>
       <c r="D196" t="n">
-        <v>329.3581516101117</v>
+        <v>326.3936334980882</v>
       </c>
       <c r="E196" t="n">
-        <v>329.7673950195312</v>
+        <v>326.6331787109375</v>
       </c>
       <c r="F196" t="n">
-        <v>6895200</v>
+        <v>14716700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>330.3862161708477</v>
+        <v>327.7211572947962</v>
       </c>
       <c r="C197" t="n">
-        <v>331.7137365067053</v>
+        <v>332.3825110173034</v>
       </c>
       <c r="D197" t="n">
-        <v>326.3936334980882</v>
+        <v>325.255736249892</v>
       </c>
       <c r="E197" t="n">
-        <v>326.6331787109375</v>
+        <v>325.994384765625</v>
       </c>
       <c r="F197" t="n">
-        <v>14716700</v>
+        <v>15132400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>327.7211572947962</v>
+        <v>328.2102765273601</v>
       </c>
       <c r="C198" t="n">
-        <v>332.3825110173034</v>
+        <v>330.6657064213508</v>
       </c>
       <c r="D198" t="n">
-        <v>325.255736249892</v>
+        <v>327.4816192000871</v>
       </c>
       <c r="E198" t="n">
-        <v>325.994384765625</v>
+        <v>327.8709106445312</v>
       </c>
       <c r="F198" t="n">
-        <v>15132400</v>
+        <v>11113400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>328.2102765273601</v>
+        <v>328.3899311009871</v>
       </c>
       <c r="C199" t="n">
-        <v>330.6657064213508</v>
+        <v>334.1791639025663</v>
       </c>
       <c r="D199" t="n">
-        <v>327.4816192000871</v>
+        <v>326.6132329961447</v>
       </c>
       <c r="E199" t="n">
-        <v>327.8709106445312</v>
+        <v>331.6139526367188</v>
       </c>
       <c r="F199" t="n">
-        <v>11113400</v>
+        <v>8197200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>328.3899311009871</v>
+        <v>331.9433302412046</v>
       </c>
       <c r="C200" t="n">
-        <v>334.1791639025663</v>
+        <v>339.3096503518051</v>
       </c>
       <c r="D200" t="n">
-        <v>326.6132329961447</v>
+        <v>329.457957205559</v>
       </c>
       <c r="E200" t="n">
-        <v>331.6139526367188</v>
+        <v>329.9071044921875</v>
       </c>
       <c r="F200" t="n">
-        <v>8197200</v>
+        <v>7050200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>331.9433302412046</v>
+        <v>331.6239148421282</v>
       </c>
       <c r="C201" t="n">
-        <v>339.3096503518051</v>
+        <v>339.0900555815327</v>
       </c>
       <c r="D201" t="n">
-        <v>329.457957205559</v>
+        <v>330.8254104732138</v>
       </c>
       <c r="E201" t="n">
-        <v>329.9071044921875</v>
+        <v>335.6065368652344</v>
       </c>
       <c r="F201" t="n">
-        <v>7050200</v>
+        <v>16717400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>331.6239148421282</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="C202" t="n">
-        <v>339.0900555815327</v>
+        <v>345.168769346924</v>
       </c>
       <c r="D202" t="n">
-        <v>330.8254104732138</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="E202" t="n">
-        <v>335.6065368652344</v>
+        <v>341.0164794921875</v>
       </c>
       <c r="F202" t="n">
-        <v>16717400</v>
+        <v>11710900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>337.6427420814022</v>
+        <v>341.1262760402287</v>
       </c>
       <c r="C203" t="n">
-        <v>345.168769346924</v>
+        <v>343.6515833825353</v>
       </c>
       <c r="D203" t="n">
-        <v>337.6427420814022</v>
+        <v>338.4512224777037</v>
       </c>
       <c r="E203" t="n">
-        <v>341.0164794921875</v>
+        <v>342.4537963867188</v>
       </c>
       <c r="F203" t="n">
-        <v>11710900</v>
+        <v>7957900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>341.1262760402287</v>
+        <v>343.9210864742992</v>
       </c>
       <c r="C204" t="n">
-        <v>343.6515833825353</v>
+        <v>352.7047566164018</v>
       </c>
       <c r="D204" t="n">
-        <v>338.4512224777037</v>
+        <v>340.3477382034001</v>
       </c>
       <c r="E204" t="n">
-        <v>342.4537963867188</v>
+        <v>350.4289855957031</v>
       </c>
       <c r="F204" t="n">
-        <v>7957900</v>
+        <v>13025900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>343.9210864742992</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="C205" t="n">
-        <v>352.7047566164018</v>
+        <v>361.45849609375</v>
       </c>
       <c r="D205" t="n">
-        <v>340.3477382034001</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="E205" t="n">
-        <v>350.4289855957031</v>
+        <v>361.45849609375</v>
       </c>
       <c r="F205" t="n">
-        <v>13025900</v>
+        <v>9814800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>351.8563396289383</v>
+        <v>362.3268927646901</v>
       </c>
       <c r="C206" t="n">
-        <v>361.45849609375</v>
+        <v>364.3431361331269</v>
       </c>
       <c r="D206" t="n">
-        <v>351.8563396289383</v>
+        <v>348.2031370590358</v>
       </c>
       <c r="E206" t="n">
-        <v>361.45849609375</v>
+        <v>356.5875549316406</v>
       </c>
       <c r="F206" t="n">
-        <v>9814800</v>
+        <v>11623800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>362.3268927646901</v>
+        <v>347.744003265132</v>
       </c>
       <c r="C207" t="n">
-        <v>364.3431361331269</v>
+        <v>355.4197158554798</v>
       </c>
       <c r="D207" t="n">
-        <v>348.2031370590358</v>
+        <v>346.2767278330053</v>
       </c>
       <c r="E207" t="n">
-        <v>356.5875549316406</v>
+        <v>351.5469360351562</v>
       </c>
       <c r="F207" t="n">
-        <v>11623800</v>
+        <v>7332500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>347.744003265132</v>
+        <v>349.650411586948</v>
       </c>
       <c r="C208" t="n">
-        <v>355.4197158554798</v>
+        <v>350.9480192181019</v>
       </c>
       <c r="D208" t="n">
-        <v>346.2767278330053</v>
+        <v>345.0489747278172</v>
       </c>
       <c r="E208" t="n">
-        <v>351.5469360351562</v>
+        <v>346.8855590820312</v>
       </c>
       <c r="F208" t="n">
-        <v>7332500</v>
+        <v>10215200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>349.650411586948</v>
+        <v>344.6597048505295</v>
       </c>
       <c r="C209" t="n">
-        <v>350.9480192181019</v>
+        <v>347.8537833381742</v>
       </c>
       <c r="D209" t="n">
-        <v>345.0489747278172</v>
+        <v>343.7813622043677</v>
       </c>
       <c r="E209" t="n">
-        <v>346.8855590820312</v>
+        <v>347.5543518066406</v>
       </c>
       <c r="F209" t="n">
-        <v>10215200</v>
+        <v>6606300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>344.6597048505295</v>
+        <v>349.9798320131086</v>
       </c>
       <c r="C210" t="n">
-        <v>347.8537833381742</v>
+        <v>350.5188392207221</v>
       </c>
       <c r="D210" t="n">
-        <v>343.7813622043677</v>
+        <v>344.6896415212494</v>
       </c>
       <c r="E210" t="n">
-        <v>347.5543518066406</v>
+        <v>348.3229064941406</v>
       </c>
       <c r="F210" t="n">
-        <v>6606300</v>
+        <v>4702800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>349.9798320131086</v>
+        <v>351.0777829959364</v>
       </c>
       <c r="C211" t="n">
-        <v>350.5188392207221</v>
+        <v>358.8233725828445</v>
       </c>
       <c r="D211" t="n">
-        <v>344.6896415212494</v>
+        <v>350.3990207986449</v>
       </c>
       <c r="E211" t="n">
-        <v>348.3229064941406</v>
+        <v>357.0866088867188</v>
       </c>
       <c r="F211" t="n">
-        <v>4702800</v>
+        <v>9964600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>351.0777829959364</v>
+        <v>355.1102963305153</v>
       </c>
       <c r="C212" t="n">
-        <v>358.8233725828445</v>
+        <v>359.2725774384029</v>
       </c>
       <c r="D212" t="n">
-        <v>350.3990207986449</v>
+        <v>353.0241754046451</v>
       </c>
       <c r="E212" t="n">
-        <v>357.0866088867188</v>
+        <v>355.3598327636719</v>
       </c>
       <c r="F212" t="n">
-        <v>9964600</v>
+        <v>6632400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>355.1102963305153</v>
+        <v>353.3435751194357</v>
       </c>
       <c r="C213" t="n">
-        <v>359.2725774384029</v>
+        <v>359.7616446111089</v>
       </c>
       <c r="D213" t="n">
-        <v>353.0241754046451</v>
+        <v>348.4726192666298</v>
       </c>
       <c r="E213" t="n">
-        <v>355.3598327636719</v>
+        <v>354.4814758300781</v>
       </c>
       <c r="F213" t="n">
-        <v>6632400</v>
+        <v>8850000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>353.3435751194357</v>
+        <v>357.3760808599296</v>
       </c>
       <c r="C214" t="n">
-        <v>359.7616446111089</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="D214" t="n">
-        <v>348.4726192666298</v>
+        <v>356.4477822451955</v>
       </c>
       <c r="E214" t="n">
-        <v>354.4814758300781</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="F214" t="n">
-        <v>8850000</v>
+        <v>9073200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>357.3760808599296</v>
+        <v>362.8958306673428</v>
       </c>
       <c r="C215" t="n">
-        <v>364.4629211425781</v>
+        <v>363.9538626468295</v>
       </c>
       <c r="D215" t="n">
-        <v>356.4477822451955</v>
+        <v>356.3380062665893</v>
       </c>
       <c r="E215" t="n">
-        <v>364.4629211425781</v>
+        <v>357.8951110839844</v>
       </c>
       <c r="F215" t="n">
-        <v>9073200</v>
+        <v>7400400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>362.8958306673428</v>
+        <v>356.4378309524324</v>
       </c>
       <c r="C216" t="n">
-        <v>363.9538626468295</v>
+        <v>362.3268844140721</v>
       </c>
       <c r="D216" t="n">
-        <v>356.3380062665893</v>
+        <v>355.7690599392462</v>
       </c>
       <c r="E216" t="n">
-        <v>357.8951110839844</v>
+        <v>359.9013977050781</v>
       </c>
       <c r="F216" t="n">
-        <v>7400400</v>
+        <v>7616800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>356.4378309524324</v>
+        <v>356.3280307190208</v>
       </c>
       <c r="C217" t="n">
-        <v>362.3268844140721</v>
+        <v>358.4540859756855</v>
       </c>
       <c r="D217" t="n">
-        <v>355.7690599392462</v>
+        <v>354.0323077481659</v>
       </c>
       <c r="E217" t="n">
-        <v>359.9013977050781</v>
+        <v>355.1602172851562</v>
       </c>
       <c r="F217" t="n">
-        <v>7616800</v>
+        <v>6027300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>356.3280307190208</v>
+        <v>355.9088319271366</v>
       </c>
       <c r="C218" t="n">
-        <v>358.4540859756855</v>
+        <v>356.8670433033565</v>
       </c>
       <c r="D218" t="n">
-        <v>354.0323077481659</v>
+        <v>351.6167869913984</v>
       </c>
       <c r="E218" t="n">
-        <v>355.1602172851562</v>
+        <v>352.7646789550781</v>
       </c>
       <c r="F218" t="n">
-        <v>6027300</v>
+        <v>4622200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>355.9088319271366</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="C219" t="n">
-        <v>356.8670433033565</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="D219" t="n">
-        <v>351.6167869913984</v>
+        <v>347.8537708520506</v>
       </c>
       <c r="E219" t="n">
-        <v>352.7646789550781</v>
+        <v>350.9480285644531</v>
       </c>
       <c r="F219" t="n">
-        <v>4622200</v>
+        <v>4183300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>351.3971758456315</v>
+        <v>352.8145729386106</v>
       </c>
       <c r="C220" t="n">
-        <v>351.3971758456315</v>
+        <v>355.1801734485531</v>
       </c>
       <c r="D220" t="n">
-        <v>347.8537708520506</v>
+        <v>350.3990468654978</v>
       </c>
       <c r="E220" t="n">
-        <v>350.9480285644531</v>
+        <v>355.0803527832031</v>
       </c>
       <c r="F220" t="n">
-        <v>4183300</v>
+        <v>4482800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>352.8145729386106</v>
+        <v>358.6836615690858</v>
       </c>
       <c r="C221" t="n">
-        <v>355.1801734485531</v>
+        <v>362.9856670774005</v>
       </c>
       <c r="D221" t="n">
-        <v>350.3990468654978</v>
+        <v>357.5856952124533</v>
       </c>
       <c r="E221" t="n">
-        <v>355.0803527832031</v>
+        <v>361.8577575683594</v>
       </c>
       <c r="F221" t="n">
-        <v>4482800</v>
+        <v>6631100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>358.6836615690858</v>
+        <v>364.3830556294341</v>
       </c>
       <c r="C222" t="n">
-        <v>362.9856670774005</v>
+        <v>370.4717503048907</v>
       </c>
       <c r="D222" t="n">
-        <v>357.5856952124533</v>
+        <v>362.057389622598</v>
       </c>
       <c r="E222" t="n">
-        <v>361.8577575683594</v>
+        <v>365.9102172851562</v>
       </c>
       <c r="F222" t="n">
-        <v>6631100</v>
+        <v>11061900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>364.3830556294341</v>
+        <v>356.3380049484608</v>
       </c>
       <c r="C223" t="n">
-        <v>370.4717503048907</v>
+        <v>373.2765382228537</v>
       </c>
       <c r="D223" t="n">
-        <v>362.057389622598</v>
+        <v>354.8208344927874</v>
       </c>
       <c r="E223" t="n">
-        <v>365.9102172851562</v>
+        <v>368.0462646484375</v>
       </c>
       <c r="F223" t="n">
-        <v>11061900</v>
+        <v>11289900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>356.3380049484608</v>
+        <v>364.3231862195555</v>
       </c>
       <c r="C224" t="n">
-        <v>373.2765382228537</v>
+        <v>366.3194776508955</v>
       </c>
       <c r="D224" t="n">
-        <v>354.8208344927874</v>
+        <v>360.0810669279579</v>
       </c>
       <c r="E224" t="n">
-        <v>368.0462646484375</v>
+        <v>365.5908203125</v>
       </c>
       <c r="F224" t="n">
-        <v>11289900</v>
+        <v>8391400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>364.3231862195555</v>
+        <v>363.0854799497644</v>
       </c>
       <c r="C225" t="n">
-        <v>366.3194776508955</v>
+        <v>366.199689577411</v>
       </c>
       <c r="D225" t="n">
-        <v>360.0810669279579</v>
+        <v>359.4322631293363</v>
       </c>
       <c r="E225" t="n">
-        <v>365.5908203125</v>
+        <v>365.4510803222656</v>
       </c>
       <c r="F225" t="n">
-        <v>8391400</v>
+        <v>7828400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>363.0854799497644</v>
+        <v>367.8166822243689</v>
       </c>
       <c r="C226" t="n">
-        <v>366.199689577411</v>
+        <v>371.2802489443513</v>
       </c>
       <c r="D226" t="n">
-        <v>359.4322631293363</v>
+        <v>363.6743837542027</v>
       </c>
       <c r="E226" t="n">
-        <v>365.4510803222656</v>
+        <v>364.991943359375</v>
       </c>
       <c r="F226" t="n">
-        <v>7828400</v>
+        <v>5521300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>367.8166822243689</v>
+        <v>361.0891957111975</v>
       </c>
       <c r="C227" t="n">
-        <v>371.2802489443513</v>
+        <v>370.4218335736103</v>
       </c>
       <c r="D227" t="n">
-        <v>363.6743837542027</v>
+        <v>359.4222790007568</v>
       </c>
       <c r="E227" t="n">
-        <v>364.991943359375</v>
+        <v>368.9046630859375</v>
       </c>
       <c r="F227" t="n">
-        <v>5521300</v>
+        <v>7497500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>361.0891957111975</v>
+        <v>371.6096355733356</v>
       </c>
       <c r="C228" t="n">
-        <v>370.4218335736103</v>
+        <v>371.7094562365133</v>
       </c>
       <c r="D228" t="n">
-        <v>359.4222790007568</v>
+        <v>366.0399959154992</v>
       </c>
       <c r="E228" t="n">
-        <v>368.9046630859375</v>
+        <v>367.8566284179688</v>
       </c>
       <c r="F228" t="n">
-        <v>7497500</v>
+        <v>6065300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>371.6096355733356</v>
+        <v>368.8847254705448</v>
       </c>
       <c r="C229" t="n">
-        <v>371.7094562365133</v>
+        <v>370.4118872220017</v>
       </c>
       <c r="D229" t="n">
-        <v>366.0399959154992</v>
+        <v>364.5727285978463</v>
       </c>
       <c r="E229" t="n">
-        <v>367.8566284179688</v>
+        <v>369.7830505371094</v>
       </c>
       <c r="F229" t="n">
-        <v>6065300</v>
+        <v>5022300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>368.8847254705448</v>
+        <v>367.8266852879935</v>
       </c>
       <c r="C230" t="n">
-        <v>370.4118872220017</v>
+        <v>369.5634490756331</v>
       </c>
       <c r="D230" t="n">
-        <v>364.5727285978463</v>
+        <v>360.8496260625997</v>
       </c>
       <c r="E230" t="n">
-        <v>369.7830505371094</v>
+        <v>361.8278198242188</v>
       </c>
       <c r="F230" t="n">
-        <v>5022300</v>
+        <v>5112500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>367.8266852879935</v>
+        <v>361.3287562034755</v>
       </c>
       <c r="C231" t="n">
-        <v>369.5634490756331</v>
+        <v>363.4947458520614</v>
       </c>
       <c r="D231" t="n">
-        <v>360.8496260625997</v>
+        <v>358.2045551780129</v>
       </c>
       <c r="E231" t="n">
-        <v>361.8278198242188</v>
+        <v>360.6500244140625</v>
       </c>
       <c r="F231" t="n">
-        <v>5112500</v>
+        <v>7552200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,25 +6449,25 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>361.3287562034755</v>
+        <v>360.9800109863281</v>
       </c>
       <c r="C232" t="n">
-        <v>363.4947458520614</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="D232" t="n">
-        <v>358.2045551780129</v>
+        <v>359.9700012207031</v>
       </c>
       <c r="E232" t="n">
-        <v>360.6500244140625</v>
+        <v>362.8200073242188</v>
       </c>
       <c r="F232" t="n">
-        <v>7552200</v>
+        <v>4440900</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -6475,25 +6475,25 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>360.9800109863281</v>
+        <v>361</v>
       </c>
       <c r="C233" t="n">
-        <v>364.5499877929688</v>
+        <v>363.3500061035156</v>
       </c>
       <c r="D233" t="n">
-        <v>359.9700012207031</v>
+        <v>358.3099975585938</v>
       </c>
       <c r="E233" t="n">
-        <v>362.8200073242188</v>
+        <v>359.4200134277344</v>
       </c>
       <c r="F233" t="n">
-        <v>4440900</v>
+        <v>3794200</v>
       </c>
       <c r="G233" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>361</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="C234" t="n">
-        <v>363.3500061035156</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="D234" t="n">
-        <v>358.3099975585938</v>
+        <v>358.7099914550781</v>
       </c>
       <c r="E234" t="n">
-        <v>359.4200134277344</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="F234" t="n">
-        <v>3794200</v>
+        <v>8142600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>363.7000122070312</v>
+        <v>365.8900146484375</v>
       </c>
       <c r="C235" t="n">
-        <v>365.4500122070312</v>
+        <v>366.7999877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>358.7099914550781</v>
+        <v>362.760009765625</v>
       </c>
       <c r="E235" t="n">
-        <v>365.4500122070312</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="F235" t="n">
-        <v>8142600</v>
+        <v>8106900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>365.8900146484375</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="C236" t="n">
-        <v>366.7999877929688</v>
+        <v>363.5599975585938</v>
       </c>
       <c r="D236" t="n">
-        <v>362.760009765625</v>
+        <v>358.5199890136719</v>
       </c>
       <c r="E236" t="n">
-        <v>364.1499938964844</v>
+        <v>358.8399963378906</v>
       </c>
       <c r="F236" t="n">
-        <v>8106900</v>
+        <v>15543400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>362.8399963378906</v>
+        <v>359.6199951171875</v>
       </c>
       <c r="C237" t="n">
-        <v>363.5599975585938</v>
+        <v>365.9100036621094</v>
       </c>
       <c r="D237" t="n">
-        <v>358.5199890136719</v>
+        <v>358.0499877929688</v>
       </c>
       <c r="E237" t="n">
-        <v>358.8399963378906</v>
+        <v>364.25</v>
       </c>
       <c r="F237" t="n">
-        <v>15543400</v>
+        <v>6820300</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>359.6199951171875</v>
+        <v>364.0899963378906</v>
       </c>
       <c r="C238" t="n">
-        <v>365.9100036621094</v>
+        <v>370.6400146484375</v>
       </c>
       <c r="D238" t="n">
-        <v>358.0499877929688</v>
+        <v>362.8999938964844</v>
       </c>
       <c r="E238" t="n">
-        <v>364.25</v>
+        <v>365.5400085449219</v>
       </c>
       <c r="F238" t="n">
-        <v>6820300</v>
+        <v>5866400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>364.0899963378906</v>
+        <v>365.1000061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>370.6400146484375</v>
+        <v>368.9299926757812</v>
       </c>
       <c r="D239" t="n">
-        <v>362.8999938964844</v>
+        <v>363.6300048828125</v>
       </c>
       <c r="E239" t="n">
-        <v>365.5400085449219</v>
+        <v>365.7300109863281</v>
       </c>
       <c r="F239" t="n">
-        <v>5866400</v>
+        <v>6151500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>365.1000061035156</v>
+        <v>367.8699951171875</v>
       </c>
       <c r="C240" t="n">
-        <v>368.9299926757812</v>
+        <v>371.7999877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>363.6300048828125</v>
+        <v>366.6600036621094</v>
       </c>
       <c r="E240" t="n">
-        <v>365.7300109863281</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F240" t="n">
-        <v>6151500</v>
+        <v>6667100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>367.8699951171875</v>
+        <v>373.260009765625</v>
       </c>
       <c r="C241" t="n">
-        <v>371.7999877929688</v>
+        <v>383.4299926757812</v>
       </c>
       <c r="D241" t="n">
-        <v>366.6600036621094</v>
+        <v>372.2099914550781</v>
       </c>
       <c r="E241" t="n">
-        <v>371.0400085449219</v>
+        <v>382.4100036621094</v>
       </c>
       <c r="F241" t="n">
-        <v>6667100</v>
+        <v>8477500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>373.260009765625</v>
+        <v>381.2099914550781</v>
       </c>
       <c r="C242" t="n">
-        <v>383.4299926757812</v>
+        <v>384.2000122070312</v>
       </c>
       <c r="D242" t="n">
-        <v>372.2099914550781</v>
+        <v>380.2699890136719</v>
       </c>
       <c r="E242" t="n">
-        <v>382.4100036621094</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="F242" t="n">
-        <v>8477500</v>
+        <v>6777600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>381.2099914550781</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C243" t="n">
-        <v>384.2000122070312</v>
+        <v>385.5700073242188</v>
       </c>
       <c r="D243" t="n">
-        <v>380.2699890136719</v>
+        <v>381.0799865722656</v>
       </c>
       <c r="E243" t="n">
-        <v>384.1400146484375</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F243" t="n">
-        <v>6777600</v>
+        <v>6075100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>384.1400146484375</v>
+        <v>381.1400146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>385.5700073242188</v>
+        <v>381.7699890136719</v>
       </c>
       <c r="D244" t="n">
-        <v>381.0799865722656</v>
+        <v>378.5</v>
       </c>
       <c r="E244" t="n">
-        <v>383.8999938964844</v>
+        <v>379.6600036621094</v>
       </c>
       <c r="F244" t="n">
-        <v>6075100</v>
+        <v>6641500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>381.1400146484375</v>
+        <v>380.2999877929688</v>
       </c>
       <c r="C245" t="n">
-        <v>381.7699890136719</v>
+        <v>383.6799926757812</v>
       </c>
       <c r="D245" t="n">
-        <v>378.5</v>
+        <v>379.0299987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>379.6600036621094</v>
+        <v>381.6000061035156</v>
       </c>
       <c r="F245" t="n">
-        <v>6641500</v>
+        <v>4643000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>380.2999877929688</v>
+        <v>381.3500061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>383.6799926757812</v>
+        <v>382.4800109863281</v>
       </c>
       <c r="D246" t="n">
-        <v>379.0299987792969</v>
+        <v>378.7999877929688</v>
       </c>
       <c r="E246" t="n">
-        <v>381.6000061035156</v>
+        <v>379.3699951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>4643000</v>
+        <v>6744800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>381.3500061035156</v>
+        <v>379.6499938964844</v>
       </c>
       <c r="C247" t="n">
-        <v>382.4800109863281</v>
+        <v>380.75</v>
       </c>
       <c r="D247" t="n">
-        <v>378.7999877929688</v>
+        <v>372.2200012207031</v>
       </c>
       <c r="E247" t="n">
-        <v>379.3699951171875</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F247" t="n">
-        <v>6744800</v>
+        <v>5857400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>379.6499938964844</v>
+        <v>374.010009765625</v>
       </c>
       <c r="C248" t="n">
-        <v>380.75</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="D248" t="n">
-        <v>372.2200012207031</v>
+        <v>374.010009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>372.6700134277344</v>
+        <v>378.3999938964844</v>
       </c>
       <c r="F248" t="n">
-        <v>5857400</v>
+        <v>5599900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>374.010009765625</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="C249" t="n">
-        <v>380.1700134277344</v>
+        <v>382.2099914550781</v>
       </c>
       <c r="D249" t="n">
-        <v>374.010009765625</v>
+        <v>376.8599853515625</v>
       </c>
       <c r="E249" t="n">
-        <v>378.3999938964844</v>
+        <v>378.75</v>
       </c>
       <c r="F249" t="n">
-        <v>5599900</v>
+        <v>3869500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>380.1700134277344</v>
+        <v>374.8900146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>382.2099914550781</v>
+        <v>377.5</v>
       </c>
       <c r="D250" t="n">
-        <v>376.8599853515625</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="E250" t="n">
-        <v>378.75</v>
+        <v>375.0700073242188</v>
       </c>
       <c r="F250" t="n">
-        <v>3869500</v>
+        <v>4645100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>374.8900146484375</v>
+        <v>371.6000061035156</v>
       </c>
       <c r="C251" t="n">
-        <v>377.5</v>
+        <v>373.5</v>
       </c>
       <c r="D251" t="n">
-        <v>373.6400146484375</v>
+        <v>367.4400024414062</v>
       </c>
       <c r="E251" t="n">
-        <v>375.0700073242188</v>
+        <v>368.6400146484375</v>
       </c>
       <c r="F251" t="n">
-        <v>4645100</v>
+        <v>4929000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="C252" t="n">
+        <v>369.4800109863281</v>
+      </c>
+      <c r="D252" t="n">
+        <v>365.8800048828125</v>
+      </c>
+      <c r="E252" t="n">
+        <v>367.3900146484375</v>
+      </c>
       <c r="F252" t="n">
-        <v>4909005</v>
+        <v>4479800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10648,37 +10656,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="D2" t="n">
         <v>368.64</v>
       </c>
-      <c r="D2" t="n">
-        <v>375.07</v>
-      </c>
       <c r="E2" t="n">
-        <v>371.6</v>
+        <v>368.45</v>
       </c>
       <c r="F2" t="n">
-        <v>373.5</v>
+        <v>369.48</v>
       </c>
       <c r="G2" t="n">
-        <v>367.44</v>
+        <v>365.88</v>
       </c>
       <c r="H2" t="n">
-        <v>4909005</v>
+        <v>4469432</v>
       </c>
       <c r="I2" t="n">
-        <v>7712759</v>
+        <v>7721091</v>
       </c>
       <c r="J2" t="n">
-        <v>688268312576</v>
+        <v>685934510080</v>
       </c>
       <c r="K2" t="n">
-        <v>31.400343</v>
+        <v>31.347271</v>
       </c>
       <c r="L2" t="n">
-        <v>24.568958</v>
+        <v>24.48565</v>
       </c>
       <c r="M2" t="n">
-        <v>11.74</v>
+        <v>11.72</v>
       </c>
       <c r="N2" t="n">
         <v>385.57</v>
@@ -10690,7 +10698,7 @@
         <v>0.761</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="R2" t="n">
         <v>0.50782</v>
@@ -10714,7 +10722,7 @@
         <v>18.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.53577</v>
+        <v>19.469528</v>
       </c>
       <c r="Z2" t="n">
         <v>0.102</v>
@@ -10726,7 +10734,7 @@
         <v>44487999488</v>
       </c>
       <c r="AC2" t="n">
-        <v>688130162688</v>
+        <v>685832667136</v>
       </c>
       <c r="AD2" t="n">
         <v>31093999616</v>
@@ -10753,7 +10761,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:14</t>
+          <t>2026-09-10 18:59:30</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>339.8916830924824</v>
+        <v>336.0424662373603</v>
       </c>
       <c r="C2" t="n">
-        <v>339.8916830924824</v>
+        <v>340.8043700650184</v>
       </c>
       <c r="D2" t="n">
-        <v>333.7706534504743</v>
+        <v>335.1892738885992</v>
       </c>
       <c r="E2" t="n">
-        <v>335.4373168945312</v>
+        <v>340.7646789550781</v>
       </c>
       <c r="F2" t="n">
-        <v>6557900</v>
+        <v>5157600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>336.0424662373603</v>
+        <v>338.5127450059508</v>
       </c>
       <c r="C3" t="n">
-        <v>340.8043700650184</v>
+        <v>340.4671161404083</v>
       </c>
       <c r="D3" t="n">
-        <v>335.1892738885992</v>
+        <v>336.4790219166126</v>
       </c>
       <c r="E3" t="n">
-        <v>340.7646789550781</v>
+        <v>336.7369384765625</v>
       </c>
       <c r="F3" t="n">
-        <v>5157600</v>
+        <v>3518300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>338.5127143274361</v>
+        <v>337.9075446663081</v>
       </c>
       <c r="C4" t="n">
-        <v>340.467085284774</v>
+        <v>339.9908890682369</v>
       </c>
       <c r="D4" t="n">
-        <v>336.4789914224089</v>
+        <v>335.7051874783653</v>
       </c>
       <c r="E4" t="n">
-        <v>336.7369079589844</v>
+        <v>336.3599243164062</v>
       </c>
       <c r="F4" t="n">
-        <v>3518300</v>
+        <v>4367500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>337.907514008316</v>
+        <v>333.5722152320537</v>
       </c>
       <c r="C5" t="n">
-        <v>339.9908582212252</v>
+        <v>337.8381165972889</v>
       </c>
       <c r="D5" t="n">
-        <v>335.7051570201907</v>
+        <v>330.8242036977477</v>
       </c>
       <c r="E5" t="n">
-        <v>336.3598937988281</v>
+        <v>337.3321533203125</v>
       </c>
       <c r="F5" t="n">
-        <v>4367500</v>
+        <v>5527700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>333.5722152320537</v>
+        <v>337.2428745138968</v>
       </c>
       <c r="C6" t="n">
-        <v>337.8381165972889</v>
+        <v>343.4532165527344</v>
       </c>
       <c r="D6" t="n">
-        <v>330.8242036977477</v>
+        <v>336.8261935269982</v>
       </c>
       <c r="E6" t="n">
-        <v>337.3321533203125</v>
+        <v>343.4532165527344</v>
       </c>
       <c r="F6" t="n">
-        <v>5527700</v>
+        <v>5763500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>337.2429044796542</v>
+        <v>341.9948757376367</v>
       </c>
       <c r="C7" t="n">
-        <v>343.4532470703125</v>
+        <v>342.5305695051567</v>
       </c>
       <c r="D7" t="n">
-        <v>336.8262234557313</v>
+        <v>335.496826171875</v>
       </c>
       <c r="E7" t="n">
-        <v>343.4532470703125</v>
+        <v>335.496826171875</v>
       </c>
       <c r="F7" t="n">
-        <v>5763500</v>
+        <v>7526600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>341.9948446289807</v>
+        <v>337.7488578495824</v>
       </c>
       <c r="C8" t="n">
-        <v>342.5305383477728</v>
+        <v>339.9710758437891</v>
       </c>
       <c r="D8" t="n">
-        <v>335.4967956542969</v>
+        <v>335.5663006942368</v>
       </c>
       <c r="E8" t="n">
-        <v>335.4967956542969</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="F8" t="n">
-        <v>7526600</v>
+        <v>13674300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>337.7488274356299</v>
+        <v>336.3202490919778</v>
       </c>
       <c r="C9" t="n">
-        <v>339.9710452297281</v>
+        <v>342.123810018113</v>
       </c>
       <c r="D9" t="n">
-        <v>335.5662704768214</v>
+        <v>335.9730199939359</v>
       </c>
       <c r="E9" t="n">
-        <v>338.8995971679688</v>
+        <v>341.6277770996094</v>
       </c>
       <c r="F9" t="n">
-        <v>13674300</v>
+        <v>5621800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>336.3202190485207</v>
+        <v>341.8559781228954</v>
       </c>
       <c r="C10" t="n">
-        <v>342.1237794562243</v>
+        <v>342.5206755840167</v>
       </c>
       <c r="D10" t="n">
-        <v>335.9729899814968</v>
+        <v>334.9512080718528</v>
       </c>
       <c r="E10" t="n">
-        <v>341.6277465820312</v>
+        <v>336.0127258300781</v>
       </c>
       <c r="F10" t="n">
-        <v>5621800</v>
+        <v>10142700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>341.8559781228954</v>
+        <v>336.4392700766844</v>
       </c>
       <c r="C11" t="n">
-        <v>342.5206755840167</v>
+        <v>337.2031498219058</v>
       </c>
       <c r="D11" t="n">
-        <v>334.9512080718528</v>
+        <v>335.2388789697807</v>
       </c>
       <c r="E11" t="n">
-        <v>336.0127258300781</v>
+        <v>335.9928283691406</v>
       </c>
       <c r="F11" t="n">
-        <v>10142700</v>
+        <v>5207400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>336.4393311929394</v>
+        <v>335.6654921112904</v>
       </c>
       <c r="C12" t="n">
-        <v>337.2032110769243</v>
+        <v>337.5008200200934</v>
       </c>
       <c r="D12" t="n">
-        <v>335.2389398679774</v>
+        <v>331.855962815555</v>
       </c>
       <c r="E12" t="n">
-        <v>335.9928894042969</v>
+        <v>332.2726135253906</v>
       </c>
       <c r="F12" t="n">
-        <v>5207400</v>
+        <v>5398700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>335.6655229404874</v>
+        <v>334.5543943395058</v>
       </c>
       <c r="C13" t="n">
-        <v>337.5008510178562</v>
+        <v>336.8063730332322</v>
       </c>
       <c r="D13" t="n">
-        <v>331.8559932948658</v>
+        <v>333.5623284395552</v>
       </c>
       <c r="E13" t="n">
-        <v>332.2726440429688</v>
+        <v>334.6932678222656</v>
       </c>
       <c r="F13" t="n">
-        <v>5398700</v>
+        <v>9619200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>334.5543943395058</v>
+        <v>334.7032090426073</v>
       </c>
       <c r="C14" t="n">
-        <v>336.8063730332322</v>
+        <v>337.9373536696546</v>
       </c>
       <c r="D14" t="n">
-        <v>333.5623284395552</v>
+        <v>332.8877114324681</v>
       </c>
       <c r="E14" t="n">
-        <v>334.6932678222656</v>
+        <v>337.4611511230469</v>
       </c>
       <c r="F14" t="n">
-        <v>9619200</v>
+        <v>7217800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>334.7031787744378</v>
+        <v>337.1238578141872</v>
       </c>
       <c r="C15" t="n">
-        <v>337.9373231090121</v>
+        <v>342.8678978564652</v>
       </c>
       <c r="D15" t="n">
-        <v>332.8876813284792</v>
+        <v>335.8242538439627</v>
       </c>
       <c r="E15" t="n">
-        <v>337.4611206054688</v>
+        <v>338.6714782714844</v>
       </c>
       <c r="F15" t="n">
-        <v>7217800</v>
+        <v>8164400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>337.1238274360646</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="C16" t="n">
-        <v>342.867866960749</v>
+        <v>346.58811100512</v>
       </c>
       <c r="D16" t="n">
-        <v>335.824223582947</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="E16" t="n">
-        <v>338.6714477539062</v>
+        <v>345.0702514648438</v>
       </c>
       <c r="F16" t="n">
-        <v>8164400</v>
+        <v>8381000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>337.6099271681015</v>
+        <v>343.4730470813312</v>
       </c>
       <c r="C17" t="n">
-        <v>346.58811100512</v>
+        <v>344.425421840401</v>
       </c>
       <c r="D17" t="n">
-        <v>337.6099271681015</v>
+        <v>340.8341482313199</v>
       </c>
       <c r="E17" t="n">
-        <v>345.0702514648438</v>
+        <v>343.2052001953125</v>
       </c>
       <c r="F17" t="n">
-        <v>8381000</v>
+        <v>5198000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>343.4730470813312</v>
+        <v>343.3639143460552</v>
       </c>
       <c r="C18" t="n">
-        <v>344.425421840401</v>
+        <v>350.3579971109944</v>
       </c>
       <c r="D18" t="n">
-        <v>340.8341482313199</v>
+        <v>343.2548016291976</v>
       </c>
       <c r="E18" t="n">
-        <v>343.2052001953125</v>
+        <v>347.0643310546875</v>
       </c>
       <c r="F18" t="n">
-        <v>5198000</v>
+        <v>5199700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>343.3639143460552</v>
+        <v>347.2329775138888</v>
       </c>
       <c r="C19" t="n">
-        <v>350.3579971109944</v>
+        <v>348.3341560741189</v>
       </c>
       <c r="D19" t="n">
-        <v>343.2548016291976</v>
+        <v>341.6178811752161</v>
       </c>
       <c r="E19" t="n">
-        <v>347.0643310546875</v>
+        <v>346.5087585449219</v>
       </c>
       <c r="F19" t="n">
-        <v>5199700</v>
+        <v>4735600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>347.2330080952501</v>
+        <v>347.2826099421288</v>
       </c>
       <c r="C20" t="n">
-        <v>348.3341867524627</v>
+        <v>351.6278637211122</v>
       </c>
       <c r="D20" t="n">
-        <v>341.6179112620468</v>
+        <v>347.2826099421288</v>
       </c>
       <c r="E20" t="n">
-        <v>346.5087890625</v>
+        <v>349.6239013671875</v>
       </c>
       <c r="F20" t="n">
-        <v>4735600</v>
+        <v>5044600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>347.2825796289147</v>
+        <v>350.9730784623077</v>
       </c>
       <c r="C21" t="n">
-        <v>351.6278330286145</v>
+        <v>352.1834000905383</v>
       </c>
       <c r="D21" t="n">
-        <v>347.2825796289147</v>
+        <v>348.3143490742109</v>
       </c>
       <c r="E21" t="n">
-        <v>349.6238708496094</v>
+        <v>348.572265625</v>
       </c>
       <c r="F21" t="n">
-        <v>5044600</v>
+        <v>3927500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>350.9730784623077</v>
+        <v>348.6814047504906</v>
       </c>
       <c r="C22" t="n">
-        <v>352.1834000905383</v>
+        <v>350.0702909620389</v>
       </c>
       <c r="D22" t="n">
-        <v>348.3143490742109</v>
+        <v>342.8381220393481</v>
       </c>
       <c r="E22" t="n">
-        <v>348.572265625</v>
+        <v>344.2865600585938</v>
       </c>
       <c r="F22" t="n">
-        <v>3927500</v>
+        <v>4434800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>348.6814047504906</v>
+        <v>344.8718644724454</v>
       </c>
       <c r="C23" t="n">
-        <v>350.0702909620389</v>
+        <v>347.619876043067</v>
       </c>
       <c r="D23" t="n">
-        <v>342.8381220393481</v>
+        <v>340.5266111021468</v>
       </c>
       <c r="E23" t="n">
-        <v>344.2865600585938</v>
+        <v>340.9234313964844</v>
       </c>
       <c r="F23" t="n">
-        <v>4434800</v>
+        <v>6296200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>344.8718644724454</v>
+        <v>340.9929139357196</v>
       </c>
       <c r="C24" t="n">
-        <v>347.619876043067</v>
+        <v>344.9016562510855</v>
       </c>
       <c r="D24" t="n">
-        <v>340.5266111021468</v>
+        <v>338.0266463951693</v>
       </c>
       <c r="E24" t="n">
-        <v>340.9234313964844</v>
+        <v>340.5762329101562</v>
       </c>
       <c r="F24" t="n">
-        <v>6296200</v>
+        <v>4030700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>340.9928833808045</v>
+        <v>338.2944549426422</v>
       </c>
       <c r="C25" t="n">
-        <v>344.9016253459246</v>
+        <v>347.2329779417331</v>
       </c>
       <c r="D25" t="n">
-        <v>338.0266161060487</v>
+        <v>337.5206447904482</v>
       </c>
       <c r="E25" t="n">
-        <v>340.5762023925781</v>
+        <v>345.6159057617188</v>
       </c>
       <c r="F25" t="n">
-        <v>4030700</v>
+        <v>5731000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>338.2944848137428</v>
+        <v>345.615925335404</v>
       </c>
       <c r="C26" t="n">
-        <v>347.2330086020973</v>
+        <v>347.3024192111109</v>
       </c>
       <c r="D26" t="n">
-        <v>337.520674593222</v>
+        <v>341.2706718210525</v>
       </c>
       <c r="E26" t="n">
-        <v>345.6159362792969</v>
+        <v>342.947265625</v>
       </c>
       <c r="F26" t="n">
-        <v>5731000</v>
+        <v>3778200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>345.615925335404</v>
+        <v>342.2627301477191</v>
       </c>
       <c r="C27" t="n">
-        <v>347.3024192111109</v>
+        <v>342.9472580300504</v>
       </c>
       <c r="D27" t="n">
-        <v>341.2706718210525</v>
+        <v>331.5186699399313</v>
       </c>
       <c r="E27" t="n">
-        <v>342.947265625</v>
+        <v>332.7388916015625</v>
       </c>
       <c r="F27" t="n">
-        <v>3778200</v>
+        <v>6241500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>342.2627301477191</v>
+        <v>335.0900922102411</v>
       </c>
       <c r="C28" t="n">
-        <v>342.9472580300504</v>
+        <v>340.7250495999637</v>
       </c>
       <c r="D28" t="n">
-        <v>331.5186699399313</v>
+        <v>334.3262123571327</v>
       </c>
       <c r="E28" t="n">
-        <v>332.7388916015625</v>
+        <v>339.1774291992188</v>
       </c>
       <c r="F28" t="n">
-        <v>6241500</v>
+        <v>6267100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>335.0900620604222</v>
+        <v>339.1873037416991</v>
       </c>
       <c r="C29" t="n">
-        <v>340.725018943138</v>
+        <v>342.2230227820154</v>
       </c>
       <c r="D29" t="n">
-        <v>334.3261822760441</v>
+        <v>336.2507973402091</v>
       </c>
       <c r="E29" t="n">
-        <v>339.1773986816406</v>
+        <v>341.6773986816406</v>
       </c>
       <c r="F29" t="n">
-        <v>6267100</v>
+        <v>4665000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>339.1873037416991</v>
+        <v>340.3976542086254</v>
       </c>
       <c r="C30" t="n">
-        <v>342.2230227820154</v>
+        <v>346.8758434662893</v>
       </c>
       <c r="D30" t="n">
-        <v>336.2507973402091</v>
+        <v>340.2786111420936</v>
       </c>
       <c r="E30" t="n">
-        <v>341.6773986816406</v>
+        <v>344.4552001953125</v>
       </c>
       <c r="F30" t="n">
-        <v>4665000</v>
+        <v>4121800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>340.3976542086254</v>
+        <v>345.0603770187118</v>
       </c>
       <c r="C31" t="n">
-        <v>346.8758434662893</v>
+        <v>345.4076061472691</v>
       </c>
       <c r="D31" t="n">
-        <v>340.2786111420936</v>
+        <v>341.7667108842852</v>
       </c>
       <c r="E31" t="n">
-        <v>344.4552001953125</v>
+        <v>342.619873046875</v>
       </c>
       <c r="F31" t="n">
-        <v>4121800</v>
+        <v>5074400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>345.0603770187118</v>
+        <v>343.4532348171426</v>
       </c>
       <c r="C32" t="n">
-        <v>345.4076061472691</v>
+        <v>344.395679279174</v>
       </c>
       <c r="D32" t="n">
-        <v>341.7667108842852</v>
+        <v>341.727019522991</v>
       </c>
       <c r="E32" t="n">
-        <v>342.619873046875</v>
+        <v>343.2151184082031</v>
       </c>
       <c r="F32" t="n">
-        <v>5074400</v>
+        <v>7217200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>343.4532042783919</v>
+        <v>345.4373721859704</v>
       </c>
       <c r="C33" t="n">
-        <v>344.3956486566242</v>
+        <v>346.3103647812057</v>
       </c>
       <c r="D33" t="n">
-        <v>341.7269891377298</v>
+        <v>342.5802174366191</v>
       </c>
       <c r="E33" t="n">
-        <v>343.215087890625</v>
+        <v>344.6238708496094</v>
       </c>
       <c r="F33" t="n">
-        <v>7217200</v>
+        <v>3576700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>345.4373415963541</v>
+        <v>346.2310248701323</v>
       </c>
       <c r="C34" t="n">
-        <v>346.3103341142831</v>
+        <v>346.7468882773667</v>
       </c>
       <c r="D34" t="n">
-        <v>342.5801871000132</v>
+        <v>342.2726913226552</v>
       </c>
       <c r="E34" t="n">
-        <v>344.6238403320312</v>
+        <v>345.0603942871094</v>
       </c>
       <c r="F34" t="n">
-        <v>3576700</v>
+        <v>5400300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>346.2310248701323</v>
+        <v>345.8143381028397</v>
       </c>
       <c r="C35" t="n">
-        <v>346.7468882773667</v>
+        <v>347.1139723604238</v>
       </c>
       <c r="D35" t="n">
-        <v>342.2726913226552</v>
+        <v>343.7508542326843</v>
       </c>
       <c r="E35" t="n">
-        <v>345.0603942871094</v>
+        <v>344.1476745605469</v>
       </c>
       <c r="F35" t="n">
-        <v>5400300</v>
+        <v>7445400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>345.8143074374688</v>
+        <v>343.2547871723516</v>
       </c>
       <c r="C36" t="n">
-        <v>347.1139415798067</v>
+        <v>348.1952860487332</v>
       </c>
       <c r="D36" t="n">
-        <v>343.7508237502946</v>
+        <v>336.3103261601942</v>
       </c>
       <c r="E36" t="n">
-        <v>344.1476440429688</v>
+        <v>338.5722351074219</v>
       </c>
       <c r="F36" t="n">
-        <v>7445400</v>
+        <v>8361700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>343.2547871723516</v>
+        <v>339.5048081094784</v>
       </c>
       <c r="C37" t="n">
-        <v>348.1952860487332</v>
+        <v>346.9453026794581</v>
       </c>
       <c r="D37" t="n">
-        <v>336.3103261601942</v>
+        <v>339.0782270202408</v>
       </c>
       <c r="E37" t="n">
-        <v>338.5722351074219</v>
+        <v>342.2925109863281</v>
       </c>
       <c r="F37" t="n">
-        <v>8361700</v>
+        <v>6411800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>339.5047778404419</v>
+        <v>339.3658942315137</v>
       </c>
       <c r="C38" t="n">
-        <v>346.9452717470537</v>
+        <v>340.2786081927618</v>
       </c>
       <c r="D38" t="n">
-        <v>339.0781967892368</v>
+        <v>335.4869431536939</v>
       </c>
       <c r="E38" t="n">
-        <v>342.29248046875</v>
+        <v>338.0365295410156</v>
       </c>
       <c r="F38" t="n">
-        <v>6411800</v>
+        <v>7301600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>339.3658942315137</v>
+        <v>338.2944350303034</v>
       </c>
       <c r="C39" t="n">
-        <v>340.2786081927618</v>
+        <v>338.502760369473</v>
       </c>
       <c r="D39" t="n">
-        <v>335.4869431536939</v>
+        <v>332.1634757026059</v>
       </c>
       <c r="E39" t="n">
-        <v>338.0365295410156</v>
+        <v>334.2269592285156</v>
       </c>
       <c r="F39" t="n">
-        <v>7301600</v>
+        <v>5538000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>338.2944659192743</v>
+        <v>333.8103374596785</v>
       </c>
       <c r="C40" t="n">
-        <v>338.5027912774657</v>
+        <v>337.6198667973582</v>
       </c>
       <c r="D40" t="n">
-        <v>332.1635060317716</v>
+        <v>331.598019653034</v>
       </c>
       <c r="E40" t="n">
-        <v>334.2269897460938</v>
+        <v>337.6000061035156</v>
       </c>
       <c r="F40" t="n">
-        <v>5538000</v>
+        <v>5920200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>333.810367634687</v>
+        <v>337.4313843500343</v>
       </c>
       <c r="C41" t="n">
-        <v>337.6198973167316</v>
+        <v>339.395655484498</v>
       </c>
       <c r="D41" t="n">
-        <v>331.5980496280586</v>
+        <v>333.6912764760034</v>
       </c>
       <c r="E41" t="n">
-        <v>337.6000366210938</v>
+        <v>337.3421020507812</v>
       </c>
       <c r="F41" t="n">
-        <v>5920200</v>
+        <v>4984600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>337.4313538243792</v>
+        <v>335.9035711966457</v>
       </c>
       <c r="C42" t="n">
-        <v>339.3956247811457</v>
+        <v>335.9630927253758</v>
       </c>
       <c r="D42" t="n">
-        <v>333.6912462886964</v>
+        <v>331.062285023625</v>
       </c>
       <c r="E42" t="n">
-        <v>337.3420715332031</v>
+        <v>334.2864990234375</v>
       </c>
       <c r="F42" t="n">
-        <v>4984600</v>
+        <v>8507900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>335.9035711966457</v>
+        <v>334.058361977199</v>
       </c>
       <c r="C43" t="n">
-        <v>335.9630927253758</v>
+        <v>335.6059823618086</v>
       </c>
       <c r="D43" t="n">
-        <v>331.062285023625</v>
+        <v>332.193273237939</v>
       </c>
       <c r="E43" t="n">
-        <v>334.2864990234375</v>
+        <v>333.3539733886719</v>
       </c>
       <c r="F43" t="n">
-        <v>8507900</v>
+        <v>5318400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>334.0583313951361</v>
+        <v>333.9790049876522</v>
       </c>
       <c r="C44" t="n">
-        <v>335.6059516380656</v>
+        <v>335.9928977092549</v>
       </c>
       <c r="D44" t="n">
-        <v>332.1932428266196</v>
+        <v>331.6675045832317</v>
       </c>
       <c r="E44" t="n">
-        <v>333.3539428710938</v>
+        <v>332.1932983398438</v>
       </c>
       <c r="F44" t="n">
-        <v>5318400</v>
+        <v>5295800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>333.9789743060267</v>
+        <v>332.838108855689</v>
       </c>
       <c r="C45" t="n">
-        <v>335.9928668426192</v>
+        <v>336.3996217972758</v>
       </c>
       <c r="D45" t="n">
-        <v>331.6674741139567</v>
+        <v>330.5563693999427</v>
       </c>
       <c r="E45" t="n">
-        <v>332.1932678222656</v>
+        <v>336.2309875488281</v>
       </c>
       <c r="F45" t="n">
-        <v>5295800</v>
+        <v>4453300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>332.838108855689</v>
+        <v>336.230963908966</v>
       </c>
       <c r="C46" t="n">
-        <v>336.3996217972758</v>
+        <v>342.2050995382295</v>
       </c>
       <c r="D46" t="n">
-        <v>330.5563693999427</v>
+        <v>335.3860315467677</v>
       </c>
       <c r="E46" t="n">
-        <v>336.2309875488281</v>
+        <v>336.8572082519531</v>
       </c>
       <c r="F46" t="n">
-        <v>4453300</v>
+        <v>6389600</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>336.230963908966</v>
+        <v>337.0162670739215</v>
       </c>
       <c r="C47" t="n">
-        <v>342.2050995382295</v>
+        <v>339.4218050228609</v>
       </c>
       <c r="D47" t="n">
-        <v>335.3860315467677</v>
+        <v>333.5967981253938</v>
       </c>
       <c r="E47" t="n">
-        <v>336.8572082519531</v>
+        <v>334.0739135742188</v>
       </c>
       <c r="F47" t="n">
-        <v>6389600</v>
+        <v>4961700</v>
       </c>
       <c r="G47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>337.01623628756</v>
+        <v>333.8850664354288</v>
       </c>
       <c r="C48" t="n">
-        <v>339.4217740167541</v>
+        <v>334.0739044051273</v>
       </c>
       <c r="D48" t="n">
-        <v>333.5967676514001</v>
+        <v>327.0659984240934</v>
       </c>
       <c r="E48" t="n">
-        <v>334.0738830566406</v>
+        <v>328.0500793457031</v>
       </c>
       <c r="F48" t="n">
-        <v>4961700</v>
+        <v>6422300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>333.8850664354288</v>
+        <v>329.1832834325262</v>
       </c>
       <c r="C49" t="n">
-        <v>334.0739044051273</v>
+        <v>331.370133257436</v>
       </c>
       <c r="D49" t="n">
-        <v>327.0659984240934</v>
+        <v>322.9904598740608</v>
       </c>
       <c r="E49" t="n">
-        <v>328.0500793457031</v>
+        <v>323.8055725097656</v>
       </c>
       <c r="F49" t="n">
-        <v>6422300</v>
+        <v>6494800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>329.1832834325262</v>
+        <v>322.5630378796905</v>
       </c>
       <c r="C50" t="n">
-        <v>331.370133257436</v>
+        <v>323.0600533463772</v>
       </c>
       <c r="D50" t="n">
-        <v>322.9904598740608</v>
+        <v>316.101836812763</v>
       </c>
       <c r="E50" t="n">
-        <v>323.8055725097656</v>
+        <v>319.2628479003906</v>
       </c>
       <c r="F50" t="n">
-        <v>6494800</v>
+        <v>9170400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>322.5630378796905</v>
+        <v>319.6007859560105</v>
       </c>
       <c r="C51" t="n">
-        <v>323.0600533463772</v>
+        <v>322.6325982306419</v>
       </c>
       <c r="D51" t="n">
-        <v>316.101836812763</v>
+        <v>317.9606411309352</v>
       </c>
       <c r="E51" t="n">
-        <v>319.2628479003906</v>
+        <v>322.1852722167969</v>
       </c>
       <c r="F51" t="n">
-        <v>9170400</v>
+        <v>7066700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>319.6008465015586</v>
+        <v>322.1853192569361</v>
       </c>
       <c r="C52" t="n">
-        <v>322.6326593505401</v>
+        <v>326.4397706758573</v>
       </c>
       <c r="D52" t="n">
-        <v>317.9607013657724</v>
+        <v>321.2111883025171</v>
       </c>
       <c r="E52" t="n">
-        <v>322.1853332519531</v>
+        <v>321.83740234375</v>
       </c>
       <c r="F52" t="n">
-        <v>7066700</v>
+        <v>6510300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>322.1852887063674</v>
+        <v>323.4377913272098</v>
       </c>
       <c r="C53" t="n">
-        <v>326.4397397218689</v>
+        <v>329.1037494702317</v>
       </c>
       <c r="D53" t="n">
-        <v>321.2111578443184</v>
+        <v>322.354301245485</v>
       </c>
       <c r="E53" t="n">
-        <v>321.8373718261719</v>
+        <v>326.0222778320312</v>
       </c>
       <c r="F53" t="n">
-        <v>6510300</v>
+        <v>8930000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>323.4377913272098</v>
+        <v>327.2747416730934</v>
       </c>
       <c r="C54" t="n">
-        <v>329.1037494702317</v>
+        <v>328.755868423024</v>
       </c>
       <c r="D54" t="n">
-        <v>322.354301245485</v>
+        <v>324.0540910886259</v>
       </c>
       <c r="E54" t="n">
-        <v>326.0222778320312</v>
+        <v>327.3343811035156</v>
       </c>
       <c r="F54" t="n">
-        <v>8930000</v>
+        <v>9337100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>327.2747416730934</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="C55" t="n">
-        <v>328.755868423024</v>
+        <v>334.0540387480419</v>
       </c>
       <c r="D55" t="n">
-        <v>324.0540910886259</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="E55" t="n">
-        <v>327.3343811035156</v>
+        <v>332.5331726074219</v>
       </c>
       <c r="F55" t="n">
-        <v>9337100</v>
+        <v>5854300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>326.9367735032804</v>
+        <v>332.533150050326</v>
       </c>
       <c r="C56" t="n">
-        <v>334.0540387480419</v>
+        <v>333.7060992116737</v>
       </c>
       <c r="D56" t="n">
-        <v>326.9367735032804</v>
+        <v>331.0719234390147</v>
       </c>
       <c r="E56" t="n">
-        <v>332.5331726074219</v>
+        <v>331.7975769042969</v>
       </c>
       <c r="F56" t="n">
-        <v>5854300</v>
+        <v>4309900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>332.533150050326</v>
+        <v>331.4397445821358</v>
       </c>
       <c r="C57" t="n">
-        <v>333.7060992116737</v>
+        <v>333.0202502105825</v>
       </c>
       <c r="D57" t="n">
-        <v>331.0719234390147</v>
+        <v>330.0182875517957</v>
       </c>
       <c r="E57" t="n">
-        <v>331.7975769042969</v>
+        <v>332.4437255859375</v>
       </c>
       <c r="F57" t="n">
-        <v>4309900</v>
+        <v>4586200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>331.4397445821358</v>
+        <v>330.9526438085897</v>
       </c>
       <c r="C58" t="n">
-        <v>333.0202502105825</v>
+        <v>331.3104803646008</v>
       </c>
       <c r="D58" t="n">
-        <v>330.0182875517957</v>
+        <v>328.1693694771195</v>
       </c>
       <c r="E58" t="n">
-        <v>332.4437255859375</v>
+        <v>328.4178771972656</v>
       </c>
       <c r="F58" t="n">
-        <v>4586200</v>
+        <v>7082300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>330.952674561706</v>
+        <v>329.4715593852143</v>
       </c>
       <c r="C59" t="n">
-        <v>331.3105111509684</v>
+        <v>330.8134768540631</v>
       </c>
       <c r="D59" t="n">
-        <v>328.1693999716056</v>
+        <v>325.2568476714639</v>
       </c>
       <c r="E59" t="n">
-        <v>328.4179077148438</v>
+        <v>327.6524658203125</v>
       </c>
       <c r="F59" t="n">
-        <v>7082300</v>
+        <v>8201900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>329.4715593852143</v>
+        <v>327.6425476074219</v>
       </c>
       <c r="C60" t="n">
-        <v>330.8134768540631</v>
+        <v>330.3662132109065</v>
       </c>
       <c r="D60" t="n">
-        <v>325.2568476714639</v>
+        <v>327.3841201721478</v>
       </c>
       <c r="E60" t="n">
-        <v>327.6524658203125</v>
+        <v>327.6425476074219</v>
       </c>
       <c r="F60" t="n">
-        <v>8201900</v>
+        <v>6296700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>327.6425170898438</v>
+        <v>329.3025639629765</v>
       </c>
       <c r="C61" t="n">
-        <v>330.3661824396382</v>
+        <v>330.3960040486967</v>
       </c>
       <c r="D61" t="n">
-        <v>327.3840896786403</v>
+        <v>322.3443474807417</v>
       </c>
       <c r="E61" t="n">
-        <v>327.6425170898438</v>
+        <v>325.1475219726562</v>
       </c>
       <c r="F61" t="n">
-        <v>6296700</v>
+        <v>6277500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>329.3025948705371</v>
+        <v>324.8791370505337</v>
       </c>
       <c r="C62" t="n">
-        <v>330.396035058885</v>
+        <v>332.1156814874498</v>
       </c>
       <c r="D62" t="n">
-        <v>322.3443777352205</v>
+        <v>324.4517110027865</v>
       </c>
       <c r="E62" t="n">
-        <v>325.1475524902344</v>
+        <v>329.2628173828125</v>
       </c>
       <c r="F62" t="n">
-        <v>6277500</v>
+        <v>5266600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>324.8791069392551</v>
+        <v>327.9109619547325</v>
       </c>
       <c r="C63" t="n">
-        <v>332.1156507054553</v>
+        <v>329.3622387687074</v>
       </c>
       <c r="D63" t="n">
-        <v>324.4516809311236</v>
+        <v>322.7718081675561</v>
       </c>
       <c r="E63" t="n">
-        <v>329.2627868652344</v>
+        <v>324.8890991210938</v>
       </c>
       <c r="F63" t="n">
-        <v>5266600</v>
+        <v>6059400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>327.9109311533039</v>
+        <v>324.6604457908234</v>
       </c>
       <c r="C64" t="n">
-        <v>329.3622078309571</v>
+        <v>326.270801469966</v>
       </c>
       <c r="D64" t="n">
-        <v>322.77177784886</v>
+        <v>323.1296599138169</v>
       </c>
       <c r="E64" t="n">
-        <v>324.8890686035156</v>
+        <v>324.5511169433594</v>
       </c>
       <c r="F64" t="n">
-        <v>6059400</v>
+        <v>4325400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>324.6604152629651</v>
+        <v>324.6902773524443</v>
       </c>
       <c r="C65" t="n">
-        <v>326.2707707906858</v>
+        <v>326.797618069185</v>
       </c>
       <c r="D65" t="n">
-        <v>323.1296295298985</v>
+        <v>323.3582492118315</v>
       </c>
       <c r="E65" t="n">
-        <v>324.5510864257812</v>
+        <v>323.7857055664062</v>
       </c>
       <c r="F65" t="n">
-        <v>4325400</v>
+        <v>5467500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>324.6902773524443</v>
+        <v>330.6147028726578</v>
       </c>
       <c r="C66" t="n">
-        <v>326.797618069185</v>
+        <v>345.2468397955696</v>
       </c>
       <c r="D66" t="n">
-        <v>323.3582492118315</v>
+        <v>328.0898557440862</v>
       </c>
       <c r="E66" t="n">
-        <v>323.7857055664062</v>
+        <v>343.5669250488281</v>
       </c>
       <c r="F66" t="n">
-        <v>5467500</v>
+        <v>12953600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>330.6146735055701</v>
+        <v>345.9227522622342</v>
       </c>
       <c r="C67" t="n">
-        <v>345.2468091287718</v>
+        <v>347.751765473026</v>
       </c>
       <c r="D67" t="n">
-        <v>328.0898266012699</v>
+        <v>343.9048707541211</v>
       </c>
       <c r="E67" t="n">
-        <v>343.56689453125</v>
+        <v>345.7537536621094</v>
       </c>
       <c r="F67" t="n">
-        <v>12953600</v>
+        <v>6942300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>345.9227522622342</v>
+        <v>345.7537887198587</v>
       </c>
       <c r="C68" t="n">
-        <v>347.751765473026</v>
+        <v>346.3701134204293</v>
       </c>
       <c r="D68" t="n">
-        <v>343.9048707541211</v>
+        <v>341.777664727478</v>
       </c>
       <c r="E68" t="n">
-        <v>345.7537536621094</v>
+        <v>344.8194274902344</v>
       </c>
       <c r="F68" t="n">
-        <v>6942300</v>
+        <v>7004600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>345.7537581195867</v>
+        <v>343.9347204472646</v>
       </c>
       <c r="C69" t="n">
-        <v>346.3700827656107</v>
+        <v>345.5450457875993</v>
       </c>
       <c r="D69" t="n">
-        <v>341.7776344791052</v>
+        <v>341.6683310172716</v>
       </c>
       <c r="E69" t="n">
-        <v>344.8193969726562</v>
+        <v>343.0500183105469</v>
       </c>
       <c r="F69" t="n">
-        <v>7004600</v>
+        <v>7269300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>343.9347204472646</v>
+        <v>343.4873664669518</v>
       </c>
       <c r="C70" t="n">
-        <v>345.5450457875993</v>
+        <v>345.7140163182048</v>
       </c>
       <c r="D70" t="n">
-        <v>341.6683310172716</v>
+        <v>341.6285335316323</v>
       </c>
       <c r="E70" t="n">
-        <v>343.0500183105469</v>
+        <v>342.3541870117188</v>
       </c>
       <c r="F70" t="n">
-        <v>7269300</v>
+        <v>7263500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>343.4873664669518</v>
+        <v>343.1096587982668</v>
       </c>
       <c r="C71" t="n">
-        <v>345.7140163182048</v>
+        <v>345.4555571592003</v>
       </c>
       <c r="D71" t="n">
-        <v>341.6285335316323</v>
+        <v>342.2150067207226</v>
       </c>
       <c r="E71" t="n">
-        <v>342.3541870117188</v>
+        <v>343.9446411132812</v>
       </c>
       <c r="F71" t="n">
-        <v>7263500</v>
+        <v>6805000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>343.1096587982668</v>
+        <v>343.9844025059169</v>
       </c>
       <c r="C72" t="n">
-        <v>345.4555571592003</v>
+        <v>347.8213777963309</v>
       </c>
       <c r="D72" t="n">
-        <v>342.2150067207226</v>
+        <v>343.9844025059169</v>
       </c>
       <c r="E72" t="n">
-        <v>343.9446411132812</v>
+        <v>347.1653137207031</v>
       </c>
       <c r="F72" t="n">
-        <v>6805000</v>
+        <v>18623900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>343.9844025059169</v>
+        <v>347.9108213067459</v>
       </c>
       <c r="C73" t="n">
-        <v>347.8213777963309</v>
+        <v>351.3302900915655</v>
       </c>
       <c r="D73" t="n">
-        <v>343.9844025059169</v>
+        <v>347.5032649901081</v>
       </c>
       <c r="E73" t="n">
-        <v>347.1653137207031</v>
+        <v>349.9883422851562</v>
       </c>
       <c r="F73" t="n">
-        <v>18623900</v>
+        <v>5043500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>347.9108213067459</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="C74" t="n">
-        <v>351.3302900915655</v>
+        <v>354.2527532371108</v>
       </c>
       <c r="D74" t="n">
-        <v>347.5032649901081</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="E74" t="n">
-        <v>349.9883422851562</v>
+        <v>351.2706604003906</v>
       </c>
       <c r="F74" t="n">
-        <v>5043500</v>
+        <v>3703200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>349.8988624434305</v>
+        <v>351.2706375438569</v>
       </c>
       <c r="C75" t="n">
-        <v>354.2527224604554</v>
+        <v>353.86504358199</v>
       </c>
       <c r="D75" t="n">
-        <v>349.8988624434305</v>
+        <v>350.9028509715926</v>
       </c>
       <c r="E75" t="n">
-        <v>351.2706298828125</v>
+        <v>353.0201416015625</v>
       </c>
       <c r="F75" t="n">
-        <v>3703200</v>
+        <v>2023600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>351.2706679101954</v>
+        <v>352.9803906057607</v>
       </c>
       <c r="C76" t="n">
-        <v>353.8650741726075</v>
+        <v>354.6006658812749</v>
       </c>
       <c r="D76" t="n">
-        <v>350.9028813061371</v>
+        <v>351.5986730469889</v>
       </c>
       <c r="E76" t="n">
-        <v>353.0201721191406</v>
+        <v>352.8809814453125</v>
       </c>
       <c r="F76" t="n">
-        <v>2023600</v>
+        <v>2017000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>352.9803906057607</v>
+        <v>353.3680687798424</v>
       </c>
       <c r="C77" t="n">
-        <v>354.6006658812749</v>
+        <v>354.4217392079314</v>
       </c>
       <c r="D77" t="n">
-        <v>351.5986730469889</v>
+        <v>351.6881539711041</v>
       </c>
       <c r="E77" t="n">
-        <v>352.8809814453125</v>
+        <v>352.4933166503906</v>
       </c>
       <c r="F77" t="n">
-        <v>2017000</v>
+        <v>3989900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>353.3680687798424</v>
+        <v>351.8869529196318</v>
       </c>
       <c r="C78" t="n">
-        <v>354.4217392079314</v>
+        <v>352.7517549841574</v>
       </c>
       <c r="D78" t="n">
-        <v>351.6881539711041</v>
+        <v>350.5549550996776</v>
       </c>
       <c r="E78" t="n">
-        <v>352.4933166503906</v>
+        <v>351.5092163085938</v>
       </c>
       <c r="F78" t="n">
-        <v>3989900</v>
+        <v>3366500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>351.8869529196318</v>
+        <v>351.539030494231</v>
       </c>
       <c r="C79" t="n">
-        <v>352.7517549841574</v>
+        <v>353.0797966289462</v>
       </c>
       <c r="D79" t="n">
-        <v>350.5549550996776</v>
+        <v>348.5967074506911</v>
       </c>
       <c r="E79" t="n">
-        <v>351.5092163085938</v>
+        <v>348.6165771484375</v>
       </c>
       <c r="F79" t="n">
-        <v>3366500</v>
+        <v>3503200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>351.539030494231</v>
+        <v>347.7816144857114</v>
       </c>
       <c r="C80" t="n">
-        <v>353.0797966289462</v>
+        <v>347.9605327817998</v>
       </c>
       <c r="D80" t="n">
-        <v>348.5967074506911</v>
+        <v>341.4297722912301</v>
       </c>
       <c r="E80" t="n">
-        <v>348.6165771484375</v>
+        <v>344.411865234375</v>
       </c>
       <c r="F80" t="n">
-        <v>3503200</v>
+        <v>5403800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>347.7816144857114</v>
+        <v>342.443665092254</v>
       </c>
       <c r="C81" t="n">
-        <v>347.9605327817998</v>
+        <v>355.4058372808095</v>
       </c>
       <c r="D81" t="n">
-        <v>341.4297722912301</v>
+        <v>341.996339026907</v>
       </c>
       <c r="E81" t="n">
-        <v>344.411865234375</v>
+        <v>351.6881408691406</v>
       </c>
       <c r="F81" t="n">
-        <v>5403800</v>
+        <v>7592200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>342.443665092254</v>
+        <v>351.5688449134013</v>
       </c>
       <c r="C82" t="n">
-        <v>355.4058372808095</v>
+        <v>356.4793600348679</v>
       </c>
       <c r="D82" t="n">
-        <v>341.996339026907</v>
+        <v>349.8988802653619</v>
       </c>
       <c r="E82" t="n">
-        <v>351.6881408691406</v>
+        <v>355.4256896972656</v>
       </c>
       <c r="F82" t="n">
-        <v>7592200</v>
+        <v>6775400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>351.5688750998228</v>
+        <v>355.0181456831753</v>
       </c>
       <c r="C83" t="n">
-        <v>356.4793906429162</v>
+        <v>356.1414055038805</v>
       </c>
       <c r="D83" t="n">
-        <v>349.8989103083969</v>
+        <v>352.3939197646881</v>
       </c>
       <c r="E83" t="n">
-        <v>355.4257202148438</v>
+        <v>353.7557373046875</v>
       </c>
       <c r="F83" t="n">
-        <v>6775400</v>
+        <v>6333900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>355.0181456831753</v>
+        <v>352.8809877738215</v>
       </c>
       <c r="C84" t="n">
-        <v>356.1414055038805</v>
+        <v>354.2229356253969</v>
       </c>
       <c r="D84" t="n">
-        <v>352.3939197646881</v>
+        <v>347.4138175407059</v>
       </c>
       <c r="E84" t="n">
-        <v>353.7557373046875</v>
+        <v>350.1275329589844</v>
       </c>
       <c r="F84" t="n">
-        <v>6333900</v>
+        <v>6357600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>352.8809877738215</v>
+        <v>350.0579077159175</v>
       </c>
       <c r="C85" t="n">
-        <v>354.2229356253969</v>
+        <v>352.5827545683982</v>
       </c>
       <c r="D85" t="n">
-        <v>347.4138175407059</v>
+        <v>347.0758151664314</v>
       </c>
       <c r="E85" t="n">
-        <v>350.1275329589844</v>
+        <v>347.6821594238281</v>
       </c>
       <c r="F85" t="n">
-        <v>6357600</v>
+        <v>4902900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>350.0579384420253</v>
+        <v>340.733891403126</v>
       </c>
       <c r="C86" t="n">
-        <v>352.582785516123</v>
+        <v>344.4416373710181</v>
       </c>
       <c r="D86" t="n">
-        <v>347.075845630788</v>
+        <v>335.3064914902319</v>
       </c>
       <c r="E86" t="n">
-        <v>347.6821899414062</v>
+        <v>341.1513977050781</v>
       </c>
       <c r="F86" t="n">
-        <v>4902900</v>
+        <v>13281300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>340.7339218833562</v>
+        <v>334.9884397502153</v>
       </c>
       <c r="C87" t="n">
-        <v>344.4416681829234</v>
+        <v>335.5053249382782</v>
       </c>
       <c r="D87" t="n">
-        <v>335.306521484956</v>
+        <v>321.8970384159538</v>
       </c>
       <c r="E87" t="n">
-        <v>341.1514282226562</v>
+        <v>325.9228820800781</v>
       </c>
       <c r="F87" t="n">
-        <v>13281300</v>
+        <v>20383500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>334.9884397502153</v>
+        <v>326.6982042036898</v>
       </c>
       <c r="C88" t="n">
-        <v>335.5053249382782</v>
+        <v>327.9307928311059</v>
       </c>
       <c r="D88" t="n">
-        <v>321.8970384159538</v>
+        <v>322.0063770709054</v>
       </c>
       <c r="E88" t="n">
-        <v>325.9228820800781</v>
+        <v>327.2051696777344</v>
       </c>
       <c r="F88" t="n">
-        <v>20383500</v>
+        <v>9388400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>326.6982042036898</v>
+        <v>327.3641650074799</v>
       </c>
       <c r="C89" t="n">
-        <v>327.9307928311059</v>
+        <v>329.7100935773221</v>
       </c>
       <c r="D89" t="n">
-        <v>322.0063770709054</v>
+        <v>324.421842198657</v>
       </c>
       <c r="E89" t="n">
-        <v>327.2051696777344</v>
+        <v>325.7936096191406</v>
       </c>
       <c r="F89" t="n">
-        <v>9388400</v>
+        <v>8587700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>327.3641956721743</v>
+        <v>324.8294159854098</v>
       </c>
       <c r="C90" t="n">
-        <v>329.7101244617631</v>
+        <v>327.2846735195349</v>
       </c>
       <c r="D90" t="n">
-        <v>324.4218725877395</v>
+        <v>323.4576484910236</v>
       </c>
       <c r="E90" t="n">
-        <v>325.7936401367188</v>
+        <v>326.34033203125</v>
       </c>
       <c r="F90" t="n">
-        <v>8587700</v>
+        <v>8341600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>324.8294159854098</v>
+        <v>320.3065853250236</v>
       </c>
       <c r="C91" t="n">
-        <v>327.2846735195349</v>
+        <v>326.3602298184734</v>
       </c>
       <c r="D91" t="n">
-        <v>323.4576484910236</v>
+        <v>319.6405712796447</v>
       </c>
       <c r="E91" t="n">
-        <v>326.34033203125</v>
+        <v>323.8751525878906</v>
       </c>
       <c r="F91" t="n">
-        <v>8341600</v>
+        <v>8279900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>320.3066155063486</v>
+        <v>324.4815084058711</v>
       </c>
       <c r="C92" t="n">
-        <v>326.3602605702113</v>
+        <v>326.708158311709</v>
       </c>
       <c r="D92" t="n">
-        <v>319.6406013982136</v>
+        <v>321.0719896048092</v>
       </c>
       <c r="E92" t="n">
-        <v>323.8751831054688</v>
+        <v>323.33837890625</v>
       </c>
       <c r="F92" t="n">
-        <v>8279900</v>
+        <v>8974600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>324.4815084058711</v>
+        <v>324.5113354316111</v>
       </c>
       <c r="C93" t="n">
-        <v>326.708158311709</v>
+        <v>326.4298382199604</v>
       </c>
       <c r="D93" t="n">
-        <v>321.0719896048092</v>
+        <v>322.0660277886144</v>
       </c>
       <c r="E93" t="n">
-        <v>323.33837890625</v>
+        <v>324.4119262695312</v>
       </c>
       <c r="F93" t="n">
-        <v>8974600</v>
+        <v>6938700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>324.5113354316111</v>
+        <v>323.9149045306469</v>
       </c>
       <c r="C94" t="n">
-        <v>326.4298382199604</v>
+        <v>325.8433269631201</v>
       </c>
       <c r="D94" t="n">
-        <v>322.0660277886144</v>
+        <v>322.6823158838599</v>
       </c>
       <c r="E94" t="n">
-        <v>324.4119262695312</v>
+        <v>324.2330017089844</v>
       </c>
       <c r="F94" t="n">
-        <v>6938700</v>
+        <v>5667900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>323.9149045306469</v>
+        <v>326.0421094095482</v>
       </c>
       <c r="C95" t="n">
-        <v>325.8433269631201</v>
+        <v>330.0182326950305</v>
       </c>
       <c r="D95" t="n">
-        <v>322.6823158838599</v>
+        <v>323.089836656661</v>
       </c>
       <c r="E95" t="n">
-        <v>324.2330017089844</v>
+        <v>326.5291748046875</v>
       </c>
       <c r="F95" t="n">
-        <v>5667900</v>
+        <v>7540200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>326.0421398816049</v>
+        <v>326.5192619706527</v>
       </c>
       <c r="C96" t="n">
-        <v>330.0182635386976</v>
+        <v>326.9665576483999</v>
       </c>
       <c r="D96" t="n">
-        <v>323.0898668527969</v>
+        <v>322.9705645834554</v>
       </c>
       <c r="E96" t="n">
-        <v>326.5292053222656</v>
+        <v>323.3184814453125</v>
       </c>
       <c r="F96" t="n">
-        <v>7540200</v>
+        <v>6365800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>326.5192927903481</v>
+        <v>324.779721039233</v>
       </c>
       <c r="C97" t="n">
-        <v>326.9665885103149</v>
+        <v>326.4298159438193</v>
       </c>
       <c r="D97" t="n">
-        <v>322.9705950681941</v>
+        <v>322.9407578402086</v>
       </c>
       <c r="E97" t="n">
-        <v>323.3185119628906</v>
+        <v>325.0282287597656</v>
       </c>
       <c r="F97" t="n">
-        <v>6365800</v>
+        <v>8106000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>324.7797515334782</v>
+        <v>328.0302144269235</v>
       </c>
       <c r="C98" t="n">
-        <v>326.4298465929955</v>
+        <v>331.370143867361</v>
       </c>
       <c r="D98" t="n">
-        <v>322.9407881617898</v>
+        <v>321.5789632505275</v>
       </c>
       <c r="E98" t="n">
-        <v>325.0282592773438</v>
+        <v>329.8194580078125</v>
       </c>
       <c r="F98" t="n">
-        <v>8106000</v>
+        <v>10214200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>328.0302144269235</v>
+        <v>330.2369306535451</v>
       </c>
       <c r="C99" t="n">
-        <v>331.370143867361</v>
+        <v>331.0122735041925</v>
       </c>
       <c r="D99" t="n">
-        <v>321.5789632505275</v>
+        <v>319.6803278657264</v>
       </c>
       <c r="E99" t="n">
-        <v>329.8194580078125</v>
+        <v>319.908935546875</v>
       </c>
       <c r="F99" t="n">
-        <v>10214200</v>
+        <v>11199100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>330.2369936591709</v>
+        <v>322.8910614362982</v>
       </c>
       <c r="C100" t="n">
-        <v>331.0123366577452</v>
+        <v>332.6922224170356</v>
       </c>
       <c r="D100" t="n">
-        <v>319.6803888572667</v>
+        <v>322.1753579360102</v>
       </c>
       <c r="E100" t="n">
-        <v>319.9089965820312</v>
+        <v>331.8472900390625</v>
       </c>
       <c r="F100" t="n">
-        <v>11199100</v>
+        <v>8502400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>322.8910614362982</v>
+        <v>329.6703793378445</v>
       </c>
       <c r="C101" t="n">
-        <v>332.6922224170356</v>
+        <v>333.7856822919601</v>
       </c>
       <c r="D101" t="n">
-        <v>322.1753579360102</v>
+        <v>326.906974335595</v>
       </c>
       <c r="E101" t="n">
-        <v>331.8472900390625</v>
+        <v>326.9666137695312</v>
       </c>
       <c r="F101" t="n">
-        <v>8502400</v>
+        <v>9081200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>329.6703793378445</v>
+        <v>325.1574551429397</v>
       </c>
       <c r="C102" t="n">
-        <v>333.7856822919601</v>
+        <v>329.332397339644</v>
       </c>
       <c r="D102" t="n">
-        <v>326.906974335595</v>
+        <v>322.4835397495656</v>
       </c>
       <c r="E102" t="n">
-        <v>326.9666137695312</v>
+        <v>327.9805297851562</v>
       </c>
       <c r="F102" t="n">
-        <v>9081200</v>
+        <v>8472300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>325.15742488804</v>
+        <v>331.0123001239136</v>
       </c>
       <c r="C103" t="n">
-        <v>329.3323666962788</v>
+        <v>335.5748984583446</v>
       </c>
       <c r="D103" t="n">
-        <v>322.4835097434655</v>
+        <v>326.8572581115669</v>
       </c>
       <c r="E103" t="n">
-        <v>327.9804992675781</v>
+        <v>327.1654052734375</v>
       </c>
       <c r="F103" t="n">
-        <v>8472300</v>
+        <v>8339000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>331.0123001239136</v>
+        <v>329.7995873671293</v>
       </c>
       <c r="C104" t="n">
-        <v>335.5748984583446</v>
+        <v>333.1295971166072</v>
       </c>
       <c r="D104" t="n">
-        <v>326.8572581115669</v>
+        <v>325.1475298017769</v>
       </c>
       <c r="E104" t="n">
-        <v>327.1654052734375</v>
+        <v>329.6007690429688</v>
       </c>
       <c r="F104" t="n">
-        <v>8339000</v>
+        <v>7798800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>329.7995873671293</v>
+        <v>328.7857002676274</v>
       </c>
       <c r="C105" t="n">
-        <v>333.1295971166072</v>
+        <v>330.8334016821115</v>
       </c>
       <c r="D105" t="n">
-        <v>325.1475298017769</v>
+        <v>321.6883044313802</v>
       </c>
       <c r="E105" t="n">
-        <v>329.6007690429688</v>
+        <v>323.6365966796875</v>
       </c>
       <c r="F105" t="n">
-        <v>7798800</v>
+        <v>8513400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,25 +3173,25 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>328.7857002676274</v>
+        <v>323.4373584411114</v>
       </c>
       <c r="C106" t="n">
-        <v>330.8334016821115</v>
+        <v>328.5871090806843</v>
       </c>
       <c r="D106" t="n">
-        <v>321.6883044313802</v>
+        <v>323.2779818799478</v>
       </c>
       <c r="E106" t="n">
-        <v>323.6365966796875</v>
+        <v>326.8838195800781</v>
       </c>
       <c r="F106" t="n">
-        <v>8513400</v>
+        <v>5801800</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3199,25 +3199,25 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>323.4373584411114</v>
+        <v>325.6387312474863</v>
       </c>
       <c r="C107" t="n">
-        <v>328.5871090806843</v>
+        <v>329.7425790622465</v>
       </c>
       <c r="D107" t="n">
-        <v>323.2779818799478</v>
+        <v>325.1406908738898</v>
       </c>
       <c r="E107" t="n">
-        <v>326.8838195800781</v>
+        <v>327.9496154785156</v>
       </c>
       <c r="F107" t="n">
-        <v>5801800</v>
+        <v>8264300</v>
       </c>
       <c r="G107" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>325.6387009449491</v>
+        <v>327.6009856634334</v>
       </c>
       <c r="C108" t="n">
-        <v>329.7425483778229</v>
+        <v>330.9378315846288</v>
       </c>
       <c r="D108" t="n">
-        <v>325.140660617698</v>
+        <v>322.7301366033025</v>
       </c>
       <c r="E108" t="n">
-        <v>327.9495849609375</v>
+        <v>322.909423828125</v>
       </c>
       <c r="F108" t="n">
-        <v>8264300</v>
+        <v>9392600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>327.6010166244024</v>
+        <v>322.5608168831966</v>
       </c>
       <c r="C109" t="n">
-        <v>330.9378628609571</v>
+        <v>325.2004551971415</v>
       </c>
       <c r="D109" t="n">
-        <v>322.7301671039365</v>
+        <v>311.5939884628011</v>
       </c>
       <c r="E109" t="n">
-        <v>322.9094543457031</v>
+        <v>312.8490295410156</v>
       </c>
       <c r="F109" t="n">
-        <v>9392600</v>
+        <v>11653900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>322.5607854182599</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="C110" t="n">
-        <v>325.2004234747151</v>
+        <v>320.1204394263468</v>
       </c>
       <c r="D110" t="n">
-        <v>311.5939580676488</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="E110" t="n">
-        <v>312.8489990234375</v>
+        <v>318.247802734375</v>
       </c>
       <c r="F110" t="n">
-        <v>11653900</v>
+        <v>8591700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>313.1777553150958</v>
+        <v>318.2477947880967</v>
       </c>
       <c r="C111" t="n">
-        <v>320.1204394263468</v>
+        <v>321.0168980150915</v>
       </c>
       <c r="D111" t="n">
-        <v>313.1777553150958</v>
+        <v>315.4786915611019</v>
       </c>
       <c r="E111" t="n">
-        <v>318.247802734375</v>
+        <v>319.0446472167969</v>
       </c>
       <c r="F111" t="n">
-        <v>8591700</v>
+        <v>7091900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>318.2477947880967</v>
+        <v>316.2456644955574</v>
       </c>
       <c r="C112" t="n">
-        <v>321.0168980150915</v>
+        <v>318.9450651881826</v>
       </c>
       <c r="D112" t="n">
-        <v>315.4786915611019</v>
+        <v>314.492583063333</v>
       </c>
       <c r="E112" t="n">
-        <v>319.0446472167969</v>
+        <v>317.6800231933594</v>
       </c>
       <c r="F112" t="n">
-        <v>7091900</v>
+        <v>5967600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>316.2456341157693</v>
+        <v>316.8632425049395</v>
       </c>
       <c r="C113" t="n">
-        <v>318.9450345490796</v>
+        <v>321.0866456850293</v>
       </c>
       <c r="D113" t="n">
-        <v>314.4925528519528</v>
+        <v>316.574400965125</v>
       </c>
       <c r="E113" t="n">
-        <v>317.6799926757812</v>
+        <v>319.692138671875</v>
       </c>
       <c r="F113" t="n">
-        <v>5967600</v>
+        <v>6831100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>316.8632122574057</v>
+        <v>317.789583394942</v>
       </c>
       <c r="C114" t="n">
-        <v>321.0866150343326</v>
+        <v>319.2637633222238</v>
       </c>
       <c r="D114" t="n">
-        <v>316.5743707451638</v>
+        <v>303.515730464103</v>
       </c>
       <c r="E114" t="n">
-        <v>319.6921081542969</v>
+        <v>305.3186340332031</v>
       </c>
       <c r="F114" t="n">
-        <v>6831100</v>
+        <v>13048000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>317.7896151590316</v>
+        <v>304.3026700645725</v>
       </c>
       <c r="C115" t="n">
-        <v>319.2637952336624</v>
+        <v>308.0578835603972</v>
       </c>
       <c r="D115" t="n">
-        <v>303.5157608014752</v>
+        <v>301.8921412670219</v>
       </c>
       <c r="E115" t="n">
-        <v>305.3186645507812</v>
+        <v>306.0159301757812</v>
       </c>
       <c r="F115" t="n">
-        <v>13048000</v>
+        <v>9120200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>304.30263971785</v>
+        <v>307.3406745970078</v>
       </c>
       <c r="C116" t="n">
-        <v>308.0578528391844</v>
+        <v>312.7095639299417</v>
       </c>
       <c r="D116" t="n">
-        <v>301.8921111606905</v>
+        <v>307.0418625590578</v>
       </c>
       <c r="E116" t="n">
-        <v>306.0158996582031</v>
+        <v>311.7632751464844</v>
       </c>
       <c r="F116" t="n">
-        <v>9120200</v>
+        <v>7624200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>307.3407046816708</v>
+        <v>313.2474703757061</v>
       </c>
       <c r="C117" t="n">
-        <v>312.7095945401492</v>
+        <v>318.1681114796254</v>
       </c>
       <c r="D117" t="n">
-        <v>307.0418926144709</v>
+        <v>312.709578284735</v>
       </c>
       <c r="E117" t="n">
-        <v>311.7633056640625</v>
+        <v>315.4587707519531</v>
       </c>
       <c r="F117" t="n">
-        <v>7624200</v>
+        <v>8725500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>313.2475006793624</v>
+        <v>313.2275530184615</v>
       </c>
       <c r="C118" t="n">
-        <v>318.168142259306</v>
+        <v>318.9749585636924</v>
       </c>
       <c r="D118" t="n">
-        <v>312.7096085363555</v>
+        <v>310.7274109356645</v>
       </c>
       <c r="E118" t="n">
-        <v>315.4588012695312</v>
+        <v>318.8853149414062</v>
       </c>
       <c r="F118" t="n">
-        <v>8725500</v>
+        <v>12412900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>313.2275230423357</v>
+        <v>314.2634710190134</v>
       </c>
       <c r="C119" t="n">
-        <v>318.9749280375353</v>
+        <v>321.3356502974509</v>
       </c>
       <c r="D119" t="n">
-        <v>310.7273811988043</v>
+        <v>313.3670044395995</v>
       </c>
       <c r="E119" t="n">
-        <v>318.8852844238281</v>
+        <v>319.2538452148438</v>
       </c>
       <c r="F119" t="n">
-        <v>12412900</v>
+        <v>6674900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>314.2634710190134</v>
+        <v>314.5722564235918</v>
       </c>
       <c r="C120" t="n">
-        <v>321.3356502974509</v>
+        <v>320.7778503840851</v>
       </c>
       <c r="D120" t="n">
-        <v>313.3670044395995</v>
+        <v>313.117987052978</v>
       </c>
       <c r="E120" t="n">
-        <v>319.2538452148438</v>
+        <v>319.5725708007812</v>
       </c>
       <c r="F120" t="n">
-        <v>6674900</v>
+        <v>5474300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>314.5722564235918</v>
+        <v>320.1801887712339</v>
       </c>
       <c r="C121" t="n">
-        <v>320.7778503840851</v>
+        <v>324.4932049097204</v>
       </c>
       <c r="D121" t="n">
-        <v>313.117987052978</v>
+        <v>318.5466018009251</v>
       </c>
       <c r="E121" t="n">
-        <v>319.5725708007812</v>
+        <v>319.2139892578125</v>
       </c>
       <c r="F121" t="n">
-        <v>5474300</v>
+        <v>5257900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>320.1801887712339</v>
+        <v>318.0784411900573</v>
       </c>
       <c r="C122" t="n">
-        <v>324.4932049097204</v>
+        <v>321.5348424853333</v>
       </c>
       <c r="D122" t="n">
-        <v>318.5466018009251</v>
+        <v>313.5363155637196</v>
       </c>
       <c r="E122" t="n">
-        <v>319.2139892578125</v>
+        <v>318.5466003417969</v>
       </c>
       <c r="F122" t="n">
-        <v>5257900</v>
+        <v>8267200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>318.0784411900573</v>
+        <v>314.8113170354491</v>
       </c>
       <c r="C123" t="n">
-        <v>321.5348424853333</v>
+        <v>316.4449040988039</v>
       </c>
       <c r="D123" t="n">
-        <v>313.5363155637196</v>
+        <v>311.0760141261629</v>
       </c>
       <c r="E123" t="n">
-        <v>318.5466003417969</v>
+        <v>316.1161804199219</v>
       </c>
       <c r="F123" t="n">
-        <v>8267200</v>
+        <v>6439700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>314.8113170354491</v>
+        <v>312.2314560667069</v>
       </c>
       <c r="C124" t="n">
-        <v>316.4449040988039</v>
+        <v>315.1599358349184</v>
       </c>
       <c r="D124" t="n">
-        <v>311.0760141261629</v>
+        <v>308.9344312933075</v>
       </c>
       <c r="E124" t="n">
-        <v>316.1161804199219</v>
+        <v>314.7316284179688</v>
       </c>
       <c r="F124" t="n">
-        <v>6439700</v>
+        <v>8381500</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>312.2314560667069</v>
+        <v>314.1937431016918</v>
       </c>
       <c r="C125" t="n">
-        <v>315.1599358349184</v>
+        <v>315.8870925327801</v>
       </c>
       <c r="D125" t="n">
-        <v>308.9344312933075</v>
+        <v>310.2293611786528</v>
       </c>
       <c r="E125" t="n">
-        <v>314.7316284179688</v>
+        <v>313.1976623535156</v>
       </c>
       <c r="F125" t="n">
-        <v>8381500</v>
+        <v>5271300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>314.1937124870568</v>
+        <v>312.0222791858673</v>
       </c>
       <c r="C126" t="n">
-        <v>315.8870617531473</v>
+        <v>313.8450934912395</v>
       </c>
       <c r="D126" t="n">
-        <v>310.2293309503021</v>
+        <v>307.1813415762761</v>
       </c>
       <c r="E126" t="n">
-        <v>313.1976318359375</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F126" t="n">
-        <v>5271300</v>
+        <v>6376700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>312.0222791858673</v>
+        <v>306.9323542029832</v>
       </c>
       <c r="C127" t="n">
-        <v>313.8450934912395</v>
+        <v>309.7313388364715</v>
       </c>
       <c r="D127" t="n">
-        <v>307.1813415762761</v>
+        <v>304.8206373596136</v>
       </c>
       <c r="E127" t="n">
-        <v>307.7490844726562</v>
+        <v>305.2987670898438</v>
       </c>
       <c r="F127" t="n">
-        <v>6376700</v>
+        <v>7514900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>306.9323235221122</v>
+        <v>306.3844668672209</v>
       </c>
       <c r="C128" t="n">
-        <v>309.7313078758147</v>
+        <v>309.1336593983733</v>
       </c>
       <c r="D128" t="n">
-        <v>304.8206068898292</v>
+        <v>305.2190694406472</v>
       </c>
       <c r="E128" t="n">
-        <v>305.2987365722656</v>
+        <v>305.9362487792969</v>
       </c>
       <c r="F128" t="n">
-        <v>7514900</v>
+        <v>4814100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>306.3844668672209</v>
+        <v>306.6434401255651</v>
       </c>
       <c r="C129" t="n">
-        <v>309.1336593983733</v>
+        <v>309.9105835049712</v>
       </c>
       <c r="D129" t="n">
-        <v>305.2190694406472</v>
+        <v>306.1752809950723</v>
       </c>
       <c r="E129" t="n">
-        <v>305.9362487792969</v>
+        <v>308.8945617675781</v>
       </c>
       <c r="F129" t="n">
-        <v>4814100</v>
+        <v>6401200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>306.6434401255651</v>
+        <v>310.0998441452866</v>
       </c>
       <c r="C130" t="n">
-        <v>309.9105835049712</v>
+        <v>311.4644698112407</v>
       </c>
       <c r="D130" t="n">
-        <v>306.1752809950723</v>
+        <v>306.1752838399166</v>
       </c>
       <c r="E130" t="n">
-        <v>308.8945617675781</v>
+        <v>307.2510375976562</v>
       </c>
       <c r="F130" t="n">
-        <v>6401200</v>
+        <v>6872200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>310.0998441452866</v>
+        <v>306.2051850075188</v>
       </c>
       <c r="C131" t="n">
-        <v>311.4644698112407</v>
+        <v>306.7331065856557</v>
       </c>
       <c r="D131" t="n">
-        <v>306.1752838399166</v>
+        <v>297.3301019351647</v>
       </c>
       <c r="E131" t="n">
-        <v>307.2510375976562</v>
+        <v>297.8480529785156</v>
       </c>
       <c r="F131" t="n">
-        <v>6872200</v>
+        <v>7191700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>306.2051850075188</v>
+        <v>296.8719016022564</v>
       </c>
       <c r="C132" t="n">
-        <v>306.7331065856557</v>
+        <v>301.2845318265138</v>
       </c>
       <c r="D132" t="n">
-        <v>297.3301019351647</v>
+        <v>295.8658503636263</v>
       </c>
       <c r="E132" t="n">
-        <v>297.8480529785156</v>
+        <v>298.5353393554688</v>
       </c>
       <c r="F132" t="n">
-        <v>7191700</v>
+        <v>6826400</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>296.8719016022564</v>
+        <v>298.6748142545254</v>
       </c>
       <c r="C133" t="n">
-        <v>301.2845318265138</v>
+        <v>301.7327894042891</v>
       </c>
       <c r="D133" t="n">
-        <v>295.8658503636263</v>
+        <v>297.8381100854838</v>
       </c>
       <c r="E133" t="n">
-        <v>298.5353393554688</v>
+        <v>300.4378662109375</v>
       </c>
       <c r="F133" t="n">
-        <v>6826400</v>
+        <v>14398100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>298.6748142545254</v>
+        <v>304.0038572697504</v>
       </c>
       <c r="C134" t="n">
-        <v>301.7327894042891</v>
+        <v>306.6434651794843</v>
       </c>
       <c r="D134" t="n">
-        <v>297.8381100854838</v>
+        <v>301.6630614260347</v>
       </c>
       <c r="E134" t="n">
-        <v>300.4378662109375</v>
+        <v>303.246826171875</v>
       </c>
       <c r="F134" t="n">
-        <v>14398100</v>
+        <v>7824500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>304.0038572697504</v>
+        <v>300.8163767349488</v>
       </c>
       <c r="C135" t="n">
-        <v>306.6434651794843</v>
+        <v>304.8405513457489</v>
       </c>
       <c r="D135" t="n">
-        <v>301.6630614260347</v>
+        <v>299.4417804808951</v>
       </c>
       <c r="E135" t="n">
-        <v>303.246826171875</v>
+        <v>302.5694885253906</v>
       </c>
       <c r="F135" t="n">
-        <v>7824500</v>
+        <v>5375900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>300.8163767349488</v>
+        <v>304.2827391072273</v>
       </c>
       <c r="C136" t="n">
-        <v>304.8405513457489</v>
+        <v>307.2809213034843</v>
       </c>
       <c r="D136" t="n">
-        <v>299.4417804808951</v>
+        <v>300.9857144661871</v>
       </c>
       <c r="E136" t="n">
-        <v>302.5694885253906</v>
+        <v>303.7149658203125</v>
       </c>
       <c r="F136" t="n">
-        <v>5375900</v>
+        <v>6280900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>304.2827391072273</v>
+        <v>302.9678939055341</v>
       </c>
       <c r="C137" t="n">
-        <v>307.2809213034843</v>
+        <v>306.6633446025994</v>
       </c>
       <c r="D137" t="n">
-        <v>300.9857144661871</v>
+        <v>301.8124367047168</v>
       </c>
       <c r="E137" t="n">
-        <v>303.7149658203125</v>
+        <v>304.33251953125</v>
       </c>
       <c r="F137" t="n">
-        <v>6280900</v>
+        <v>7652700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>302.9679242862715</v>
+        <v>303.1273151321971</v>
       </c>
       <c r="C138" t="n">
-        <v>306.6633753539059</v>
+        <v>303.3962460038449</v>
       </c>
       <c r="D138" t="n">
-        <v>301.8124669695884</v>
+        <v>293.166507172264</v>
       </c>
       <c r="E138" t="n">
-        <v>304.3325500488281</v>
+        <v>294.3617858886719</v>
       </c>
       <c r="F138" t="n">
-        <v>7652700</v>
+        <v>9974400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>303.127283705864</v>
+        <v>297.5592048794472</v>
       </c>
       <c r="C139" t="n">
-        <v>303.3962145496307</v>
+        <v>299.5015440476056</v>
       </c>
       <c r="D139" t="n">
-        <v>293.1664767786049</v>
+        <v>294.7303392781201</v>
       </c>
       <c r="E139" t="n">
-        <v>294.3617553710938</v>
+        <v>298.3660278320312</v>
       </c>
       <c r="F139" t="n">
-        <v>9974400</v>
+        <v>9330300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>297.5592048794472</v>
+        <v>300.4179440831887</v>
       </c>
       <c r="C140" t="n">
-        <v>299.5015440476056</v>
+        <v>302.1511147673973</v>
       </c>
       <c r="D140" t="n">
-        <v>294.7303392781201</v>
+        <v>295.4275700673832</v>
       </c>
       <c r="E140" t="n">
-        <v>298.3660278320312</v>
+        <v>301.055419921875</v>
       </c>
       <c r="F140" t="n">
-        <v>9330300</v>
+        <v>10246900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>300.4179440831887</v>
+        <v>303.8544032182521</v>
       </c>
       <c r="C141" t="n">
-        <v>302.1511147673973</v>
+        <v>303.8544032182521</v>
       </c>
       <c r="D141" t="n">
-        <v>295.4275700673832</v>
+        <v>292.7381694353985</v>
       </c>
       <c r="E141" t="n">
-        <v>301.055419921875</v>
+        <v>297.3400573730469</v>
       </c>
       <c r="F141" t="n">
-        <v>10246900</v>
+        <v>7707600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>303.8544344044319</v>
+        <v>296.6328211241279</v>
       </c>
       <c r="C142" t="n">
-        <v>303.8544344044319</v>
+        <v>301.2845313811459</v>
       </c>
       <c r="D142" t="n">
-        <v>292.7381994806606</v>
+        <v>294.6904819925192</v>
       </c>
       <c r="E142" t="n">
-        <v>297.340087890625</v>
+        <v>299.6210632324219</v>
       </c>
       <c r="F142" t="n">
-        <v>7707600</v>
+        <v>4376000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>296.6328211241279</v>
+        <v>299.5612984468797</v>
       </c>
       <c r="C143" t="n">
-        <v>301.2845313811459</v>
+        <v>303.2268985064469</v>
       </c>
       <c r="D143" t="n">
-        <v>294.6904819925192</v>
+        <v>298.286316373369</v>
       </c>
       <c r="E143" t="n">
-        <v>299.6210632324219</v>
+        <v>302.1411437988281</v>
       </c>
       <c r="F143" t="n">
-        <v>4376000</v>
+        <v>5501000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>299.5612984468797</v>
+        <v>301.2546730003434</v>
       </c>
       <c r="C144" t="n">
-        <v>303.2268985064469</v>
+        <v>303.7847266884853</v>
       </c>
       <c r="D144" t="n">
-        <v>298.286316373369</v>
+        <v>299.9398390775635</v>
       </c>
       <c r="E144" t="n">
-        <v>302.1411437988281</v>
+        <v>301.3642272949219</v>
       </c>
       <c r="F144" t="n">
-        <v>5501000</v>
+        <v>4413900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>301.2546730003434</v>
+        <v>306.5239246667074</v>
       </c>
       <c r="C145" t="n">
-        <v>303.7847266884853</v>
+        <v>309.8607706923777</v>
       </c>
       <c r="D145" t="n">
-        <v>299.9398390775635</v>
+        <v>306.4940434616348</v>
       </c>
       <c r="E145" t="n">
-        <v>301.3642272949219</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F145" t="n">
-        <v>4413900</v>
+        <v>6879300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>306.5239246667074</v>
+        <v>306.7928541611418</v>
       </c>
       <c r="C146" t="n">
-        <v>309.8607706923777</v>
+        <v>308.3666482846536</v>
       </c>
       <c r="D146" t="n">
-        <v>306.4940434616348</v>
+        <v>302.4001346469872</v>
       </c>
       <c r="E146" t="n">
-        <v>307.7490844726562</v>
+        <v>307.0817260742188</v>
       </c>
       <c r="F146" t="n">
-        <v>6879300</v>
+        <v>4811500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>306.792884650012</v>
+        <v>307.5000714824076</v>
       </c>
       <c r="C147" t="n">
-        <v>308.3666789299265</v>
+        <v>307.7889434035062</v>
       </c>
       <c r="D147" t="n">
-        <v>302.4001646993119</v>
+        <v>302.3204699616491</v>
       </c>
       <c r="E147" t="n">
-        <v>307.0817565917969</v>
+        <v>303.1671142578125</v>
       </c>
       <c r="F147" t="n">
-        <v>4811500</v>
+        <v>5190000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>307.5000714824076</v>
+        <v>302.7388065700545</v>
       </c>
       <c r="C148" t="n">
-        <v>307.7889434035062</v>
+        <v>308.5360036681458</v>
       </c>
       <c r="D148" t="n">
-        <v>302.3204699616491</v>
+        <v>301.155041869684</v>
       </c>
       <c r="E148" t="n">
-        <v>303.1671142578125</v>
+        <v>308.1774291992188</v>
       </c>
       <c r="F148" t="n">
-        <v>5190000</v>
+        <v>6787200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>302.7388065700545</v>
+        <v>307.2610301082847</v>
       </c>
       <c r="C149" t="n">
-        <v>308.5360036681458</v>
+        <v>310.8967187654788</v>
       </c>
       <c r="D149" t="n">
-        <v>301.155041869684</v>
+        <v>306.2848600302058</v>
       </c>
       <c r="E149" t="n">
-        <v>308.1774291992188</v>
+        <v>310.149658203125</v>
       </c>
       <c r="F149" t="n">
-        <v>6787200</v>
+        <v>5571000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>307.2610301082847</v>
+        <v>311.7732763548231</v>
       </c>
       <c r="C150" t="n">
-        <v>310.8967187654788</v>
+        <v>315.4886685147176</v>
       </c>
       <c r="D150" t="n">
-        <v>306.2848600302058</v>
+        <v>310.2990658939648</v>
       </c>
       <c r="E150" t="n">
-        <v>310.149658203125</v>
+        <v>314.671875</v>
       </c>
       <c r="F150" t="n">
-        <v>5571000</v>
+        <v>4831400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>311.7732461183575</v>
+        <v>315.1101522104624</v>
       </c>
       <c r="C151" t="n">
-        <v>315.4886379179251</v>
+        <v>316.7536793728972</v>
       </c>
       <c r="D151" t="n">
-        <v>310.2990358004714</v>
+        <v>313.3371296864953</v>
       </c>
       <c r="E151" t="n">
-        <v>314.6718444824219</v>
+        <v>313.8650512695312</v>
       </c>
       <c r="F151" t="n">
-        <v>4831400</v>
+        <v>5695800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>315.1101522104624</v>
+        <v>315.3591594617635</v>
       </c>
       <c r="C152" t="n">
-        <v>316.7536793728972</v>
+        <v>318.1880250357548</v>
       </c>
       <c r="D152" t="n">
-        <v>313.3371296864953</v>
+        <v>313.9447114757824</v>
       </c>
       <c r="E152" t="n">
-        <v>313.8650512695312</v>
+        <v>315.7774963378906</v>
       </c>
       <c r="F152" t="n">
-        <v>5695800</v>
+        <v>8082300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>315.3591594617635</v>
+        <v>315.1599141162692</v>
       </c>
       <c r="C153" t="n">
-        <v>318.1880250357548</v>
+        <v>316.3054007933923</v>
       </c>
       <c r="D153" t="n">
-        <v>313.9447114757824</v>
+        <v>311.1257996104973</v>
       </c>
       <c r="E153" t="n">
-        <v>315.7774963378906</v>
+        <v>312.7095642089844</v>
       </c>
       <c r="F153" t="n">
-        <v>8082300</v>
+        <v>5506800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>315.159944872979</v>
+        <v>312.7793368499103</v>
       </c>
       <c r="C154" t="n">
-        <v>316.305431661891</v>
+        <v>315.6480543727783</v>
       </c>
       <c r="D154" t="n">
-        <v>311.1258299735145</v>
+        <v>307.6096751468197</v>
       </c>
       <c r="E154" t="n">
-        <v>312.7095947265625</v>
+        <v>308.7252807617188</v>
       </c>
       <c r="F154" t="n">
-        <v>5506800</v>
+        <v>6806900</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>312.7793059315876</v>
+        <v>309.791044929962</v>
       </c>
       <c r="C155" t="n">
-        <v>315.6480231708821</v>
+        <v>310.1396488303614</v>
       </c>
       <c r="D155" t="n">
-        <v>307.6096447395195</v>
+        <v>306.8525949268221</v>
       </c>
       <c r="E155" t="n">
-        <v>308.7252502441406</v>
+        <v>310.0699462890625</v>
       </c>
       <c r="F155" t="n">
-        <v>6806900</v>
+        <v>5666600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>309.7910754200902</v>
+        <v>309.2830795800573</v>
       </c>
       <c r="C156" t="n">
-        <v>310.1396793547997</v>
+        <v>310.9764290509568</v>
       </c>
       <c r="D156" t="n">
-        <v>306.8526251277434</v>
+        <v>303.8146058713554</v>
       </c>
       <c r="E156" t="n">
-        <v>310.0699768066406</v>
+        <v>307.66943359375</v>
       </c>
       <c r="F156" t="n">
-        <v>5666600</v>
+        <v>7275000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>309.2830795800573</v>
+        <v>305.8963913711518</v>
       </c>
       <c r="C157" t="n">
-        <v>310.9764290509568</v>
+        <v>308.7651086725988</v>
       </c>
       <c r="D157" t="n">
-        <v>303.8146058713554</v>
+        <v>303.3065754519026</v>
       </c>
       <c r="E157" t="n">
-        <v>307.66943359375</v>
+        <v>308.2073059082031</v>
       </c>
       <c r="F157" t="n">
-        <v>7275000</v>
+        <v>5616900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>305.8963913711518</v>
+        <v>306.3047740402819</v>
       </c>
       <c r="C158" t="n">
-        <v>308.7651086725988</v>
+        <v>309.6017985990326</v>
       </c>
       <c r="D158" t="n">
-        <v>303.3065754519026</v>
+        <v>304.8604449214708</v>
       </c>
       <c r="E158" t="n">
-        <v>308.2073059082031</v>
+        <v>308.4363708496094</v>
       </c>
       <c r="F158" t="n">
-        <v>5616900</v>
+        <v>6261500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>306.3048043469537</v>
+        <v>310.9763962887836</v>
       </c>
       <c r="C159" t="n">
-        <v>309.6018292319215</v>
+        <v>312.7294775914766</v>
       </c>
       <c r="D159" t="n">
-        <v>304.8604750852367</v>
+        <v>307.5299352956203</v>
       </c>
       <c r="E159" t="n">
-        <v>308.4364013671875</v>
+        <v>308.0877380371094</v>
       </c>
       <c r="F159" t="n">
-        <v>6261500</v>
+        <v>8839900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>310.9763962887836</v>
+        <v>335.0815497318694</v>
       </c>
       <c r="C160" t="n">
-        <v>312.7294775914766</v>
+        <v>340.6396971989305</v>
       </c>
       <c r="D160" t="n">
-        <v>307.5299352956203</v>
+        <v>332.4817936312549</v>
       </c>
       <c r="E160" t="n">
-        <v>308.0877380371094</v>
+        <v>333.5475769042969</v>
       </c>
       <c r="F160" t="n">
-        <v>8839900</v>
+        <v>16658600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>335.0815497318694</v>
+        <v>330.8183038995719</v>
       </c>
       <c r="C161" t="n">
-        <v>340.6396971989305</v>
+        <v>331.1968194140059</v>
       </c>
       <c r="D161" t="n">
-        <v>332.4817936312549</v>
+        <v>326.7941295221779</v>
       </c>
       <c r="E161" t="n">
-        <v>333.5475769042969</v>
+        <v>328.5472412109375</v>
       </c>
       <c r="F161" t="n">
-        <v>16658600</v>
+        <v>11241100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>330.8183346281009</v>
+        <v>331.5753517735461</v>
       </c>
       <c r="C162" t="n">
-        <v>331.1968501776938</v>
+        <v>334.5337126996377</v>
       </c>
       <c r="D162" t="n">
-        <v>326.7941598769157</v>
+        <v>326.6447400974031</v>
       </c>
       <c r="E162" t="n">
-        <v>328.5472717285156</v>
+        <v>326.7443542480469</v>
       </c>
       <c r="F162" t="n">
-        <v>11241100</v>
+        <v>6726100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>331.5753827423343</v>
+        <v>326.7144870306598</v>
       </c>
       <c r="C163" t="n">
-        <v>334.5337439447337</v>
+        <v>328.4974800902166</v>
       </c>
       <c r="D163" t="n">
-        <v>326.6447706056774</v>
+        <v>324.1246709928955</v>
       </c>
       <c r="E163" t="n">
-        <v>326.744384765625</v>
+        <v>325.5690002441406</v>
       </c>
       <c r="F163" t="n">
-        <v>6726100</v>
+        <v>6712400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>326.7144870306598</v>
+        <v>323.8357986413566</v>
       </c>
       <c r="C164" t="n">
-        <v>328.4974800902166</v>
+        <v>324.3039578106427</v>
       </c>
       <c r="D164" t="n">
-        <v>324.1246709928955</v>
+        <v>318.3972062477142</v>
       </c>
       <c r="E164" t="n">
-        <v>325.5690002441406</v>
+        <v>320.7678833007812</v>
       </c>
       <c r="F164" t="n">
-        <v>6712400</v>
+        <v>5893200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>323.8357678318997</v>
+        <v>322.4811180854182</v>
       </c>
       <c r="C165" t="n">
-        <v>324.3039269566456</v>
+        <v>323.3078516694185</v>
       </c>
       <c r="D165" t="n">
-        <v>318.3971759556802</v>
+        <v>316.7536542120865</v>
       </c>
       <c r="E165" t="n">
-        <v>320.7678527832031</v>
+        <v>317.5505065917969</v>
       </c>
       <c r="F165" t="n">
-        <v>5893200</v>
+        <v>7808400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>322.4811180854182</v>
+        <v>318.2876119079176</v>
       </c>
       <c r="C166" t="n">
-        <v>323.3078516694185</v>
+        <v>322.4213404283596</v>
       </c>
       <c r="D166" t="n">
-        <v>316.7536542120865</v>
+        <v>318.2876119079176</v>
       </c>
       <c r="E166" t="n">
-        <v>317.5505065917969</v>
+        <v>320.0207824707031</v>
       </c>
       <c r="F166" t="n">
-        <v>7808400</v>
+        <v>7186100</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>318.2876422602183</v>
+        <v>319.7319477733878</v>
       </c>
       <c r="C167" t="n">
-        <v>322.4213711748579</v>
+        <v>319.8116512556435</v>
       </c>
       <c r="D167" t="n">
-        <v>318.2876422602183</v>
+        <v>314.9208911627371</v>
       </c>
       <c r="E167" t="n">
-        <v>320.0208129882812</v>
+        <v>317.5405883789062</v>
       </c>
       <c r="F167" t="n">
-        <v>7186100</v>
+        <v>5950200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>319.7319477733878</v>
+        <v>317.8493745260795</v>
       </c>
       <c r="C168" t="n">
-        <v>319.8116512556435</v>
+        <v>323.90553213234</v>
       </c>
       <c r="D168" t="n">
-        <v>314.9208911627371</v>
+        <v>316.7636501525053</v>
       </c>
       <c r="E168" t="n">
-        <v>317.5405883789062</v>
+        <v>322.5906982421875</v>
       </c>
       <c r="F168" t="n">
-        <v>5950200</v>
+        <v>9586200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,25 +4811,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>317.8493444570379</v>
+        <v>323.7186157532602</v>
       </c>
       <c r="C169" t="n">
-        <v>323.9055014903766</v>
+        <v>328.3001007904417</v>
       </c>
       <c r="D169" t="n">
-        <v>316.7636201861749</v>
+        <v>323.5988431448615</v>
       </c>
       <c r="E169" t="n">
-        <v>322.5906677246094</v>
+        <v>325.8147277832031</v>
       </c>
       <c r="F169" t="n">
-        <v>9586200</v>
+        <v>6235200</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -4837,25 +4837,25 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>323.7186157532602</v>
+        <v>323.1895917984963</v>
       </c>
       <c r="C170" t="n">
-        <v>328.3001007904417</v>
+        <v>324.8165740981451</v>
       </c>
       <c r="D170" t="n">
-        <v>323.5988431448615</v>
+        <v>319.2069699014023</v>
       </c>
       <c r="E170" t="n">
-        <v>325.8147277832031</v>
+        <v>319.7160339355469</v>
       </c>
       <c r="F170" t="n">
-        <v>6235200</v>
+        <v>7950400</v>
       </c>
       <c r="G170" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>323.1895917984963</v>
+        <v>320.7740745871976</v>
       </c>
       <c r="C171" t="n">
-        <v>324.8165740981451</v>
+        <v>322.7304316048222</v>
       </c>
       <c r="D171" t="n">
-        <v>319.2069699014023</v>
+        <v>319.6561562914121</v>
       </c>
       <c r="E171" t="n">
-        <v>319.7160339355469</v>
+        <v>321.9219360351562</v>
       </c>
       <c r="F171" t="n">
-        <v>7950400</v>
+        <v>5277400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>320.7740745871976</v>
+        <v>323.3992105807512</v>
       </c>
       <c r="C172" t="n">
-        <v>322.7304316048222</v>
+        <v>328.3999303437295</v>
       </c>
       <c r="D172" t="n">
-        <v>319.6561562914121</v>
+        <v>323.2395036115653</v>
       </c>
       <c r="E172" t="n">
-        <v>321.9219360351562</v>
+        <v>325.1459655761719</v>
       </c>
       <c r="F172" t="n">
-        <v>5277400</v>
+        <v>6054500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>323.3992105807512</v>
+        <v>323.8283954010087</v>
       </c>
       <c r="C173" t="n">
-        <v>328.3999303437295</v>
+        <v>332.8117065140525</v>
       </c>
       <c r="D173" t="n">
-        <v>323.2395036115653</v>
+        <v>323.1696155974001</v>
       </c>
       <c r="E173" t="n">
-        <v>325.1459655761719</v>
+        <v>332.023193359375</v>
       </c>
       <c r="F173" t="n">
-        <v>6054500</v>
+        <v>5305800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>323.8283954010087</v>
+        <v>332.7118894931572</v>
       </c>
       <c r="C174" t="n">
-        <v>332.8117065140525</v>
+        <v>334.5485043686942</v>
       </c>
       <c r="D174" t="n">
-        <v>323.1696155974001</v>
+        <v>328.8790136983196</v>
       </c>
       <c r="E174" t="n">
-        <v>332.023193359375</v>
+        <v>329.2982482910156</v>
       </c>
       <c r="F174" t="n">
-        <v>5305800</v>
+        <v>12858100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>332.7118894931572</v>
+        <v>329.4779084191791</v>
       </c>
       <c r="C175" t="n">
-        <v>334.5485043686942</v>
+        <v>331.0450044691208</v>
       </c>
       <c r="D175" t="n">
-        <v>328.8790136983196</v>
+        <v>326.2139829663294</v>
       </c>
       <c r="E175" t="n">
-        <v>329.2982482910156</v>
+        <v>330.1366882324219</v>
       </c>
       <c r="F175" t="n">
-        <v>12858100</v>
+        <v>9422500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>329.4779084191791</v>
+        <v>329.2283866364193</v>
       </c>
       <c r="C176" t="n">
-        <v>331.0450044691208</v>
+        <v>331.9034099041888</v>
       </c>
       <c r="D176" t="n">
-        <v>326.2139829663294</v>
+        <v>326.6332016248708</v>
       </c>
       <c r="E176" t="n">
-        <v>330.1366882324219</v>
+        <v>330.5060119628906</v>
       </c>
       <c r="F176" t="n">
-        <v>9422500</v>
+        <v>7034500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>329.2283866364193</v>
+        <v>329.9071152744464</v>
       </c>
       <c r="C177" t="n">
-        <v>331.9034099041888</v>
+        <v>332.8117230001985</v>
       </c>
       <c r="D177" t="n">
-        <v>326.6332016248708</v>
+        <v>328.2102858122996</v>
       </c>
       <c r="E177" t="n">
-        <v>330.5060119628906</v>
+        <v>328.2701721191406</v>
       </c>
       <c r="F177" t="n">
-        <v>7034500</v>
+        <v>7462100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>329.9071152744464</v>
+        <v>325.8546513791287</v>
       </c>
       <c r="C178" t="n">
-        <v>332.8117230001985</v>
+        <v>327.890877227978</v>
       </c>
       <c r="D178" t="n">
-        <v>328.2102858122996</v>
+        <v>323.908285453</v>
       </c>
       <c r="E178" t="n">
-        <v>328.2701721191406</v>
+        <v>325.8746337890625</v>
       </c>
       <c r="F178" t="n">
-        <v>7462100</v>
+        <v>8705100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>325.8546513791287</v>
+        <v>325.2258042905605</v>
       </c>
       <c r="C179" t="n">
-        <v>327.890877227978</v>
+        <v>330.8453695289686</v>
       </c>
       <c r="D179" t="n">
-        <v>323.908285453</v>
+        <v>325.0561365774909</v>
       </c>
       <c r="E179" t="n">
-        <v>325.8746337890625</v>
+        <v>327.0025024414062</v>
       </c>
       <c r="F179" t="n">
-        <v>8705100</v>
+        <v>5917400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>325.2258042905605</v>
+        <v>325.4054745838858</v>
       </c>
       <c r="C180" t="n">
-        <v>330.8453695289686</v>
+        <v>326.473467283892</v>
       </c>
       <c r="D180" t="n">
-        <v>325.0561365774909</v>
+        <v>320.304934449476</v>
       </c>
       <c r="E180" t="n">
-        <v>327.0025024414062</v>
+        <v>324.3474426269531</v>
       </c>
       <c r="F180" t="n">
-        <v>5917400</v>
+        <v>8105400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>325.4054745838858</v>
+        <v>324.8964310814758</v>
       </c>
       <c r="C181" t="n">
-        <v>326.473467283892</v>
+        <v>331.0550035619541</v>
       </c>
       <c r="D181" t="n">
-        <v>320.304934449476</v>
+        <v>324.7467153160326</v>
       </c>
       <c r="E181" t="n">
-        <v>324.3474426269531</v>
+        <v>325.7548217773438</v>
       </c>
       <c r="F181" t="n">
-        <v>8105400</v>
+        <v>14104500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>324.8964310814758</v>
+        <v>326.6531732008884</v>
       </c>
       <c r="C182" t="n">
-        <v>331.0550035619541</v>
+        <v>327.2520362551611</v>
       </c>
       <c r="D182" t="n">
-        <v>324.7467153160326</v>
+        <v>318.0890659929148</v>
       </c>
       <c r="E182" t="n">
-        <v>325.7548217773438</v>
+        <v>322.1714782714844</v>
       </c>
       <c r="F182" t="n">
-        <v>14104500</v>
+        <v>10079300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>326.6531732008884</v>
+        <v>321.911976472278</v>
       </c>
       <c r="C183" t="n">
-        <v>327.2520362551611</v>
+        <v>322.900130958607</v>
       </c>
       <c r="D183" t="n">
-        <v>318.0890659929148</v>
+        <v>312.8088926463686</v>
       </c>
       <c r="E183" t="n">
-        <v>322.1714782714844</v>
+        <v>316.7315979003906</v>
       </c>
       <c r="F183" t="n">
-        <v>10079300</v>
+        <v>10125300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>321.911976472278</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="C184" t="n">
-        <v>322.900130958607</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="D184" t="n">
-        <v>312.8088926463686</v>
+        <v>308.4270199555073</v>
       </c>
       <c r="E184" t="n">
-        <v>316.7315979003906</v>
+        <v>311.8207092285156</v>
       </c>
       <c r="F184" t="n">
-        <v>10125300</v>
+        <v>8992800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>317.0609741306723</v>
+        <v>316.2025752130079</v>
       </c>
       <c r="C185" t="n">
-        <v>317.0609741306723</v>
+        <v>324.1577974184449</v>
       </c>
       <c r="D185" t="n">
-        <v>308.4270199555073</v>
+        <v>316.1127457580593</v>
       </c>
       <c r="E185" t="n">
-        <v>311.8207092285156</v>
+        <v>319.5862731933594</v>
       </c>
       <c r="F185" t="n">
-        <v>8992800</v>
+        <v>6981700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>316.2025752130079</v>
+        <v>321.8021573858913</v>
       </c>
       <c r="C186" t="n">
-        <v>324.1577974184449</v>
+        <v>325.3755359367605</v>
       </c>
       <c r="D186" t="n">
-        <v>316.1127457580593</v>
+        <v>320.3748163907789</v>
       </c>
       <c r="E186" t="n">
-        <v>319.5862731933594</v>
+        <v>322.9700012207031</v>
       </c>
       <c r="F186" t="n">
-        <v>6981700</v>
+        <v>7176300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>321.8021573858913</v>
+        <v>320.7541174065557</v>
       </c>
       <c r="C187" t="n">
-        <v>325.3755359367605</v>
+        <v>323.3193590911711</v>
       </c>
       <c r="D187" t="n">
-        <v>320.3748163907789</v>
+        <v>317.8395186449595</v>
       </c>
       <c r="E187" t="n">
-        <v>322.9700012207031</v>
+        <v>319.0772399902344</v>
       </c>
       <c r="F187" t="n">
-        <v>7176300</v>
+        <v>5582000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>320.7541174065557</v>
+        <v>318.0691001697331</v>
       </c>
       <c r="C188" t="n">
-        <v>323.3193590911711</v>
+        <v>324.8864216353897</v>
       </c>
       <c r="D188" t="n">
-        <v>317.8395186449595</v>
+        <v>316.4121747162161</v>
       </c>
       <c r="E188" t="n">
-        <v>319.0772399902344</v>
+        <v>324.4472351074219</v>
       </c>
       <c r="F188" t="n">
-        <v>5582000</v>
+        <v>6340400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>318.0691001697331</v>
+        <v>326.0143312805488</v>
       </c>
       <c r="C189" t="n">
-        <v>324.8864216353897</v>
+        <v>326.2938108474966</v>
       </c>
       <c r="D189" t="n">
-        <v>316.4121747162161</v>
+        <v>319.5862707797614</v>
       </c>
       <c r="E189" t="n">
-        <v>324.4472351074219</v>
+        <v>322.3611145019531</v>
       </c>
       <c r="F189" t="n">
-        <v>6340400</v>
+        <v>5793100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>326.0143312805488</v>
+        <v>321.4029160285921</v>
       </c>
       <c r="C190" t="n">
-        <v>326.2938108474966</v>
+        <v>323.1097366498532</v>
       </c>
       <c r="D190" t="n">
-        <v>319.5862707797614</v>
+        <v>317.3703988636284</v>
       </c>
       <c r="E190" t="n">
-        <v>322.3611145019531</v>
+        <v>318.4583740234375</v>
       </c>
       <c r="F190" t="n">
-        <v>5793100</v>
+        <v>5958900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>321.4029160285921</v>
+        <v>321.1633691478087</v>
       </c>
       <c r="C191" t="n">
-        <v>323.1097366498532</v>
+        <v>325.3256196452838</v>
       </c>
       <c r="D191" t="n">
-        <v>317.3703988636284</v>
+        <v>319.206981650181</v>
       </c>
       <c r="E191" t="n">
-        <v>318.4583740234375</v>
+        <v>321.7922058105469</v>
       </c>
       <c r="F191" t="n">
-        <v>5958900</v>
+        <v>5543200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>321.1633691478087</v>
+        <v>322.7603745094088</v>
       </c>
       <c r="C192" t="n">
-        <v>325.3256196452838</v>
+        <v>325.8346802814496</v>
       </c>
       <c r="D192" t="n">
-        <v>319.206981650181</v>
+        <v>322.1515202620241</v>
       </c>
       <c r="E192" t="n">
-        <v>321.7922058105469</v>
+        <v>323.2195434570312</v>
       </c>
       <c r="F192" t="n">
-        <v>5543200</v>
+        <v>6803000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>322.7603745094088</v>
+        <v>325.0860736201939</v>
       </c>
       <c r="C193" t="n">
-        <v>325.8346802814496</v>
+        <v>332.6719869892291</v>
       </c>
       <c r="D193" t="n">
-        <v>322.1515202620241</v>
+        <v>323.7785051975129</v>
       </c>
       <c r="E193" t="n">
-        <v>323.2195434570312</v>
+        <v>332.5022888183594</v>
       </c>
       <c r="F193" t="n">
-        <v>6803000</v>
+        <v>9248400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>325.0860736201939</v>
+        <v>332.8816048599044</v>
       </c>
       <c r="C194" t="n">
-        <v>332.6719869892291</v>
+        <v>336.1954560330155</v>
       </c>
       <c r="D194" t="n">
-        <v>323.7785051975129</v>
+        <v>329.3581516101117</v>
       </c>
       <c r="E194" t="n">
-        <v>332.5022888183594</v>
+        <v>329.7673950195312</v>
       </c>
       <c r="F194" t="n">
-        <v>9248400</v>
+        <v>6895200</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>332.8816048599044</v>
+        <v>330.3862161708477</v>
       </c>
       <c r="C195" t="n">
-        <v>336.1954560330155</v>
+        <v>331.7137365067053</v>
       </c>
       <c r="D195" t="n">
-        <v>329.3581516101117</v>
+        <v>326.3936334980882</v>
       </c>
       <c r="E195" t="n">
-        <v>329.7673950195312</v>
+        <v>326.6331787109375</v>
       </c>
       <c r="F195" t="n">
-        <v>6895200</v>
+        <v>14716700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>330.3862161708477</v>
+        <v>327.7211572947962</v>
       </c>
       <c r="C196" t="n">
-        <v>331.7137365067053</v>
+        <v>332.3825110173034</v>
       </c>
       <c r="D196" t="n">
-        <v>326.3936334980882</v>
+        <v>325.255736249892</v>
       </c>
       <c r="E196" t="n">
-        <v>326.6331787109375</v>
+        <v>325.994384765625</v>
       </c>
       <c r="F196" t="n">
-        <v>14716700</v>
+        <v>15132400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>327.7211572947962</v>
+        <v>328.2102765273601</v>
       </c>
       <c r="C197" t="n">
-        <v>332.3825110173034</v>
+        <v>330.6657064213508</v>
       </c>
       <c r="D197" t="n">
-        <v>325.255736249892</v>
+        <v>327.4816192000871</v>
       </c>
       <c r="E197" t="n">
-        <v>325.994384765625</v>
+        <v>327.8709106445312</v>
       </c>
       <c r="F197" t="n">
-        <v>15132400</v>
+        <v>11113400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>328.2102765273601</v>
+        <v>328.3899311009871</v>
       </c>
       <c r="C198" t="n">
-        <v>330.6657064213508</v>
+        <v>334.1791639025663</v>
       </c>
       <c r="D198" t="n">
-        <v>327.4816192000871</v>
+        <v>326.6132329961447</v>
       </c>
       <c r="E198" t="n">
-        <v>327.8709106445312</v>
+        <v>331.6139526367188</v>
       </c>
       <c r="F198" t="n">
-        <v>11113400</v>
+        <v>8197200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>328.3899311009871</v>
+        <v>331.9433302412046</v>
       </c>
       <c r="C199" t="n">
-        <v>334.1791639025663</v>
+        <v>339.3096503518051</v>
       </c>
       <c r="D199" t="n">
-        <v>326.6132329961447</v>
+        <v>329.457957205559</v>
       </c>
       <c r="E199" t="n">
-        <v>331.6139526367188</v>
+        <v>329.9071044921875</v>
       </c>
       <c r="F199" t="n">
-        <v>8197200</v>
+        <v>7050200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>331.9433302412046</v>
+        <v>331.6239148421282</v>
       </c>
       <c r="C200" t="n">
-        <v>339.3096503518051</v>
+        <v>339.0900555815327</v>
       </c>
       <c r="D200" t="n">
-        <v>329.457957205559</v>
+        <v>330.8254104732138</v>
       </c>
       <c r="E200" t="n">
-        <v>329.9071044921875</v>
+        <v>335.6065368652344</v>
       </c>
       <c r="F200" t="n">
-        <v>7050200</v>
+        <v>16717400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>331.6239148421282</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="C201" t="n">
-        <v>339.0900555815327</v>
+        <v>345.168769346924</v>
       </c>
       <c r="D201" t="n">
-        <v>330.8254104732138</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="E201" t="n">
-        <v>335.6065368652344</v>
+        <v>341.0164794921875</v>
       </c>
       <c r="F201" t="n">
-        <v>16717400</v>
+        <v>11710900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>337.6427420814022</v>
+        <v>341.1262760402287</v>
       </c>
       <c r="C202" t="n">
-        <v>345.168769346924</v>
+        <v>343.6515833825353</v>
       </c>
       <c r="D202" t="n">
-        <v>337.6427420814022</v>
+        <v>338.4512224777037</v>
       </c>
       <c r="E202" t="n">
-        <v>341.0164794921875</v>
+        <v>342.4537963867188</v>
       </c>
       <c r="F202" t="n">
-        <v>11710900</v>
+        <v>7957900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>341.1262760402287</v>
+        <v>343.9210864742992</v>
       </c>
       <c r="C203" t="n">
-        <v>343.6515833825353</v>
+        <v>352.7047566164018</v>
       </c>
       <c r="D203" t="n">
-        <v>338.4512224777037</v>
+        <v>340.3477382034001</v>
       </c>
       <c r="E203" t="n">
-        <v>342.4537963867188</v>
+        <v>350.4289855957031</v>
       </c>
       <c r="F203" t="n">
-        <v>7957900</v>
+        <v>13025900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>343.9210864742992</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="C204" t="n">
-        <v>352.7047566164018</v>
+        <v>361.45849609375</v>
       </c>
       <c r="D204" t="n">
-        <v>340.3477382034001</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="E204" t="n">
-        <v>350.4289855957031</v>
+        <v>361.45849609375</v>
       </c>
       <c r="F204" t="n">
-        <v>13025900</v>
+        <v>9814800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>351.8563396289383</v>
+        <v>362.3268927646901</v>
       </c>
       <c r="C205" t="n">
-        <v>361.45849609375</v>
+        <v>364.3431361331269</v>
       </c>
       <c r="D205" t="n">
-        <v>351.8563396289383</v>
+        <v>348.2031370590358</v>
       </c>
       <c r="E205" t="n">
-        <v>361.45849609375</v>
+        <v>356.5875549316406</v>
       </c>
       <c r="F205" t="n">
-        <v>9814800</v>
+        <v>11623800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>362.3268927646901</v>
+        <v>347.744003265132</v>
       </c>
       <c r="C206" t="n">
-        <v>364.3431361331269</v>
+        <v>355.4197158554798</v>
       </c>
       <c r="D206" t="n">
-        <v>348.2031370590358</v>
+        <v>346.2767278330053</v>
       </c>
       <c r="E206" t="n">
-        <v>356.5875549316406</v>
+        <v>351.5469360351562</v>
       </c>
       <c r="F206" t="n">
-        <v>11623800</v>
+        <v>7332500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>347.744003265132</v>
+        <v>349.650411586948</v>
       </c>
       <c r="C207" t="n">
-        <v>355.4197158554798</v>
+        <v>350.9480192181019</v>
       </c>
       <c r="D207" t="n">
-        <v>346.2767278330053</v>
+        <v>345.0489747278172</v>
       </c>
       <c r="E207" t="n">
-        <v>351.5469360351562</v>
+        <v>346.8855590820312</v>
       </c>
       <c r="F207" t="n">
-        <v>7332500</v>
+        <v>10215200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>349.650411586948</v>
+        <v>344.6597048505295</v>
       </c>
       <c r="C208" t="n">
-        <v>350.9480192181019</v>
+        <v>347.8537833381742</v>
       </c>
       <c r="D208" t="n">
-        <v>345.0489747278172</v>
+        <v>343.7813622043677</v>
       </c>
       <c r="E208" t="n">
-        <v>346.8855590820312</v>
+        <v>347.5543518066406</v>
       </c>
       <c r="F208" t="n">
-        <v>10215200</v>
+        <v>6606300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>344.6597048505295</v>
+        <v>349.9798320131086</v>
       </c>
       <c r="C209" t="n">
-        <v>347.8537833381742</v>
+        <v>350.5188392207221</v>
       </c>
       <c r="D209" t="n">
-        <v>343.7813622043677</v>
+        <v>344.6896415212494</v>
       </c>
       <c r="E209" t="n">
-        <v>347.5543518066406</v>
+        <v>348.3229064941406</v>
       </c>
       <c r="F209" t="n">
-        <v>6606300</v>
+        <v>4702800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>349.9798320131086</v>
+        <v>351.0777829959364</v>
       </c>
       <c r="C210" t="n">
-        <v>350.5188392207221</v>
+        <v>358.8233725828445</v>
       </c>
       <c r="D210" t="n">
-        <v>344.6896415212494</v>
+        <v>350.3990207986449</v>
       </c>
       <c r="E210" t="n">
-        <v>348.3229064941406</v>
+        <v>357.0866088867188</v>
       </c>
       <c r="F210" t="n">
-        <v>4702800</v>
+        <v>9964600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>351.0777829959364</v>
+        <v>355.1102963305153</v>
       </c>
       <c r="C211" t="n">
-        <v>358.8233725828445</v>
+        <v>359.2725774384029</v>
       </c>
       <c r="D211" t="n">
-        <v>350.3990207986449</v>
+        <v>353.0241754046451</v>
       </c>
       <c r="E211" t="n">
-        <v>357.0866088867188</v>
+        <v>355.3598327636719</v>
       </c>
       <c r="F211" t="n">
-        <v>9964600</v>
+        <v>6632400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>355.1102963305153</v>
+        <v>353.3435751194357</v>
       </c>
       <c r="C212" t="n">
-        <v>359.2725774384029</v>
+        <v>359.7616446111089</v>
       </c>
       <c r="D212" t="n">
-        <v>353.0241754046451</v>
+        <v>348.4726192666298</v>
       </c>
       <c r="E212" t="n">
-        <v>355.3598327636719</v>
+        <v>354.4814758300781</v>
       </c>
       <c r="F212" t="n">
-        <v>6632400</v>
+        <v>8850000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>353.3435751194357</v>
+        <v>357.3760808599296</v>
       </c>
       <c r="C213" t="n">
-        <v>359.7616446111089</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="D213" t="n">
-        <v>348.4726192666298</v>
+        <v>356.4477822451955</v>
       </c>
       <c r="E213" t="n">
-        <v>354.4814758300781</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="F213" t="n">
-        <v>8850000</v>
+        <v>9073200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>357.3760808599296</v>
+        <v>362.8958306673428</v>
       </c>
       <c r="C214" t="n">
-        <v>364.4629211425781</v>
+        <v>363.9538626468295</v>
       </c>
       <c r="D214" t="n">
-        <v>356.4477822451955</v>
+        <v>356.3380062665893</v>
       </c>
       <c r="E214" t="n">
-        <v>364.4629211425781</v>
+        <v>357.8951110839844</v>
       </c>
       <c r="F214" t="n">
-        <v>9073200</v>
+        <v>7400400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>362.8958306673428</v>
+        <v>356.4378309524324</v>
       </c>
       <c r="C215" t="n">
-        <v>363.9538626468295</v>
+        <v>362.3268844140721</v>
       </c>
       <c r="D215" t="n">
-        <v>356.3380062665893</v>
+        <v>355.7690599392462</v>
       </c>
       <c r="E215" t="n">
-        <v>357.8951110839844</v>
+        <v>359.9013977050781</v>
       </c>
       <c r="F215" t="n">
-        <v>7400400</v>
+        <v>7616800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>356.4378309524324</v>
+        <v>356.3280307190208</v>
       </c>
       <c r="C216" t="n">
-        <v>362.3268844140721</v>
+        <v>358.4540859756855</v>
       </c>
       <c r="D216" t="n">
-        <v>355.7690599392462</v>
+        <v>354.0323077481659</v>
       </c>
       <c r="E216" t="n">
-        <v>359.9013977050781</v>
+        <v>355.1602172851562</v>
       </c>
       <c r="F216" t="n">
-        <v>7616800</v>
+        <v>6027300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>356.3280307190208</v>
+        <v>355.9088319271366</v>
       </c>
       <c r="C217" t="n">
-        <v>358.4540859756855</v>
+        <v>356.8670433033565</v>
       </c>
       <c r="D217" t="n">
-        <v>354.0323077481659</v>
+        <v>351.6167869913984</v>
       </c>
       <c r="E217" t="n">
-        <v>355.1602172851562</v>
+        <v>352.7646789550781</v>
       </c>
       <c r="F217" t="n">
-        <v>6027300</v>
+        <v>4622200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>355.9088319271366</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="C218" t="n">
-        <v>356.8670433033565</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="D218" t="n">
-        <v>351.6167869913984</v>
+        <v>347.8537708520506</v>
       </c>
       <c r="E218" t="n">
-        <v>352.7646789550781</v>
+        <v>350.9480285644531</v>
       </c>
       <c r="F218" t="n">
-        <v>4622200</v>
+        <v>4183300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>351.3971758456315</v>
+        <v>352.8145729386106</v>
       </c>
       <c r="C219" t="n">
-        <v>351.3971758456315</v>
+        <v>355.1801734485531</v>
       </c>
       <c r="D219" t="n">
-        <v>347.8537708520506</v>
+        <v>350.3990468654978</v>
       </c>
       <c r="E219" t="n">
-        <v>350.9480285644531</v>
+        <v>355.0803527832031</v>
       </c>
       <c r="F219" t="n">
-        <v>4183300</v>
+        <v>4482800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>352.8145729386106</v>
+        <v>358.6836615690858</v>
       </c>
       <c r="C220" t="n">
-        <v>355.1801734485531</v>
+        <v>362.9856670774005</v>
       </c>
       <c r="D220" t="n">
-        <v>350.3990468654978</v>
+        <v>357.5856952124533</v>
       </c>
       <c r="E220" t="n">
-        <v>355.0803527832031</v>
+        <v>361.8577575683594</v>
       </c>
       <c r="F220" t="n">
-        <v>4482800</v>
+        <v>6631100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>358.6836615690858</v>
+        <v>364.3830556294341</v>
       </c>
       <c r="C221" t="n">
-        <v>362.9856670774005</v>
+        <v>370.4717503048907</v>
       </c>
       <c r="D221" t="n">
-        <v>357.5856952124533</v>
+        <v>362.057389622598</v>
       </c>
       <c r="E221" t="n">
-        <v>361.8577575683594</v>
+        <v>365.9102172851562</v>
       </c>
       <c r="F221" t="n">
-        <v>6631100</v>
+        <v>11061900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>364.3830556294341</v>
+        <v>356.3380049484608</v>
       </c>
       <c r="C222" t="n">
-        <v>370.4717503048907</v>
+        <v>373.2765382228537</v>
       </c>
       <c r="D222" t="n">
-        <v>362.057389622598</v>
+        <v>354.8208344927874</v>
       </c>
       <c r="E222" t="n">
-        <v>365.9102172851562</v>
+        <v>368.0462646484375</v>
       </c>
       <c r="F222" t="n">
-        <v>11061900</v>
+        <v>11289900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>356.3380049484608</v>
+        <v>364.3231862195555</v>
       </c>
       <c r="C223" t="n">
-        <v>373.2765382228537</v>
+        <v>366.3194776508955</v>
       </c>
       <c r="D223" t="n">
-        <v>354.8208344927874</v>
+        <v>360.0810669279579</v>
       </c>
       <c r="E223" t="n">
-        <v>368.0462646484375</v>
+        <v>365.5908203125</v>
       </c>
       <c r="F223" t="n">
-        <v>11289900</v>
+        <v>8391400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>364.3231862195555</v>
+        <v>363.0854799497644</v>
       </c>
       <c r="C224" t="n">
-        <v>366.3194776508955</v>
+        <v>366.199689577411</v>
       </c>
       <c r="D224" t="n">
-        <v>360.0810669279579</v>
+        <v>359.4322631293363</v>
       </c>
       <c r="E224" t="n">
-        <v>365.5908203125</v>
+        <v>365.4510803222656</v>
       </c>
       <c r="F224" t="n">
-        <v>8391400</v>
+        <v>7828400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>363.0854799497644</v>
+        <v>367.8166822243689</v>
       </c>
       <c r="C225" t="n">
-        <v>366.199689577411</v>
+        <v>371.2802489443513</v>
       </c>
       <c r="D225" t="n">
-        <v>359.4322631293363</v>
+        <v>363.6743837542027</v>
       </c>
       <c r="E225" t="n">
-        <v>365.4510803222656</v>
+        <v>364.991943359375</v>
       </c>
       <c r="F225" t="n">
-        <v>7828400</v>
+        <v>5521300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>367.8166822243689</v>
+        <v>361.0891957111975</v>
       </c>
       <c r="C226" t="n">
-        <v>371.2802489443513</v>
+        <v>370.4218335736103</v>
       </c>
       <c r="D226" t="n">
-        <v>363.6743837542027</v>
+        <v>359.4222790007568</v>
       </c>
       <c r="E226" t="n">
-        <v>364.991943359375</v>
+        <v>368.9046630859375</v>
       </c>
       <c r="F226" t="n">
-        <v>5521300</v>
+        <v>7497500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>361.0891957111975</v>
+        <v>371.6096355733356</v>
       </c>
       <c r="C227" t="n">
-        <v>370.4218335736103</v>
+        <v>371.7094562365133</v>
       </c>
       <c r="D227" t="n">
-        <v>359.4222790007568</v>
+        <v>366.0399959154992</v>
       </c>
       <c r="E227" t="n">
-        <v>368.9046630859375</v>
+        <v>367.8566284179688</v>
       </c>
       <c r="F227" t="n">
-        <v>7497500</v>
+        <v>6065300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>371.6096355733356</v>
+        <v>368.8847254705448</v>
       </c>
       <c r="C228" t="n">
-        <v>371.7094562365133</v>
+        <v>370.4118872220017</v>
       </c>
       <c r="D228" t="n">
-        <v>366.0399959154992</v>
+        <v>364.5727285978463</v>
       </c>
       <c r="E228" t="n">
-        <v>367.8566284179688</v>
+        <v>369.7830505371094</v>
       </c>
       <c r="F228" t="n">
-        <v>6065300</v>
+        <v>5022300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>368.8847254705448</v>
+        <v>367.8266852879935</v>
       </c>
       <c r="C229" t="n">
-        <v>370.4118872220017</v>
+        <v>369.5634490756331</v>
       </c>
       <c r="D229" t="n">
-        <v>364.5727285978463</v>
+        <v>360.8496260625997</v>
       </c>
       <c r="E229" t="n">
-        <v>369.7830505371094</v>
+        <v>361.8278198242188</v>
       </c>
       <c r="F229" t="n">
-        <v>5022300</v>
+        <v>5112500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>367.8266852879935</v>
+        <v>361.3287562034755</v>
       </c>
       <c r="C230" t="n">
-        <v>369.5634490756331</v>
+        <v>363.4947458520614</v>
       </c>
       <c r="D230" t="n">
-        <v>360.8496260625997</v>
+        <v>358.2045551780129</v>
       </c>
       <c r="E230" t="n">
-        <v>361.8278198242188</v>
+        <v>360.6500244140625</v>
       </c>
       <c r="F230" t="n">
-        <v>5112500</v>
+        <v>7552200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,25 +6423,25 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>361.3287562034755</v>
+        <v>360.9800109863281</v>
       </c>
       <c r="C231" t="n">
-        <v>363.4947458520614</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="D231" t="n">
-        <v>358.2045551780129</v>
+        <v>359.9700012207031</v>
       </c>
       <c r="E231" t="n">
-        <v>360.6500244140625</v>
+        <v>362.8200073242188</v>
       </c>
       <c r="F231" t="n">
-        <v>7552200</v>
+        <v>4440900</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -6449,25 +6449,25 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>360.9800109863281</v>
+        <v>361</v>
       </c>
       <c r="C232" t="n">
-        <v>364.5499877929688</v>
+        <v>363.3500061035156</v>
       </c>
       <c r="D232" t="n">
-        <v>359.9700012207031</v>
+        <v>358.3099975585938</v>
       </c>
       <c r="E232" t="n">
-        <v>362.8200073242188</v>
+        <v>359.4200134277344</v>
       </c>
       <c r="F232" t="n">
-        <v>4440900</v>
+        <v>3794200</v>
       </c>
       <c r="G232" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>361</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="C233" t="n">
-        <v>363.3500061035156</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="D233" t="n">
-        <v>358.3099975585938</v>
+        <v>358.7099914550781</v>
       </c>
       <c r="E233" t="n">
-        <v>359.4200134277344</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>3794200</v>
+        <v>8142600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>363.7000122070312</v>
+        <v>365.8900146484375</v>
       </c>
       <c r="C234" t="n">
-        <v>365.4500122070312</v>
+        <v>366.7999877929688</v>
       </c>
       <c r="D234" t="n">
-        <v>358.7099914550781</v>
+        <v>362.760009765625</v>
       </c>
       <c r="E234" t="n">
-        <v>365.4500122070312</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="F234" t="n">
-        <v>8142600</v>
+        <v>8106900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>365.8900146484375</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="C235" t="n">
-        <v>366.7999877929688</v>
+        <v>363.5599975585938</v>
       </c>
       <c r="D235" t="n">
-        <v>362.760009765625</v>
+        <v>358.5199890136719</v>
       </c>
       <c r="E235" t="n">
-        <v>364.1499938964844</v>
+        <v>358.8399963378906</v>
       </c>
       <c r="F235" t="n">
-        <v>8106900</v>
+        <v>15543400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>362.8399963378906</v>
+        <v>359.6199951171875</v>
       </c>
       <c r="C236" t="n">
-        <v>363.5599975585938</v>
+        <v>365.9100036621094</v>
       </c>
       <c r="D236" t="n">
-        <v>358.5199890136719</v>
+        <v>358.0499877929688</v>
       </c>
       <c r="E236" t="n">
-        <v>358.8399963378906</v>
+        <v>364.25</v>
       </c>
       <c r="F236" t="n">
-        <v>15543400</v>
+        <v>6820300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>359.6199951171875</v>
+        <v>364.0899963378906</v>
       </c>
       <c r="C237" t="n">
-        <v>365.9100036621094</v>
+        <v>370.6400146484375</v>
       </c>
       <c r="D237" t="n">
-        <v>358.0499877929688</v>
+        <v>362.8999938964844</v>
       </c>
       <c r="E237" t="n">
-        <v>364.25</v>
+        <v>365.5400085449219</v>
       </c>
       <c r="F237" t="n">
-        <v>6820300</v>
+        <v>5866400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>364.0899963378906</v>
+        <v>365.1000061035156</v>
       </c>
       <c r="C238" t="n">
-        <v>370.6400146484375</v>
+        <v>368.9299926757812</v>
       </c>
       <c r="D238" t="n">
-        <v>362.8999938964844</v>
+        <v>363.6300048828125</v>
       </c>
       <c r="E238" t="n">
-        <v>365.5400085449219</v>
+        <v>365.7300109863281</v>
       </c>
       <c r="F238" t="n">
-        <v>5866400</v>
+        <v>6151500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>365.1000061035156</v>
+        <v>367.8699951171875</v>
       </c>
       <c r="C239" t="n">
-        <v>368.9299926757812</v>
+        <v>371.7999877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>363.6300048828125</v>
+        <v>366.6600036621094</v>
       </c>
       <c r="E239" t="n">
-        <v>365.7300109863281</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F239" t="n">
-        <v>6151500</v>
+        <v>6667100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>367.8699951171875</v>
+        <v>373.260009765625</v>
       </c>
       <c r="C240" t="n">
-        <v>371.7999877929688</v>
+        <v>383.4299926757812</v>
       </c>
       <c r="D240" t="n">
-        <v>366.6600036621094</v>
+        <v>372.2099914550781</v>
       </c>
       <c r="E240" t="n">
-        <v>371.0400085449219</v>
+        <v>382.4100036621094</v>
       </c>
       <c r="F240" t="n">
-        <v>6667100</v>
+        <v>8477500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>373.260009765625</v>
+        <v>381.2099914550781</v>
       </c>
       <c r="C241" t="n">
-        <v>383.4299926757812</v>
+        <v>384.2000122070312</v>
       </c>
       <c r="D241" t="n">
-        <v>372.2099914550781</v>
+        <v>380.2699890136719</v>
       </c>
       <c r="E241" t="n">
-        <v>382.4100036621094</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="F241" t="n">
-        <v>8477500</v>
+        <v>6777600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>381.2099914550781</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C242" t="n">
-        <v>384.2000122070312</v>
+        <v>385.5700073242188</v>
       </c>
       <c r="D242" t="n">
-        <v>380.2699890136719</v>
+        <v>381.0799865722656</v>
       </c>
       <c r="E242" t="n">
-        <v>384.1400146484375</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F242" t="n">
-        <v>6777600</v>
+        <v>6075100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>384.1400146484375</v>
+        <v>381.1400146484375</v>
       </c>
       <c r="C243" t="n">
-        <v>385.5700073242188</v>
+        <v>381.7699890136719</v>
       </c>
       <c r="D243" t="n">
-        <v>381.0799865722656</v>
+        <v>378.5</v>
       </c>
       <c r="E243" t="n">
-        <v>383.8999938964844</v>
+        <v>379.6600036621094</v>
       </c>
       <c r="F243" t="n">
-        <v>6075100</v>
+        <v>6641500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>381.1400146484375</v>
+        <v>380.2999877929688</v>
       </c>
       <c r="C244" t="n">
-        <v>381.7699890136719</v>
+        <v>383.6799926757812</v>
       </c>
       <c r="D244" t="n">
-        <v>378.5</v>
+        <v>379.0299987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>379.6600036621094</v>
+        <v>381.6000061035156</v>
       </c>
       <c r="F244" t="n">
-        <v>6641500</v>
+        <v>4643000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>380.2999877929688</v>
+        <v>381.3500061035156</v>
       </c>
       <c r="C245" t="n">
-        <v>383.6799926757812</v>
+        <v>382.4800109863281</v>
       </c>
       <c r="D245" t="n">
-        <v>379.0299987792969</v>
+        <v>378.7999877929688</v>
       </c>
       <c r="E245" t="n">
-        <v>381.6000061035156</v>
+        <v>379.3699951171875</v>
       </c>
       <c r="F245" t="n">
-        <v>4643000</v>
+        <v>6744800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>381.3500061035156</v>
+        <v>379.6499938964844</v>
       </c>
       <c r="C246" t="n">
-        <v>382.4800109863281</v>
+        <v>380.75</v>
       </c>
       <c r="D246" t="n">
-        <v>378.7999877929688</v>
+        <v>372.2200012207031</v>
       </c>
       <c r="E246" t="n">
-        <v>379.3699951171875</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F246" t="n">
-        <v>6744800</v>
+        <v>5857400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>379.6499938964844</v>
+        <v>374.010009765625</v>
       </c>
       <c r="C247" t="n">
-        <v>380.75</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="D247" t="n">
-        <v>372.2200012207031</v>
+        <v>374.010009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>372.6700134277344</v>
+        <v>378.3999938964844</v>
       </c>
       <c r="F247" t="n">
-        <v>5857400</v>
+        <v>5599900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>374.010009765625</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="C248" t="n">
-        <v>380.1700134277344</v>
+        <v>382.2099914550781</v>
       </c>
       <c r="D248" t="n">
-        <v>374.010009765625</v>
+        <v>376.8599853515625</v>
       </c>
       <c r="E248" t="n">
-        <v>378.3999938964844</v>
+        <v>378.75</v>
       </c>
       <c r="F248" t="n">
-        <v>5599900</v>
+        <v>3869500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>380.1700134277344</v>
+        <v>374.8900146484375</v>
       </c>
       <c r="C249" t="n">
-        <v>382.2099914550781</v>
+        <v>377.5</v>
       </c>
       <c r="D249" t="n">
-        <v>376.8599853515625</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="E249" t="n">
-        <v>378.75</v>
+        <v>375.0700073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>3869500</v>
+        <v>4645100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>374.8900146484375</v>
+        <v>371.6000061035156</v>
       </c>
       <c r="C250" t="n">
-        <v>377.5</v>
+        <v>373.5</v>
       </c>
       <c r="D250" t="n">
-        <v>373.6400146484375</v>
+        <v>367.4400024414062</v>
       </c>
       <c r="E250" t="n">
-        <v>375.0700073242188</v>
+        <v>368.6400146484375</v>
       </c>
       <c r="F250" t="n">
-        <v>4645100</v>
+        <v>4929000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>371.6000061035156</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="C251" t="n">
-        <v>373.5</v>
+        <v>369.4800109863281</v>
       </c>
       <c r="D251" t="n">
-        <v>367.4400024414062</v>
+        <v>365.8800048828125</v>
       </c>
       <c r="E251" t="n">
-        <v>368.6400146484375</v>
+        <v>367.3900146484375</v>
       </c>
       <c r="F251" t="n">
-        <v>4929000</v>
+        <v>4479800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>368.4500122070312</v>
+        <v>366.3999938964844</v>
       </c>
       <c r="C252" t="n">
-        <v>369.4800109863281</v>
+        <v>368</v>
       </c>
       <c r="D252" t="n">
-        <v>365.8800048828125</v>
+        <v>365.5199890136719</v>
       </c>
       <c r="E252" t="n">
-        <v>367.3900146484375</v>
+        <v>367.2099914550781</v>
       </c>
       <c r="F252" t="n">
-        <v>4479800</v>
+        <v>3800200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10656,37 +10656,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="D2" t="n">
         <v>367.39</v>
       </c>
-      <c r="D2" t="n">
-        <v>368.64</v>
-      </c>
       <c r="E2" t="n">
-        <v>368.45</v>
+        <v>366.4</v>
       </c>
       <c r="F2" t="n">
-        <v>369.48</v>
+        <v>367.98</v>
       </c>
       <c r="G2" t="n">
-        <v>365.88</v>
+        <v>365.52</v>
       </c>
       <c r="H2" t="n">
-        <v>4469432</v>
+        <v>3742141</v>
       </c>
       <c r="I2" t="n">
-        <v>7721091</v>
+        <v>7696844</v>
       </c>
       <c r="J2" t="n">
-        <v>685934510080</v>
+        <v>685598441472</v>
       </c>
       <c r="K2" t="n">
-        <v>31.347271</v>
+        <v>31.251915</v>
       </c>
       <c r="L2" t="n">
-        <v>24.48565</v>
+        <v>24.47365</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72</v>
+        <v>11.75</v>
       </c>
       <c r="N2" t="n">
         <v>385.57</v>
@@ -10722,7 +10722,7 @@
         <v>18.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.469528</v>
+        <v>19.459988</v>
       </c>
       <c r="Z2" t="n">
         <v>0.102</v>
@@ -10734,7 +10734,7 @@
         <v>44487999488</v>
       </c>
       <c r="AC2" t="n">
-        <v>685832667136</v>
+        <v>685501841408</v>
       </c>
       <c r="AD2" t="n">
         <v>31093999616</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:30</t>
+          <t>2026-09-11 19:03:07</t>
         </is>
       </c>
     </row>

--- a/data/V_data.xlsx
+++ b/data/V_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>336.0424662373603</v>
+        <v>338.5127143274361</v>
       </c>
       <c r="C2" t="n">
-        <v>340.8043700650184</v>
+        <v>340.467085284774</v>
       </c>
       <c r="D2" t="n">
-        <v>335.1892738885992</v>
+        <v>336.4789914224089</v>
       </c>
       <c r="E2" t="n">
-        <v>340.7646789550781</v>
+        <v>336.7369079589844</v>
       </c>
       <c r="F2" t="n">
-        <v>5157600</v>
+        <v>3518300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>338.5127450059508</v>
+        <v>337.9075446663081</v>
       </c>
       <c r="C3" t="n">
-        <v>340.4671161404083</v>
+        <v>339.9908890682369</v>
       </c>
       <c r="D3" t="n">
-        <v>336.4790219166126</v>
+        <v>335.7051874783653</v>
       </c>
       <c r="E3" t="n">
-        <v>336.7369384765625</v>
+        <v>336.3599243164062</v>
       </c>
       <c r="F3" t="n">
-        <v>3518300</v>
+        <v>4367500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>337.9075446663081</v>
+        <v>333.5722152320537</v>
       </c>
       <c r="C4" t="n">
-        <v>339.9908890682369</v>
+        <v>337.8381165972889</v>
       </c>
       <c r="D4" t="n">
-        <v>335.7051874783653</v>
+        <v>330.8242036977477</v>
       </c>
       <c r="E4" t="n">
-        <v>336.3599243164062</v>
+        <v>337.3321533203125</v>
       </c>
       <c r="F4" t="n">
-        <v>4367500</v>
+        <v>5527700</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>333.5722152320537</v>
+        <v>337.2428745138968</v>
       </c>
       <c r="C5" t="n">
-        <v>337.8381165972889</v>
+        <v>343.4532165527344</v>
       </c>
       <c r="D5" t="n">
-        <v>330.8242036977477</v>
+        <v>336.8261935269982</v>
       </c>
       <c r="E5" t="n">
-        <v>337.3321533203125</v>
+        <v>343.4532165527344</v>
       </c>
       <c r="F5" t="n">
-        <v>5527700</v>
+        <v>5763500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>337.2428745138968</v>
+        <v>341.9948757376367</v>
       </c>
       <c r="C6" t="n">
-        <v>343.4532165527344</v>
+        <v>342.5305695051567</v>
       </c>
       <c r="D6" t="n">
-        <v>336.8261935269982</v>
+        <v>335.496826171875</v>
       </c>
       <c r="E6" t="n">
-        <v>343.4532165527344</v>
+        <v>335.496826171875</v>
       </c>
       <c r="F6" t="n">
-        <v>5763500</v>
+        <v>7526600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>341.9948757376367</v>
+        <v>337.7488578495824</v>
       </c>
       <c r="C7" t="n">
-        <v>342.5305695051567</v>
+        <v>339.9710758437891</v>
       </c>
       <c r="D7" t="n">
-        <v>335.496826171875</v>
+        <v>335.5663006942368</v>
       </c>
       <c r="E7" t="n">
-        <v>335.496826171875</v>
+        <v>338.8996276855469</v>
       </c>
       <c r="F7" t="n">
-        <v>7526600</v>
+        <v>13674300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>337.7488578495824</v>
+        <v>336.3202490919778</v>
       </c>
       <c r="C8" t="n">
-        <v>339.9710758437891</v>
+        <v>342.123810018113</v>
       </c>
       <c r="D8" t="n">
-        <v>335.5663006942368</v>
+        <v>335.9730199939359</v>
       </c>
       <c r="E8" t="n">
-        <v>338.8996276855469</v>
+        <v>341.6277770996094</v>
       </c>
       <c r="F8" t="n">
-        <v>13674300</v>
+        <v>5621800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>336.3202490919778</v>
+        <v>341.8559470746173</v>
       </c>
       <c r="C9" t="n">
-        <v>342.123810018113</v>
+        <v>342.5206444753691</v>
       </c>
       <c r="D9" t="n">
-        <v>335.9730199939359</v>
+        <v>334.9511776506846</v>
       </c>
       <c r="E9" t="n">
-        <v>341.6277770996094</v>
+        <v>336.0126953125</v>
       </c>
       <c r="F9" t="n">
-        <v>5621800</v>
+        <v>10142700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>341.8559781228954</v>
+        <v>336.439361751067</v>
       </c>
       <c r="C10" t="n">
-        <v>342.5206755840167</v>
+        <v>337.2032417044336</v>
       </c>
       <c r="D10" t="n">
-        <v>334.9512080718528</v>
+        <v>335.2389703170758</v>
       </c>
       <c r="E10" t="n">
-        <v>336.0127258300781</v>
+        <v>335.992919921875</v>
       </c>
       <c r="F10" t="n">
-        <v>10142700</v>
+        <v>5207400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>336.4392700766844</v>
+        <v>335.6654921112904</v>
       </c>
       <c r="C11" t="n">
-        <v>337.2031498219058</v>
+        <v>337.5008200200934</v>
       </c>
       <c r="D11" t="n">
-        <v>335.2388789697807</v>
+        <v>331.855962815555</v>
       </c>
       <c r="E11" t="n">
-        <v>335.9928283691406</v>
+        <v>332.2726135253906</v>
       </c>
       <c r="F11" t="n">
-        <v>5207400</v>
+        <v>5398700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>335.6654921112904</v>
+        <v>334.5543943395058</v>
       </c>
       <c r="C12" t="n">
-        <v>337.5008200200934</v>
+        <v>336.8063730332322</v>
       </c>
       <c r="D12" t="n">
-        <v>331.855962815555</v>
+        <v>333.5623284395552</v>
       </c>
       <c r="E12" t="n">
-        <v>332.2726135253906</v>
+        <v>334.6932678222656</v>
       </c>
       <c r="F12" t="n">
-        <v>5398700</v>
+        <v>9619200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>334.5543943395058</v>
+        <v>334.7031787744378</v>
       </c>
       <c r="C13" t="n">
-        <v>336.8063730332322</v>
+        <v>337.9373231090121</v>
       </c>
       <c r="D13" t="n">
-        <v>333.5623284395552</v>
+        <v>332.8876813284792</v>
       </c>
       <c r="E13" t="n">
-        <v>334.6932678222656</v>
+        <v>337.4611206054688</v>
       </c>
       <c r="F13" t="n">
-        <v>9619200</v>
+        <v>7217800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>334.7032090426073</v>
+        <v>337.1238578141872</v>
       </c>
       <c r="C14" t="n">
-        <v>337.9373536696546</v>
+        <v>342.8678978564652</v>
       </c>
       <c r="D14" t="n">
-        <v>332.8877114324681</v>
+        <v>335.8242538439627</v>
       </c>
       <c r="E14" t="n">
-        <v>337.4611511230469</v>
+        <v>338.6714782714844</v>
       </c>
       <c r="F14" t="n">
-        <v>7217800</v>
+        <v>8164400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>337.1238578141872</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="C15" t="n">
-        <v>342.8678978564652</v>
+        <v>346.58811100512</v>
       </c>
       <c r="D15" t="n">
-        <v>335.8242538439627</v>
+        <v>337.6099271681015</v>
       </c>
       <c r="E15" t="n">
-        <v>338.6714782714844</v>
+        <v>345.0702514648438</v>
       </c>
       <c r="F15" t="n">
-        <v>8164400</v>
+        <v>8381000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>337.6099271681015</v>
+        <v>343.4730776227261</v>
       </c>
       <c r="C16" t="n">
-        <v>346.58811100512</v>
+        <v>344.4254524664805</v>
       </c>
       <c r="D16" t="n">
-        <v>337.6099271681015</v>
+        <v>340.8341785380658</v>
       </c>
       <c r="E16" t="n">
-        <v>345.0702514648438</v>
+        <v>343.2052307128906</v>
       </c>
       <c r="F16" t="n">
-        <v>8381000</v>
+        <v>5198000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>343.4730470813312</v>
+        <v>343.3639143460552</v>
       </c>
       <c r="C17" t="n">
-        <v>344.425421840401</v>
+        <v>350.3579971109944</v>
       </c>
       <c r="D17" t="n">
-        <v>340.8341482313199</v>
+        <v>343.2548016291976</v>
       </c>
       <c r="E17" t="n">
-        <v>343.2052001953125</v>
+        <v>347.0643310546875</v>
       </c>
       <c r="F17" t="n">
-        <v>5198000</v>
+        <v>5199700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>343.3639143460552</v>
+        <v>347.2329775138888</v>
       </c>
       <c r="C18" t="n">
-        <v>350.3579971109944</v>
+        <v>348.3341560741189</v>
       </c>
       <c r="D18" t="n">
-        <v>343.2548016291976</v>
+        <v>341.6178811752161</v>
       </c>
       <c r="E18" t="n">
-        <v>347.0643310546875</v>
+        <v>346.5087585449219</v>
       </c>
       <c r="F18" t="n">
-        <v>5199700</v>
+        <v>4735600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>347.2329775138888</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="C19" t="n">
-        <v>348.3341560741189</v>
+        <v>351.6278330286145</v>
       </c>
       <c r="D19" t="n">
-        <v>341.6178811752161</v>
+        <v>347.2825796289147</v>
       </c>
       <c r="E19" t="n">
-        <v>346.5087585449219</v>
+        <v>349.6238708496094</v>
       </c>
       <c r="F19" t="n">
-        <v>4735600</v>
+        <v>5044600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>347.2826099421288</v>
+        <v>350.9730784623077</v>
       </c>
       <c r="C20" t="n">
-        <v>351.6278637211122</v>
+        <v>352.1834000905383</v>
       </c>
       <c r="D20" t="n">
-        <v>347.2826099421288</v>
+        <v>348.3143490742109</v>
       </c>
       <c r="E20" t="n">
-        <v>349.6239013671875</v>
+        <v>348.572265625</v>
       </c>
       <c r="F20" t="n">
-        <v>5044600</v>
+        <v>3927500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>350.9730784623077</v>
+        <v>348.6814047504906</v>
       </c>
       <c r="C21" t="n">
-        <v>352.1834000905383</v>
+        <v>350.0702909620389</v>
       </c>
       <c r="D21" t="n">
-        <v>348.3143490742109</v>
+        <v>342.8381220393481</v>
       </c>
       <c r="E21" t="n">
-        <v>348.572265625</v>
+        <v>344.2865600585938</v>
       </c>
       <c r="F21" t="n">
-        <v>3927500</v>
+        <v>4434800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>348.6814047504906</v>
+        <v>344.8718644724454</v>
       </c>
       <c r="C22" t="n">
-        <v>350.0702909620389</v>
+        <v>347.619876043067</v>
       </c>
       <c r="D22" t="n">
-        <v>342.8381220393481</v>
+        <v>340.5266111021468</v>
       </c>
       <c r="E22" t="n">
-        <v>344.2865600585938</v>
+        <v>340.9234313964844</v>
       </c>
       <c r="F22" t="n">
-        <v>4434800</v>
+        <v>6296200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>344.8718644724454</v>
+        <v>340.9928833808045</v>
       </c>
       <c r="C23" t="n">
-        <v>347.619876043067</v>
+        <v>344.9016253459246</v>
       </c>
       <c r="D23" t="n">
-        <v>340.5266111021468</v>
+        <v>338.0266161060487</v>
       </c>
       <c r="E23" t="n">
-        <v>340.9234313964844</v>
+        <v>340.5762023925781</v>
       </c>
       <c r="F23" t="n">
-        <v>6296200</v>
+        <v>4030700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>340.9929139357196</v>
+        <v>338.2944848137428</v>
       </c>
       <c r="C24" t="n">
-        <v>344.9016562510855</v>
+        <v>347.2330086020973</v>
       </c>
       <c r="D24" t="n">
-        <v>338.0266463951693</v>
+        <v>337.520674593222</v>
       </c>
       <c r="E24" t="n">
-        <v>340.5762329101562</v>
+        <v>345.6159362792969</v>
       </c>
       <c r="F24" t="n">
-        <v>4030700</v>
+        <v>5731000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>338.2944549426422</v>
+        <v>345.6158945803519</v>
       </c>
       <c r="C25" t="n">
-        <v>347.2329779417331</v>
+        <v>347.3023883059841</v>
       </c>
       <c r="D25" t="n">
-        <v>337.5206447904482</v>
+        <v>341.2706414526681</v>
       </c>
       <c r="E25" t="n">
-        <v>345.6159057617188</v>
+        <v>342.9472351074219</v>
       </c>
       <c r="F25" t="n">
-        <v>5731000</v>
+        <v>3778200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>345.615925335404</v>
+        <v>342.2627615387884</v>
       </c>
       <c r="C26" t="n">
-        <v>347.3024192111109</v>
+        <v>342.947289483902</v>
       </c>
       <c r="D26" t="n">
-        <v>341.2706718210525</v>
+        <v>331.5187003455953</v>
       </c>
       <c r="E26" t="n">
-        <v>342.947265625</v>
+        <v>332.7389221191406</v>
       </c>
       <c r="F26" t="n">
-        <v>3778200</v>
+        <v>6241500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>342.2627301477191</v>
+        <v>335.0900922102411</v>
       </c>
       <c r="C27" t="n">
-        <v>342.9472580300504</v>
+        <v>340.7250495999637</v>
       </c>
       <c r="D27" t="n">
-        <v>331.5186699399313</v>
+        <v>334.3262123571327</v>
       </c>
       <c r="E27" t="n">
-        <v>332.7388916015625</v>
+        <v>339.1774291992188</v>
       </c>
       <c r="F27" t="n">
-        <v>6241500</v>
+        <v>6267100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>335.0900922102411</v>
+        <v>339.1873340368696</v>
       </c>
       <c r="C28" t="n">
-        <v>340.7250495999637</v>
+        <v>342.223053348327</v>
       </c>
       <c r="D28" t="n">
-        <v>334.3262123571327</v>
+        <v>336.2508273730998</v>
       </c>
       <c r="E28" t="n">
-        <v>339.1774291992188</v>
+        <v>341.6774291992188</v>
       </c>
       <c r="F28" t="n">
-        <v>6267100</v>
+        <v>4665000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>339.1873037416991</v>
+        <v>340.3976240505323</v>
       </c>
       <c r="C29" t="n">
-        <v>342.2230227820154</v>
+        <v>346.8758127342502</v>
       </c>
       <c r="D29" t="n">
-        <v>336.2507973402091</v>
+        <v>340.2785809945473</v>
       </c>
       <c r="E29" t="n">
-        <v>341.6773986816406</v>
+        <v>344.4551696777344</v>
       </c>
       <c r="F29" t="n">
-        <v>4665000</v>
+        <v>4121800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>340.3976542086254</v>
+        <v>345.0603770187118</v>
       </c>
       <c r="C30" t="n">
-        <v>346.8758434662893</v>
+        <v>345.4076061472691</v>
       </c>
       <c r="D30" t="n">
-        <v>340.2786111420936</v>
+        <v>341.7667108842852</v>
       </c>
       <c r="E30" t="n">
-        <v>344.4552001953125</v>
+        <v>342.619873046875</v>
       </c>
       <c r="F30" t="n">
-        <v>4121800</v>
+        <v>5074400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>345.0603770187118</v>
+        <v>343.4532348171426</v>
       </c>
       <c r="C31" t="n">
-        <v>345.4076061472691</v>
+        <v>344.395679279174</v>
       </c>
       <c r="D31" t="n">
-        <v>341.7667108842852</v>
+        <v>341.727019522991</v>
       </c>
       <c r="E31" t="n">
-        <v>342.619873046875</v>
+        <v>343.2151184082031</v>
       </c>
       <c r="F31" t="n">
-        <v>5074400</v>
+        <v>7217200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>343.4532348171426</v>
+        <v>345.4373415963541</v>
       </c>
       <c r="C32" t="n">
-        <v>344.395679279174</v>
+        <v>346.3103341142831</v>
       </c>
       <c r="D32" t="n">
-        <v>341.727019522991</v>
+        <v>342.5801871000132</v>
       </c>
       <c r="E32" t="n">
-        <v>343.2151184082031</v>
+        <v>344.6238403320312</v>
       </c>
       <c r="F32" t="n">
-        <v>7217200</v>
+        <v>3576700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>345.4373721859704</v>
+        <v>346.2310248701323</v>
       </c>
       <c r="C33" t="n">
-        <v>346.3103647812057</v>
+        <v>346.7468882773667</v>
       </c>
       <c r="D33" t="n">
-        <v>342.5802174366191</v>
+        <v>342.2726913226552</v>
       </c>
       <c r="E33" t="n">
-        <v>344.6238708496094</v>
+        <v>345.0603942871094</v>
       </c>
       <c r="F33" t="n">
-        <v>3576700</v>
+        <v>5400300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>346.2310248701323</v>
+        <v>345.8143074374688</v>
       </c>
       <c r="C34" t="n">
-        <v>346.7468882773667</v>
+        <v>347.1139415798067</v>
       </c>
       <c r="D34" t="n">
-        <v>342.2726913226552</v>
+        <v>343.7508237502946</v>
       </c>
       <c r="E34" t="n">
-        <v>345.0603942871094</v>
+        <v>344.1476440429688</v>
       </c>
       <c r="F34" t="n">
-        <v>5400300</v>
+        <v>7445400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>345.8143381028397</v>
+        <v>343.2548181119967</v>
       </c>
       <c r="C35" t="n">
-        <v>347.1139723604238</v>
+        <v>348.1953174336955</v>
       </c>
       <c r="D35" t="n">
-        <v>343.7508542326843</v>
+        <v>336.3103564738927</v>
       </c>
       <c r="E35" t="n">
-        <v>344.1476745605469</v>
+        <v>338.572265625</v>
       </c>
       <c r="F35" t="n">
-        <v>7445400</v>
+        <v>8361700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>343.2547871723516</v>
+        <v>339.5047778404419</v>
       </c>
       <c r="C36" t="n">
-        <v>348.1952860487332</v>
+        <v>346.9452717470537</v>
       </c>
       <c r="D36" t="n">
-        <v>336.3103261601942</v>
+        <v>339.0781967892368</v>
       </c>
       <c r="E36" t="n">
-        <v>338.5722351074219</v>
+        <v>342.29248046875</v>
       </c>
       <c r="F36" t="n">
-        <v>8361700</v>
+        <v>6411800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>339.5048081094784</v>
+        <v>339.3658635939219</v>
       </c>
       <c r="C37" t="n">
-        <v>346.9453026794581</v>
+        <v>340.2785774727712</v>
       </c>
       <c r="D37" t="n">
-        <v>339.0782270202408</v>
+        <v>335.4869128662897</v>
       </c>
       <c r="E37" t="n">
-        <v>342.2925109863281</v>
+        <v>338.0364990234375</v>
       </c>
       <c r="F37" t="n">
-        <v>6411800</v>
+        <v>7301600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>339.3658942315137</v>
+        <v>338.2944659192743</v>
       </c>
       <c r="C38" t="n">
-        <v>340.2786081927618</v>
+        <v>338.5027912774657</v>
       </c>
       <c r="D38" t="n">
-        <v>335.4869431536939</v>
+        <v>332.1635060317716</v>
       </c>
       <c r="E38" t="n">
-        <v>338.0365295410156</v>
+        <v>334.2269897460938</v>
       </c>
       <c r="F38" t="n">
-        <v>7301600</v>
+        <v>5538000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>338.2944350303034</v>
+        <v>333.810367634687</v>
       </c>
       <c r="C39" t="n">
-        <v>338.502760369473</v>
+        <v>337.6198973167316</v>
       </c>
       <c r="D39" t="n">
-        <v>332.1634757026059</v>
+        <v>331.5980496280586</v>
       </c>
       <c r="E39" t="n">
-        <v>334.2269592285156</v>
+        <v>337.6000366210938</v>
       </c>
       <c r="F39" t="n">
-        <v>5538000</v>
+        <v>5920200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>333.8103374596785</v>
+        <v>337.4313538243792</v>
       </c>
       <c r="C40" t="n">
-        <v>337.6198667973582</v>
+        <v>339.3956247811457</v>
       </c>
       <c r="D40" t="n">
-        <v>331.598019653034</v>
+        <v>333.6912462886964</v>
       </c>
       <c r="E40" t="n">
-        <v>337.6000061035156</v>
+        <v>337.3420715332031</v>
       </c>
       <c r="F40" t="n">
-        <v>5920200</v>
+        <v>4984600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>337.4313843500343</v>
+        <v>335.9035711966457</v>
       </c>
       <c r="C41" t="n">
-        <v>339.395655484498</v>
+        <v>335.9630927253758</v>
       </c>
       <c r="D41" t="n">
-        <v>333.6912764760034</v>
+        <v>331.062285023625</v>
       </c>
       <c r="E41" t="n">
-        <v>337.3421020507812</v>
+        <v>334.2864990234375</v>
       </c>
       <c r="F41" t="n">
-        <v>4984600</v>
+        <v>8507900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>335.9035711966457</v>
+        <v>334.058361977199</v>
       </c>
       <c r="C42" t="n">
-        <v>335.9630927253758</v>
+        <v>335.6059823618086</v>
       </c>
       <c r="D42" t="n">
-        <v>331.062285023625</v>
+        <v>332.193273237939</v>
       </c>
       <c r="E42" t="n">
-        <v>334.2864990234375</v>
+        <v>333.3539733886719</v>
       </c>
       <c r="F42" t="n">
-        <v>8507900</v>
+        <v>5318400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>334.058361977199</v>
+        <v>333.9789743060267</v>
       </c>
       <c r="C43" t="n">
-        <v>335.6059823618086</v>
+        <v>335.9928668426192</v>
       </c>
       <c r="D43" t="n">
-        <v>332.193273237939</v>
+        <v>331.6674741139567</v>
       </c>
       <c r="E43" t="n">
-        <v>333.3539733886719</v>
+        <v>332.1932678222656</v>
       </c>
       <c r="F43" t="n">
-        <v>5318400</v>
+        <v>5295800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>333.9790049876522</v>
+        <v>332.8380786460612</v>
       </c>
       <c r="C44" t="n">
-        <v>335.9928977092549</v>
+        <v>336.3995912643918</v>
       </c>
       <c r="D44" t="n">
-        <v>331.6675045832317</v>
+        <v>330.5563393974141</v>
       </c>
       <c r="E44" t="n">
-        <v>332.1932983398438</v>
+        <v>336.23095703125</v>
       </c>
       <c r="F44" t="n">
-        <v>5295800</v>
+        <v>4453300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,25 +1587,25 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>332.838108855689</v>
+        <v>336.230963908966</v>
       </c>
       <c r="C45" t="n">
-        <v>336.3996217972758</v>
+        <v>342.2050995382295</v>
       </c>
       <c r="D45" t="n">
-        <v>330.5563693999427</v>
+        <v>335.3860315467677</v>
       </c>
       <c r="E45" t="n">
-        <v>336.2309875488281</v>
+        <v>336.8572082519531</v>
       </c>
       <c r="F45" t="n">
-        <v>4453300</v>
+        <v>6389600</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>336.230963908966</v>
+        <v>337.01623628756</v>
       </c>
       <c r="C46" t="n">
-        <v>342.2050995382295</v>
+        <v>339.4217740167541</v>
       </c>
       <c r="D46" t="n">
-        <v>335.3860315467677</v>
+        <v>333.5967676514001</v>
       </c>
       <c r="E46" t="n">
-        <v>336.8572082519531</v>
+        <v>334.0738830566406</v>
       </c>
       <c r="F46" t="n">
-        <v>6389600</v>
+        <v>4961700</v>
       </c>
       <c r="G46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>337.0162670739215</v>
+        <v>333.8850664354288</v>
       </c>
       <c r="C47" t="n">
-        <v>339.4218050228609</v>
+        <v>334.0739044051273</v>
       </c>
       <c r="D47" t="n">
-        <v>333.5967981253938</v>
+        <v>327.0659984240934</v>
       </c>
       <c r="E47" t="n">
-        <v>334.0739135742188</v>
+        <v>328.0500793457031</v>
       </c>
       <c r="F47" t="n">
-        <v>4961700</v>
+        <v>6422300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>333.8850664354288</v>
+        <v>329.1832834325262</v>
       </c>
       <c r="C48" t="n">
-        <v>334.0739044051273</v>
+        <v>331.370133257436</v>
       </c>
       <c r="D48" t="n">
-        <v>327.0659984240934</v>
+        <v>322.9904598740608</v>
       </c>
       <c r="E48" t="n">
-        <v>328.0500793457031</v>
+        <v>323.8055725097656</v>
       </c>
       <c r="F48" t="n">
-        <v>6422300</v>
+        <v>6494800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>329.1832834325262</v>
+        <v>322.5630378796905</v>
       </c>
       <c r="C49" t="n">
-        <v>331.370133257436</v>
+        <v>323.0600533463772</v>
       </c>
       <c r="D49" t="n">
-        <v>322.9904598740608</v>
+        <v>316.101836812763</v>
       </c>
       <c r="E49" t="n">
-        <v>323.8055725097656</v>
+        <v>319.2628479003906</v>
       </c>
       <c r="F49" t="n">
-        <v>6494800</v>
+        <v>9170400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>322.5630378796905</v>
+        <v>319.6008162287846</v>
       </c>
       <c r="C50" t="n">
-        <v>323.0600533463772</v>
+        <v>322.632628790591</v>
       </c>
       <c r="D50" t="n">
-        <v>316.101836812763</v>
+        <v>317.9606712483538</v>
       </c>
       <c r="E50" t="n">
-        <v>319.2628479003906</v>
+        <v>322.185302734375</v>
       </c>
       <c r="F50" t="n">
-        <v>9170400</v>
+        <v>7066700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>319.6007859560105</v>
+        <v>322.1852887063674</v>
       </c>
       <c r="C51" t="n">
-        <v>322.6325982306419</v>
+        <v>326.4397397218689</v>
       </c>
       <c r="D51" t="n">
-        <v>317.9606411309352</v>
+        <v>321.2111578443184</v>
       </c>
       <c r="E51" t="n">
-        <v>322.1852722167969</v>
+        <v>321.8373718261719</v>
       </c>
       <c r="F51" t="n">
-        <v>7066700</v>
+        <v>6510300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>322.1853192569361</v>
+        <v>323.437821602865</v>
       </c>
       <c r="C52" t="n">
-        <v>326.4397706758573</v>
+        <v>329.1037802762534</v>
       </c>
       <c r="D52" t="n">
-        <v>321.2111883025171</v>
+        <v>322.3543314197192</v>
       </c>
       <c r="E52" t="n">
-        <v>321.83740234375</v>
+        <v>326.0223083496094</v>
       </c>
       <c r="F52" t="n">
-        <v>6510300</v>
+        <v>8930000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>323.4377913272098</v>
+        <v>327.2747416730934</v>
       </c>
       <c r="C53" t="n">
-        <v>329.1037494702317</v>
+        <v>328.755868423024</v>
       </c>
       <c r="D53" t="n">
-        <v>322.354301245485</v>
+        <v>324.0540910886259</v>
       </c>
       <c r="E53" t="n">
-        <v>326.0222778320312</v>
+        <v>327.3343811035156</v>
       </c>
       <c r="F53" t="n">
-        <v>8930000</v>
+        <v>9337100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>327.2747416730934</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="C54" t="n">
-        <v>328.755868423024</v>
+        <v>334.0540387480419</v>
       </c>
       <c r="D54" t="n">
-        <v>324.0540910886259</v>
+        <v>326.9367735032804</v>
       </c>
       <c r="E54" t="n">
-        <v>327.3343811035156</v>
+        <v>332.5331726074219</v>
       </c>
       <c r="F54" t="n">
-        <v>9337100</v>
+        <v>5854300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>326.9367735032804</v>
+        <v>332.5331806355595</v>
       </c>
       <c r="C55" t="n">
-        <v>334.0540387480419</v>
+        <v>333.7061299047911</v>
       </c>
       <c r="D55" t="n">
-        <v>326.9367735032804</v>
+        <v>331.0719538898497</v>
       </c>
       <c r="E55" t="n">
-        <v>332.5331726074219</v>
+        <v>331.797607421875</v>
       </c>
       <c r="F55" t="n">
-        <v>5854300</v>
+        <v>4309900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>332.533150050326</v>
+        <v>331.4397445821358</v>
       </c>
       <c r="C56" t="n">
-        <v>333.7060992116737</v>
+        <v>333.0202502105825</v>
       </c>
       <c r="D56" t="n">
-        <v>331.0719234390147</v>
+        <v>330.0182875517957</v>
       </c>
       <c r="E56" t="n">
-        <v>331.7975769042969</v>
+        <v>332.4437255859375</v>
       </c>
       <c r="F56" t="n">
-        <v>4309900</v>
+        <v>4586200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>331.4397445821358</v>
+        <v>330.952674561706</v>
       </c>
       <c r="C57" t="n">
-        <v>333.0202502105825</v>
+        <v>331.3105111509684</v>
       </c>
       <c r="D57" t="n">
-        <v>330.0182875517957</v>
+        <v>328.1693999716056</v>
       </c>
       <c r="E57" t="n">
-        <v>332.4437255859375</v>
+        <v>328.4179077148438</v>
       </c>
       <c r="F57" t="n">
-        <v>4586200</v>
+        <v>7082300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>330.9526438085897</v>
+        <v>329.4715593852143</v>
       </c>
       <c r="C58" t="n">
-        <v>331.3104803646008</v>
+        <v>330.8134768540631</v>
       </c>
       <c r="D58" t="n">
-        <v>328.1693694771195</v>
+        <v>325.2568476714639</v>
       </c>
       <c r="E58" t="n">
-        <v>328.4178771972656</v>
+        <v>327.6524658203125</v>
       </c>
       <c r="F58" t="n">
-        <v>7082300</v>
+        <v>8201900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>329.4715593852143</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="C59" t="n">
-        <v>330.8134768540631</v>
+        <v>330.3661824396382</v>
       </c>
       <c r="D59" t="n">
-        <v>325.2568476714639</v>
+        <v>327.3840896786403</v>
       </c>
       <c r="E59" t="n">
-        <v>327.6524658203125</v>
+        <v>327.6425170898438</v>
       </c>
       <c r="F59" t="n">
-        <v>8201900</v>
+        <v>6296700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>327.6425476074219</v>
+        <v>329.3025948705371</v>
       </c>
       <c r="C60" t="n">
-        <v>330.3662132109065</v>
+        <v>330.396035058885</v>
       </c>
       <c r="D60" t="n">
-        <v>327.3841201721478</v>
+        <v>322.3443777352205</v>
       </c>
       <c r="E60" t="n">
-        <v>327.6425476074219</v>
+        <v>325.1475524902344</v>
       </c>
       <c r="F60" t="n">
-        <v>6296700</v>
+        <v>6277500</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>329.3025639629765</v>
+        <v>324.8791069392551</v>
       </c>
       <c r="C61" t="n">
-        <v>330.3960040486967</v>
+        <v>332.1156507054553</v>
       </c>
       <c r="D61" t="n">
-        <v>322.3443474807417</v>
+        <v>324.4516809311236</v>
       </c>
       <c r="E61" t="n">
-        <v>325.1475219726562</v>
+        <v>329.2627868652344</v>
       </c>
       <c r="F61" t="n">
-        <v>6277500</v>
+        <v>5266600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>324.8791370505337</v>
+        <v>327.9109311533039</v>
       </c>
       <c r="C62" t="n">
-        <v>332.1156814874498</v>
+        <v>329.3622078309571</v>
       </c>
       <c r="D62" t="n">
-        <v>324.4517110027865</v>
+        <v>322.77177784886</v>
       </c>
       <c r="E62" t="n">
-        <v>329.2628173828125</v>
+        <v>324.8890686035156</v>
       </c>
       <c r="F62" t="n">
-        <v>5266600</v>
+        <v>6059400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>327.9109619547325</v>
+        <v>324.6604152629651</v>
       </c>
       <c r="C63" t="n">
-        <v>329.3622387687074</v>
+        <v>326.2707707906858</v>
       </c>
       <c r="D63" t="n">
-        <v>322.7718081675561</v>
+        <v>323.1296295298985</v>
       </c>
       <c r="E63" t="n">
-        <v>324.8890991210938</v>
+        <v>324.5510864257812</v>
       </c>
       <c r="F63" t="n">
-        <v>6059400</v>
+        <v>4325400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>324.6604457908234</v>
+        <v>324.6902773524443</v>
       </c>
       <c r="C64" t="n">
-        <v>326.270801469966</v>
+        <v>326.797618069185</v>
       </c>
       <c r="D64" t="n">
-        <v>323.1296599138169</v>
+        <v>323.3582492118315</v>
       </c>
       <c r="E64" t="n">
-        <v>324.5511169433594</v>
+        <v>323.7857055664062</v>
       </c>
       <c r="F64" t="n">
-        <v>4325400</v>
+        <v>5467500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>324.6902773524443</v>
+        <v>330.6147028726578</v>
       </c>
       <c r="C65" t="n">
-        <v>326.797618069185</v>
+        <v>345.2468397955696</v>
       </c>
       <c r="D65" t="n">
-        <v>323.3582492118315</v>
+        <v>328.0898557440862</v>
       </c>
       <c r="E65" t="n">
-        <v>323.7857055664062</v>
+        <v>343.5669250488281</v>
       </c>
       <c r="F65" t="n">
-        <v>5467500</v>
+        <v>12953600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>330.6147028726578</v>
+        <v>345.9227522622342</v>
       </c>
       <c r="C66" t="n">
-        <v>345.2468397955696</v>
+        <v>347.751765473026</v>
       </c>
       <c r="D66" t="n">
-        <v>328.0898557440862</v>
+        <v>343.9048707541211</v>
       </c>
       <c r="E66" t="n">
-        <v>343.5669250488281</v>
+        <v>345.7537536621094</v>
       </c>
       <c r="F66" t="n">
-        <v>12953600</v>
+        <v>6942300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>345.9227522622342</v>
+        <v>345.7537581195867</v>
       </c>
       <c r="C67" t="n">
-        <v>347.751765473026</v>
+        <v>346.3700827656107</v>
       </c>
       <c r="D67" t="n">
-        <v>343.9048707541211</v>
+        <v>341.7776344791052</v>
       </c>
       <c r="E67" t="n">
-        <v>345.7537536621094</v>
+        <v>344.8193969726562</v>
       </c>
       <c r="F67" t="n">
-        <v>6942300</v>
+        <v>7004600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>345.7537887198587</v>
+        <v>343.9347204472646</v>
       </c>
       <c r="C68" t="n">
-        <v>346.3701134204293</v>
+        <v>345.5450457875993</v>
       </c>
       <c r="D68" t="n">
-        <v>341.777664727478</v>
+        <v>341.6683310172716</v>
       </c>
       <c r="E68" t="n">
-        <v>344.8194274902344</v>
+        <v>343.0500183105469</v>
       </c>
       <c r="F68" t="n">
-        <v>7004600</v>
+        <v>7269300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>343.9347204472646</v>
+        <v>343.4873664669518</v>
       </c>
       <c r="C69" t="n">
-        <v>345.5450457875993</v>
+        <v>345.7140163182048</v>
       </c>
       <c r="D69" t="n">
-        <v>341.6683310172716</v>
+        <v>341.6285335316323</v>
       </c>
       <c r="E69" t="n">
-        <v>343.0500183105469</v>
+        <v>342.3541870117188</v>
       </c>
       <c r="F69" t="n">
-        <v>7269300</v>
+        <v>7263500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>343.4873664669518</v>
+        <v>343.1096892417585</v>
       </c>
       <c r="C70" t="n">
-        <v>345.7140163182048</v>
+        <v>345.4555878108393</v>
       </c>
       <c r="D70" t="n">
-        <v>341.6285335316323</v>
+        <v>342.2150370848335</v>
       </c>
       <c r="E70" t="n">
-        <v>342.3541870117188</v>
+        <v>343.9446716308594</v>
       </c>
       <c r="F70" t="n">
-        <v>7263500</v>
+        <v>6805000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>343.1096587982668</v>
+        <v>343.9843722679569</v>
       </c>
       <c r="C71" t="n">
-        <v>345.4555571592003</v>
+        <v>347.8213472210815</v>
       </c>
       <c r="D71" t="n">
-        <v>342.2150067207226</v>
+        <v>343.9843722679569</v>
       </c>
       <c r="E71" t="n">
-        <v>343.9446411132812</v>
+        <v>347.165283203125</v>
       </c>
       <c r="F71" t="n">
-        <v>6805000</v>
+        <v>18623900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>343.9844025059169</v>
+        <v>347.9108213067459</v>
       </c>
       <c r="C72" t="n">
-        <v>347.8213777963309</v>
+        <v>351.3302900915655</v>
       </c>
       <c r="D72" t="n">
-        <v>343.9844025059169</v>
+        <v>347.5032649901081</v>
       </c>
       <c r="E72" t="n">
-        <v>347.1653137207031</v>
+        <v>349.9883422851562</v>
       </c>
       <c r="F72" t="n">
-        <v>18623900</v>
+        <v>5043500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>347.9108213067459</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="C73" t="n">
-        <v>351.3302900915655</v>
+        <v>354.2527532371108</v>
       </c>
       <c r="D73" t="n">
-        <v>347.5032649901081</v>
+        <v>349.8988928418326</v>
       </c>
       <c r="E73" t="n">
-        <v>349.9883422851562</v>
+        <v>351.2706604003906</v>
       </c>
       <c r="F73" t="n">
-        <v>5043500</v>
+        <v>3703200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>349.8988928418326</v>
+        <v>351.2706679101954</v>
       </c>
       <c r="C74" t="n">
-        <v>354.2527532371108</v>
+        <v>353.8650741726075</v>
       </c>
       <c r="D74" t="n">
-        <v>349.8988928418326</v>
+        <v>350.9028813061371</v>
       </c>
       <c r="E74" t="n">
-        <v>351.2706604003906</v>
+        <v>353.0201721191406</v>
       </c>
       <c r="F74" t="n">
-        <v>3703200</v>
+        <v>2023600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>351.2706375438569</v>
+        <v>352.9803906057607</v>
       </c>
       <c r="C75" t="n">
-        <v>353.86504358199</v>
+        <v>354.6006658812749</v>
       </c>
       <c r="D75" t="n">
-        <v>350.9028509715926</v>
+        <v>351.5986730469889</v>
       </c>
       <c r="E75" t="n">
-        <v>353.0201416015625</v>
+        <v>352.8809814453125</v>
       </c>
       <c r="F75" t="n">
-        <v>2023600</v>
+        <v>2017000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>352.9803906057607</v>
+        <v>353.3680687798424</v>
       </c>
       <c r="C76" t="n">
-        <v>354.6006658812749</v>
+        <v>354.4217392079314</v>
       </c>
       <c r="D76" t="n">
-        <v>351.5986730469889</v>
+        <v>351.6881539711041</v>
       </c>
       <c r="E76" t="n">
-        <v>352.8809814453125</v>
+        <v>352.4933166503906</v>
       </c>
       <c r="F76" t="n">
-        <v>2017000</v>
+        <v>3989900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>353.3680687798424</v>
+        <v>351.8869529196318</v>
       </c>
       <c r="C77" t="n">
-        <v>354.4217392079314</v>
+        <v>352.7517549841574</v>
       </c>
       <c r="D77" t="n">
-        <v>351.6881539711041</v>
+        <v>350.5549550996776</v>
       </c>
       <c r="E77" t="n">
-        <v>352.4933166503906</v>
+        <v>351.5092163085938</v>
       </c>
       <c r="F77" t="n">
-        <v>3989900</v>
+        <v>3366500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>351.8869529196318</v>
+        <v>351.539030494231</v>
       </c>
       <c r="C78" t="n">
-        <v>352.7517549841574</v>
+        <v>353.0797966289462</v>
       </c>
       <c r="D78" t="n">
-        <v>350.5549550996776</v>
+        <v>348.5967074506911</v>
       </c>
       <c r="E78" t="n">
-        <v>351.5092163085938</v>
+        <v>348.6165771484375</v>
       </c>
       <c r="F78" t="n">
-        <v>3366500</v>
+        <v>3503200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>351.539030494231</v>
+        <v>347.7816144857114</v>
       </c>
       <c r="C79" t="n">
-        <v>353.0797966289462</v>
+        <v>347.9605327817998</v>
       </c>
       <c r="D79" t="n">
-        <v>348.5967074506911</v>
+        <v>341.4297722912301</v>
       </c>
       <c r="E79" t="n">
-        <v>348.6165771484375</v>
+        <v>344.411865234375</v>
       </c>
       <c r="F79" t="n">
-        <v>3503200</v>
+        <v>5403800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>347.7816144857114</v>
+        <v>342.443665092254</v>
       </c>
       <c r="C80" t="n">
-        <v>347.9605327817998</v>
+        <v>355.4058372808095</v>
       </c>
       <c r="D80" t="n">
-        <v>341.4297722912301</v>
+        <v>341.996339026907</v>
       </c>
       <c r="E80" t="n">
-        <v>344.411865234375</v>
+        <v>351.6881408691406</v>
       </c>
       <c r="F80" t="n">
-        <v>5403800</v>
+        <v>7592200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>342.443665092254</v>
+        <v>351.5688750998228</v>
       </c>
       <c r="C81" t="n">
-        <v>355.4058372808095</v>
+        <v>356.4793906429162</v>
       </c>
       <c r="D81" t="n">
-        <v>341.996339026907</v>
+        <v>349.8989103083969</v>
       </c>
       <c r="E81" t="n">
-        <v>351.6881408691406</v>
+        <v>355.4257202148438</v>
       </c>
       <c r="F81" t="n">
-        <v>7592200</v>
+        <v>6775400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>351.5688449134013</v>
+        <v>355.0181456831753</v>
       </c>
       <c r="C82" t="n">
-        <v>356.4793600348679</v>
+        <v>356.1414055038805</v>
       </c>
       <c r="D82" t="n">
-        <v>349.8988802653619</v>
+        <v>352.3939197646881</v>
       </c>
       <c r="E82" t="n">
-        <v>355.4256896972656</v>
+        <v>353.7557373046875</v>
       </c>
       <c r="F82" t="n">
-        <v>6775400</v>
+        <v>6333900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>355.0181456831753</v>
+        <v>352.8809877738215</v>
       </c>
       <c r="C83" t="n">
-        <v>356.1414055038805</v>
+        <v>354.2229356253969</v>
       </c>
       <c r="D83" t="n">
-        <v>352.3939197646881</v>
+        <v>347.4138175407059</v>
       </c>
       <c r="E83" t="n">
-        <v>353.7557373046875</v>
+        <v>350.1275329589844</v>
       </c>
       <c r="F83" t="n">
-        <v>6333900</v>
+        <v>6357600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>352.8809877738215</v>
+        <v>350.0579384420253</v>
       </c>
       <c r="C84" t="n">
-        <v>354.2229356253969</v>
+        <v>352.582785516123</v>
       </c>
       <c r="D84" t="n">
-        <v>347.4138175407059</v>
+        <v>347.075845630788</v>
       </c>
       <c r="E84" t="n">
-        <v>350.1275329589844</v>
+        <v>347.6821899414062</v>
       </c>
       <c r="F84" t="n">
-        <v>6357600</v>
+        <v>4902900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>350.0579077159175</v>
+        <v>340.7339218833562</v>
       </c>
       <c r="C85" t="n">
-        <v>352.5827545683982</v>
+        <v>344.4416681829234</v>
       </c>
       <c r="D85" t="n">
-        <v>347.0758151664314</v>
+        <v>335.306521484956</v>
       </c>
       <c r="E85" t="n">
-        <v>347.6821594238281</v>
+        <v>341.1514282226562</v>
       </c>
       <c r="F85" t="n">
-        <v>4902900</v>
+        <v>13281300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>340.733891403126</v>
+        <v>334.9884397502153</v>
       </c>
       <c r="C86" t="n">
-        <v>344.4416373710181</v>
+        <v>335.5053249382782</v>
       </c>
       <c r="D86" t="n">
-        <v>335.3064914902319</v>
+        <v>321.8970384159538</v>
       </c>
       <c r="E86" t="n">
-        <v>341.1513977050781</v>
+        <v>325.9228820800781</v>
       </c>
       <c r="F86" t="n">
-        <v>13281300</v>
+        <v>20383500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>334.9884397502153</v>
+        <v>326.6982042036898</v>
       </c>
       <c r="C87" t="n">
-        <v>335.5053249382782</v>
+        <v>327.9307928311059</v>
       </c>
       <c r="D87" t="n">
-        <v>321.8970384159538</v>
+        <v>322.0063770709054</v>
       </c>
       <c r="E87" t="n">
-        <v>325.9228820800781</v>
+        <v>327.2051696777344</v>
       </c>
       <c r="F87" t="n">
-        <v>20383500</v>
+        <v>9388400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>326.6982042036898</v>
+        <v>327.3641650074799</v>
       </c>
       <c r="C88" t="n">
-        <v>327.9307928311059</v>
+        <v>329.7100935773221</v>
       </c>
       <c r="D88" t="n">
-        <v>322.0063770709054</v>
+        <v>324.421842198657</v>
       </c>
       <c r="E88" t="n">
-        <v>327.2051696777344</v>
+        <v>325.7936096191406</v>
       </c>
       <c r="F88" t="n">
-        <v>9388400</v>
+        <v>8587700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>327.3641650074799</v>
+        <v>324.8294159854098</v>
       </c>
       <c r="C89" t="n">
-        <v>329.7100935773221</v>
+        <v>327.2846735195349</v>
       </c>
       <c r="D89" t="n">
-        <v>324.421842198657</v>
+        <v>323.4576484910236</v>
       </c>
       <c r="E89" t="n">
-        <v>325.7936096191406</v>
+        <v>326.34033203125</v>
       </c>
       <c r="F89" t="n">
-        <v>8587700</v>
+        <v>8341600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>324.8294159854098</v>
+        <v>320.3065853250236</v>
       </c>
       <c r="C90" t="n">
-        <v>327.2846735195349</v>
+        <v>326.3602298184734</v>
       </c>
       <c r="D90" t="n">
-        <v>323.4576484910236</v>
+        <v>319.6405712796447</v>
       </c>
       <c r="E90" t="n">
-        <v>326.34033203125</v>
+        <v>323.8751525878906</v>
       </c>
       <c r="F90" t="n">
-        <v>8341600</v>
+        <v>8279900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>320.3065853250236</v>
+        <v>324.4815084058711</v>
       </c>
       <c r="C91" t="n">
-        <v>326.3602298184734</v>
+        <v>326.708158311709</v>
       </c>
       <c r="D91" t="n">
-        <v>319.6405712796447</v>
+        <v>321.0719896048092</v>
       </c>
       <c r="E91" t="n">
-        <v>323.8751525878906</v>
+        <v>323.33837890625</v>
       </c>
       <c r="F91" t="n">
-        <v>8279900</v>
+        <v>8974600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>324.4815084058711</v>
+        <v>324.5113659585408</v>
       </c>
       <c r="C92" t="n">
-        <v>326.708158311709</v>
+        <v>326.4298689273645</v>
       </c>
       <c r="D92" t="n">
-        <v>321.0719896048092</v>
+        <v>322.0660580855128</v>
       </c>
       <c r="E92" t="n">
-        <v>323.33837890625</v>
+        <v>324.4119567871094</v>
       </c>
       <c r="F92" t="n">
-        <v>8974600</v>
+        <v>6938700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>324.5113354316111</v>
+        <v>323.9149045306469</v>
       </c>
       <c r="C93" t="n">
-        <v>326.4298382199604</v>
+        <v>325.8433269631201</v>
       </c>
       <c r="D93" t="n">
-        <v>322.0660277886144</v>
+        <v>322.6823158838599</v>
       </c>
       <c r="E93" t="n">
-        <v>324.4119262695312</v>
+        <v>324.2330017089844</v>
       </c>
       <c r="F93" t="n">
-        <v>6938700</v>
+        <v>5667900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>323.9149045306469</v>
+        <v>326.0421398816049</v>
       </c>
       <c r="C94" t="n">
-        <v>325.8433269631201</v>
+        <v>330.0182635386976</v>
       </c>
       <c r="D94" t="n">
-        <v>322.6823158838599</v>
+        <v>323.0898668527969</v>
       </c>
       <c r="E94" t="n">
-        <v>324.2330017089844</v>
+        <v>326.5292053222656</v>
       </c>
       <c r="F94" t="n">
-        <v>5667900</v>
+        <v>7540200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>326.0421094095482</v>
+        <v>326.5192927903481</v>
       </c>
       <c r="C95" t="n">
-        <v>330.0182326950305</v>
+        <v>326.9665885103149</v>
       </c>
       <c r="D95" t="n">
-        <v>323.089836656661</v>
+        <v>322.9705950681941</v>
       </c>
       <c r="E95" t="n">
-        <v>326.5291748046875</v>
+        <v>323.3185119628906</v>
       </c>
       <c r="F95" t="n">
-        <v>7540200</v>
+        <v>6365800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>326.5192619706527</v>
+        <v>324.7797515334782</v>
       </c>
       <c r="C96" t="n">
-        <v>326.9665576483999</v>
+        <v>326.4298465929955</v>
       </c>
       <c r="D96" t="n">
-        <v>322.9705645834554</v>
+        <v>322.9407881617898</v>
       </c>
       <c r="E96" t="n">
-        <v>323.3184814453125</v>
+        <v>325.0282592773438</v>
       </c>
       <c r="F96" t="n">
-        <v>6365800</v>
+        <v>8106000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>324.779721039233</v>
+        <v>328.0301840749007</v>
       </c>
       <c r="C97" t="n">
-        <v>326.4298159438193</v>
+        <v>331.3701132063007</v>
       </c>
       <c r="D97" t="n">
-        <v>322.9407578402086</v>
+        <v>321.578933495427</v>
       </c>
       <c r="E97" t="n">
-        <v>325.0282287597656</v>
+        <v>329.8194274902344</v>
       </c>
       <c r="F97" t="n">
-        <v>8106000</v>
+        <v>10214200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>328.0302144269235</v>
+        <v>330.236962156358</v>
       </c>
       <c r="C98" t="n">
-        <v>331.370143867361</v>
+        <v>331.0123050809688</v>
       </c>
       <c r="D98" t="n">
-        <v>321.5789632505275</v>
+        <v>319.6803583614965</v>
       </c>
       <c r="E98" t="n">
-        <v>329.8194580078125</v>
+        <v>319.9089660644531</v>
       </c>
       <c r="F98" t="n">
-        <v>10214200</v>
+        <v>11199100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>330.2369306535451</v>
+        <v>322.8910614362982</v>
       </c>
       <c r="C99" t="n">
-        <v>331.0122735041925</v>
+        <v>332.6922224170356</v>
       </c>
       <c r="D99" t="n">
-        <v>319.6803278657264</v>
+        <v>322.1753579360102</v>
       </c>
       <c r="E99" t="n">
-        <v>319.908935546875</v>
+        <v>331.8472900390625</v>
       </c>
       <c r="F99" t="n">
-        <v>11199100</v>
+        <v>8502400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>322.8910614362982</v>
+        <v>329.6703793378445</v>
       </c>
       <c r="C100" t="n">
-        <v>332.6922224170356</v>
+        <v>333.7856822919601</v>
       </c>
       <c r="D100" t="n">
-        <v>322.1753579360102</v>
+        <v>326.906974335595</v>
       </c>
       <c r="E100" t="n">
-        <v>331.8472900390625</v>
+        <v>326.9666137695312</v>
       </c>
       <c r="F100" t="n">
-        <v>8502400</v>
+        <v>9081200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>329.6703793378445</v>
+        <v>325.15742488804</v>
       </c>
       <c r="C101" t="n">
-        <v>333.7856822919601</v>
+        <v>329.3323666962788</v>
       </c>
       <c r="D101" t="n">
-        <v>326.906974335595</v>
+        <v>322.4835097434655</v>
       </c>
       <c r="E101" t="n">
-        <v>326.9666137695312</v>
+        <v>327.9804992675781</v>
       </c>
       <c r="F101" t="n">
-        <v>9081200</v>
+        <v>8472300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>325.1574551429397</v>
+        <v>331.0123001239136</v>
       </c>
       <c r="C102" t="n">
-        <v>329.332397339644</v>
+        <v>335.5748984583446</v>
       </c>
       <c r="D102" t="n">
-        <v>322.4835397495656</v>
+        <v>326.8572581115669</v>
       </c>
       <c r="E102" t="n">
-        <v>327.9805297851562</v>
+        <v>327.1654052734375</v>
       </c>
       <c r="F102" t="n">
-        <v>8472300</v>
+        <v>8339000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>331.0123001239136</v>
+        <v>329.7995873671293</v>
       </c>
       <c r="C103" t="n">
-        <v>335.5748984583446</v>
+        <v>333.1295971166072</v>
       </c>
       <c r="D103" t="n">
-        <v>326.8572581115669</v>
+        <v>325.1475298017769</v>
       </c>
       <c r="E103" t="n">
-        <v>327.1654052734375</v>
+        <v>329.6007690429688</v>
       </c>
       <c r="F103" t="n">
-        <v>8339000</v>
+        <v>7798800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>329.7995873671293</v>
+        <v>328.7857002676274</v>
       </c>
       <c r="C104" t="n">
-        <v>333.1295971166072</v>
+        <v>330.8334016821115</v>
       </c>
       <c r="D104" t="n">
-        <v>325.1475298017769</v>
+        <v>321.6883044313802</v>
       </c>
       <c r="E104" t="n">
-        <v>329.6007690429688</v>
+        <v>323.6365966796875</v>
       </c>
       <c r="F104" t="n">
-        <v>7798800</v>
+        <v>8513400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,25 +3147,25 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>328.7857002676274</v>
+        <v>323.4373584411114</v>
       </c>
       <c r="C105" t="n">
-        <v>330.8334016821115</v>
+        <v>328.5871090806843</v>
       </c>
       <c r="D105" t="n">
-        <v>321.6883044313802</v>
+        <v>323.2779818799478</v>
       </c>
       <c r="E105" t="n">
-        <v>323.6365966796875</v>
+        <v>326.8838195800781</v>
       </c>
       <c r="F105" t="n">
-        <v>8513400</v>
+        <v>5801800</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3173,25 +3173,25 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>323.4373584411114</v>
+        <v>325.6387009449491</v>
       </c>
       <c r="C106" t="n">
-        <v>328.5871090806843</v>
+        <v>329.7425483778229</v>
       </c>
       <c r="D106" t="n">
-        <v>323.2779818799478</v>
+        <v>325.140660617698</v>
       </c>
       <c r="E106" t="n">
-        <v>326.8838195800781</v>
+        <v>327.9495849609375</v>
       </c>
       <c r="F106" t="n">
-        <v>5801800</v>
+        <v>8264300</v>
       </c>
       <c r="G106" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>325.6387312474863</v>
+        <v>327.6010166244024</v>
       </c>
       <c r="C107" t="n">
-        <v>329.7425790622465</v>
+        <v>330.9378628609571</v>
       </c>
       <c r="D107" t="n">
-        <v>325.1406908738898</v>
+        <v>322.7301671039365</v>
       </c>
       <c r="E107" t="n">
-        <v>327.9496154785156</v>
+        <v>322.9094543457031</v>
       </c>
       <c r="F107" t="n">
-        <v>8264300</v>
+        <v>9392600</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>327.6009856634334</v>
+        <v>322.5607854182599</v>
       </c>
       <c r="C108" t="n">
-        <v>330.9378315846288</v>
+        <v>325.2004234747151</v>
       </c>
       <c r="D108" t="n">
-        <v>322.7301366033025</v>
+        <v>311.5939580676488</v>
       </c>
       <c r="E108" t="n">
-        <v>322.909423828125</v>
+        <v>312.8489990234375</v>
       </c>
       <c r="F108" t="n">
-        <v>9392600</v>
+        <v>11653900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>322.5608168831966</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="C109" t="n">
-        <v>325.2004551971415</v>
+        <v>320.1204394263468</v>
       </c>
       <c r="D109" t="n">
-        <v>311.5939884628011</v>
+        <v>313.1777553150958</v>
       </c>
       <c r="E109" t="n">
-        <v>312.8490295410156</v>
+        <v>318.247802734375</v>
       </c>
       <c r="F109" t="n">
-        <v>11653900</v>
+        <v>8591700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>313.1777553150958</v>
+        <v>318.2477947880967</v>
       </c>
       <c r="C110" t="n">
-        <v>320.1204394263468</v>
+        <v>321.0168980150915</v>
       </c>
       <c r="D110" t="n">
-        <v>313.1777553150958</v>
+        <v>315.4786915611019</v>
       </c>
       <c r="E110" t="n">
-        <v>318.247802734375</v>
+        <v>319.0446472167969</v>
       </c>
       <c r="F110" t="n">
-        <v>8591700</v>
+        <v>7091900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>318.2477947880967</v>
+        <v>316.2456341157693</v>
       </c>
       <c r="C111" t="n">
-        <v>321.0168980150915</v>
+        <v>318.9450345490796</v>
       </c>
       <c r="D111" t="n">
-        <v>315.4786915611019</v>
+        <v>314.4925528519528</v>
       </c>
       <c r="E111" t="n">
-        <v>319.0446472167969</v>
+        <v>317.6799926757812</v>
       </c>
       <c r="F111" t="n">
-        <v>7091900</v>
+        <v>5967600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>316.2456644955574</v>
+        <v>316.8632122574057</v>
       </c>
       <c r="C112" t="n">
-        <v>318.9450651881826</v>
+        <v>321.0866150343326</v>
       </c>
       <c r="D112" t="n">
-        <v>314.492583063333</v>
+        <v>316.5743707451638</v>
       </c>
       <c r="E112" t="n">
-        <v>317.6800231933594</v>
+        <v>319.6921081542969</v>
       </c>
       <c r="F112" t="n">
-        <v>5967600</v>
+        <v>6831100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>316.8632425049395</v>
+        <v>317.7896151590316</v>
       </c>
       <c r="C113" t="n">
-        <v>321.0866456850293</v>
+        <v>319.2637952336624</v>
       </c>
       <c r="D113" t="n">
-        <v>316.574400965125</v>
+        <v>303.5157608014752</v>
       </c>
       <c r="E113" t="n">
-        <v>319.692138671875</v>
+        <v>305.3186645507812</v>
       </c>
       <c r="F113" t="n">
-        <v>6831100</v>
+        <v>13048000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>317.789583394942</v>
+        <v>304.30263971785</v>
       </c>
       <c r="C114" t="n">
-        <v>319.2637633222238</v>
+        <v>308.0578528391844</v>
       </c>
       <c r="D114" t="n">
-        <v>303.515730464103</v>
+        <v>301.8921111606905</v>
       </c>
       <c r="E114" t="n">
-        <v>305.3186340332031</v>
+        <v>306.0158996582031</v>
       </c>
       <c r="F114" t="n">
-        <v>13048000</v>
+        <v>9120200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>304.3026700645725</v>
+        <v>307.3407046816708</v>
       </c>
       <c r="C115" t="n">
-        <v>308.0578835603972</v>
+        <v>312.7095945401492</v>
       </c>
       <c r="D115" t="n">
-        <v>301.8921412670219</v>
+        <v>307.0418926144709</v>
       </c>
       <c r="E115" t="n">
-        <v>306.0159301757812</v>
+        <v>311.7633056640625</v>
       </c>
       <c r="F115" t="n">
-        <v>9120200</v>
+        <v>7624200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>307.3406745970078</v>
+        <v>313.2475006793624</v>
       </c>
       <c r="C116" t="n">
-        <v>312.7095639299417</v>
+        <v>318.168142259306</v>
       </c>
       <c r="D116" t="n">
-        <v>307.0418625590578</v>
+        <v>312.7096085363555</v>
       </c>
       <c r="E116" t="n">
-        <v>311.7632751464844</v>
+        <v>315.4588012695312</v>
       </c>
       <c r="F116" t="n">
-        <v>7624200</v>
+        <v>8725500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>313.2474703757061</v>
+        <v>313.2275230423357</v>
       </c>
       <c r="C117" t="n">
-        <v>318.1681114796254</v>
+        <v>318.9749280375353</v>
       </c>
       <c r="D117" t="n">
-        <v>312.709578284735</v>
+        <v>310.7273811988043</v>
       </c>
       <c r="E117" t="n">
-        <v>315.4587707519531</v>
+        <v>318.8852844238281</v>
       </c>
       <c r="F117" t="n">
-        <v>8725500</v>
+        <v>12412900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>313.2275530184615</v>
+        <v>314.2634710190134</v>
       </c>
       <c r="C118" t="n">
-        <v>318.9749585636924</v>
+        <v>321.3356502974509</v>
       </c>
       <c r="D118" t="n">
-        <v>310.7274109356645</v>
+        <v>313.3670044395995</v>
       </c>
       <c r="E118" t="n">
-        <v>318.8853149414062</v>
+        <v>319.2538452148438</v>
       </c>
       <c r="F118" t="n">
-        <v>12412900</v>
+        <v>6674900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>314.2634710190134</v>
+        <v>314.5722564235918</v>
       </c>
       <c r="C119" t="n">
-        <v>321.3356502974509</v>
+        <v>320.7778503840851</v>
       </c>
       <c r="D119" t="n">
-        <v>313.3670044395995</v>
+        <v>313.117987052978</v>
       </c>
       <c r="E119" t="n">
-        <v>319.2538452148438</v>
+        <v>319.5725708007812</v>
       </c>
       <c r="F119" t="n">
-        <v>6674900</v>
+        <v>5474300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>314.5722564235918</v>
+        <v>320.1801887712339</v>
       </c>
       <c r="C120" t="n">
-        <v>320.7778503840851</v>
+        <v>324.4932049097204</v>
       </c>
       <c r="D120" t="n">
-        <v>313.117987052978</v>
+        <v>318.5466018009251</v>
       </c>
       <c r="E120" t="n">
-        <v>319.5725708007812</v>
+        <v>319.2139892578125</v>
       </c>
       <c r="F120" t="n">
-        <v>5474300</v>
+        <v>5257900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>320.1801887712339</v>
+        <v>318.0784411900573</v>
       </c>
       <c r="C121" t="n">
-        <v>324.4932049097204</v>
+        <v>321.5348424853333</v>
       </c>
       <c r="D121" t="n">
-        <v>318.5466018009251</v>
+        <v>313.5363155637196</v>
       </c>
       <c r="E121" t="n">
-        <v>319.2139892578125</v>
+        <v>318.5466003417969</v>
       </c>
       <c r="F121" t="n">
-        <v>5257900</v>
+        <v>8267200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>318.0784411900573</v>
+        <v>314.8113170354491</v>
       </c>
       <c r="C122" t="n">
-        <v>321.5348424853333</v>
+        <v>316.4449040988039</v>
       </c>
       <c r="D122" t="n">
-        <v>313.5363155637196</v>
+        <v>311.0760141261629</v>
       </c>
       <c r="E122" t="n">
-        <v>318.5466003417969</v>
+        <v>316.1161804199219</v>
       </c>
       <c r="F122" t="n">
-        <v>8267200</v>
+        <v>6439700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>314.8113170354491</v>
+        <v>312.2314560667069</v>
       </c>
       <c r="C123" t="n">
-        <v>316.4449040988039</v>
+        <v>315.1599358349184</v>
       </c>
       <c r="D123" t="n">
-        <v>311.0760141261629</v>
+        <v>308.9344312933075</v>
       </c>
       <c r="E123" t="n">
-        <v>316.1161804199219</v>
+        <v>314.7316284179688</v>
       </c>
       <c r="F123" t="n">
-        <v>6439700</v>
+        <v>8381500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>312.2314560667069</v>
+        <v>314.1937124870568</v>
       </c>
       <c r="C124" t="n">
-        <v>315.1599358349184</v>
+        <v>315.8870617531473</v>
       </c>
       <c r="D124" t="n">
-        <v>308.9344312933075</v>
+        <v>310.2293309503021</v>
       </c>
       <c r="E124" t="n">
-        <v>314.7316284179688</v>
+        <v>313.1976318359375</v>
       </c>
       <c r="F124" t="n">
-        <v>8381500</v>
+        <v>5271300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>314.1937431016918</v>
+        <v>312.0222791858673</v>
       </c>
       <c r="C125" t="n">
-        <v>315.8870925327801</v>
+        <v>313.8450934912395</v>
       </c>
       <c r="D125" t="n">
-        <v>310.2293611786528</v>
+        <v>307.1813415762761</v>
       </c>
       <c r="E125" t="n">
-        <v>313.1976623535156</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F125" t="n">
-        <v>5271300</v>
+        <v>6376700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>312.0222791858673</v>
+        <v>306.9323235221122</v>
       </c>
       <c r="C126" t="n">
-        <v>313.8450934912395</v>
+        <v>309.7313078758147</v>
       </c>
       <c r="D126" t="n">
-        <v>307.1813415762761</v>
+        <v>304.8206068898292</v>
       </c>
       <c r="E126" t="n">
-        <v>307.7490844726562</v>
+        <v>305.2987365722656</v>
       </c>
       <c r="F126" t="n">
-        <v>6376700</v>
+        <v>7514900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>306.9323542029832</v>
+        <v>306.3844668672209</v>
       </c>
       <c r="C127" t="n">
-        <v>309.7313388364715</v>
+        <v>309.1336593983733</v>
       </c>
       <c r="D127" t="n">
-        <v>304.8206373596136</v>
+        <v>305.2190694406472</v>
       </c>
       <c r="E127" t="n">
-        <v>305.2987670898438</v>
+        <v>305.9362487792969</v>
       </c>
       <c r="F127" t="n">
-        <v>7514900</v>
+        <v>4814100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>306.3844668672209</v>
+        <v>306.6434401255651</v>
       </c>
       <c r="C128" t="n">
-        <v>309.1336593983733</v>
+        <v>309.9105835049712</v>
       </c>
       <c r="D128" t="n">
-        <v>305.2190694406472</v>
+        <v>306.1752809950723</v>
       </c>
       <c r="E128" t="n">
-        <v>305.9362487792969</v>
+        <v>308.8945617675781</v>
       </c>
       <c r="F128" t="n">
-        <v>4814100</v>
+        <v>6401200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>306.6434401255651</v>
+        <v>310.0998441452866</v>
       </c>
       <c r="C129" t="n">
-        <v>309.9105835049712</v>
+        <v>311.4644698112407</v>
       </c>
       <c r="D129" t="n">
-        <v>306.1752809950723</v>
+        <v>306.1752838399166</v>
       </c>
       <c r="E129" t="n">
-        <v>308.8945617675781</v>
+        <v>307.2510375976562</v>
       </c>
       <c r="F129" t="n">
-        <v>6401200</v>
+        <v>6872200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>310.0998441452866</v>
+        <v>306.2051850075188</v>
       </c>
       <c r="C130" t="n">
-        <v>311.4644698112407</v>
+        <v>306.7331065856557</v>
       </c>
       <c r="D130" t="n">
-        <v>306.1752838399166</v>
+        <v>297.3301019351647</v>
       </c>
       <c r="E130" t="n">
-        <v>307.2510375976562</v>
+        <v>297.8480529785156</v>
       </c>
       <c r="F130" t="n">
-        <v>6872200</v>
+        <v>7191700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>306.2051850075188</v>
+        <v>296.8719016022564</v>
       </c>
       <c r="C131" t="n">
-        <v>306.7331065856557</v>
+        <v>301.2845318265138</v>
       </c>
       <c r="D131" t="n">
-        <v>297.3301019351647</v>
+        <v>295.8658503636263</v>
       </c>
       <c r="E131" t="n">
-        <v>297.8480529785156</v>
+        <v>298.5353393554688</v>
       </c>
       <c r="F131" t="n">
-        <v>7191700</v>
+        <v>6826400</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>296.8719016022564</v>
+        <v>298.6748142545254</v>
       </c>
       <c r="C132" t="n">
-        <v>301.2845318265138</v>
+        <v>301.7327894042891</v>
       </c>
       <c r="D132" t="n">
-        <v>295.8658503636263</v>
+        <v>297.8381100854838</v>
       </c>
       <c r="E132" t="n">
-        <v>298.5353393554688</v>
+        <v>300.4378662109375</v>
       </c>
       <c r="F132" t="n">
-        <v>6826400</v>
+        <v>14398100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>298.6748142545254</v>
+        <v>304.0038572697504</v>
       </c>
       <c r="C133" t="n">
-        <v>301.7327894042891</v>
+        <v>306.6434651794843</v>
       </c>
       <c r="D133" t="n">
-        <v>297.8381100854838</v>
+        <v>301.6630614260347</v>
       </c>
       <c r="E133" t="n">
-        <v>300.4378662109375</v>
+        <v>303.246826171875</v>
       </c>
       <c r="F133" t="n">
-        <v>14398100</v>
+        <v>7824500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>304.0038572697504</v>
+        <v>300.8163767349488</v>
       </c>
       <c r="C134" t="n">
-        <v>306.6434651794843</v>
+        <v>304.8405513457489</v>
       </c>
       <c r="D134" t="n">
-        <v>301.6630614260347</v>
+        <v>299.4417804808951</v>
       </c>
       <c r="E134" t="n">
-        <v>303.246826171875</v>
+        <v>302.5694885253906</v>
       </c>
       <c r="F134" t="n">
-        <v>7824500</v>
+        <v>5375900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>300.8163767349488</v>
+        <v>304.2827391072273</v>
       </c>
       <c r="C135" t="n">
-        <v>304.8405513457489</v>
+        <v>307.2809213034843</v>
       </c>
       <c r="D135" t="n">
-        <v>299.4417804808951</v>
+        <v>300.9857144661871</v>
       </c>
       <c r="E135" t="n">
-        <v>302.5694885253906</v>
+        <v>303.7149658203125</v>
       </c>
       <c r="F135" t="n">
-        <v>5375900</v>
+        <v>6280900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>304.2827391072273</v>
+        <v>302.9679242862715</v>
       </c>
       <c r="C136" t="n">
-        <v>307.2809213034843</v>
+        <v>306.6633753539059</v>
       </c>
       <c r="D136" t="n">
-        <v>300.9857144661871</v>
+        <v>301.8124669695884</v>
       </c>
       <c r="E136" t="n">
-        <v>303.7149658203125</v>
+        <v>304.3325500488281</v>
       </c>
       <c r="F136" t="n">
-        <v>6280900</v>
+        <v>7652700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>302.9678939055341</v>
+        <v>303.127283705864</v>
       </c>
       <c r="C137" t="n">
-        <v>306.6633446025994</v>
+        <v>303.3962145496307</v>
       </c>
       <c r="D137" t="n">
-        <v>301.8124367047168</v>
+        <v>293.1664767786049</v>
       </c>
       <c r="E137" t="n">
-        <v>304.33251953125</v>
+        <v>294.3617553710938</v>
       </c>
       <c r="F137" t="n">
-        <v>7652700</v>
+        <v>9974400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>303.1273151321971</v>
+        <v>297.5592048794472</v>
       </c>
       <c r="C138" t="n">
-        <v>303.3962460038449</v>
+        <v>299.5015440476056</v>
       </c>
       <c r="D138" t="n">
-        <v>293.166507172264</v>
+        <v>294.7303392781201</v>
       </c>
       <c r="E138" t="n">
-        <v>294.3617858886719</v>
+        <v>298.3660278320312</v>
       </c>
       <c r="F138" t="n">
-        <v>9974400</v>
+        <v>9330300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>297.5592048794472</v>
+        <v>300.4179440831887</v>
       </c>
       <c r="C139" t="n">
-        <v>299.5015440476056</v>
+        <v>302.1511147673973</v>
       </c>
       <c r="D139" t="n">
-        <v>294.7303392781201</v>
+        <v>295.4275700673832</v>
       </c>
       <c r="E139" t="n">
-        <v>298.3660278320312</v>
+        <v>301.055419921875</v>
       </c>
       <c r="F139" t="n">
-        <v>9330300</v>
+        <v>10246900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>300.4179440831887</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="C140" t="n">
-        <v>302.1511147673973</v>
+        <v>303.8544344044319</v>
       </c>
       <c r="D140" t="n">
-        <v>295.4275700673832</v>
+        <v>292.7381994806606</v>
       </c>
       <c r="E140" t="n">
-        <v>301.055419921875</v>
+        <v>297.340087890625</v>
       </c>
       <c r="F140" t="n">
-        <v>10246900</v>
+        <v>7707600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>303.8544032182521</v>
+        <v>296.6328211241279</v>
       </c>
       <c r="C141" t="n">
-        <v>303.8544032182521</v>
+        <v>301.2845313811459</v>
       </c>
       <c r="D141" t="n">
-        <v>292.7381694353985</v>
+        <v>294.6904819925192</v>
       </c>
       <c r="E141" t="n">
-        <v>297.3400573730469</v>
+        <v>299.6210632324219</v>
       </c>
       <c r="F141" t="n">
-        <v>7707600</v>
+        <v>4376000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>296.6328211241279</v>
+        <v>299.5612984468797</v>
       </c>
       <c r="C142" t="n">
-        <v>301.2845313811459</v>
+        <v>303.2268985064469</v>
       </c>
       <c r="D142" t="n">
-        <v>294.6904819925192</v>
+        <v>298.286316373369</v>
       </c>
       <c r="E142" t="n">
-        <v>299.6210632324219</v>
+        <v>302.1411437988281</v>
       </c>
       <c r="F142" t="n">
-        <v>4376000</v>
+        <v>5501000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>299.5612984468797</v>
+        <v>301.2546730003434</v>
       </c>
       <c r="C143" t="n">
-        <v>303.2268985064469</v>
+        <v>303.7847266884853</v>
       </c>
       <c r="D143" t="n">
-        <v>298.286316373369</v>
+        <v>299.9398390775635</v>
       </c>
       <c r="E143" t="n">
-        <v>302.1411437988281</v>
+        <v>301.3642272949219</v>
       </c>
       <c r="F143" t="n">
-        <v>5501000</v>
+        <v>4413900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>301.2546730003434</v>
+        <v>306.5239246667074</v>
       </c>
       <c r="C144" t="n">
-        <v>303.7847266884853</v>
+        <v>309.8607706923777</v>
       </c>
       <c r="D144" t="n">
-        <v>299.9398390775635</v>
+        <v>306.4940434616348</v>
       </c>
       <c r="E144" t="n">
-        <v>301.3642272949219</v>
+        <v>307.7490844726562</v>
       </c>
       <c r="F144" t="n">
-        <v>4413900</v>
+        <v>6879300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>306.5239246667074</v>
+        <v>306.792884650012</v>
       </c>
       <c r="C145" t="n">
-        <v>309.8607706923777</v>
+        <v>308.3666789299265</v>
       </c>
       <c r="D145" t="n">
-        <v>306.4940434616348</v>
+        <v>302.4001646993119</v>
       </c>
       <c r="E145" t="n">
-        <v>307.7490844726562</v>
+        <v>307.0817565917969</v>
       </c>
       <c r="F145" t="n">
-        <v>6879300</v>
+        <v>4811500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>306.7928541611418</v>
+        <v>307.5000714824076</v>
       </c>
       <c r="C146" t="n">
-        <v>308.3666482846536</v>
+        <v>307.7889434035062</v>
       </c>
       <c r="D146" t="n">
-        <v>302.4001346469872</v>
+        <v>302.3204699616491</v>
       </c>
       <c r="E146" t="n">
-        <v>307.0817260742188</v>
+        <v>303.1671142578125</v>
       </c>
       <c r="F146" t="n">
-        <v>4811500</v>
+        <v>5190000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>307.5000714824076</v>
+        <v>302.7388065700545</v>
       </c>
       <c r="C147" t="n">
-        <v>307.7889434035062</v>
+        <v>308.5360036681458</v>
       </c>
       <c r="D147" t="n">
-        <v>302.3204699616491</v>
+        <v>301.155041869684</v>
       </c>
       <c r="E147" t="n">
-        <v>303.1671142578125</v>
+        <v>308.1774291992188</v>
       </c>
       <c r="F147" t="n">
-        <v>5190000</v>
+        <v>6787200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>302.7388065700545</v>
+        <v>307.2610301082847</v>
       </c>
       <c r="C148" t="n">
-        <v>308.5360036681458</v>
+        <v>310.8967187654788</v>
       </c>
       <c r="D148" t="n">
-        <v>301.155041869684</v>
+        <v>306.2848600302058</v>
       </c>
       <c r="E148" t="n">
-        <v>308.1774291992188</v>
+        <v>310.149658203125</v>
       </c>
       <c r="F148" t="n">
-        <v>6787200</v>
+        <v>5571000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>307.2610301082847</v>
+        <v>311.7732461183575</v>
       </c>
       <c r="C149" t="n">
-        <v>310.8967187654788</v>
+        <v>315.4886379179251</v>
       </c>
       <c r="D149" t="n">
-        <v>306.2848600302058</v>
+        <v>310.2990358004714</v>
       </c>
       <c r="E149" t="n">
-        <v>310.149658203125</v>
+        <v>314.6718444824219</v>
       </c>
       <c r="F149" t="n">
-        <v>5571000</v>
+        <v>4831400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>311.7732763548231</v>
+        <v>315.1101522104624</v>
       </c>
       <c r="C150" t="n">
-        <v>315.4886685147176</v>
+        <v>316.7536793728972</v>
       </c>
       <c r="D150" t="n">
-        <v>310.2990658939648</v>
+        <v>313.3371296864953</v>
       </c>
       <c r="E150" t="n">
-        <v>314.671875</v>
+        <v>313.8650512695312</v>
       </c>
       <c r="F150" t="n">
-        <v>4831400</v>
+        <v>5695800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>315.1101522104624</v>
+        <v>315.3591594617635</v>
       </c>
       <c r="C151" t="n">
-        <v>316.7536793728972</v>
+        <v>318.1880250357548</v>
       </c>
       <c r="D151" t="n">
-        <v>313.3371296864953</v>
+        <v>313.9447114757824</v>
       </c>
       <c r="E151" t="n">
-        <v>313.8650512695312</v>
+        <v>315.7774963378906</v>
       </c>
       <c r="F151" t="n">
-        <v>5695800</v>
+        <v>8082300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>315.3591594617635</v>
+        <v>315.159944872979</v>
       </c>
       <c r="C152" t="n">
-        <v>318.1880250357548</v>
+        <v>316.305431661891</v>
       </c>
       <c r="D152" t="n">
-        <v>313.9447114757824</v>
+        <v>311.1258299735145</v>
       </c>
       <c r="E152" t="n">
-        <v>315.7774963378906</v>
+        <v>312.7095947265625</v>
       </c>
       <c r="F152" t="n">
-        <v>8082300</v>
+        <v>5506800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>315.1599141162692</v>
+        <v>312.7793059315876</v>
       </c>
       <c r="C153" t="n">
-        <v>316.3054007933923</v>
+        <v>315.6480231708821</v>
       </c>
       <c r="D153" t="n">
-        <v>311.1257996104973</v>
+        <v>307.6096447395195</v>
       </c>
       <c r="E153" t="n">
-        <v>312.7095642089844</v>
+        <v>308.7252502441406</v>
       </c>
       <c r="F153" t="n">
-        <v>5506800</v>
+        <v>6806900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>312.7793368499103</v>
+        <v>309.7910754200902</v>
       </c>
       <c r="C154" t="n">
-        <v>315.6480543727783</v>
+        <v>310.1396793547997</v>
       </c>
       <c r="D154" t="n">
-        <v>307.6096751468197</v>
+        <v>306.8526251277434</v>
       </c>
       <c r="E154" t="n">
-        <v>308.7252807617188</v>
+        <v>310.0699768066406</v>
       </c>
       <c r="F154" t="n">
-        <v>6806900</v>
+        <v>5666600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>309.791044929962</v>
+        <v>309.2830795800573</v>
       </c>
       <c r="C155" t="n">
-        <v>310.1396488303614</v>
+        <v>310.9764290509568</v>
       </c>
       <c r="D155" t="n">
-        <v>306.8525949268221</v>
+        <v>303.8146058713554</v>
       </c>
       <c r="E155" t="n">
-        <v>310.0699462890625</v>
+        <v>307.66943359375</v>
       </c>
       <c r="F155" t="n">
-        <v>5666600</v>
+        <v>7275000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>309.2830795800573</v>
+        <v>305.8963913711518</v>
       </c>
       <c r="C156" t="n">
-        <v>310.9764290509568</v>
+        <v>308.7651086725988</v>
       </c>
       <c r="D156" t="n">
-        <v>303.8146058713554</v>
+        <v>303.3065754519026</v>
       </c>
       <c r="E156" t="n">
-        <v>307.66943359375</v>
+        <v>308.2073059082031</v>
       </c>
       <c r="F156" t="n">
-        <v>7275000</v>
+        <v>5616900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>305.8963913711518</v>
+        <v>306.3048043469537</v>
       </c>
       <c r="C157" t="n">
-        <v>308.7651086725988</v>
+        <v>309.6018292319215</v>
       </c>
       <c r="D157" t="n">
-        <v>303.3065754519026</v>
+        <v>304.8604750852367</v>
       </c>
       <c r="E157" t="n">
-        <v>308.2073059082031</v>
+        <v>308.4364013671875</v>
       </c>
       <c r="F157" t="n">
-        <v>5616900</v>
+        <v>6261500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>306.3047740402819</v>
+        <v>310.9763962887836</v>
       </c>
       <c r="C158" t="n">
-        <v>309.6017985990326</v>
+        <v>312.7294775914766</v>
       </c>
       <c r="D158" t="n">
-        <v>304.8604449214708</v>
+        <v>307.5299352956203</v>
       </c>
       <c r="E158" t="n">
-        <v>308.4363708496094</v>
+        <v>308.0877380371094</v>
       </c>
       <c r="F158" t="n">
-        <v>6261500</v>
+        <v>8839900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>310.9763962887836</v>
+        <v>335.0815497318694</v>
       </c>
       <c r="C159" t="n">
-        <v>312.7294775914766</v>
+        <v>340.6396971989305</v>
       </c>
       <c r="D159" t="n">
-        <v>307.5299352956203</v>
+        <v>332.4817936312549</v>
       </c>
       <c r="E159" t="n">
-        <v>308.0877380371094</v>
+        <v>333.5475769042969</v>
       </c>
       <c r="F159" t="n">
-        <v>8839900</v>
+        <v>16658600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>335.0815497318694</v>
+        <v>330.8183346281009</v>
       </c>
       <c r="C160" t="n">
-        <v>340.6396971989305</v>
+        <v>331.1968501776938</v>
       </c>
       <c r="D160" t="n">
-        <v>332.4817936312549</v>
+        <v>326.7941598769157</v>
       </c>
       <c r="E160" t="n">
-        <v>333.5475769042969</v>
+        <v>328.5472717285156</v>
       </c>
       <c r="F160" t="n">
-        <v>16658600</v>
+        <v>11241100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>330.8183038995719</v>
+        <v>331.5753827423343</v>
       </c>
       <c r="C161" t="n">
-        <v>331.1968194140059</v>
+        <v>334.5337439447337</v>
       </c>
       <c r="D161" t="n">
-        <v>326.7941295221779</v>
+        <v>326.6447706056774</v>
       </c>
       <c r="E161" t="n">
-        <v>328.5472412109375</v>
+        <v>326.744384765625</v>
       </c>
       <c r="F161" t="n">
-        <v>11241100</v>
+        <v>6726100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>331.5753517735461</v>
+        <v>326.7144870306598</v>
       </c>
       <c r="C162" t="n">
-        <v>334.5337126996377</v>
+        <v>328.4974800902166</v>
       </c>
       <c r="D162" t="n">
-        <v>326.6447400974031</v>
+        <v>324.1246709928955</v>
       </c>
       <c r="E162" t="n">
-        <v>326.7443542480469</v>
+        <v>325.5690002441406</v>
       </c>
       <c r="F162" t="n">
-        <v>6726100</v>
+        <v>6712400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>326.7144870306598</v>
+        <v>323.8357678318997</v>
       </c>
       <c r="C163" t="n">
-        <v>328.4974800902166</v>
+        <v>324.3039269566456</v>
       </c>
       <c r="D163" t="n">
-        <v>324.1246709928955</v>
+        <v>318.3971759556802</v>
       </c>
       <c r="E163" t="n">
-        <v>325.5690002441406</v>
+        <v>320.7678527832031</v>
       </c>
       <c r="F163" t="n">
-        <v>6712400</v>
+        <v>5893200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>323.8357986413566</v>
+        <v>322.4811180854182</v>
       </c>
       <c r="C164" t="n">
-        <v>324.3039578106427</v>
+        <v>323.3078516694185</v>
       </c>
       <c r="D164" t="n">
-        <v>318.3972062477142</v>
+        <v>316.7536542120865</v>
       </c>
       <c r="E164" t="n">
-        <v>320.7678833007812</v>
+        <v>317.5505065917969</v>
       </c>
       <c r="F164" t="n">
-        <v>5893200</v>
+        <v>7808400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>322.4811180854182</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="C165" t="n">
-        <v>323.3078516694185</v>
+        <v>322.4213711748579</v>
       </c>
       <c r="D165" t="n">
-        <v>316.7536542120865</v>
+        <v>318.2876422602183</v>
       </c>
       <c r="E165" t="n">
-        <v>317.5505065917969</v>
+        <v>320.0208129882812</v>
       </c>
       <c r="F165" t="n">
-        <v>7808400</v>
+        <v>7186100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>318.2876119079176</v>
+        <v>319.7319477733878</v>
       </c>
       <c r="C166" t="n">
-        <v>322.4213404283596</v>
+        <v>319.8116512556435</v>
       </c>
       <c r="D166" t="n">
-        <v>318.2876119079176</v>
+        <v>314.9208911627371</v>
       </c>
       <c r="E166" t="n">
-        <v>320.0207824707031</v>
+        <v>317.5405883789062</v>
       </c>
       <c r="F166" t="n">
-        <v>7186100</v>
+        <v>5950200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>319.7319477733878</v>
+        <v>317.8493444570379</v>
       </c>
       <c r="C167" t="n">
-        <v>319.8116512556435</v>
+        <v>323.9055014903766</v>
       </c>
       <c r="D167" t="n">
-        <v>314.9208911627371</v>
+        <v>316.7636201861749</v>
       </c>
       <c r="E167" t="n">
-        <v>317.5405883789062</v>
+        <v>322.5906677246094</v>
       </c>
       <c r="F167" t="n">
-        <v>5950200</v>
+        <v>9586200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,25 +4785,25 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>317.8493745260795</v>
+        <v>323.7186157532602</v>
       </c>
       <c r="C168" t="n">
-        <v>323.90553213234</v>
+        <v>328.3001007904417</v>
       </c>
       <c r="D168" t="n">
-        <v>316.7636501525053</v>
+        <v>323.5988431448615</v>
       </c>
       <c r="E168" t="n">
-        <v>322.5906982421875</v>
+        <v>325.8147277832031</v>
       </c>
       <c r="F168" t="n">
-        <v>9586200</v>
+        <v>6235200</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -4811,25 +4811,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>323.7186157532602</v>
+        <v>323.1895917984963</v>
       </c>
       <c r="C169" t="n">
-        <v>328.3001007904417</v>
+        <v>324.8165740981451</v>
       </c>
       <c r="D169" t="n">
-        <v>323.5988431448615</v>
+        <v>319.2069699014023</v>
       </c>
       <c r="E169" t="n">
-        <v>325.8147277832031</v>
+        <v>319.7160339355469</v>
       </c>
       <c r="F169" t="n">
-        <v>6235200</v>
+        <v>7950400</v>
       </c>
       <c r="G169" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>323.1895917984963</v>
+        <v>320.7740745871976</v>
       </c>
       <c r="C170" t="n">
-        <v>324.8165740981451</v>
+        <v>322.7304316048222</v>
       </c>
       <c r="D170" t="n">
-        <v>319.2069699014023</v>
+        <v>319.6561562914121</v>
       </c>
       <c r="E170" t="n">
-        <v>319.7160339355469</v>
+        <v>321.9219360351562</v>
       </c>
       <c r="F170" t="n">
-        <v>7950400</v>
+        <v>5277400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>320.7740745871976</v>
+        <v>323.3992105807512</v>
       </c>
       <c r="C171" t="n">
-        <v>322.7304316048222</v>
+        <v>328.3999303437295</v>
       </c>
       <c r="D171" t="n">
-        <v>319.6561562914121</v>
+        <v>323.2395036115653</v>
       </c>
       <c r="E171" t="n">
-        <v>321.9219360351562</v>
+        <v>325.1459655761719</v>
       </c>
       <c r="F171" t="n">
-        <v>5277400</v>
+        <v>6054500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>323.3992105807512</v>
+        <v>323.8283954010087</v>
       </c>
       <c r="C172" t="n">
-        <v>328.3999303437295</v>
+        <v>332.8117065140525</v>
       </c>
       <c r="D172" t="n">
-        <v>323.2395036115653</v>
+        <v>323.1696155974001</v>
       </c>
       <c r="E172" t="n">
-        <v>325.1459655761719</v>
+        <v>332.023193359375</v>
       </c>
       <c r="F172" t="n">
-        <v>6054500</v>
+        <v>5305800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>323.8283954010087</v>
+        <v>332.7118894931572</v>
       </c>
       <c r="C173" t="n">
-        <v>332.8117065140525</v>
+        <v>334.5485043686942</v>
       </c>
       <c r="D173" t="n">
-        <v>323.1696155974001</v>
+        <v>328.8790136983196</v>
       </c>
       <c r="E173" t="n">
-        <v>332.023193359375</v>
+        <v>329.2982482910156</v>
       </c>
       <c r="F173" t="n">
-        <v>5305800</v>
+        <v>12858100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>332.7118894931572</v>
+        <v>329.4779084191791</v>
       </c>
       <c r="C174" t="n">
-        <v>334.5485043686942</v>
+        <v>331.0450044691208</v>
       </c>
       <c r="D174" t="n">
-        <v>328.8790136983196</v>
+        <v>326.2139829663294</v>
       </c>
       <c r="E174" t="n">
-        <v>329.2982482910156</v>
+        <v>330.1366882324219</v>
       </c>
       <c r="F174" t="n">
-        <v>12858100</v>
+        <v>9422500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>329.4779084191791</v>
+        <v>329.2283866364193</v>
       </c>
       <c r="C175" t="n">
-        <v>331.0450044691208</v>
+        <v>331.9034099041888</v>
       </c>
       <c r="D175" t="n">
-        <v>326.2139829663294</v>
+        <v>326.6332016248708</v>
       </c>
       <c r="E175" t="n">
-        <v>330.1366882324219</v>
+        <v>330.5060119628906</v>
       </c>
       <c r="F175" t="n">
-        <v>9422500</v>
+        <v>7034500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>329.2283866364193</v>
+        <v>329.9071152744464</v>
       </c>
       <c r="C176" t="n">
-        <v>331.9034099041888</v>
+        <v>332.8117230001985</v>
       </c>
       <c r="D176" t="n">
-        <v>326.6332016248708</v>
+        <v>328.2102858122996</v>
       </c>
       <c r="E176" t="n">
-        <v>330.5060119628906</v>
+        <v>328.2701721191406</v>
       </c>
       <c r="F176" t="n">
-        <v>7034500</v>
+        <v>7462100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>329.9071152744464</v>
+        <v>325.8546513791287</v>
       </c>
       <c r="C177" t="n">
-        <v>332.8117230001985</v>
+        <v>327.890877227978</v>
       </c>
       <c r="D177" t="n">
-        <v>328.2102858122996</v>
+        <v>323.908285453</v>
       </c>
       <c r="E177" t="n">
-        <v>328.2701721191406</v>
+        <v>325.8746337890625</v>
       </c>
       <c r="F177" t="n">
-        <v>7462100</v>
+        <v>8705100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>325.8546513791287</v>
+        <v>325.2258042905605</v>
       </c>
       <c r="C178" t="n">
-        <v>327.890877227978</v>
+        <v>330.8453695289686</v>
       </c>
       <c r="D178" t="n">
-        <v>323.908285453</v>
+        <v>325.0561365774909</v>
       </c>
       <c r="E178" t="n">
-        <v>325.8746337890625</v>
+        <v>327.0025024414062</v>
       </c>
       <c r="F178" t="n">
-        <v>8705100</v>
+        <v>5917400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>325.2258042905605</v>
+        <v>325.4054745838858</v>
       </c>
       <c r="C179" t="n">
-        <v>330.8453695289686</v>
+        <v>326.473467283892</v>
       </c>
       <c r="D179" t="n">
-        <v>325.0561365774909</v>
+        <v>320.304934449476</v>
       </c>
       <c r="E179" t="n">
-        <v>327.0025024414062</v>
+        <v>324.3474426269531</v>
       </c>
       <c r="F179" t="n">
-        <v>5917400</v>
+        <v>8105400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>325.4054745838858</v>
+        <v>324.8964310814758</v>
       </c>
       <c r="C180" t="n">
-        <v>326.473467283892</v>
+        <v>331.0550035619541</v>
       </c>
       <c r="D180" t="n">
-        <v>320.304934449476</v>
+        <v>324.7467153160326</v>
       </c>
       <c r="E180" t="n">
-        <v>324.3474426269531</v>
+        <v>325.7548217773438</v>
       </c>
       <c r="F180" t="n">
-        <v>8105400</v>
+        <v>14104500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>324.8964310814758</v>
+        <v>326.6531732008884</v>
       </c>
       <c r="C181" t="n">
-        <v>331.0550035619541</v>
+        <v>327.2520362551611</v>
       </c>
       <c r="D181" t="n">
-        <v>324.7467153160326</v>
+        <v>318.0890659929148</v>
       </c>
       <c r="E181" t="n">
-        <v>325.7548217773438</v>
+        <v>322.1714782714844</v>
       </c>
       <c r="F181" t="n">
-        <v>14104500</v>
+        <v>10079300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>326.6531732008884</v>
+        <v>321.911976472278</v>
       </c>
       <c r="C182" t="n">
-        <v>327.2520362551611</v>
+        <v>322.900130958607</v>
       </c>
       <c r="D182" t="n">
-        <v>318.0890659929148</v>
+        <v>312.8088926463686</v>
       </c>
       <c r="E182" t="n">
-        <v>322.1714782714844</v>
+        <v>316.7315979003906</v>
       </c>
       <c r="F182" t="n">
-        <v>10079300</v>
+        <v>10125300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>321.911976472278</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="C183" t="n">
-        <v>322.900130958607</v>
+        <v>317.0609741306723</v>
       </c>
       <c r="D183" t="n">
-        <v>312.8088926463686</v>
+        <v>308.4270199555073</v>
       </c>
       <c r="E183" t="n">
-        <v>316.7315979003906</v>
+        <v>311.8207092285156</v>
       </c>
       <c r="F183" t="n">
-        <v>10125300</v>
+        <v>8992800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>317.0609741306723</v>
+        <v>316.2025752130079</v>
       </c>
       <c r="C184" t="n">
-        <v>317.0609741306723</v>
+        <v>324.1577974184449</v>
       </c>
       <c r="D184" t="n">
-        <v>308.4270199555073</v>
+        <v>316.1127457580593</v>
       </c>
       <c r="E184" t="n">
-        <v>311.8207092285156</v>
+        <v>319.5862731933594</v>
       </c>
       <c r="F184" t="n">
-        <v>8992800</v>
+        <v>6981700</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>316.2025752130079</v>
+        <v>321.8021573858913</v>
       </c>
       <c r="C185" t="n">
-        <v>324.1577974184449</v>
+        <v>325.3755359367605</v>
       </c>
       <c r="D185" t="n">
-        <v>316.1127457580593</v>
+        <v>320.3748163907789</v>
       </c>
       <c r="E185" t="n">
-        <v>319.5862731933594</v>
+        <v>322.9700012207031</v>
       </c>
       <c r="F185" t="n">
-        <v>6981700</v>
+        <v>7176300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>321.8021573858913</v>
+        <v>320.7541174065557</v>
       </c>
       <c r="C186" t="n">
-        <v>325.3755359367605</v>
+        <v>323.3193590911711</v>
       </c>
       <c r="D186" t="n">
-        <v>320.3748163907789</v>
+        <v>317.8395186449595</v>
       </c>
       <c r="E186" t="n">
-        <v>322.9700012207031</v>
+        <v>319.0772399902344</v>
       </c>
       <c r="F186" t="n">
-        <v>7176300</v>
+        <v>5582000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>320.7541174065557</v>
+        <v>318.0691001697331</v>
       </c>
       <c r="C187" t="n">
-        <v>323.3193590911711</v>
+        <v>324.8864216353897</v>
       </c>
       <c r="D187" t="n">
-        <v>317.8395186449595</v>
+        <v>316.4121747162161</v>
       </c>
       <c r="E187" t="n">
-        <v>319.0772399902344</v>
+        <v>324.4472351074219</v>
       </c>
       <c r="F187" t="n">
-        <v>5582000</v>
+        <v>6340400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>318.0691001697331</v>
+        <v>326.0143312805488</v>
       </c>
       <c r="C188" t="n">
-        <v>324.8864216353897</v>
+        <v>326.2938108474966</v>
       </c>
       <c r="D188" t="n">
-        <v>316.4121747162161</v>
+        <v>319.5862707797614</v>
       </c>
       <c r="E188" t="n">
-        <v>324.4472351074219</v>
+        <v>322.3611145019531</v>
       </c>
       <c r="F188" t="n">
-        <v>6340400</v>
+        <v>5793100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>326.0143312805488</v>
+        <v>321.4029160285921</v>
       </c>
       <c r="C189" t="n">
-        <v>326.2938108474966</v>
+        <v>323.1097366498532</v>
       </c>
       <c r="D189" t="n">
-        <v>319.5862707797614</v>
+        <v>317.3703988636284</v>
       </c>
       <c r="E189" t="n">
-        <v>322.3611145019531</v>
+        <v>318.4583740234375</v>
       </c>
       <c r="F189" t="n">
-        <v>5793100</v>
+        <v>5958900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>321.4029160285921</v>
+        <v>321.1633691478087</v>
       </c>
       <c r="C190" t="n">
-        <v>323.1097366498532</v>
+        <v>325.3256196452838</v>
       </c>
       <c r="D190" t="n">
-        <v>317.3703988636284</v>
+        <v>319.206981650181</v>
       </c>
       <c r="E190" t="n">
-        <v>318.4583740234375</v>
+        <v>321.7922058105469</v>
       </c>
       <c r="F190" t="n">
-        <v>5958900</v>
+        <v>5543200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>321.1633691478087</v>
+        <v>322.7603745094088</v>
       </c>
       <c r="C191" t="n">
-        <v>325.3256196452838</v>
+        <v>325.8346802814496</v>
       </c>
       <c r="D191" t="n">
-        <v>319.206981650181</v>
+        <v>322.1515202620241</v>
       </c>
       <c r="E191" t="n">
-        <v>321.7922058105469</v>
+        <v>323.2195434570312</v>
       </c>
       <c r="F191" t="n">
-        <v>5543200</v>
+        <v>6803000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>322.7603745094088</v>
+        <v>325.0860736201939</v>
       </c>
       <c r="C192" t="n">
-        <v>325.8346802814496</v>
+        <v>332.6719869892291</v>
       </c>
       <c r="D192" t="n">
-        <v>322.1515202620241</v>
+        <v>323.7785051975129</v>
       </c>
       <c r="E192" t="n">
-        <v>323.2195434570312</v>
+        <v>332.5022888183594</v>
       </c>
       <c r="F192" t="n">
-        <v>6803000</v>
+        <v>9248400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>325.0860736201939</v>
+        <v>332.8816048599044</v>
       </c>
       <c r="C193" t="n">
-        <v>332.6719869892291</v>
+        <v>336.1954560330155</v>
       </c>
       <c r="D193" t="n">
-        <v>323.7785051975129</v>
+        <v>329.3581516101117</v>
       </c>
       <c r="E193" t="n">
-        <v>332.5022888183594</v>
+        <v>329.7673950195312</v>
       </c>
       <c r="F193" t="n">
-        <v>9248400</v>
+        <v>6895200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>332.8816048599044</v>
+        <v>330.3862161708477</v>
       </c>
       <c r="C194" t="n">
-        <v>336.1954560330155</v>
+        <v>331.7137365067053</v>
       </c>
       <c r="D194" t="n">
-        <v>329.3581516101117</v>
+        <v>326.3936334980882</v>
       </c>
       <c r="E194" t="n">
-        <v>329.7673950195312</v>
+        <v>326.6331787109375</v>
       </c>
       <c r="F194" t="n">
-        <v>6895200</v>
+        <v>14716700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>330.3862161708477</v>
+        <v>327.7211572947962</v>
       </c>
       <c r="C195" t="n">
-        <v>331.7137365067053</v>
+        <v>332.3825110173034</v>
       </c>
       <c r="D195" t="n">
-        <v>326.3936334980882</v>
+        <v>325.255736249892</v>
       </c>
       <c r="E195" t="n">
-        <v>326.6331787109375</v>
+        <v>325.994384765625</v>
       </c>
       <c r="F195" t="n">
-        <v>14716700</v>
+        <v>15132400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>327.7211572947962</v>
+        <v>328.2102765273601</v>
       </c>
       <c r="C196" t="n">
-        <v>332.3825110173034</v>
+        <v>330.6657064213508</v>
       </c>
       <c r="D196" t="n">
-        <v>325.255736249892</v>
+        <v>327.4816192000871</v>
       </c>
       <c r="E196" t="n">
-        <v>325.994384765625</v>
+        <v>327.8709106445312</v>
       </c>
       <c r="F196" t="n">
-        <v>15132400</v>
+        <v>11113400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>328.2102765273601</v>
+        <v>328.3899311009871</v>
       </c>
       <c r="C197" t="n">
-        <v>330.6657064213508</v>
+        <v>334.1791639025663</v>
       </c>
       <c r="D197" t="n">
-        <v>327.4816192000871</v>
+        <v>326.6132329961447</v>
       </c>
       <c r="E197" t="n">
-        <v>327.8709106445312</v>
+        <v>331.6139526367188</v>
       </c>
       <c r="F197" t="n">
-        <v>11113400</v>
+        <v>8197200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>328.3899311009871</v>
+        <v>331.9433302412046</v>
       </c>
       <c r="C198" t="n">
-        <v>334.1791639025663</v>
+        <v>339.3096503518051</v>
       </c>
       <c r="D198" t="n">
-        <v>326.6132329961447</v>
+        <v>329.457957205559</v>
       </c>
       <c r="E198" t="n">
-        <v>331.6139526367188</v>
+        <v>329.9071044921875</v>
       </c>
       <c r="F198" t="n">
-        <v>8197200</v>
+        <v>7050200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>331.9433302412046</v>
+        <v>331.6239148421282</v>
       </c>
       <c r="C199" t="n">
-        <v>339.3096503518051</v>
+        <v>339.0900555815327</v>
       </c>
       <c r="D199" t="n">
-        <v>329.457957205559</v>
+        <v>330.8254104732138</v>
       </c>
       <c r="E199" t="n">
-        <v>329.9071044921875</v>
+        <v>335.6065368652344</v>
       </c>
       <c r="F199" t="n">
-        <v>7050200</v>
+        <v>16717400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>331.6239148421282</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="C200" t="n">
-        <v>339.0900555815327</v>
+        <v>345.168769346924</v>
       </c>
       <c r="D200" t="n">
-        <v>330.8254104732138</v>
+        <v>337.6427420814022</v>
       </c>
       <c r="E200" t="n">
-        <v>335.6065368652344</v>
+        <v>341.0164794921875</v>
       </c>
       <c r="F200" t="n">
-        <v>16717400</v>
+        <v>11710900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>337.6427420814022</v>
+        <v>341.1262760402287</v>
       </c>
       <c r="C201" t="n">
-        <v>345.168769346924</v>
+        <v>343.6515833825353</v>
       </c>
       <c r="D201" t="n">
-        <v>337.6427420814022</v>
+        <v>338.4512224777037</v>
       </c>
       <c r="E201" t="n">
-        <v>341.0164794921875</v>
+        <v>342.4537963867188</v>
       </c>
       <c r="F201" t="n">
-        <v>11710900</v>
+        <v>7957900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>341.1262760402287</v>
+        <v>343.9210864742992</v>
       </c>
       <c r="C202" t="n">
-        <v>343.6515833825353</v>
+        <v>352.7047566164018</v>
       </c>
       <c r="D202" t="n">
-        <v>338.4512224777037</v>
+        <v>340.3477382034001</v>
       </c>
       <c r="E202" t="n">
-        <v>342.4537963867188</v>
+        <v>350.4289855957031</v>
       </c>
       <c r="F202" t="n">
-        <v>7957900</v>
+        <v>13025900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>343.9210864742992</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="C203" t="n">
-        <v>352.7047566164018</v>
+        <v>361.45849609375</v>
       </c>
       <c r="D203" t="n">
-        <v>340.3477382034001</v>
+        <v>351.8563396289383</v>
       </c>
       <c r="E203" t="n">
-        <v>350.4289855957031</v>
+        <v>361.45849609375</v>
       </c>
       <c r="F203" t="n">
-        <v>13025900</v>
+        <v>9814800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>351.8563396289383</v>
+        <v>362.3268927646901</v>
       </c>
       <c r="C204" t="n">
-        <v>361.45849609375</v>
+        <v>364.3431361331269</v>
       </c>
       <c r="D204" t="n">
-        <v>351.8563396289383</v>
+        <v>348.2031370590358</v>
       </c>
       <c r="E204" t="n">
-        <v>361.45849609375</v>
+        <v>356.5875549316406</v>
       </c>
       <c r="F204" t="n">
-        <v>9814800</v>
+        <v>11623800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>362.3268927646901</v>
+        <v>347.744003265132</v>
       </c>
       <c r="C205" t="n">
-        <v>364.3431361331269</v>
+        <v>355.4197158554798</v>
       </c>
       <c r="D205" t="n">
-        <v>348.2031370590358</v>
+        <v>346.2767278330053</v>
       </c>
       <c r="E205" t="n">
-        <v>356.5875549316406</v>
+        <v>351.5469360351562</v>
       </c>
       <c r="F205" t="n">
-        <v>11623800</v>
+        <v>7332500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>347.744003265132</v>
+        <v>349.650411586948</v>
       </c>
       <c r="C206" t="n">
-        <v>355.4197158554798</v>
+        <v>350.9480192181019</v>
       </c>
       <c r="D206" t="n">
-        <v>346.2767278330053</v>
+        <v>345.0489747278172</v>
       </c>
       <c r="E206" t="n">
-        <v>351.5469360351562</v>
+        <v>346.8855590820312</v>
       </c>
       <c r="F206" t="n">
-        <v>7332500</v>
+        <v>10215200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>349.650411586948</v>
+        <v>344.6597048505295</v>
       </c>
       <c r="C207" t="n">
-        <v>350.9480192181019</v>
+        <v>347.8537833381742</v>
       </c>
       <c r="D207" t="n">
-        <v>345.0489747278172</v>
+        <v>343.7813622043677</v>
       </c>
       <c r="E207" t="n">
-        <v>346.8855590820312</v>
+        <v>347.5543518066406</v>
       </c>
       <c r="F207" t="n">
-        <v>10215200</v>
+        <v>6606300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>344.6597048505295</v>
+        <v>349.9798320131086</v>
       </c>
       <c r="C208" t="n">
-        <v>347.8537833381742</v>
+        <v>350.5188392207221</v>
       </c>
       <c r="D208" t="n">
-        <v>343.7813622043677</v>
+        <v>344.6896415212494</v>
       </c>
       <c r="E208" t="n">
-        <v>347.5543518066406</v>
+        <v>348.3229064941406</v>
       </c>
       <c r="F208" t="n">
-        <v>6606300</v>
+        <v>4702800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>349.9798320131086</v>
+        <v>351.0777829959364</v>
       </c>
       <c r="C209" t="n">
-        <v>350.5188392207221</v>
+        <v>358.8233725828445</v>
       </c>
       <c r="D209" t="n">
-        <v>344.6896415212494</v>
+        <v>350.3990207986449</v>
       </c>
       <c r="E209" t="n">
-        <v>348.3229064941406</v>
+        <v>357.0866088867188</v>
       </c>
       <c r="F209" t="n">
-        <v>4702800</v>
+        <v>9964600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>351.0777829959364</v>
+        <v>355.1102963305153</v>
       </c>
       <c r="C210" t="n">
-        <v>358.8233725828445</v>
+        <v>359.2725774384029</v>
       </c>
       <c r="D210" t="n">
-        <v>350.3990207986449</v>
+        <v>353.0241754046451</v>
       </c>
       <c r="E210" t="n">
-        <v>357.0866088867188</v>
+        <v>355.3598327636719</v>
       </c>
       <c r="F210" t="n">
-        <v>9964600</v>
+        <v>6632400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>355.1102963305153</v>
+        <v>353.3435751194357</v>
       </c>
       <c r="C211" t="n">
-        <v>359.2725774384029</v>
+        <v>359.7616446111089</v>
       </c>
       <c r="D211" t="n">
-        <v>353.0241754046451</v>
+        <v>348.4726192666298</v>
       </c>
       <c r="E211" t="n">
-        <v>355.3598327636719</v>
+        <v>354.4814758300781</v>
       </c>
       <c r="F211" t="n">
-        <v>6632400</v>
+        <v>8850000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>353.3435751194357</v>
+        <v>357.3760808599296</v>
       </c>
       <c r="C212" t="n">
-        <v>359.7616446111089</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="D212" t="n">
-        <v>348.4726192666298</v>
+        <v>356.4477822451955</v>
       </c>
       <c r="E212" t="n">
-        <v>354.4814758300781</v>
+        <v>364.4629211425781</v>
       </c>
       <c r="F212" t="n">
-        <v>8850000</v>
+        <v>9073200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>357.3760808599296</v>
+        <v>362.8958306673428</v>
       </c>
       <c r="C213" t="n">
-        <v>364.4629211425781</v>
+        <v>363.9538626468295</v>
       </c>
       <c r="D213" t="n">
-        <v>356.4477822451955</v>
+        <v>356.3380062665893</v>
       </c>
       <c r="E213" t="n">
-        <v>364.4629211425781</v>
+        <v>357.8951110839844</v>
       </c>
       <c r="F213" t="n">
-        <v>9073200</v>
+        <v>7400400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>362.8958306673428</v>
+        <v>356.4378309524324</v>
       </c>
       <c r="C214" t="n">
-        <v>363.9538626468295</v>
+        <v>362.3268844140721</v>
       </c>
       <c r="D214" t="n">
-        <v>356.3380062665893</v>
+        <v>355.7690599392462</v>
       </c>
       <c r="E214" t="n">
-        <v>357.8951110839844</v>
+        <v>359.9013977050781</v>
       </c>
       <c r="F214" t="n">
-        <v>7400400</v>
+        <v>7616800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>356.4378309524324</v>
+        <v>356.3280307190208</v>
       </c>
       <c r="C215" t="n">
-        <v>362.3268844140721</v>
+        <v>358.4540859756855</v>
       </c>
       <c r="D215" t="n">
-        <v>355.7690599392462</v>
+        <v>354.0323077481659</v>
       </c>
       <c r="E215" t="n">
-        <v>359.9013977050781</v>
+        <v>355.1602172851562</v>
       </c>
       <c r="F215" t="n">
-        <v>7616800</v>
+        <v>6027300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>356.3280307190208</v>
+        <v>355.9088319271366</v>
       </c>
       <c r="C216" t="n">
-        <v>358.4540859756855</v>
+        <v>356.8670433033565</v>
       </c>
       <c r="D216" t="n">
-        <v>354.0323077481659</v>
+        <v>351.6167869913984</v>
       </c>
       <c r="E216" t="n">
-        <v>355.1602172851562</v>
+        <v>352.7646789550781</v>
       </c>
       <c r="F216" t="n">
-        <v>6027300</v>
+        <v>4622200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>355.9088319271366</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="C217" t="n">
-        <v>356.8670433033565</v>
+        <v>351.3971758456315</v>
       </c>
       <c r="D217" t="n">
-        <v>351.6167869913984</v>
+        <v>347.8537708520506</v>
       </c>
       <c r="E217" t="n">
-        <v>352.7646789550781</v>
+        <v>350.9480285644531</v>
       </c>
       <c r="F217" t="n">
-        <v>4622200</v>
+        <v>4183300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>351.3971758456315</v>
+        <v>352.8145729386106</v>
       </c>
       <c r="C218" t="n">
-        <v>351.3971758456315</v>
+        <v>355.1801734485531</v>
       </c>
       <c r="D218" t="n">
-        <v>347.8537708520506</v>
+        <v>350.3990468654978</v>
       </c>
       <c r="E218" t="n">
-        <v>350.9480285644531</v>
+        <v>355.0803527832031</v>
       </c>
       <c r="F218" t="n">
-        <v>4183300</v>
+        <v>4482800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>352.8145729386106</v>
+        <v>358.6836615690858</v>
       </c>
       <c r="C219" t="n">
-        <v>355.1801734485531</v>
+        <v>362.9856670774005</v>
       </c>
       <c r="D219" t="n">
-        <v>350.3990468654978</v>
+        <v>357.5856952124533</v>
       </c>
       <c r="E219" t="n">
-        <v>355.0803527832031</v>
+        <v>361.8577575683594</v>
       </c>
       <c r="F219" t="n">
-        <v>4482800</v>
+        <v>6631100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>358.6836615690858</v>
+        <v>364.3830556294341</v>
       </c>
       <c r="C220" t="n">
-        <v>362.9856670774005</v>
+        <v>370.4717503048907</v>
       </c>
       <c r="D220" t="n">
-        <v>357.5856952124533</v>
+        <v>362.057389622598</v>
       </c>
       <c r="E220" t="n">
-        <v>361.8577575683594</v>
+        <v>365.9102172851562</v>
       </c>
       <c r="F220" t="n">
-        <v>6631100</v>
+        <v>11061900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>364.3830556294341</v>
+        <v>356.3380049484608</v>
       </c>
       <c r="C221" t="n">
-        <v>370.4717503048907</v>
+        <v>373.2765382228537</v>
       </c>
       <c r="D221" t="n">
-        <v>362.057389622598</v>
+        <v>354.8208344927874</v>
       </c>
       <c r="E221" t="n">
-        <v>365.9102172851562</v>
+        <v>368.0462646484375</v>
       </c>
       <c r="F221" t="n">
-        <v>11061900</v>
+        <v>11289900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>356.3380049484608</v>
+        <v>364.3231862195555</v>
       </c>
       <c r="C222" t="n">
-        <v>373.2765382228537</v>
+        <v>366.3194776508955</v>
       </c>
       <c r="D222" t="n">
-        <v>354.8208344927874</v>
+        <v>360.0810669279579</v>
       </c>
       <c r="E222" t="n">
-        <v>368.0462646484375</v>
+        <v>365.5908203125</v>
       </c>
       <c r="F222" t="n">
-        <v>11289900</v>
+        <v>8391400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>364.3231862195555</v>
+        <v>363.0854799497644</v>
       </c>
       <c r="C223" t="n">
-        <v>366.3194776508955</v>
+        <v>366.199689577411</v>
       </c>
       <c r="D223" t="n">
-        <v>360.0810669279579</v>
+        <v>359.4322631293363</v>
       </c>
       <c r="E223" t="n">
-        <v>365.5908203125</v>
+        <v>365.4510803222656</v>
       </c>
       <c r="F223" t="n">
-        <v>8391400</v>
+        <v>7828400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>363.0854799497644</v>
+        <v>367.8166822243689</v>
       </c>
       <c r="C224" t="n">
-        <v>366.199689577411</v>
+        <v>371.2802489443513</v>
       </c>
       <c r="D224" t="n">
-        <v>359.4322631293363</v>
+        <v>363.6743837542027</v>
       </c>
       <c r="E224" t="n">
-        <v>365.4510803222656</v>
+        <v>364.991943359375</v>
       </c>
       <c r="F224" t="n">
-        <v>7828400</v>
+        <v>5521300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>367.8166822243689</v>
+        <v>361.0891957111975</v>
       </c>
       <c r="C225" t="n">
-        <v>371.2802489443513</v>
+        <v>370.4218335736103</v>
       </c>
       <c r="D225" t="n">
-        <v>363.6743837542027</v>
+        <v>359.4222790007568</v>
       </c>
       <c r="E225" t="n">
-        <v>364.991943359375</v>
+        <v>368.9046630859375</v>
       </c>
       <c r="F225" t="n">
-        <v>5521300</v>
+        <v>7497500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>361.0891957111975</v>
+        <v>371.6096355733356</v>
       </c>
       <c r="C226" t="n">
-        <v>370.4218335736103</v>
+        <v>371.7094562365133</v>
       </c>
       <c r="D226" t="n">
-        <v>359.4222790007568</v>
+        <v>366.0399959154992</v>
       </c>
       <c r="E226" t="n">
-        <v>368.9046630859375</v>
+        <v>367.8566284179688</v>
       </c>
       <c r="F226" t="n">
-        <v>7497500</v>
+        <v>6065300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>371.6096355733356</v>
+        <v>368.8847254705448</v>
       </c>
       <c r="C227" t="n">
-        <v>371.7094562365133</v>
+        <v>370.4118872220017</v>
       </c>
       <c r="D227" t="n">
-        <v>366.0399959154992</v>
+        <v>364.5727285978463</v>
       </c>
       <c r="E227" t="n">
-        <v>367.8566284179688</v>
+        <v>369.7830505371094</v>
       </c>
       <c r="F227" t="n">
-        <v>6065300</v>
+        <v>5022300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>368.8847254705448</v>
+        <v>367.8266852879935</v>
       </c>
       <c r="C228" t="n">
-        <v>370.4118872220017</v>
+        <v>369.5634490756331</v>
       </c>
       <c r="D228" t="n">
-        <v>364.5727285978463</v>
+        <v>360.8496260625997</v>
       </c>
       <c r="E228" t="n">
-        <v>369.7830505371094</v>
+        <v>361.8278198242188</v>
       </c>
       <c r="F228" t="n">
-        <v>5022300</v>
+        <v>5112500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>367.8266852879935</v>
+        <v>361.3287562034755</v>
       </c>
       <c r="C229" t="n">
-        <v>369.5634490756331</v>
+        <v>363.4947458520614</v>
       </c>
       <c r="D229" t="n">
-        <v>360.8496260625997</v>
+        <v>358.2045551780129</v>
       </c>
       <c r="E229" t="n">
-        <v>361.8278198242188</v>
+        <v>360.6500244140625</v>
       </c>
       <c r="F229" t="n">
-        <v>5112500</v>
+        <v>7552200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,25 +6397,25 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>361.3287562034755</v>
+        <v>360.9800109863281</v>
       </c>
       <c r="C230" t="n">
-        <v>363.4947458520614</v>
+        <v>364.5499877929688</v>
       </c>
       <c r="D230" t="n">
-        <v>358.2045551780129</v>
+        <v>359.9700012207031</v>
       </c>
       <c r="E230" t="n">
-        <v>360.6500244140625</v>
+        <v>362.8200073242188</v>
       </c>
       <c r="F230" t="n">
-        <v>7552200</v>
+        <v>4440900</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -6423,25 +6423,25 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>360.9800109863281</v>
+        <v>361</v>
       </c>
       <c r="C231" t="n">
-        <v>364.5499877929688</v>
+        <v>363.3500061035156</v>
       </c>
       <c r="D231" t="n">
-        <v>359.9700012207031</v>
+        <v>358.3099975585938</v>
       </c>
       <c r="E231" t="n">
-        <v>362.8200073242188</v>
+        <v>359.4200134277344</v>
       </c>
       <c r="F231" t="n">
-        <v>4440900</v>
+        <v>3794200</v>
       </c>
       <c r="G231" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>361</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="C232" t="n">
-        <v>363.3500061035156</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="D232" t="n">
-        <v>358.3099975585938</v>
+        <v>358.7099914550781</v>
       </c>
       <c r="E232" t="n">
-        <v>359.4200134277344</v>
+        <v>365.4500122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>3794200</v>
+        <v>8142600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>363.7000122070312</v>
+        <v>365.8900146484375</v>
       </c>
       <c r="C233" t="n">
-        <v>365.4500122070312</v>
+        <v>366.7999877929688</v>
       </c>
       <c r="D233" t="n">
-        <v>358.7099914550781</v>
+        <v>362.760009765625</v>
       </c>
       <c r="E233" t="n">
-        <v>365.4500122070312</v>
+        <v>364.1499938964844</v>
       </c>
       <c r="F233" t="n">
-        <v>8142600</v>
+        <v>8106900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>365.8900146484375</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="C234" t="n">
-        <v>366.7999877929688</v>
+        <v>363.5599975585938</v>
       </c>
       <c r="D234" t="n">
-        <v>362.760009765625</v>
+        <v>358.5199890136719</v>
       </c>
       <c r="E234" t="n">
-        <v>364.1499938964844</v>
+        <v>358.8399963378906</v>
       </c>
       <c r="F234" t="n">
-        <v>8106900</v>
+        <v>15543400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>362.8399963378906</v>
+        <v>359.6199951171875</v>
       </c>
       <c r="C235" t="n">
-        <v>363.5599975585938</v>
+        <v>365.9100036621094</v>
       </c>
       <c r="D235" t="n">
-        <v>358.5199890136719</v>
+        <v>358.0499877929688</v>
       </c>
       <c r="E235" t="n">
-        <v>358.8399963378906</v>
+        <v>364.25</v>
       </c>
       <c r="F235" t="n">
-        <v>15543400</v>
+        <v>6820300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>359.6199951171875</v>
+        <v>364.0899963378906</v>
       </c>
       <c r="C236" t="n">
-        <v>365.9100036621094</v>
+        <v>370.6400146484375</v>
       </c>
       <c r="D236" t="n">
-        <v>358.0499877929688</v>
+        <v>362.8999938964844</v>
       </c>
       <c r="E236" t="n">
-        <v>364.25</v>
+        <v>365.5400085449219</v>
       </c>
       <c r="F236" t="n">
-        <v>6820300</v>
+        <v>5866400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>364.0899963378906</v>
+        <v>365.1000061035156</v>
       </c>
       <c r="C237" t="n">
-        <v>370.6400146484375</v>
+        <v>368.9299926757812</v>
       </c>
       <c r="D237" t="n">
-        <v>362.8999938964844</v>
+        <v>363.6300048828125</v>
       </c>
       <c r="E237" t="n">
-        <v>365.5400085449219</v>
+        <v>365.7300109863281</v>
       </c>
       <c r="F237" t="n">
-        <v>5866400</v>
+        <v>6151500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>365.1000061035156</v>
+        <v>367.8699951171875</v>
       </c>
       <c r="C238" t="n">
-        <v>368.9299926757812</v>
+        <v>371.7999877929688</v>
       </c>
       <c r="D238" t="n">
-        <v>363.6300048828125</v>
+        <v>366.6600036621094</v>
       </c>
       <c r="E238" t="n">
-        <v>365.7300109863281</v>
+        <v>371.0400085449219</v>
       </c>
       <c r="F238" t="n">
-        <v>6151500</v>
+        <v>6667100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>367.8699951171875</v>
+        <v>373.260009765625</v>
       </c>
       <c r="C239" t="n">
-        <v>371.7999877929688</v>
+        <v>383.4299926757812</v>
       </c>
       <c r="D239" t="n">
-        <v>366.6600036621094</v>
+        <v>372.2099914550781</v>
       </c>
       <c r="E239" t="n">
-        <v>371.0400085449219</v>
+        <v>382.4100036621094</v>
       </c>
       <c r="F239" t="n">
-        <v>6667100</v>
+        <v>8477500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>373.260009765625</v>
+        <v>381.2099914550781</v>
       </c>
       <c r="C240" t="n">
-        <v>383.4299926757812</v>
+        <v>384.2000122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>372.2099914550781</v>
+        <v>380.2699890136719</v>
       </c>
       <c r="E240" t="n">
-        <v>382.4100036621094</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="F240" t="n">
-        <v>8477500</v>
+        <v>6777600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>381.2099914550781</v>
+        <v>384.1400146484375</v>
       </c>
       <c r="C241" t="n">
-        <v>384.2000122070312</v>
+        <v>385.5700073242188</v>
       </c>
       <c r="D241" t="n">
-        <v>380.2699890136719</v>
+        <v>381.0799865722656</v>
       </c>
       <c r="E241" t="n">
-        <v>384.1400146484375</v>
+        <v>383.8999938964844</v>
       </c>
       <c r="F241" t="n">
-        <v>6777600</v>
+        <v>6075100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>384.1400146484375</v>
+        <v>381.1400146484375</v>
       </c>
       <c r="C242" t="n">
-        <v>385.5700073242188</v>
+        <v>381.7699890136719</v>
       </c>
       <c r="D242" t="n">
-        <v>381.0799865722656</v>
+        <v>378.5</v>
       </c>
       <c r="E242" t="n">
-        <v>383.8999938964844</v>
+        <v>379.6600036621094</v>
       </c>
       <c r="F242" t="n">
-        <v>6075100</v>
+        <v>6641500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>381.1400146484375</v>
+        <v>380.2999877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>381.7699890136719</v>
+        <v>383.6799926757812</v>
       </c>
       <c r="D243" t="n">
-        <v>378.5</v>
+        <v>379.0299987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>379.6600036621094</v>
+        <v>381.6000061035156</v>
       </c>
       <c r="F243" t="n">
-        <v>6641500</v>
+        <v>4643000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>380.2999877929688</v>
+        <v>381.3500061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>383.6799926757812</v>
+        <v>382.4800109863281</v>
       </c>
       <c r="D244" t="n">
-        <v>379.0299987792969</v>
+        <v>378.7999877929688</v>
       </c>
       <c r="E244" t="n">
-        <v>381.6000061035156</v>
+        <v>379.3699951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>4643000</v>
+        <v>6744800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>381.3500061035156</v>
+        <v>379.6499938964844</v>
       </c>
       <c r="C245" t="n">
-        <v>382.4800109863281</v>
+        <v>380.75</v>
       </c>
       <c r="D245" t="n">
-        <v>378.7999877929688</v>
+        <v>372.2200012207031</v>
       </c>
       <c r="E245" t="n">
-        <v>379.3699951171875</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="F245" t="n">
-        <v>6744800</v>
+        <v>5857400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>379.6499938964844</v>
+        <v>374.010009765625</v>
       </c>
       <c r="C246" t="n">
-        <v>380.75</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="D246" t="n">
-        <v>372.2200012207031</v>
+        <v>374.010009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>372.6700134277344</v>
+        <v>378.3999938964844</v>
       </c>
       <c r="F246" t="n">
-        <v>5857400</v>
+        <v>5599900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>374.010009765625</v>
+        <v>380.1700134277344</v>
       </c>
       <c r="C247" t="n">
-        <v>380.1700134277344</v>
+        <v>382.2099914550781</v>
       </c>
       <c r="D247" t="n">
-        <v>374.010009765625</v>
+        <v>376.8599853515625</v>
       </c>
       <c r="E247" t="n">
-        <v>378.3999938964844</v>
+        <v>378.75</v>
       </c>
       <c r="F247" t="n">
-        <v>5599900</v>
+        <v>3869500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>380.1700134277344</v>
+        <v>374.8900146484375</v>
       </c>
       <c r="C248" t="n">
-        <v>382.2099914550781</v>
+        <v>377.5</v>
       </c>
       <c r="D248" t="n">
-        <v>376.8599853515625</v>
+        <v>373.6400146484375</v>
       </c>
       <c r="E248" t="n">
-        <v>378.75</v>
+        <v>375.0700073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>3869500</v>
+        <v>4645100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>374.8900146484375</v>
+        <v>371.6000061035156</v>
       </c>
       <c r="C249" t="n">
-        <v>377.5</v>
+        <v>373.5</v>
       </c>
       <c r="D249" t="n">
-        <v>373.6400146484375</v>
+        <v>367.4400024414062</v>
       </c>
       <c r="E249" t="n">
-        <v>375.0700073242188</v>
+        <v>368.6400146484375</v>
       </c>
       <c r="F249" t="n">
-        <v>4645100</v>
+        <v>4929000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>371.6000061035156</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>373.5</v>
+        <v>369.4800109863281</v>
       </c>
       <c r="D250" t="n">
-        <v>367.4400024414062</v>
+        <v>365.8800048828125</v>
       </c>
       <c r="E250" t="n">
-        <v>368.6400146484375</v>
+        <v>367.3900146484375</v>
       </c>
       <c r="F250" t="n">
-        <v>4929000</v>
+        <v>4479800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>368.4500122070312</v>
+        <v>366.3999938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>369.4800109863281</v>
+        <v>368</v>
       </c>
       <c r="D251" t="n">
-        <v>365.8800048828125</v>
+        <v>365.5199890136719</v>
       </c>
       <c r="E251" t="n">
-        <v>367.3900146484375</v>
+        <v>367.2099914550781</v>
       </c>
       <c r="F251" t="n">
-        <v>4479800</v>
+        <v>3800200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>366.3999938964844</v>
+        <v>368.9200134277344</v>
       </c>
       <c r="C252" t="n">
-        <v>368</v>
+        <v>371.8099975585938</v>
       </c>
       <c r="D252" t="n">
-        <v>365.5199890136719</v>
+        <v>367.9800109863281</v>
       </c>
       <c r="E252" t="n">
-        <v>367.2099914550781</v>
+        <v>370.4500122070312</v>
       </c>
       <c r="F252" t="n">
-        <v>3800200</v>
+        <v>3492700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10656,37 +10656,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="D2" t="n">
         <v>367.21</v>
       </c>
-      <c r="D2" t="n">
-        <v>367.39</v>
-      </c>
       <c r="E2" t="n">
-        <v>366.4</v>
+        <v>368.92</v>
       </c>
       <c r="F2" t="n">
+        <v>371.8125</v>
+      </c>
+      <c r="G2" t="n">
         <v>367.98</v>
       </c>
-      <c r="G2" t="n">
-        <v>365.52</v>
-      </c>
       <c r="H2" t="n">
-        <v>3742141</v>
+        <v>3490928</v>
       </c>
       <c r="I2" t="n">
-        <v>7696844</v>
+        <v>7600922</v>
       </c>
       <c r="J2" t="n">
-        <v>685598441472</v>
+        <v>691647676416</v>
       </c>
       <c r="K2" t="n">
-        <v>31.251915</v>
+        <v>31.554516</v>
       </c>
       <c r="L2" t="n">
-        <v>24.47365</v>
+        <v>24.68959</v>
       </c>
       <c r="M2" t="n">
-        <v>11.75</v>
+        <v>11.74</v>
       </c>
       <c r="N2" t="n">
         <v>385.57</v>
@@ -10698,7 +10698,7 @@
         <v>0.761</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="R2" t="n">
         <v>0.50782</v>
@@ -10722,7 +10722,7 @@
         <v>18.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.459988</v>
+        <v>19.631691</v>
       </c>
       <c r="Z2" t="n">
         <v>0.102</v>
@@ -10734,7 +10734,7 @@
         <v>44487999488</v>
       </c>
       <c r="AC2" t="n">
-        <v>685501841408</v>
+        <v>691456835584</v>
       </c>
       <c r="AD2" t="n">
         <v>31093999616</v>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:07</t>
+          <t>2026-09-12 21:47:11</t>
         </is>
       </c>
     </row>
